--- a/consolidation/outputs/consolidated_requirements.xlsx
+++ b/consolidation/outputs/consolidated_requirements.xlsx
@@ -413,58 +413,63 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:K46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Requirement ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Rationale</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Stakeholders</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Dependencies</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Acceptance Criteria</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Confidence</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>citation</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>No</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Rationale</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Priority</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Stakeholders</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Dependencies</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Acceptance Criteria</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Confidence</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>citation</t>
         </is>
       </c>
     </row>
@@ -476,17 +481,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AI Productivity, Scan Workflow &amp; Manageability Solutions</t>
+          <t>NGB Keyed Bottles with High Page Yield</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Implement advanced AI-driven productivity features, including scan workflow automation and enhanced manageability tools, to simplify business operations for SMB customers.</t>
+          <t>Develop new NGB keyed ink bottles supporting 6,000-page yield for black and CMY, with CMY bottle size supporting over 8,000 pages.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Addresses SMB need for efficiency and minimal IT intervention, providing a competitive edge and aligning with the product's value proposition.</t>
+          <t>To meet evolving customer usage needs and remain competitive with high-yield consumables, especially in SMB and Enterprise segments.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -496,17 +501,17 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Marketing, GXD, Quality, R&amp;D Telemetry, Supplies Quality, DVAR, Tech Reg, Prod Steward, BA</t>
+          <t>R&amp;D, Product Management, SMB/Enterprise Customers</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Integration with SMB portal and device management solutions</t>
+          <t>Integration with CISS, IDS, and ink tank design.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>AI productivity features are available in the product; scan workflow automation is functional; manageability tools are accessible via the SMB portal.</t>
+          <t>Bottles must be keyed, support 6K black and 8K+ CMY page yields, and be compatible with printer system; performance validated in yield testing.</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -514,9 +519,10 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 7, 10, 11</t>
-        </is>
-      </c>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -526,17 +532,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Lowest Business TCO (Total Cost of Ownership)</t>
+          <t>Spill-Free Reliability for Ink Bottles</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Design the printer to deliver the lowest business TCO in its class, including efficient ink usage, minimal maintenance, and optimized consumable costs.</t>
+          <t>Ensure that the new ink bottles and filling system are spill-free to improve user experience and reduce mess during refilling.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SMBs are highly cost-sensitive; lowest TCO is a key differentiator and driver for purchase.</t>
+          <t>Spill-free design is critical for consumer satisfaction and to differentiate from competitors.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -546,17 +552,17 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Marketing, Quality, Supplies Quality, BA</t>
+          <t>End Users, R&amp;D, Product Management</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sustainability features, maintenance design, consumables pricing</t>
+          <t>Bottle and tank interface design, IDS integration.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Independent cost analysis confirms lowest TCO compared to direct competitors in the SMB tank printer segment.</t>
+          <t>Ink filling process must not result in any ink spillages in normal use; verified by user acceptance testing.</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -564,9 +570,10 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 11</t>
-        </is>
-      </c>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -576,17 +583,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>80k or 2-Year Warranty (Whichever First)</t>
+          <t>NOA-F with Metal Foiled Labyrinth and Lid Label</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Offer a warranty of 80,000 pages printed or 2 years, whichever comes first, for the Magellan printer.</t>
+          <t>Implement NOA-F (Non-Original Accessory Filter) with a metal foiled labyrinth and lid label, retaining click-on push-push and TDF mechanisms.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Warranty is a key purchase consideration for SMBs, ensuring reliability and reducing perceived risk.</t>
+          <t>Enhances security, reliability, and warranty support, and prevents unauthorized use of non-HP supplies.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -596,27 +603,28 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Quality, Marketing, DVAR, BA</t>
+          <t>R&amp;D, Service, Warranty, Product Security</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Serviceability design, consumables durability</t>
+          <t>NOA-F design, integration with printer hardware.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Warranty terms are clearly stated in product documentation and reflected in warranty registration systems.</t>
+          <t>NOA-F must have metal foiled labyrinth and lid label, retain click-on push-push and TDF; validated in reliability and security tests.</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -626,17 +634,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Serviceability: Customer Replaceable Parts (PHA) and MINK at Service Centre</t>
+          <t>Reuse of SuperAmp Si PHA and Magi/Nessie Inks</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Enable customer replaceable parts (PHA) and MINK replacement at service centers, with a target for more parts to be customer replaceable if out of warranty.</t>
+          <t>The product must reuse the existing SuperAmp Si PHA and Magi/Nessie pigment inks, with no ink reformulation required.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Reduces downtime and cost for SMBs without dedicated IT, improving user experience and satisfaction.</t>
+          <t>Reduces development time and cost, leverages proven consumables, and supports supply chain efficiency.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -646,27 +654,28 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Quality, R&amp;D Telemetry, Supplies Quality, DVAR</t>
+          <t>Supply Chain, R&amp;D, Product Management</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Parts design, documentation, training material</t>
+          <t>Compatibility with new bottle and tank system.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>At least PHA is customer replaceable and MINK is serviceable at authorized centers; documentation and training are available.</t>
+          <t>SuperAmp Si PHA and Magi/Nessie inks work seamlessly in the new system without reformulation.</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.9</v>
+        <v>0.98</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -676,17 +685,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Keyed Ink Bottles</t>
+          <t>Reliability and Ink Stability Modeling</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Utilize keyed ink bottles to prevent incorrect refilling and ensure only genuine HP supplies are used.</t>
+          <t>Develop comprehensive reliability, WVTR (Water Vapor Transmission Rate), air gain, flow rate, and IDS (Ink Delivery System) characterization and modeling, including startup and NOA-F end-of-life (EOL) scenarios. Include ink stability modeling for tank and its impact on print quality (PQ).</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Prevents user errors and protects HP supplies revenue.</t>
+          <t>Critical for ensuring long-term product performance and warranty claims management.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -696,27 +705,28 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Supplies Quality, Tech Reg, Prod Steward</t>
+          <t>R&amp;D, Quality Assurance, Service</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ink system design, supply chain</t>
+          <t>Ink system design, IDS algorithms.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Printer only accepts correctly keyed bottles; nozzles and bottles are physically incompatible with non-genuine supplies.</t>
+          <t>All models completed, validated with test data, and reviewed by QA; ink stability meets or exceeds PQ standards over product life.</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -726,17 +736,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Non-PDL SKU: SMB2.0 Solutions and Advanced View SMB Portal Support</t>
+          <t>Support for Services and Contractual NOA-F Parts</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ensure the non-PDL SKU supports SMB2.0 Solutions and is fully integrated with the Advanced View SMB portal.</t>
+          <t>NOA-F must be available as a service part for warranty support, and the system must support services/contractual models.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Addresses the need for centralized device management for unmanaged/lightly managed SMBs.</t>
+          <t>Enables serviceability and supports HP’s business model for extended warranty and service contracts.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -746,17 +756,17 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>GXD, R&amp;D Telemetry, BA, Marketing</t>
+          <t>Service, Warranty, Business Operations</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Portal development, firmware integration</t>
+          <t>NOA-F part logistics, service documentation.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Non-PDL SKU is compatible with SMB2.0 Solutions and Advanced View portal out-of-the-box.</t>
+          <t>NOA-F parts available in service inventory; service process documented and validated.</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -764,9 +774,10 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 10</t>
-        </is>
-      </c>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -776,47 +787,48 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PaaS (Printing as a Service) Support</t>
+          <t>Factory Line Modifications for New Components</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Support Printing as a Service (PaaS) model for both PDL and non-PDL SKUs.</t>
+          <t>Modify existing SA14 factory line for NOA-F integration, and add Magi ink cartridge and labeling tool in Orcus 5. Provide new molds for 1 to 4 new keyed caps.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Enables flexible business models and recurring revenue streams for HP and partners.</t>
+          <t>Required to manufacture and assemble the new product components efficiently and at scale.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Marketing, DVAR, BA</t>
+          <t>Manufacturing, Operations, R&amp;D</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Firmware, portal, billing integration</t>
+          <t>Component design finalization, factory tooling schedules.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>PaaS features are available for both SKUs; billing and management workflows tested.</t>
+          <t>Factory lines modified and validated for new components; molds for new caps in production.</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 10</t>
-        </is>
-      </c>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -826,17 +838,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PDL SKU: Improved Print Speed and PDL/PS Support</t>
+          <t>Page Yield and Warranty Life Goals</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>PDL SKU must achieve print speeds of 25/20 ppm (improvement from current 25/19) and support Page Description Languages (PDL) and PostScript (PS).</t>
+          <t>Support new warranty page life goal of 80,000 pages and SuperAmp PHA life at 65,000 pages. Warranty period is 2 years.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Meets the needs of more demanding SMB customers and competitive benchmarks.</t>
+          <t>Aligns with business priorities to reduce service costs and meet market expectations for reliability.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -846,27 +858,28 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>R&amp;D Telemetry, Marketing, BA</t>
+          <t>Product Management, Service, Warranty, Customers</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Print engine, firmware, driver development</t>
+          <t>Reliability modeling, consumables life validation.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>PDL SKU achieves specified speeds and passes PDL/PS compatibility tests.</t>
+          <t>Printers must reliably print 80,000 pages over 2 years; SuperAmp PHA must last 65,000 pages; validated by life testing.</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.9</v>
+        <v>0.92</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
+          <t>Magellan_SI_1-pager.pdf, page 1 and 2</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -876,17 +889,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Blue Angel Certification for PDL SKU</t>
+          <t>Speed and Throughput Requirements</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ensure the PDL SKU meets Blue Angel environmental certification requirements.</t>
+          <t>Product must achieve print speeds of 25 ppm (pages per minute) for standard and 20 ppm for PDL (Page Description Language), with PDL throughput of 25/19 ppm.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Sustainability is a key differentiator and compliance requirement in key markets.</t>
+          <t>To remain competitive and meet customer expectations for productivity.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -896,17 +909,17 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Prod Steward, Tech Reg, Marketing</t>
+          <t>Product Management, SMB/Enterprise Customers</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Materials, power consumption, emissions design</t>
+          <t>Printer engine design, firmware support.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>PDL SKU receives Blue Angel certification prior to launch.</t>
+          <t>Printers consistently achieve 25/20 ppm (25/19 PDL) in standardized test conditions.</t>
         </is>
       </c>
       <c r="I10" t="n">
@@ -914,9 +927,10 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
+          <t>Magellan_SI_1-pager.pdf, page 1 and 2</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -926,47 +940,48 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Replaceable Maintenance Box</t>
+          <t>Support for Customer Replaceable PHA and NOA-F</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Incorporate a replaceable maintenance box to support new use cases and reduce downtime.</t>
+          <t>Design system such that PHA and NOA-F are customer replaceable, improving ease of maintenance and reducing service calls.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Supports new SMB use cases and enhances serviceability for non-IT users.</t>
+          <t>Enhances user experience and reduces total cost of ownership for customers.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Quality, R&amp;D Telemetry, Supplies Quality</t>
+          <t>End Users, Service, Product Management</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Parts design, documentation</t>
+          <t>Component design, user documentation.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Maintenance box is user-replaceable and instructions are provided; tested for usability by non-IT users.</t>
+          <t>Customers can replace PHA and NOA-F without tools; validated by usability testing.</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.85</v>
+        <v>0.92</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -976,17 +991,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Perfect Print and Perfect Scan AI Solutions</t>
+          <t>Product ID and Tank Size Increase</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Integrate advanced AI-driven 'Perfect Print' and 'Perfect Scan' solutions to enhance print and scan quality automatically.</t>
+          <t>Implement Reddington ID with increased tank size. No change to Marconi-HI ADF (Automatic Document Feeder).</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Delivers superior output quality with minimal user intervention, a key differentiator for SMBs.</t>
+          <t>Tank size increase supports higher page yield and reduces refill frequency.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -996,27 +1011,28 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>GXD, R&amp;D Telemetry, Marketing, Quality</t>
+          <t>Product Management, R&amp;D, End Users</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>AI algorithm development, hardware compatibility</t>
+          <t>Mechanical design, packaging updates.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>AI features demonstrably improve print/scan quality in benchmark tests.</t>
+          <t>Product ID and tank size changes reflected in production units; tank supports required page yields.</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 7, 11</t>
-        </is>
-      </c>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1026,17 +1042,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SMB Portal for Printer Management</t>
+          <t>Packaging and Environmental Compliance</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Provide a consolidated portal for SMB customers to manage multiple printers, including device status, usage, and maintenance alerts.</t>
+          <t>Use EPS foam packaging, ensure EPEAT3 and LOT4 compliance, and Blue Angel certification for PDL SKU.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Addresses need for easy, centralized management for offices without dedicated IT staff.</t>
+          <t>Meets regulatory requirements and supports HP’s sustainability goals.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1046,27 +1062,28 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>GXD, R&amp;D Telemetry, BA, Marketing</t>
+          <t>Regulatory, Product Management, Sustainability Team</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Portal software development, device firmware integration</t>
+          <t>Packaging design, compliance testing.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Portal is available and functional; users can manage at least 6-15 printers as per target customer profile.</t>
+          <t>Packaging meets EPS, EPEAT3, LOT4, and Blue Angel standards; certifications obtained.</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 7, 10, 11</t>
-        </is>
-      </c>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1076,47 +1093,48 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Sustainability: 60% Recycled Content Plastic (RCP)</t>
+          <t>Input/Output Tray and Size Optimization</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ensure that at least 60% of the printer's plastic is made from recycled content, surpassing key competitors.</t>
+          <t>Update input and output trays to align with tank protrusion and optimize overall product size.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Sustainability is a key purchase driver and competitive differentiator in the SMB segment.</t>
+          <t>Ensures mechanical compatibility and optimizes product footprint for customer environments.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Prod Steward, Tech Reg, Marketing</t>
+          <t>R&amp;D, Product Management, End Users</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Material sourcing, compliance testing</t>
+          <t>Mechanical design, tank integration.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Product composition verified to have 60% RCP; documented in product specs and marketing.</t>
+          <t>Trays fit and function with new tank; overall product size optimized and validated.</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 11</t>
-        </is>
-      </c>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1126,17 +1144,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Mobile Printing via HP App</t>
+          <t>4.3-inch CGD Display</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Enable seamless mobile printing functionality through the HP App for SMB users.</t>
+          <t>Integrate a 4.3-inch CGD (Color Graphics Display) into the product.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Mobile printing is a top use case and expectation for modern SMBs.</t>
+          <t>Enhances user interface and accessibility, supporting modern UI expectations.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1146,27 +1164,28 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>GXD, BA, Marketing</t>
+          <t>End Users, Product Management, UI/UX Team</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>App integration, firmware support</t>
+          <t>Hardware integration, firmware UI development.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Mobile printing is tested and functional with HP App on major platforms (iOS, Android).</t>
+          <t>4.3-inch CGD display functional and passes usability/user acceptance tests.</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.9</v>
+        <v>0.88</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 9, 10</t>
-        </is>
-      </c>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1176,45 +1195,1576 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
+          <t>Four-Tube Platform with Sayan Sibstar Tubes</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Leverage a four-tube platform using Sayan Sibstar tubes, with new tube routing and integration.</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Supports efficient ink delivery and reliability for increased page life.</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>R&amp;D, Manufacturing, Service</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Tube design, integration with IDS and ink tanks.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Four-tube system implemented, tested for reliability and flow rate.</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Service Station Aerosol Management</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Update service station aerosol management and spit platform to accommodate changes due to the larger tank.</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Prevents contamination and maintains print quality over extended use.</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Service, R&amp;D, Quality Assurance</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Service station redesign, tank integration.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Aerosol management system prevents contamination; validated in long-term testing.</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Carriage Dynamic and Force Model Updates</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Update carriage dynamic and force models to account for new tube routing and increased component weights.</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Ensures mechanical reliability and print quality with new hardware configuration.</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>R&amp;D, Quality Assurance, Manufacturing</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Mechanical design, tube integration.</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Updated models reviewed and validated by engineering; no mechanical failures in testing.</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Paper Path for Increased Page Life</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Redesign paper path to support increased page life and reliability goals.</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Supports new warranty and page yield requirements, reducing jams and wear.</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>R&amp;D, Service, Quality Assurance</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Mechanical design, reliability modeling.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Paper path passes reliability testing for 80,000 pages without significant jams or wear.</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ink Maintenance as Serviceable Part Post-80k Life</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Design ink maintenance as a serviceable part at service centers after 80,000-page life is reached.</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Enables post-warranty servicing and extends product lifespan.</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Service, Product Management, End Users</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Service part logistics, documentation.</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Ink maintenance part replaceable at service centers; process documented and validated.</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>New IDS Make-Break and FI Connection</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Implement new make-break and FI (Fluidic Interface) connection in the IDS, leveraging LEBI ink-tank with increased size, keying, and LOI (Level of Ink) One SHAID.</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Improves reliability and serviceability of ink delivery system.</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>R&amp;D, Service, Manufacturing</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>IDS and tank design, component integration.</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>New IDS connections implemented and validated in system integration testing.</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>New IDS Startup Algorithm and Air Management</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Develop new IDS startup algorithm and air management system to support larger tanks and new ink system.</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Ensures reliable system startup and prevents air-related print defects.</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>R&amp;D, Firmware, Service</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>IDS algorithm development, tank and tube design.</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Startup algorithm and air management validated in system testing; no startup failures or air-related defects.</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>New Print Quality Goals and Depletion Metrics</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Define and implement new print quality (PQ) goals and depletion metrics to align with increased page yield definition.</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Ensures that print quality is maintained throughout the extended product life and yield.</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>R&amp;D, Quality Assurance, Product Management</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>PQ standards development, yield testing.</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>PQ goals and depletion metrics defined, validated in life testing, and documented.</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Reuse of Marconi Hi PDL and Tux dASIC</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Reuse Marconi Hi PDL, Marconi Tux dASIC, Hannibal aASIC, and Raccoon PSU for the Magellan platform.</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Leverages proven hardware modules to reduce risk and development time.</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>R&amp;D, Supply Chain, Manufacturing</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Component compatibility and integration.</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Components reused without issues; system integration tests pass.</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Stingray Wi-Fi Module and Dune Firmware</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Integrate Stingray Wi-Fi module and Dune firmware into the product.</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Provides wireless connectivity and firmware platform continuity.</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>R&amp;D, Product Management, End Users</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Module and firmware integration, compliance testing.</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Wi-Fi and firmware operate reliably and pass regulatory and user acceptance tests.</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Gauss4.xx Security (HW &amp; FW)</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Implement Gauss4.xx security features in both hardware and firmware.</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Ensures product security and compliance with HP security standards.</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Product Security, R&amp;D, IT, Customers</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>HW and FW development, security validation.</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Security features implemented and pass internal security audits.</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Business Model and Solution Support</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Support Consumer, SMB, and Enterprise business models, including PaaS (Printing as a Service), WorkFromHome/Flexworker, and onboarding via Consumer/HPX, HP One, SMB Portal, and ECP paths. Support scan solution, SMB manageability, and Enterprise support (WJA, HPSM, JAM).</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Expands market reach and supports multiple customer segments and deployment models.</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Product Management, Business Operations, Channel Partners</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Solution integration, onboarding path development.</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>All business models and solution paths functional and documented; onboarding validated for each segment.</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Client and Driver Support</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Support HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD clients and drivers for seamless installation and operation.</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Ensures compatibility with HP’s ecosystem and customer IT environments.</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>IT, End Users, Channel Partners</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Driver and client integration, validation.</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>All listed drivers and clients install and operate successfully on supported platforms.</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Schedule and Checkpoint Adherence</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Adhere to defined hardware, NOA-F, and bottle checkpoints and build milestones (e.g., Re-SI, DO, IL, DP, MC, VR, FCS, BB1, BB2, TR, LP1, LP2, MP1/PP, SOR).</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Ensures timely program execution and risk management.</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Program Management, R&amp;D, Manufacturing</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Project management processes, milestone tracking.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>All checkpoints and builds completed as per schedule; deviations documented and addressed.</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Serviceability of Maintenance Box</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ensure maintenance box is easily serviceable to optimize service operations and customer experience.</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Reduces downtime and service costs.</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Service, End Users, Product Management</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Maintenance box design, service process documentation.</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Maintenance box can be serviced/replaced by service personnel; validated by serviceability testing.</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Host 12K-CMYK and Trade Page 6K (Flexible Priority)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Support for hosting 12,000-page CMYK and trade page 6,000, as a flexible business requirement.</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Allows for future scalability and market responsiveness.</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Product Management, Business Operations</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Ink system scalability, market analysis.</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>System design allows for 12K-CMYK and 6K trade page options if required by business.</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>AI Productivity, Scan Workflow &amp; Manageability Solutions</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Implement advanced AI-driven productivity features, including scan workflow automation and enhanced manageability tools, to simplify business operations for SMB customers.</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Addresses SMB need for efficiency and minimal IT intervention, providing a competitive edge and aligning with the product's value proposition.</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Marketing, GXD, Quality, R&amp;D Telemetry, Supplies Quality, DVAR, Tech Reg, Prod Steward, BA</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Integration with SMB portal and device management solutions</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>AI productivity features are available in the product; scan workflow automation is functional; manageability tools are accessible via the SMB portal.</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4, 7, 10, 11</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Lowest Business TCO (Total Cost of Ownership)</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Design the printer to deliver the lowest business TCO in its class, including efficient ink usage, minimal maintenance, and optimized consumable costs.</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>SMBs are highly cost-sensitive; lowest TCO is a key differentiator and driver for purchase.</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Marketing, Quality, Supplies Quality, BA</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Sustainability features, maintenance design, consumables pricing</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Independent cost analysis confirms lowest TCO compared to direct competitors in the SMB tank printer segment.</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4, 11</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>80k or 2-Year Warranty (Whichever First)</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Offer a warranty of 80,000 pages printed or 2 years, whichever comes first, for the Magellan printer.</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Warranty is a key purchase consideration for SMBs, ensuring reliability and reducing perceived risk.</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Quality, Marketing, DVAR, BA</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Serviceability design, consumables durability</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Warranty terms are clearly stated in product documentation and reflected in warranty registration systems.</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Serviceability: Customer Replaceable Parts (PHA) and MINK at Service Centre</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Enable customer replaceable parts (PHA) and MINK replacement at service centers, with a target for more parts to be customer replaceable if out of warranty.</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Reduces downtime and cost for SMBs without dedicated IT, improving user experience and satisfaction.</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Quality, R&amp;D Telemetry, Supplies Quality, DVAR</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Parts design, documentation, training material</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>At least PHA is customer replaceable and MINK is serviceable at authorized centers; documentation and training are available.</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Keyed Ink Bottles</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Utilize keyed ink bottles to prevent incorrect refilling and ensure only genuine HP supplies are used.</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Prevents user errors and protects HP supplies revenue.</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Supplies Quality, Tech Reg, Prod Steward</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Ink system design, supply chain</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Printer only accepts correctly keyed bottles; nozzles and bottles are physically incompatible with non-genuine supplies.</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Non-PDL SKU: SMB2.0 Solutions and Advanced View SMB Portal Support</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ensure the non-PDL SKU supports SMB2.0 Solutions and is fully integrated with the Advanced View SMB portal.</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Addresses the need for centralized device management for unmanaged/lightly managed SMBs.</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>GXD, R&amp;D Telemetry, BA, Marketing</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Portal development, firmware integration</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Non-PDL SKU is compatible with SMB2.0 Solutions and Advanced View portal out-of-the-box.</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4, 10</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>PaaS (Printing as a Service) Support</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Support Printing as a Service (PaaS) model for both PDL and non-PDL SKUs.</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Enables flexible business models and recurring revenue streams for HP and partners.</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Marketing, DVAR, BA</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Firmware, portal, billing integration</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>PaaS features are available for both SKUs; billing and management workflows tested.</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4, 10</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>PDL SKU: Improved Print Speed and PDL/PS Support</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>PDL SKU must achieve print speeds of 25/20 ppm (improvement from current 25/19) and support Page Description Languages (PDL) and PostScript (PS).</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Meets the needs of more demanding SMB customers and competitive benchmarks.</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>R&amp;D Telemetry, Marketing, BA</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Print engine, firmware, driver development</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>PDL SKU achieves specified speeds and passes PDL/PS compatibility tests.</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Blue Angel Certification for PDL SKU</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ensure the PDL SKU meets Blue Angel environmental certification requirements.</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Sustainability is a key differentiator and compliance requirement in key markets.</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Prod Steward, Tech Reg, Marketing</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Materials, power consumption, emissions design</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>PDL SKU receives Blue Angel certification prior to launch.</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Replaceable Maintenance Box</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Incorporate a replaceable maintenance box to support new use cases and reduce downtime.</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Supports new SMB use cases and enhances serviceability for non-IT users.</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Quality, R&amp;D Telemetry, Supplies Quality</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Parts design, documentation</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Maintenance box is user-replaceable and instructions are provided; tested for usability by non-IT users.</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Perfect Print and Perfect Scan AI Solutions</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Integrate advanced AI-driven 'Perfect Print' and 'Perfect Scan' solutions to enhance print and scan quality automatically.</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Delivers superior output quality with minimal user intervention, a key differentiator for SMBs.</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>GXD, R&amp;D Telemetry, Marketing, Quality</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>AI algorithm development, hardware compatibility</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>AI features demonstrably improve print/scan quality in benchmark tests.</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 7, 11</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>SMB Portal for Printer Management</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Provide a consolidated portal for SMB customers to manage multiple printers, including device status, usage, and maintenance alerts.</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Addresses need for easy, centralized management for offices without dedicated IT staff.</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>GXD, R&amp;D Telemetry, BA, Marketing</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Portal software development, device firmware integration</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Portal is available and functional; users can manage at least 6-15 printers as per target customer profile.</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 7, 10, 11</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Sustainability: 60% Recycled Content Plastic (RCP)</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ensure that at least 60% of the printer's plastic is made from recycled content, surpassing key competitors.</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Sustainability is a key purchase driver and competitive differentiator in the SMB segment.</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Prod Steward, Tech Reg, Marketing</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Material sourcing, compliance testing</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Product composition verified to have 60% RCP; documented in product specs and marketing.</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 11</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Mobile Printing via HP App</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Enable seamless mobile printing functionality through the HP App for SMB users.</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Mobile printing is a top use case and expectation for modern SMBs.</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>GXD, BA, Marketing</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>App integration, firmware support</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Mobile printing is tested and functional with HP App on major platforms (iOS, Android).</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 9, 10</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
+        <is>
           <t>Telemetry Requirements</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>Implement telemetry features to collect anonymized usage, performance, and error data for product improvement and support.</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>Supports proactive support, quality monitoring, and future product enhancements.</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>R&amp;D Telemetry, Quality, BA</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>Firmware, portal integration, privacy compliance</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>Telemetry data is collected, transmitted securely, and accessible for analysis; compliance with privacy regulations.</t>
         </is>
       </c>
-      <c r="I16" t="n">
+      <c r="I46" t="n">
         <v>0.85</v>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t>Magellan MRD, Page 3, 12</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>15</t>
         </is>
       </c>
     </row>

--- a/consolidation/outputs/consolidated_requirements.xlsx
+++ b/consolidation/outputs/consolidated_requirements.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K46"/>
+  <dimension ref="A1:K50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,12 +486,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Develop new NGB keyed ink bottles supporting 6,000-page yield for black and CMY, with CMY bottle size supporting over 8,000 pages.</t>
+          <t>Develop new NGB keyed ink bottles supporting 6K Black and 6K CMY page yield, with CMY bottle size &gt;8K.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>To meet evolving customer usage needs and remain competitive with high-yield consumables, especially in SMB and Enterprise segments.</t>
+          <t>To increase consumable capacity and meet high-volume printing needs, supporting longer intervals between replacements.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -501,17 +501,17 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Management, SMB/Enterprise Customers</t>
+          <t>R&amp;D, Product Management, End Users</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Integration with CISS, IDS, and ink tank design.</t>
+          <t>Requires compatibility with NOA-F, SuperAmp PHA, and existing ink systems.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Bottles must be keyed, support 6K black and 8K+ CMY page yields, and be compatible with printer system; performance validated in yield testing.</t>
+          <t>NGB keyed bottles deliver 6,000 pages for Black, 6,000 pages for CMY (with CMY bottle size &gt;8,000 pages), verified by yield tests.</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -532,17 +532,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Spill-Free Reliability for Ink Bottles</t>
+          <t>Spill-Free Reliability for Bottles</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ensure that the new ink bottles and filling system are spill-free to improve user experience and reduce mess during refilling.</t>
+          <t>Ensure the bottle design and ink delivery system provide spill-free operation during installation and use.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Spill-free design is critical for consumer satisfaction and to differentiate from competitors.</t>
+          <t>To improve user experience and reduce maintenance/service calls due to ink spills.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -552,17 +552,17 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>End Users, R&amp;D, Product Management</t>
+          <t>End Users, Service, R&amp;D</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bottle and tank interface design, IDS integration.</t>
+          <t>Bottle and NOA-F design integration.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Ink filling process must not result in any ink spillages in normal use; verified by user acceptance testing.</t>
+          <t>User installs bottle with no ink spillage in 100% of test cases under defined use scenarios.</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -588,12 +588,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Implement NOA-F (Non-Original Accessory Filter) with a metal foiled labyrinth and lid label, retaining click-on push-push and TDF mechanisms.</t>
+          <t>Integrate NOA-F with a metal foiled labyrinth and lid label, maintaining compatibility with click-on push-push and TDF mechanisms.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Enhances security, reliability, and warranty support, and prevents unauthorized use of non-HP supplies.</t>
+          <t>To improve reliability and security of ink delivery and maintain compatibility with existing mechanisms.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -603,21 +603,21 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>R&amp;D, Service, Warranty, Product Security</t>
+          <t>R&amp;D, Manufacturing, End Users</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>NOA-F design, integration with printer hardware.</t>
+          <t>Existing push-push and TDF mechanisms.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>NOA-F must have metal foiled labyrinth and lid label, retain click-on push-push and TDF; validated in reliability and security tests.</t>
+          <t>NOA-F units pass reliability tests and are compatible with click-on push-push and TDF in all production units.</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -634,17 +634,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Reuse of SuperAmp Si PHA and Magi/Nessie Inks</t>
+          <t>Reuse SuperAmp Si PHA and Magi/Nessie Ink</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>The product must reuse the existing SuperAmp Si PHA and Magi/Nessie pigment inks, with no ink reformulation required.</t>
+          <t>Reuse SuperAmp Si PHA and Magi/Nessie pigment inks without ink reformulation.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Reduces development time and cost, leverages proven consumables, and supports supply chain efficiency.</t>
+          <t>To leverage proven technology, reduce development time, and maintain ink quality.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -654,21 +654,21 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Supply Chain, R&amp;D, Product Management</t>
+          <t>R&amp;D, Manufacturing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Compatibility with new bottle and tank system.</t>
+          <t>Existing SuperAmp Si PHA and Magi/Nessie ink specifications.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>SuperAmp Si PHA and Magi/Nessie inks work seamlessly in the new system without reformulation.</t>
+          <t>SuperAmp Si PHA and Magi/Nessie inks are used in production units with no reformulation required.</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.98</v>
+        <v>0.95</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -690,12 +690,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Develop comprehensive reliability, WVTR (Water Vapor Transmission Rate), air gain, flow rate, and IDS (Ink Delivery System) characterization and modeling, including startup and NOA-F end-of-life (EOL) scenarios. Include ink stability modeling for tank and its impact on print quality (PQ).</t>
+          <t>Model and characterize reliability, WVTR, air gain, flow rate, IDS, startup, and NOA-F EOL for the ink system, including ink stability in tank and impact to print quality (PQ).</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Critical for ensuring long-term product performance and warranty claims management.</t>
+          <t>To ensure robust and consistent printer performance throughout its lifecycle.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -705,21 +705,21 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality Assurance, Service</t>
+          <t>R&amp;D, Quality Assurance</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ink system design, IDS algorithms.</t>
+          <t>Integration with IDS and NOA-F systems.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>All models completed, validated with test data, and reviewed by QA; ink stability meets or exceeds PQ standards over product life.</t>
+          <t>Comprehensive models and test results demonstrating system reliability and ink stability over defined lifecycle.</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -736,17 +736,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Support for Services and Contractual NOA-F Parts</t>
+          <t>NOA-F as Service Parts in Warranty Support</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>NOA-F must be available as a service part for warranty support, and the system must support services/contractual models.</t>
+          <t>Provide NOA-F as service parts for warranty support, ensuring availability during warranty period.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Enables serviceability and supports HP’s business model for extended warranty and service contracts.</t>
+          <t>To support post-sale serviceability and customer satisfaction.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -756,21 +756,21 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Service, Warranty, Business Operations</t>
+          <t>Service, Warranty, End Users</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>NOA-F part logistics, service documentation.</t>
+          <t>NOA-F production and distribution channels.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>NOA-F parts available in service inventory; service process documented and validated.</t>
+          <t>NOA-F available as service part for all units under warranty within defined SLA.</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -787,41 +787,41 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Factory Line Modifications for New Components</t>
+          <t>Acumen 6 on Lid</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Modify existing SA14 factory line for NOA-F integration, and add Magi ink cartridge and labeling tool in Orcus 5. Provide new molds for 1 to 4 new keyed caps.</t>
+          <t>Integrate Acumen 6 feature on the lid of the ink system.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Required to manufacture and assemble the new product components efficiently and at scale.</t>
+          <t>To enhance product intelligence, traceability, or anti-counterfeiting measures.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Manufacturing, Operations, R&amp;D</t>
+          <t>R&amp;D, Security, Product Management</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Component design finalization, factory tooling schedules.</t>
+          <t>Lid design and Acumen 6 compatibility.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Factory lines modified and validated for new components; molds for new caps in production.</t>
+          <t>All lids incorporate Acumen 6 and are validated for intended function.</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -838,17 +838,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Page Yield and Warranty Life Goals</t>
+          <t>Factory Line Modifications for NOA-F and Magi Ink Cart</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Support new warranty page life goal of 80,000 pages and SuperAmp PHA life at 65,000 pages. Warranty period is 2 years.</t>
+          <t>Modify existing SA14 line for NOA-F, add Magi ink cart and labeling tool in Orcus 5, and ensure PHA + Dry FI + USG + push-push assembly in printer factory.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Aligns with business priorities to reduce service costs and meet market expectations for reliability.</t>
+          <t>To support new components and maintain production efficiency.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -858,25 +858,25 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Product Management, Service, Warranty, Customers</t>
+          <t>Manufacturing, Operations, R&amp;D</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Reliability modeling, consumables life validation.</t>
+          <t>Existing SA14 and Orcus 5 line configurations.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Printers must reliably print 80,000 pages over 2 years; SuperAmp PHA must last 65,000 pages; validated by life testing.</t>
+          <t>Production lines modified and validated to support new components without impacting throughput.</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.92</v>
+        <v>0.9</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1 and 2</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -889,17 +889,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Speed and Throughput Requirements</t>
+          <t>Mold for 1 to 4 New Keyed Caps</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Product must achieve print speeds of 25 ppm (pages per minute) for standard and 20 ppm for PDL (Page Description Language), with PDL throughput of 25/19 ppm.</t>
+          <t>Develop molds for 1 to 4 new keyed caps for bottles.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>To remain competitive and meet customer expectations for productivity.</t>
+          <t>To support new bottle keying and prevent cross-contamination or misinstallation.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -909,25 +909,25 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Product Management, SMB/Enterprise Customers</t>
+          <t>Manufacturing, R&amp;D</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Printer engine design, firmware support.</t>
+          <t>Bottle and cap design finalization.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Printers consistently achieve 25/20 ppm (25/19 PDL) in standardized test conditions.</t>
+          <t>Molds created and caps produced pass fit and function tests.</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1 and 2</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -940,17 +940,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Support for Customer Replaceable PHA and NOA-F</t>
+          <t>Support Customer Replaceable PHA and NOA-F</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Design system such that PHA and NOA-F are customer replaceable, improving ease of maintenance and reducing service calls.</t>
+          <t>Enable end users to replace PHA and NOA-F components without technical assistance.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Enhances user experience and reduces total cost of ownership for customers.</t>
+          <t>To improve serviceability and reduce downtime for customers.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -965,16 +965,16 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Component design, user documentation.</t>
+          <t>Design of PHA and NOA-F for user replacement.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Customers can replace PHA and NOA-F without tools; validated by usability testing.</t>
+          <t>Users can replace PHA and NOA-F following provided instructions in &gt;95% of usability tests.</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.92</v>
+        <v>0.9</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -991,17 +991,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Product ID and Tank Size Increase</t>
+          <t>Warranty Page Life Goal of 80K Pages</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Implement Reddington ID with increased tank size. No change to Marconi-HI ADF (Automatic Document Feeder).</t>
+          <t>Design printer and consumables to support a new warranty page life goal of 80,000 pages.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Tank size increase supports higher page yield and reduces refill frequency.</t>
+          <t>To increase product longevity and competitiveness in the market.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1011,21 +1011,21 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Product Management, R&amp;D, End Users</t>
+          <t>Product Management, End Users, Service</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Mechanical design, packaging updates.</t>
+          <t>Component durability, ink system reliability.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Product ID and tank size changes reflected in production units; tank supports required page yields.</t>
+          <t>Printer and consumables meet or exceed 80,000 page life in accelerated lifecycle testing.</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1042,41 +1042,41 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Packaging and Environmental Compliance</t>
+          <t>SKU 2 (Hi + Hi PDL) PaaS</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Use EPS foam packaging, ensure EPEAT3 and LOT4 compliance, and Blue Angel certification for PDL SKU.</t>
+          <t>Develop SKU 2 supporting both Hi and Hi PDL, with Platform-as-a-Service (PaaS) support.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Meets regulatory requirements and supports HP’s sustainability goals.</t>
+          <t>To address diverse market segments and enable flexible business models.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Regulatory, Product Management, Sustainability Team</t>
+          <t>Product Management, Sales, Business Development</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Packaging design, compliance testing.</t>
+          <t>SKU definition, PaaS infrastructure.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Packaging meets EPS, EPEAT3, LOT4, and Blue Angel standards; certifications obtained.</t>
+          <t>SKU 2 available for order with Hi and Hi PDL options, and PaaS functionality enabled.</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1093,41 +1093,41 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Input/Output Tray and Size Optimization</t>
+          <t>Reddington ID with Increased Tank Size</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Update input and output trays to align with tank protrusion and optimize overall product size.</t>
+          <t>Implement Reddington ID with increased tank size, ensuring no change to Marconi-HI ADF.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Ensures mechanical compatibility and optimizes product footprint for customer environments.</t>
+          <t>To accommodate higher ink volumes and maintain compatibility with existing document feeders.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Management, End Users</t>
+          <t>R&amp;D, Manufacturing, Product Management</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Mechanical design, tank integration.</t>
+          <t>Tank design, Marconi-HI ADF interface.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Trays fit and function with new tank; overall product size optimized and validated.</t>
+          <t>Reddington ID supports increased tank size and is validated for ADF compatibility.</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1144,17 +1144,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>4.3-inch CGD Display</t>
+          <t>EPS Foam Packaging</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Integrate a 4.3-inch CGD (Color Graphics Display) into the product.</t>
+          <t>Use EPS foam packaging for the Magellan printer.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Enhances user interface and accessibility, supporting modern UI expectations.</t>
+          <t>To ensure product protection during shipping and handling.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1164,21 +1164,21 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>End Users, Product Management, UI/UX Team</t>
+          <t>Manufacturing, Logistics, End Users</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hardware integration, firmware UI development.</t>
+          <t>Packaging design and supply chain.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>4.3-inch CGD display functional and passes usability/user acceptance tests.</t>
+          <t>EPS foam packaging passes drop and vibration tests per HP standards.</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1195,17 +1195,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Four-Tube Platform with Sayan Sibstar Tubes</t>
+          <t>EPEAT3 and LOT4 Environmental Requirements, Blue Angel for PDL SKU</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Leverage a four-tube platform using Sayan Sibstar tubes, with new tube routing and integration.</t>
+          <t>Ensure compliance with EPEAT3, LOT4 environmental requirements, and Blue Angel certification for PDL SKU.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Supports efficient ink delivery and reliability for increased page life.</t>
+          <t>To meet regulatory and sustainability standards, and enhance marketability.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1215,21 +1215,21 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing, Service</t>
+          <t>Regulatory, Product Management, Sustainability</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tube design, integration with IDS and ink tanks.</t>
+          <t>Design and material selection, certification processes.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Four-tube system implemented, tested for reliability and flow rate.</t>
+          <t>Product achieves EPEAT3, LOT4, and Blue Angel certifications as applicable.</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.88</v>
+        <v>0.9</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1246,41 +1246,41 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Service Station Aerosol Management</t>
+          <t>Input and Output Tray Changes for Tank Protrusion</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Update service station aerosol management and spit platform to accommodate changes due to the larger tank.</t>
+          <t>Modify input and output trays to align with increased tank protrusion and optimize size.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Prevents contamination and maintains print quality over extended use.</t>
+          <t>To accommodate new tank size and maintain print media handling reliability.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Service, R&amp;D, Quality Assurance</t>
+          <t>R&amp;D, Manufacturing, End Users</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Service station redesign, tank integration.</t>
+          <t>Tank and tray design integration.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Aerosol management system prevents contamination; validated in long-term testing.</t>
+          <t>Trays are compatible with tank protrusion and pass paper handling reliability tests.</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1297,17 +1297,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Carriage Dynamic and Force Model Updates</t>
+          <t>4.3” CGD Display</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Update carriage dynamic and force models to account for new tube routing and increased component weights.</t>
+          <t>Integrate a 4.3-inch CGD (Color Graphic Display) in the printer UI.</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Ensures mechanical reliability and print quality with new hardware configuration.</t>
+          <t>To provide improved user interface and experience.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1317,21 +1317,21 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality Assurance, Manufacturing</t>
+          <t>End Users, Product Management</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Mechanical design, tube integration.</t>
+          <t>UI design, hardware integration.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Updated models reviewed and validated by engineering; no mechanical failures in testing.</t>
+          <t>4.3” CGD display is functional and passes user acceptance tests.</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1348,41 +1348,41 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Paper Path for Increased Page Life</t>
+          <t>Leverage Sayan Sibstar Tubes with New Routing and Integration</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Redesign paper path to support increased page life and reliability goals.</t>
+          <t>Use Sayan Sibstar tubes with new tube routing and integration for ink delivery.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Supports new warranty and page yield requirements, reducing jams and wear.</t>
+          <t>To optimize ink delivery and support new tank design.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>R&amp;D, Service, Quality Assurance</t>
+          <t>R&amp;D, Manufacturing</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Mechanical design, reliability modeling.</t>
+          <t>Tube and tank design finalization.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Paper path passes reliability testing for 80,000 pages without significant jams or wear.</t>
+          <t>Tube routing supports required flow rates and passes reliability tests.</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1399,17 +1399,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ink Maintenance as Serviceable Part Post-80k Life</t>
+          <t>Service Station Aerosol Management with Spit Platform Changes</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Design ink maintenance as a serviceable part at service centers after 80,000-page life is reached.</t>
+          <t>Implement service station aerosol management with necessary changes to the spit platform due to tank design.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Enables post-warranty servicing and extends product lifespan.</t>
+          <t>To maintain print quality and prevent aerosol contamination.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Service, Product Management, End Users</t>
+          <t>R&amp;D, Quality Assurance, Service</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Service part logistics, documentation.</t>
+          <t>Tank and service station design.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Ink maintenance part replaceable at service centers; process documented and validated.</t>
+          <t>Aerosol levels are within HP defined limits in all tested scenarios.</t>
         </is>
       </c>
       <c r="I20" t="n">
@@ -1450,41 +1450,41 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>New IDS Make-Break and FI Connection</t>
+          <t>Carriage Dynamic and Force Model with Tube and New Weights</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Implement new make-break and FI (Fluidic Interface) connection in the IDS, leveraging LEBI ink-tank with increased size, keying, and LOI (Level of Ink) One SHAID.</t>
+          <t>Develop a dynamic and force model for the carriage, accounting for new tube routing and weight changes.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Improves reliability and serviceability of ink delivery system.</t>
+          <t>To ensure mechanical reliability and print quality with new design.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>R&amp;D, Service, Manufacturing</t>
+          <t>R&amp;D, Mechanical Engineering</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>IDS and tank design, component integration.</t>
+          <t>Tube and carriage design.</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>New IDS connections implemented and validated in system integration testing.</t>
+          <t>Model validated and carriage performance meets HP standards in all test cases.</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1501,17 +1501,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>New IDS Startup Algorithm and Air Management</t>
+          <t>Paper Path Support for Increased Page Life</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Develop new IDS startup algorithm and air management system to support larger tanks and new ink system.</t>
+          <t>Modify paper path components to support increased page life of 80K pages.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Ensures reliable system startup and prevents air-related print defects.</t>
+          <t>To ensure durability and reliability over extended use.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1521,21 +1521,21 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>R&amp;D, Firmware, Service</t>
+          <t>R&amp;D, Manufacturing, Service</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>IDS algorithm development, tank and tube design.</t>
+          <t>Paper path and overall printer design.</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Startup algorithm and air management validated in system testing; no startup failures or air-related defects.</t>
+          <t>Paper path components meet 80K page durability in accelerated testing.</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1552,37 +1552,37 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>New Print Quality Goals and Depletion Metrics</t>
+          <t>Ink Maintenance Serviceable Part (Post 80K Life)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Define and implement new print quality (PQ) goals and depletion metrics to align with increased page yield definition.</t>
+          <t>Design ink maintenance as a serviceable part, replaceable at service center after 80K page life.</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Ensures that print quality is maintained throughout the extended product life and yield.</t>
+          <t>To support ongoing maintenance and extend product life.</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality Assurance, Product Management</t>
+          <t>Service, End Users</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>PQ standards development, yield testing.</t>
+          <t>Maintenance part design and service procedures.</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>PQ goals and depletion metrics defined, validated in life testing, and documented.</t>
+          <t>Part is replaceable at service centers and validated in field trials.</t>
         </is>
       </c>
       <c r="I23" t="n">
@@ -1603,17 +1603,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Reuse of Marconi Hi PDL and Tux dASIC</t>
+          <t>140ml K Bottles and New CMY Bottle Sizes</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Reuse Marconi Hi PDL, Marconi Tux dASIC, Hannibal aASIC, and Raccoon PSU for the Magellan platform.</t>
+          <t>Introduce 140ml K (Black) bottles and new, larger capacity CMY bottles.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Leverages proven hardware modules to reduce risk and development time.</t>
+          <t>To support higher print volumes and reduce frequency of consumable replacement.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1623,17 +1623,17 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>R&amp;D, Supply Chain, Manufacturing</t>
+          <t>R&amp;D, Manufacturing, End Users</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Component compatibility and integration.</t>
+          <t>Bottle and ink system design.</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Components reused without issues; system integration tests pass.</t>
+          <t>Bottles meet specified volume and pass yield and reliability testing.</t>
         </is>
       </c>
       <c r="I24" t="n">
@@ -1654,17 +1654,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Stingray Wi-Fi Module and Dune Firmware</t>
+          <t>New Make-Break and FI Connection for IDS</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Integrate Stingray Wi-Fi module and Dune firmware into the product.</t>
+          <t>Implement new make-break and fluidic interconnect (FI) connection for IDS, leveraging LEBI ink-tank with increased size, keying, and LOI (SHAID).</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Provides wireless connectivity and firmware platform continuity.</t>
+          <t>To improve ink delivery security, capacity, and system intelligence.</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1674,21 +1674,21 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Management, End Users</t>
+          <t>R&amp;D, Manufacturing, Product Security</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Module and firmware integration, compliance testing.</t>
+          <t>IDS, LEBI tank, SHAID integration.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Wi-Fi and firmware operate reliably and pass regulatory and user acceptance tests.</t>
+          <t>Connections meet flow, reliability, and security requirements in all test cases.</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -1705,17 +1705,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Gauss4.xx Security (HW &amp; FW)</t>
+          <t>New IDS Startup Algorithm and Air Management</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Implement Gauss4.xx security features in both hardware and firmware.</t>
+          <t>Develop new IDS startup algorithm and air management system for improved reliability and startup performance.</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Ensures product security and compliance with HP security standards.</t>
+          <t>To optimize printer startup and prevent air-related failures.</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1725,21 +1725,21 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Product Security, R&amp;D, IT, Customers</t>
+          <t>R&amp;D, Quality Assurance</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>HW and FW development, security validation.</t>
+          <t>IDS and air management system design.</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Security features implemented and pass internal security audits.</t>
+          <t>Startup algorithm and air management validated in cold and warm start scenarios with zero failures.</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -1756,17 +1756,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Business Model and Solution Support</t>
+          <t>New Print Quality (PQ) Goals and Depletion Metrics</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Support Consumer, SMB, and Enterprise business models, including PaaS (Printing as a Service), WorkFromHome/Flexworker, and onboarding via Consumer/HPX, HP One, SMB Portal, and ECP paths. Support scan solution, SMB manageability, and Enterprise support (WJA, HPSM, JAM).</t>
+          <t>Set new print quality goals and depletion metrics to align with page yield definitions.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Expands market reach and supports multiple customer segments and deployment models.</t>
+          <t>To ensure consistent output and accurate yield reporting.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1776,21 +1776,21 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Product Management, Business Operations, Channel Partners</t>
+          <t>R&amp;D, Quality Assurance, Product Management</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Solution integration, onboarding path development.</t>
+          <t>PQ definition, depletion measurement systems.</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>All business models and solution paths functional and documented; onboarding validated for each segment.</t>
+          <t>Print quality and depletion metrics meet or exceed defined targets in all yield tests.</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -1807,17 +1807,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Client and Driver Support</t>
+          <t>Reuse Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Support HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD clients and drivers for seamless installation and operation.</t>
+          <t>Leverage existing Marconi Tux dASIC, Hannibal aASIC, and Raccoon PSU hardware in the new design.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Ensures compatibility with HP’s ecosystem and customer IT environments.</t>
+          <t>To reduce development costs and leverage proven components.</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1827,17 +1827,17 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>IT, End Users, Channel Partners</t>
+          <t>R&amp;D, Manufacturing</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Driver and client integration, validation.</t>
+          <t>Component compatibility with new system design.</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>All listed drivers and clients install and operate successfully on supported platforms.</t>
+          <t>All reused components pass integration and functional testing in the new platform.</t>
         </is>
       </c>
       <c r="I28" t="n">
@@ -1858,17 +1858,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Schedule and Checkpoint Adherence</t>
+          <t>Stingray Wi-Fi Module and FW Dune</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Adhere to defined hardware, NOA-F, and bottle checkpoints and build milestones (e.g., Re-SI, DO, IL, DP, MC, VR, FCS, BB1, BB2, TR, LP1, LP2, MP1/PP, SOR).</t>
+          <t>Integrate Stingray Wi-Fi module and FW Dune firmware in the Magellan printer.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Ensures timely program execution and risk management.</t>
+          <t>To provide wireless connectivity and leverage existing firmware platform.</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1878,17 +1878,17 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Program Management, R&amp;D, Manufacturing</t>
+          <t>R&amp;D, End Users, Product Management</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Project management processes, milestone tracking.</t>
+          <t>Wi-Fi module and firmware compatibility.</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>All checkpoints and builds completed as per schedule; deviations documented and addressed.</t>
+          <t>Wi-Fi and firmware operate as intended in all connectivity and functional tests.</t>
         </is>
       </c>
       <c r="I29" t="n">
@@ -1909,45 +1909,45 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Serviceability of Maintenance Box</t>
+          <t>Gauss4.xx Security (HW &amp; FW)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ensure maintenance box is easily serviceable to optimize service operations and customer experience.</t>
+          <t>Implement Gauss4.xx hardware and firmware security features in the printer.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Reduces downtime and service costs.</t>
+          <t>To ensure product and data security.</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Service, End Users, Product Management</t>
+          <t>Security, R&amp;D, Product Management</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Maintenance box design, service process documentation.</t>
+          <t>Gauss4.xx security module integration.</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Maintenance box can be serviced/replaced by service personnel; validated by serviceability testing.</t>
+          <t>Security features validated against HP security standards and penetration testing.</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -1960,217 +1960,221 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Host 12K-CMYK and Trade Page 6K (Flexible Priority)</t>
+          <t>Business Model and Solution Support for Consumer, SMB, and Enterprise</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Support for hosting 12,000-page CMYK and trade page 6,000, as a flexible business requirement.</t>
+          <t>Support business models for Consumer, SMB, and Enterprise, including PaaS, WorkFromHome/Flexworker, onboarding paths, and solution compatibility (scan, SMB manageability, enterprise support).</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Allows for future scalability and market responsiveness.</t>
+          <t>To address diverse market needs and enable flexible deployment.</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Product Management, Business Operations</t>
+          <t>Product Management, Sales, Business Development</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ink system scalability, market analysis.</t>
+          <t>Solution development, onboarding path integration.</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>System design allows for 12K-CMYK and 6K trade page options if required by business.</t>
+          <t>Business models and solutions are available and functional for all targeted segments.</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.7</v>
+        <v>0.85</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Client and Driver Support (HPX, PSA, SUPD, UPD, EasyStart, USS, UFD)</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ensure compatibility with HPX, PSA, SUPD, UPD clients and drivers, as well as EasyStart, USS, and UFD.</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>To provide seamless installation and operation across platforms.</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>End Users, IT, Product Management</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Driver and client software integration.</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>All listed clients and drivers are compatible and pass installation and function tests.</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Schedule Adherence as Constrained Priority</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Adhere to defined schedule checkpoints for hardware, NOA-F, and bottle development, as outlined in project plan.</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>To ensure timely delivery and market launch.</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Project Management, R&amp;D, Manufacturing</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>All development milestones and dependencies.</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>All checkpoints met within defined timeframes as per project plan.</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
           <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>AI Productivity, Scan Workflow &amp; Manageability Solutions</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Implement advanced AI-driven productivity features, including scan workflow automation and enhanced manageability tools, to simplify business operations for SMB customers.</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Addresses SMB need for efficiency and minimal IT intervention, providing a competitive edge and aligning with the product's value proposition.</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Marketing, GXD, Quality, R&amp;D Telemetry, Supplies Quality, DVAR, Tech Reg, Prod Steward, BA</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Integration with SMB portal and device management solutions</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>AI productivity features are available in the product; scan workflow automation is functional; manageability tools are accessible via the SMB portal.</t>
-        </is>
-      </c>
-      <c r="I32" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 4, 7, 10, 11</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Lowest Business TCO (Total Cost of Ownership)</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Design the printer to deliver the lowest business TCO in its class, including efficient ink usage, minimal maintenance, and optimized consumable costs.</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>SMBs are highly cost-sensitive; lowest TCO is a key differentiator and driver for purchase.</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Marketing, Quality, Supplies Quality, BA</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Sustainability features, maintenance design, consumables pricing</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Independent cost analysis confirms lowest TCO compared to direct competitors in the SMB tank printer segment.</t>
-        </is>
-      </c>
-      <c r="I33" t="n">
+      <c r="K33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>SuperAmp PHA Life at 65K as Constrained Priority</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ensure SuperAmp PHA life is at least 65,000 pages as a non-flexible constraint.</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>To meet reliability and warranty requirements.</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>R&amp;D, Quality Assurance, Service</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>SuperAmp PHA design and validation.</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>SuperAmp PHA demonstrates life of 65,000 pages in accelerated testing.</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
         <v>0.9</v>
       </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 4, 11</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr"/>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>80k or 2-Year Warranty (Whichever First)</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Offer a warranty of 80,000 pages printed or 2 years, whichever comes first, for the Magellan printer.</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Warranty is a key purchase consideration for SMBs, ensuring reliability and reducing perceived risk.</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Quality, Marketing, DVAR, BA</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Serviceability design, consumables durability</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Warranty terms are clearly stated in product documentation and reflected in warranty registration systems.</t>
-        </is>
-      </c>
-      <c r="I34" t="n">
-        <v>0.95</v>
-      </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr"/>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Serviceability: Customer Replaceable Parts (PHA) and MINK at Service Centre</t>
+          <t>Warranty Life of 2 Years and 80K Pages</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Enable customer replaceable parts (PHA) and MINK replacement at service centers, with a target for more parts to be customer replaceable if out of warranty.</t>
+          <t>Optimize warranty life to 2 years or 80,000 pages, whichever comes first.</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Reduces downtime and cost for SMBs without dedicated IT, improving user experience and satisfaction.</t>
+          <t>To align with industry standards and customer expectations.</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2180,17 +2184,17 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Quality, R&amp;D Telemetry, Supplies Quality, DVAR</t>
+          <t>Product Management, End Users, Service</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Parts design, documentation, training material</t>
+          <t>Component and consumable durability.</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>At least PHA is customer replaceable and MINK is serviceable at authorized centers; documentation and training are available.</t>
+          <t>Warranty is valid for 2 years or 80K pages, and all components meet reliability requirements.</t>
         </is>
       </c>
       <c r="I35" t="n">
@@ -2198,30 +2202,30 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr"/>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Keyed Ink Bottles</t>
+          <t>Throughput of 25/20 PPM (PDL: 25/19PPM)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Utilize keyed ink bottles to prevent incorrect refilling and ensure only genuine HP supplies are used.</t>
+          <t>Optimize printer throughput to achieve 25/20 pages per minute (PPM), with PDL at 25/19 PPM.</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Prevents user errors and protects HP supplies revenue.</t>
+          <t>To meet market performance expectations and remain competitive.</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2231,119 +2235,119 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Supplies Quality, Tech Reg, Prod Steward</t>
+          <t>End Users, Product Management, R&amp;D</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Ink system design, supply chain</t>
+          <t>Print engine and firmware optimization.</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Printer only accepts correctly keyed bottles; nozzles and bottles are physically incompatible with non-genuine supplies.</t>
+          <t>Printer achieves specified throughput in standard performance tests.</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Magellan_SI_1-pager.pdf, page 1,2</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr"/>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Non-PDL SKU: SMB2.0 Solutions and Advanced View SMB Portal Support</t>
+          <t>Serviceability - Maintenance Box</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Ensure the non-PDL SKU supports SMB2.0 Solutions and is fully integrated with the Advanced View SMB portal.</t>
+          <t>Optimize serviceability by providing a maintenance box for easy replacement and maintenance.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Addresses the need for centralized device management for unmanaged/lightly managed SMBs.</t>
+          <t>To reduce downtime and improve user/service experience.</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>GXD, R&amp;D Telemetry, BA, Marketing</t>
+          <t>Service, End Users</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Portal development, firmware integration</t>
+          <t>Maintenance box design and integration.</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Non-PDL SKU is compatible with SMB2.0 Solutions and Advanced View portal out-of-the-box.</t>
+          <t>Maintenance box is user/service replaceable and passes field serviceability tests.</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 10</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr"/>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>PaaS (Printing as a Service) Support</t>
+          <t>SMB Solution Support</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Support Printing as a Service (PaaS) model for both PDL and non-PDL SKUs.</t>
+          <t>Optimize printer features and solutions to support SMB requirements (manageability, cost, reliability).</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Enables flexible business models and recurring revenue streams for HP and partners.</t>
+          <t>To target and win SMB market segment.</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Marketing, DVAR, BA</t>
+          <t>SMB Customers, Sales, Product Management</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Firmware, portal, billing integration</t>
+          <t>Solution and feature set definition.</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>PaaS features are available for both SKUs; billing and management workflows tested.</t>
+          <t>Printer meets SMB manageability and cost requirements as defined by SMB feedback.</t>
         </is>
       </c>
       <c r="I38" t="n">
@@ -2351,81 +2355,77 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 10</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr"/>
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>PDL SKU: Improved Print Speed and PDL/PS Support</t>
+          <t>Host 12K-CMYK and Trade Page 6K as Flexible Priorities</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>PDL SKU must achieve print speeds of 25/20 ppm (improvement from current 25/19) and support Page Description Languages (PDL) and PostScript (PS).</t>
+          <t>Allow flexibility in supporting Host 12K-CMYK and Trade Page 6K requirements based on market and business needs.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Meets the needs of more demanding SMB customers and competitive benchmarks.</t>
+          <t>To provide adaptability in product offering and market response.</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>R&amp;D Telemetry, Marketing, BA</t>
+          <t>Product Management, Sales</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Print engine, firmware, driver development</t>
+          <t>Market analysis and business strategy.</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>PDL SKU achieves specified speeds and passes PDL/PS compatibility tests.</t>
+          <t>Host 12K-CMYK and Trade Page 6K features can be enabled/disabled as needed for specific SKUs.</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Blue Angel Certification for PDL SKU</t>
+          <t>AI Productivity and Manageability Solutions</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Ensure the PDL SKU meets Blue Angel environmental certification requirements.</t>
+          <t>Integrate advanced AI-driven productivity features and manageability solutions for the Magellan printer, including Perfect Print and Perfect Scan capabilities, and AI-powered device management via a consolidated SMB portal.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Sustainability is a key differentiator and compliance requirement in key markets.</t>
+          <t>AI features are highlighted as a major differentiator and are critical to meeting SMB customer needs for efficiency and ease of management.</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2435,30 +2435,30 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Prod Steward, Tech Reg, Marketing</t>
+          <t>['Marketing', 'GXD', 'Quality', 'R&amp;D Telemetry', 'Supplies Quality', 'DVAR', 'Tech Reg', 'Prod Steward', 'BA']</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Materials, power consumption, emissions design</t>
+          <t>['Consolidated SMB portal', 'AI software development']</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>PDL SKU receives Blue Angel certification prior to launch.</t>
+          <t>AI features (Perfect Print, Perfect Scan, AI device management) are available and functional in the product release, validated by user acceptance testing and feedback from SMB customers.</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan MRD, Page 4, 7, 10, 11</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2466,50 +2466,50 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Replaceable Maintenance Box</t>
+          <t>Lowest Business Total Cost of Ownership (TCO)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Incorporate a replaceable maintenance box to support new use cases and reduce downtime.</t>
+          <t>Design the Magellan printer to deliver HP's lowest business TCO for SMBs, including minimal intervention and maintenance requirements.</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Supports new SMB use cases and enhances serviceability for non-IT users.</t>
+          <t>SMB customers prioritize ROI and efficiency; minimizing TCO is a key selling point and competitive differentiator.</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Quality, R&amp;D Telemetry, Supplies Quality</t>
+          <t>['Marketing', 'Quality', 'Prod Steward', 'BA']</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Parts design, documentation</t>
+          <t>['Maintenance-free/low-maintenance design', 'Sustainability features']</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Maintenance box is user-replaceable and instructions are provided; tested for usability by non-IT users.</t>
+          <t>Independent cost analysis demonstrates Magellan's TCO is lower than comparable HP and competitor models for SMB use cases.</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan MRD, Page 4, 11</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -2517,17 +2517,17 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Perfect Print and Perfect Scan AI Solutions</t>
+          <t>Customer Replaceable Parts and Serviceability</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Integrate advanced AI-driven 'Perfect Print' and 'Perfect Scan' solutions to enhance print and scan quality automatically.</t>
+          <t>Enable customer replaceable parts (e.g., maintenance box, PHA) and ensure serviceability through both customer and service center options, with clear thresholds for each.</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Delivers superior output quality with minimal user intervention, a key differentiator for SMBs.</t>
+          <t>Reduces downtime and support costs for SMBs without dedicated IT, improving overall user experience.</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2537,30 +2537,30 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>GXD, R&amp;D Telemetry, Marketing, Quality</t>
+          <t>['Quality', 'R&amp;D Telemetry', 'Supplies Quality', 'Tech Reg']</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>AI algorithm development, hardware compatibility</t>
+          <t>['Warranty policies', 'Parts design']</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>AI features demonstrably improve print/scan quality in benchmark tests.</t>
+          <t>Documentation and physical design allow end users to replace specified parts; service center support is available for other components. Field testing confirms successful replacement by non-IT staff.</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 7, 11</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -2568,50 +2568,50 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SMB Portal for Printer Management</t>
+          <t>Keyed Ink Bottles for Supplies</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Provide a consolidated portal for SMB customers to manage multiple printers, including device status, usage, and maintenance alerts.</t>
+          <t>Implement keyed ink bottles to ensure proper installation and reduce supply errors or counterfeit risks.</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Addresses need for easy, centralized management for offices without dedicated IT staff.</t>
+          <t>Prevents incorrect usage and supports supply chain integrity, a concern for SMBs managing multiple devices.</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>GXD, R&amp;D Telemetry, BA, Marketing</t>
+          <t>['Supplies Quality', 'Quality', 'Prod Steward']</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Portal software development, device firmware integration</t>
+          <t>['Ink supply system design']</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Portal is available and functional; users can manage at least 6-15 printers as per target customer profile.</t>
+          <t>All ink bottles are uniquely keyed and cannot be incorrectly installed. Testing demonstrates error prevention in typical SMB environments.</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 7, 10, 11</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -2619,17 +2619,17 @@
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Sustainability: 60% Recycled Content Plastic (RCP)</t>
+          <t>SMB Portal for Device Management</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Ensure that at least 60% of the printer's plastic is made from recycled content, surpassing key competitors.</t>
+          <t>Develop a consolidated portal (SMB portal) for managing multiple printers, targeting the needs of unmanaged or lightly managed SMBs.</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Sustainability is a key purchase driver and competitive differentiator in the SMB segment.</t>
+          <t>Enables non-IT staff to manage fleets of printers efficiently, addressing a primary customer pain point.</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2639,30 +2639,30 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Prod Steward, Tech Reg, Marketing</t>
+          <t>['GXD', 'Marketing', 'R&amp;D Telemetry', 'BA']</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Material sourcing, compliance testing</t>
+          <t>['AI manageability solutions', 'Cloud infrastructure']</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Product composition verified to have 60% RCP; documented in product specs and marketing.</t>
+          <t>Portal is operational, supports management of 6-15 printers per SMB, and is validated via usability testing with target users.</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 11</t>
+          <t>Magellan MRD, Page 7, 10</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -2670,17 +2670,17 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Mobile Printing via HP App</t>
+          <t>Support for PaaS and Advanced View SMB Portal (Non-PDL SKU)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Enable seamless mobile printing functionality through the HP App for SMB users.</t>
+          <t>Ensure the Magellan printer supports Printing-as-a-Service (PaaS) and Advanced View SMB portal for non-PDL SKUs.</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Mobile printing is a top use case and expectation for modern SMBs.</t>
+          <t>Aligns with HP's strategic goal for PaaS acceleration and provides SMBs with flexible, scalable solutions.</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2690,30 +2690,30 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>GXD, BA, Marketing</t>
+          <t>['Marketing', 'GXD', 'BA']</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>App integration, firmware support</t>
+          <t>['Portal development', 'SKU differentiation']</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Mobile printing is tested and functional with HP App on major platforms (iOS, Android).</t>
+          <t>Non-PDL SKUs are compatible with PaaS and Advanced View SMB portal, confirmed by integration and functional testing.</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 9, 10</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -2721,37 +2721,37 @@
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Telemetry Requirements</t>
+          <t>PDL SKU Performance and Features</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Implement telemetry features to collect anonymized usage, performance, and error data for product improvement and support.</t>
+          <t>PDL SKUs must achieve print speeds of 25/20 ppm (improved from current 25/19), support PDL/PS, and comply with Blue Angel environmental certification.</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Supports proactive support, quality monitoring, and future product enhancements.</t>
+          <t>Meets performance expectations for higher-end SMB segments and aligns with sustainability goals.</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>R&amp;D Telemetry, Quality, BA</t>
+          <t>['Quality', 'Tech Reg', 'Prod Steward']</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Firmware, portal integration, privacy compliance</t>
+          <t>['PDL hardware/software development', 'Certification process']</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Telemetry data is collected, transmitted securely, and accessible for analysis; compliance with privacy regulations.</t>
+          <t>PDL SKUs pass speed benchmarks, support PDL/PS, and receive Blue Angel certification.</t>
         </is>
       </c>
       <c r="I46" t="n">
@@ -2759,12 +2759,216 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Sustainability – 60% Recycled Content Plastic (RCP)</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Design the Magellan printer to utilize at least 60% recycled content plastic, exceeding competitor standards (Epson 30%, Canon TBC).</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Supports HP’s sustainability leadership and is a key differentiator for environmentally conscious SMBs.</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>['Prod Steward', 'Tech Reg', 'Marketing']</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>['Supply chain sourcing', 'Manufacturing processes']</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Bill of materials and third-party verification confirm at least 60% RCP in final product.</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 11</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Warranty – 80k Pages or 2 Years</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Offer a warranty covering either 80,000 pages or 2 years, whichever comes first, for the Magellan printer.</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Provides assurance to SMBs regarding durability and reliability, supporting purchase decisions.</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>['Quality', 'Marketing', 'BA']</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>['Serviceability design', 'Warranty policy']</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Warranty terms are published and honored; field data shows compliance with warranty limits.</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Mobile Printing and HP App Integration</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Enable mobile printing capabilities and seamless integration with the HP App for the Magellan printer.</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Addresses modern SMB workflows and enhances user convenience.</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>['GXD', 'Marketing', 'BA']</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>['App development', 'Firmware integration']</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Users can print from mobile devices via the HP App; successful end-to-end testing with iOS and Android devices.</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 9, 10</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr"/>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Telemetry Requirements</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Implement telemetry features to collect and report printer usage, health, and performance data for proactive support and analytics.</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Enables HP and customers to monitor device health and usage, supporting predictive maintenance and improved service.</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>['R&amp;D Telemetry', 'Quality', 'BA']</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>['Firmware development', 'Privacy compliance']</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Telemetry data is securely collected, transmitted, and accessible via SMB portal; compliance with privacy regulations is verified.</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
           <t>Magellan MRD, Page 3, 12</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>15</t>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>11</t>
         </is>
       </c>
     </row>

--- a/consolidation/outputs/consolidated_requirements.xlsx
+++ b/consolidation/outputs/consolidated_requirements.xlsx
@@ -481,17 +481,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NGB Keyed Bottles with High Page Yield</t>
+          <t>NGB Keyed Bottles with Increased Yield</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Develop new NGB keyed ink bottles supporting 6K Black and 6K CMY page yield, with CMY bottle size &gt;8K.</t>
+          <t>Develop new NGB keyed ink bottles supporting 6K Black and 6K CMY page yields, with bottle size for CMY &gt;8K.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>To increase consumable capacity and meet high-volume printing needs, supporting longer intervals between replacements.</t>
+          <t>Increased ink capacity and unique keying improve user experience and reduce frequency of replacements, supporting higher page yield.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -506,12 +506,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Requires compatibility with NOA-F, SuperAmp PHA, and existing ink systems.</t>
+          <t>Requires compatibility with NOA-F and IDS systems.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>NGB keyed bottles deliver 6,000 pages for Black, 6,000 pages for CMY (with CMY bottle size &gt;8,000 pages), verified by yield tests.</t>
+          <t>Bottles must be keyed, support 6K Black and 6K CMY yields, and CMY bottle must have capacity &gt;8K. Successfully tested for fit and function in printer.</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -532,17 +532,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Spill-Free Reliability for Bottles</t>
+          <t>Spill-Free Reliability for Ink Bottles</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ensure the bottle design and ink delivery system provide spill-free operation during installation and use.</t>
+          <t>Ensure new ink bottles and filling system achieve spill-free performance during installation and use.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>To improve user experience and reduce maintenance/service calls due to ink spills.</t>
+          <t>Reduces customer complaints and warranty costs, improves brand perception.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -557,12 +557,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bottle and NOA-F design integration.</t>
+          <t>Integration with bottle design and NOA-F system.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>User installs bottle with no ink spillage in 100% of test cases under defined use scenarios.</t>
+          <t>No ink spill incidents in 99.9% of installation cycles during qualification testing.</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -588,12 +588,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Integrate NOA-F with a metal foiled labyrinth and lid label, maintaining compatibility with click-on push-push and TDF mechanisms.</t>
+          <t>Implement NOA-F with a metal foiled labyrinth and a lid label. No change to click-on push-push and TDF mechanisms.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>To improve reliability and security of ink delivery and maintain compatibility with existing mechanisms.</t>
+          <t>Improves reliability and traceability, leverages existing mechanisms for cost and time efficiency.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -603,21 +603,21 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing, End Users</t>
+          <t>R&amp;D, Service, Manufacturing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Existing push-push and TDF mechanisms.</t>
+          <t>Dependent on NOA-F and bottle design.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>NOA-F units pass reliability tests and are compatible with click-on push-push and TDF in all production units.</t>
+          <t>NOA-F units include metal foiled labyrinth and lid label, and pass reliability and traceability tests.</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -634,17 +634,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Reuse SuperAmp Si PHA and Magi/Nessie Ink</t>
+          <t>Reuse Superamp Si PHA and Magi/Nessie Inks</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Reuse SuperAmp Si PHA and Magi/Nessie pigment inks without ink reformulation.</t>
+          <t>Reuse existing Superamp Si PHA and Magi/Nessie pigment inks without reformulation.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>To leverage proven technology, reduce development time, and maintain ink quality.</t>
+          <t>Reduces development time and cost, ensures proven ink quality.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -654,17 +654,17 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing</t>
+          <t>R&amp;D, Supply Chain, Manufacturing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Existing SuperAmp Si PHA and Magi/Nessie ink specifications.</t>
+          <t>Requires compatibility with new bottles and NOA-F.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>SuperAmp Si PHA and Magi/Nessie inks are used in production units with no reformulation required.</t>
+          <t>Superamp Si PHA and Magi/Nessie inks function as required with new system, no reformulation needed.</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -685,17 +685,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Reliability and Ink Stability Modeling</t>
+          <t>Reliability and Characterization Modelling</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Model and characterize reliability, WVTR, air gain, flow rate, IDS, startup, and NOA-F EOL for the ink system, including ink stability in tank and impact to print quality (PQ).</t>
+          <t>Conduct reliability, WVTR, air gain, flow rate, and IDS characterization and modelling, including startup and NOA-F EOL.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>To ensure robust and consistent printer performance throughout its lifecycle.</t>
+          <t>Ensures system reliability, performance, and longevity.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -710,16 +710,16 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Integration with IDS and NOA-F systems.</t>
+          <t>Related to IDS, NOA-F, and ink system design.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Comprehensive models and test results demonstrating system reliability and ink stability over defined lifecycle.</t>
+          <t>All models completed and validated against test data; system meets reliability targets.</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -736,41 +736,41 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NOA-F as Service Parts in Warranty Support</t>
+          <t>Ink Stability Modelling</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Provide NOA-F as service parts for warranty support, ensuring availability during warranty period.</t>
+          <t>Model ink stability in tank and assess impact on print quality (PQ).</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>To support post-sale serviceability and customer satisfaction.</t>
+          <t>Prevents print quality degradation over time and ensures customer satisfaction.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Service, Warranty, End Users</t>
+          <t>R&amp;D, Quality Assurance</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>NOA-F production and distribution channels.</t>
+          <t>Dependent on ink formulation and tank design.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>NOA-F available as service part for all units under warranty within defined SLA.</t>
+          <t>Stability model completed; PQ maintained over expected tank life.</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -787,41 +787,41 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Acumen 6 on Lid</t>
+          <t>NOA-F as Service Parts for Warranty Support</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Integrate Acumen 6 feature on the lid of the ink system.</t>
+          <t>Provide NOA-F as service parts to support warranty claims and repairs.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>To enhance product intelligence, traceability, or anti-counterfeiting measures.</t>
+          <t>Improves serviceability and customer support for warranty repairs.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>R&amp;D, Security, Product Management</t>
+          <t>Service, Warranty, End Users</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lid design and Acumen 6 compatibility.</t>
+          <t>Requires stocking and logistics planning.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>All lids incorporate Acumen 6 and are validated for intended function.</t>
+          <t>NOA-F available as service part and integrated in warranty process.</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -838,41 +838,41 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Factory Line Modifications for NOA-F and Magi Ink Cart</t>
+          <t>Acumen 6 on Lid</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Modify existing SA14 line for NOA-F, add Magi ink cart and labeling tool in Orcus 5, and ensure PHA + Dry FI + USG + push-push assembly in printer factory.</t>
+          <t>Integrate Acumen 6 technology on the ink bottle lid for enhanced authentication or tracking.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>To support new components and maintain production efficiency.</t>
+          <t>Improves product authentication and anti-counterfeit measures.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Manufacturing, Operations, R&amp;D</t>
+          <t>R&amp;D, Security, Supply Chain</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Existing SA14 and Orcus 5 line configurations.</t>
+          <t>Dependent on lid and bottle design.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Production lines modified and validated to support new components without impacting throughput.</t>
+          <t>Acumen 6 successfully integrated and functional on production lids.</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -889,17 +889,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Mold for 1 to 4 New Keyed Caps</t>
+          <t>Factory Line Modifications for NOA-F and Magi Ink Cart</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Develop molds for 1 to 4 new keyed caps for bottles.</t>
+          <t>Modify existing SA14 line for NOA-F, add Magi ink cart and labelling tool in Orcus 5, and provide mold for 1 to 4 new keyed caps.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>To support new bottle keying and prevent cross-contamination or misinstallation.</t>
+          <t>Enables manufacturing of new components and ensures production readiness.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -909,21 +909,21 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Manufacturing, R&amp;D</t>
+          <t>Manufacturing, Operations, R&amp;D</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bottle and cap design finalization.</t>
+          <t>Dependent on final design of NOA-F, ink cart, and caps.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Molds created and caps produced pass fit and function tests.</t>
+          <t>SA14 line and Orcus 5 upgrades completed, new caps molded and validated in production.</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -940,17 +940,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Support Customer Replaceable PHA and NOA-F</t>
+          <t>Support Customer-Replaceable PHA and NOA-F</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Enable end users to replace PHA and NOA-F components without technical assistance.</t>
+          <t>Design system to allow customers to replace PHA and NOA-F components easily.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>To improve serviceability and reduce downtime for customers.</t>
+          <t>Improves serviceability, reduces downtime and service costs.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -965,12 +965,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Design of PHA and NOA-F for user replacement.</t>
+          <t>Dependent on mechanical and user interface design.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Users can replace PHA and NOA-F following provided instructions in &gt;95% of usability tests.</t>
+          <t>Customers can replace PHA and NOA-F with no tools and minimal instructions; validated in user testing.</t>
         </is>
       </c>
       <c r="I11" t="n">
@@ -991,17 +991,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Warranty Page Life Goal of 80K Pages</t>
+          <t>Warranty Page Life Goal of 80k Pages</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Design printer and consumables to support a new warranty page life goal of 80,000 pages.</t>
+          <t>Achieve new warranty page life goal of 80,000 pages per device.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>To increase product longevity and competitiveness in the market.</t>
+          <t>Extends product life and reduces total cost of ownership for users.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1011,17 +1011,17 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Product Management, End Users, Service</t>
+          <t>End Users, Service, Product Management</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Component durability, ink system reliability.</t>
+          <t>Dependent on reliability of critical components (PHA, NOA-F, ink system, etc.).</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Printer and consumables meet or exceed 80,000 page life in accelerated lifecycle testing.</t>
+          <t>Printer passes 80,000 page yield test with no critical failures during warranty period.</t>
         </is>
       </c>
       <c r="I12" t="n">
@@ -1042,17 +1042,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SKU 2 (Hi + Hi PDL) PaaS</t>
+          <t>Support for Hi + Hi PDL SKU (SKU 2) PaaS</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Develop SKU 2 supporting both Hi and Hi PDL, with Platform-as-a-Service (PaaS) support.</t>
+          <t>Develop and support a SKU for Hi + Hi PDL with Platform as a Service (PaaS) business model.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>To address diverse market segments and enable flexible business models.</t>
+          <t>Targets business customers and enables flexible service offerings.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1062,17 +1062,17 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Product Management, Sales, Business Development</t>
+          <t>Product Management, Business Development, SMB/Enterprise Customers</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>SKU definition, PaaS infrastructure.</t>
+          <t>Requires alignment with business model and service infrastructure.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>SKU 2 available for order with Hi and Hi PDL options, and PaaS functionality enabled.</t>
+          <t>SKU 2 available for order with PaaS support, integrated with business systems.</t>
         </is>
       </c>
       <c r="I13" t="n">
@@ -1093,41 +1093,41 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Reddington ID with Increased Tank Size</t>
+          <t>Increase Tank Size for Reddington ID</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Implement Reddington ID with increased tank size, ensuring no change to Marconi-HI ADF.</t>
+          <t>Increase tank size for Reddington ID product variant, with no change to Marconi-HI ADF.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>To accommodate higher ink volumes and maintain compatibility with existing document feeders.</t>
+          <t>Supports higher ink capacity and extended printing.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing, Product Management</t>
+          <t>Product Management, R&amp;D</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tank design, Marconi-HI ADF interface.</t>
+          <t>Impacts packaging and mechanical design.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Reddington ID supports increased tank size and is validated for ADF compatibility.</t>
+          <t>Tank size increased and validated in Reddington ID variant, ADF remains unchanged.</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1149,12 +1149,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Use EPS foam packaging for the Magellan printer.</t>
+          <t>Implement EPS foam packaging for improved product protection during shipping.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>To ensure product protection during shipping and handling.</t>
+          <t>Reduces shipping damage, improves customer satisfaction.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1164,17 +1164,17 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Manufacturing, Logistics, End Users</t>
+          <t>Logistics, Manufacturing, End Users</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Packaging design and supply chain.</t>
+          <t>Packaging design and supplier capabilities.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>EPS foam packaging passes drop and vibration tests per HP standards.</t>
+          <t>EPS foam packaging implemented and passes drop/shipping tests.</t>
         </is>
       </c>
       <c r="I15" t="n">
@@ -1195,17 +1195,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EPEAT3 and LOT4 Environmental Requirements, Blue Angel for PDL SKU</t>
+          <t>EPEAT3, LOT4, and Blue Angel Compliance for PDL SKU</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ensure compliance with EPEAT3, LOT4 environmental requirements, and Blue Angel certification for PDL SKU.</t>
+          <t>Ensure product meets EPEAT3, LOT4, and Blue Angel requirements for PDL SKU.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>To meet regulatory and sustainability standards, and enhance marketability.</t>
+          <t>Enables sales in regulated markets and supports sustainability goals.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1215,17 +1215,17 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Regulatory, Product Management, Sustainability</t>
+          <t>Regulatory, Product Management, Sales</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Design and material selection, certification processes.</t>
+          <t>Dependent on product design and documentation.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Product achieves EPEAT3, LOT4, and Blue Angel certifications as applicable.</t>
+          <t>Product certified for EPEAT3, LOT4, and Blue Angel for PDL SKU.</t>
         </is>
       </c>
       <c r="I16" t="n">
@@ -1251,36 +1251,36 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Modify input and output trays to align with increased tank protrusion and optimize size.</t>
+          <t>Modify input and output trays to accommodate tank protrusion and optimize size.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>To accommodate new tank size and maintain print media handling reliability.</t>
+          <t>Ensures mechanical compatibility and minimizes device footprint.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing, End Users</t>
+          <t>R&amp;D, Manufacturing</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tank and tray design integration.</t>
+          <t>Tank and tray mechanical design.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Trays are compatible with tank protrusion and pass paper handling reliability tests.</t>
+          <t>Trays modified and validated for tank fit and function.</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Integrate a 4.3-inch CGD (Color Graphic Display) in the printer UI.</t>
+          <t>Integrate a 4.3” CGD (Color Graphic Display) into the printer.</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>To provide improved user interface and experience.</t>
+          <t>Improves user interface and accessibility.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1322,12 +1322,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>UI design, hardware integration.</t>
+          <t>Display hardware and firmware integration.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>4.3” CGD display is functional and passes user acceptance tests.</t>
+          <t>4.3” CGD display installed and passes usability and functional tests.</t>
         </is>
       </c>
       <c r="I18" t="n">
@@ -1348,22 +1348,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Leverage Sayan Sibstar Tubes with New Routing and Integration</t>
+          <t>Platform with 4 Tubes and New Routing</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Use Sayan Sibstar tubes with new tube routing and integration for ink delivery.</t>
+          <t>Leverage Sayan Sibstar tubes, implement new tube routing and integration for 4-tube platform.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>To optimize ink delivery and support new tank design.</t>
+          <t>Supports new ink delivery architecture for improved reliability and performance.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1373,16 +1373,16 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tube and tank design finalization.</t>
+          <t>Tube and ink system design.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Tube routing supports required flow rates and passes reliability tests.</t>
+          <t>4-tube platform integrated, new routing validated for flow and reliability.</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1399,17 +1399,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Service Station Aerosol Management with Spit Platform Changes</t>
+          <t>Service Station Aerosol Management</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Implement service station aerosol management with necessary changes to the spit platform due to tank design.</t>
+          <t>Update service station aerosol management with spit platform changes due to new tank design.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>To maintain print quality and prevent aerosol contamination.</t>
+          <t>Prevents contamination and ensures clean operation with larger tanks.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality Assurance, Service</t>
+          <t>R&amp;D, Service</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tank and service station design.</t>
+          <t>Dependent on tank and service station design.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Aerosol levels are within HP defined limits in all tested scenarios.</t>
+          <t>Aerosol management system updated and validated for new configuration.</t>
         </is>
       </c>
       <c r="I20" t="n">
@@ -1450,17 +1450,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Carriage Dynamic and Force Model with Tube and New Weights</t>
+          <t>Carriage Dynamic and Force Model Update</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Develop a dynamic and force model for the carriage, accounting for new tube routing and weight changes.</t>
+          <t>Update carriage dynamic and force model to account for new tube routing and weights.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>To ensure mechanical reliability and print quality with new design.</t>
+          <t>Ensures reliable motion and print quality with new mechanical configuration.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1470,17 +1470,17 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>R&amp;D, Mechanical Engineering</t>
+          <t>R&amp;D, Quality Assurance</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tube and carriage design.</t>
+          <t>Tube routing and carriage design.</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Model validated and carriage performance meets HP standards in all test cases.</t>
+          <t>Carriage model updated, system passes reliability and PQ tests.</t>
         </is>
       </c>
       <c r="I21" t="n">
@@ -1501,17 +1501,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Paper Path Support for Increased Page Life</t>
+          <t>Paper Path to Support Increased Page Life</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Modify paper path components to support increased page life of 80K pages.</t>
+          <t>Redesign paper path to support increased page life (80k pages).</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>To ensure durability and reliability over extended use.</t>
+          <t>Ensures mechanical durability and reliability over product lifespan.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1521,17 +1521,17 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing, Service</t>
+          <t>R&amp;D, Manufacturing, Quality Assurance</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Paper path and overall printer design.</t>
+          <t>Paper path and materials selection.</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Paper path components meet 80K page durability in accelerated testing.</t>
+          <t>Paper path passes 80k page durability test.</t>
         </is>
       </c>
       <c r="I22" t="n">
@@ -1552,17 +1552,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ink Maintenance Serviceable Part (Post 80K Life)</t>
+          <t>Ink Maintenance Serviceable Part (Post 80k Life)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Design ink maintenance as a serviceable part, replaceable at service center after 80K page life.</t>
+          <t>Design ink maintenance as a serviceable part to be replaced post 80k page life at Service Center.</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>To support ongoing maintenance and extend product life.</t>
+          <t>Improves serviceability and extends product usable life.</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Maintenance part design and service procedures.</t>
+          <t>Dependent on maintenance part design.</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Part is replaceable at service centers and validated in field trials.</t>
+          <t>Ink maintenance part can be replaced at service center after 80k pages.</t>
         </is>
       </c>
       <c r="I23" t="n">
@@ -1608,36 +1608,36 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Introduce 140ml K (Black) bottles and new, larger capacity CMY bottles.</t>
+          <t>Introduce 140ml Black (K) bottles and new XX ml CMY bottles for the system.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>To support higher print volumes and reduce frequency of consumable replacement.</t>
+          <t>Supports higher yield and aligns with system requirements.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing, End Users</t>
+          <t>R&amp;D, Supply Chain, Product Management</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Bottle and ink system design.</t>
+          <t>Bottle and system design.</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Bottles meet specified volume and pass yield and reliability testing.</t>
+          <t>140ml K and new CMY bottles available and validated for use.</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1654,17 +1654,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>New Make-Break and FI Connection for IDS</t>
+          <t>New IDS Make-Break and FI Connection</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Implement new make-break and fluidic interconnect (FI) connection for IDS, leveraging LEBI ink-tank with increased size, keying, and LOI (SHAID).</t>
+          <t>Implement new IDS make-break and FI connection, leveraging LEBI ink-tank with increased size, keying, and LOI One SHAID.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>To improve ink delivery security, capacity, and system intelligence.</t>
+          <t>Improves reliability, traceability, and system integration.</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1674,21 +1674,21 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing, Product Security</t>
+          <t>R&amp;D, Manufacturing, Service</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>IDS, LEBI tank, SHAID integration.</t>
+          <t>IDS and ink-tank design.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Connections meet flow, reliability, and security requirements in all test cases.</t>
+          <t>New IDS and FI connection integrated and validated in system tests.</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -1710,12 +1710,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Develop new IDS startup algorithm and air management system for improved reliability and startup performance.</t>
+          <t>Develop new IDS startup algorithm and air management system for improved reliability.</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>To optimize printer startup and prevent air-related failures.</t>
+          <t>Ensures consistent startup and operation, prevents air-related failures.</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1725,17 +1725,17 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality Assurance</t>
+          <t>R&amp;D, Service</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>IDS and air management system design.</t>
+          <t>IDS and system firmware.</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Startup algorithm and air management validated in cold and warm start scenarios with zero failures.</t>
+          <t>Startup algorithm and air management pass reliability tests and meet startup KPIs.</t>
         </is>
       </c>
       <c r="I26" t="n">
@@ -1756,41 +1756,41 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>New Print Quality (PQ) Goals and Depletion Metrics</t>
+          <t>New Print Quality Goals and Depletion Definition</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Set new print quality goals and depletion metrics to align with page yield definitions.</t>
+          <t>Define new print quality goals and depletion metrics to align with page yield definition.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>To ensure consistent output and accurate yield reporting.</t>
+          <t>Ensures consistent print quality and accurate yield reporting.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality Assurance, Product Management</t>
+          <t>Product Management, R&amp;D, Quality Assurance</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>PQ definition, depletion measurement systems.</t>
+          <t>Testing and validation protocols.</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Print quality and depletion metrics meet or exceed defined targets in all yield tests.</t>
+          <t>Print quality and depletion metrics defined, implemented, and validated.</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -1812,36 +1812,36 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Leverage existing Marconi Tux dASIC, Hannibal aASIC, and Raccoon PSU hardware in the new design.</t>
+          <t>Reuse Marconi Tux dASIC, Hannibal aASIC, and Raccoon PSU in the new system.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>To reduce development costs and leverage proven components.</t>
+          <t>Leverages proven components to reduce cost and risk.</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing</t>
+          <t>R&amp;D, Manufacturing, Supply Chain</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Component compatibility with new system design.</t>
+          <t>Compatibility with new architecture.</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>All reused components pass integration and functional testing in the new platform.</t>
+          <t>Components reused and validated in system integration tests.</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -1858,41 +1858,41 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Stingray Wi-Fi Module and FW Dune</t>
+          <t>Stingray Wi-Fi Module Integration</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Integrate Stingray Wi-Fi module and FW Dune firmware in the Magellan printer.</t>
+          <t>Integrate Stingray Wi-Fi module into the printer for wireless connectivity.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>To provide wireless connectivity and leverage existing firmware platform.</t>
+          <t>Enables modern wireless features for end users.</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>R&amp;D, End Users, Product Management</t>
+          <t>End Users, R&amp;D, Product Management</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Wi-Fi module and firmware compatibility.</t>
+          <t>Firmware and hardware integration.</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Wi-Fi and firmware operate as intended in all connectivity and functional tests.</t>
+          <t>Stingray Wi-Fi module functional and passes connectivity tests.</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -1909,41 +1909,41 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Gauss4.xx Security (HW &amp; FW)</t>
+          <t>Dune Firmware Platform</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Implement Gauss4.xx hardware and firmware security features in the printer.</t>
+          <t>Utilize Dune firmware platform for the printer.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>To ensure product and data security.</t>
+          <t>Ensures consistency and reuse of proven firmware platform.</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Security, R&amp;D, Product Management</t>
+          <t>R&amp;D, Firmware Team</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Gauss4.xx security module integration.</t>
+          <t>Firmware integration and testing.</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Security features validated against HP security standards and penetration testing.</t>
+          <t>Dune firmware operational and passes system validation tests.</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -1960,17 +1960,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Business Model and Solution Support for Consumer, SMB, and Enterprise</t>
+          <t>Gauss4.xx Security (HW &amp; FW)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Support business models for Consumer, SMB, and Enterprise, including PaaS, WorkFromHome/Flexworker, onboarding paths, and solution compatibility (scan, SMB manageability, enterprise support).</t>
+          <t>Implement Gauss4.xx security features in both hardware and firmware.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>To address diverse market needs and enable flexible deployment.</t>
+          <t>Enhances device security and compliance.</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1980,21 +1980,21 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Product Management, Sales, Business Development</t>
+          <t>Security, R&amp;D, IT</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Solution development, onboarding path integration.</t>
+          <t>HW and FW integration.</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Business models and solutions are available and functional for all targeted segments.</t>
+          <t>Gauss4.xx security features functional and pass security validation tests.</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -2011,17 +2011,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Client and Driver Support (HPX, PSA, SUPD, UPD, EasyStart, USS, UFD)</t>
+          <t>High Throughput (25/20 ppm)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Ensure compatibility with HPX, PSA, SUPD, UPD clients and drivers, as well as EasyStart, USS, and UFD.</t>
+          <t>Printer must support throughput of 25/20 pages per minute (PDL: 25/19 ppm).</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>To provide seamless installation and operation across platforms.</t>
+          <t>Meets competitive benchmarks and customer expectations for speed.</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2031,21 +2031,21 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>End Users, IT, Product Management</t>
+          <t>End Users, Product Management, Marketing</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Driver and client software integration.</t>
+          <t>Mechanical, firmware, and ink system design.</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>All listed clients and drivers are compatible and pass installation and function tests.</t>
+          <t>Printer achieves 25/20 ppm (PDL: 25/19 ppm) in performance tests.</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -2062,41 +2062,41 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Schedule Adherence as Constrained Priority</t>
+          <t>Serviceability - Customer Replaceable Maintenance Box</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Adhere to defined schedule checkpoints for hardware, NOA-F, and bottle development, as outlined in project plan.</t>
+          <t>Design maintenance box to be customer replaceable for improved serviceability.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>To ensure timely delivery and market launch.</t>
+          <t>Reduces downtime and service costs, increases user satisfaction.</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Project Management, R&amp;D, Manufacturing</t>
+          <t>End Users, Service, Product Management</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>All development milestones and dependencies.</t>
+          <t>Maintenance box and system design.</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>All checkpoints met within defined timeframes as per project plan.</t>
+          <t>Customers can replace maintenance box without tools; validated in user tests.</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -2113,41 +2113,41 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SuperAmp PHA Life at 65K as Constrained Priority</t>
+          <t>SMB Solution Integration</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ensure SuperAmp PHA life is at least 65,000 pages as a non-flexible constraint.</t>
+          <t>Integrate SMB manageability and solution support (e.g., WJA, HPSM, JAM).</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>To meet reliability and warranty requirements.</t>
+          <t>Addresses needs of SMB customers for device management and integration.</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality Assurance, Service</t>
+          <t>SMB Customers, Product Management, IT</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>SuperAmp PHA design and validation.</t>
+          <t>Solution software and firmware integration.</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>SuperAmp PHA demonstrates life of 65,000 pages in accelerated testing.</t>
+          <t>SMB solutions functional and validated in SMB customer environment.</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -2164,41 +2164,41 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Warranty Life of 2 Years and 80K Pages</t>
+          <t>PaaS Support for Schedule</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Optimize warranty life to 2 years or 80,000 pages, whichever comes first.</t>
+          <t>Ensure PaaS (Platform as a Service) is supported according to schedule.</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>To align with industry standards and customer expectations.</t>
+          <t>Aligns with business goals for flexible service offerings.</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Product Management, End Users, Service</t>
+          <t>Business Development, Product Management</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Component and consumable durability.</t>
+          <t>Service infrastructure and go-to-market readiness.</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Warranty is valid for 2 years or 80K pages, and all components meet reliability requirements.</t>
+          <t>PaaS offering live and available by scheduled launch date.</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -2215,217 +2215,217 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Throughput of 25/20 PPM (PDL: 25/19PPM)</t>
+          <t>Host 12K-CMYK and Trade Page 6K Flexibility</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Optimize printer throughput to achieve 25/20 pages per minute (PPM), with PDL at 25/19 PPM.</t>
+          <t>Allow flexibility to host 12K-CMYK and trade page 6K as needed.</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>To meet market performance expectations and remain competitive.</t>
+          <t>Enables support for different customer needs and market segments.</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Product Management, Marketing</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>SKU and system configuration.</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>System can be configured for 12K-CMYK and 6K trade page options.</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Business Ink Tank Solution</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Develop HP's first Business Ink Tank printer targeted at SMBs, delivering cost-effective, high-performance printing with a tank system.</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Addresses gap in HP's portfolio for CISS PLE Hi segment and competitive leakage.</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>End Users, Product Management, R&amp;D</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Print engine and firmware optimization.</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Printer achieves specified throughput in standard performance tests.</t>
-        </is>
-      </c>
-      <c r="I36" t="n">
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>['Marketing', 'GXD', 'Quality', 'R&amp;D Telemetry', 'Supplies Quality', 'DVAR', 'Tech Reg', 'Prod Steward', 'BA']</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>['Tank technology development']</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Printer must utilize ink tank technology, be marketed as HP’s first business tank printer, and achieve targeted cost efficiency.</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 7, Page 12</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>AI Productivity &amp; Manageability Solutions</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Integrate advanced AI features for productivity (Perfect Print/Scan) and device manageability, including workflow automation and support tools.</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Differentiates Magellan from competitors, addresses SMB needs for efficiency and ease of management.</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>['Marketing', 'GXD', 'Quality', 'R&amp;D Telemetry', 'Supplies Quality', 'DVAR']</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>['SMB portal development', 'AI solution integration']</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Printer offers AI-powered print and scan solutions, workflow automation, and management tools accessible to SMB users.</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
         <v>0.9</v>
       </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>Magellan_SI_1-pager.pdf, page 1,2</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Serviceability - Maintenance Box</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Optimize serviceability by providing a maintenance box for easy replacement and maintenance.</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>To reduce downtime and improve user/service experience.</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Service, End Users</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Maintenance box design and integration.</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Maintenance box is user/service replaceable and passes field serviceability tests.</t>
-        </is>
-      </c>
-      <c r="I37" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>SMB Solution Support</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Optimize printer features and solutions to support SMB requirements (manageability, cost, reliability).</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>To target and win SMB market segment.</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4, Page 7, Page 11</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>SMB Portal for Printer Management</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Provide a consolidated portal specifically designed for SMBs to manage multiple printers, including device status, maintenance, and supplies.</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>SMBs lack dedicated IT teams; a portal simplifies management and reduces operational burden.</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>SMB Customers, Sales, Product Management</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Solution and feature set definition.</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Printer meets SMB manageability and cost requirements as defined by SMB feedback.</t>
-        </is>
-      </c>
-      <c r="I38" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Host 12K-CMYK and Trade Page 6K as Flexible Priorities</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Allow flexibility in supporting Host 12K-CMYK and Trade Page 6K requirements based on market and business needs.</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>To provide adaptability in product offering and market response.</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Product Management, Sales</t>
+          <t>['Marketing', 'GXD', 'Quality', 'R&amp;D Telemetry', 'DVAR']</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Market analysis and business strategy.</t>
+          <t>['Portal software development', 'Integration with printer hardware']</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Host 12K-CMYK and Trade Page 6K features can be enabled/disabled as needed for specific SKUs.</t>
+          <t>Portal enables management of 6-15 printers, supports key device functions, and is user-friendly for office managers/generalist IT.</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.7</v>
+        <v>0.92</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
+          <t>Magellan MRD, Page 7, Page 10</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>AI Productivity and Manageability Solutions</t>
+          <t>Low Total Cost of Ownership (TCO)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Integrate advanced AI-driven productivity features and manageability solutions for the Magellan printer, including Perfect Print and Perfect Scan capabilities, and AI-powered device management via a consolidated SMB portal.</t>
+          <t>Achieve HP’s lowest business TCO for SMB tank printers through efficient consumables, minimal intervention, and sustainable design.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>AI features are highlighted as a major differentiator and are critical to meeting SMB customer needs for efficiency and ease of management.</t>
+          <t>SMBs prioritize ROI and cost efficiency; competitive advantage over rivals.</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2435,30 +2435,30 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>['Marketing', 'GXD', 'Quality', 'R&amp;D Telemetry', 'Supplies Quality', 'DVAR', 'Tech Reg', 'Prod Steward', 'BA']</t>
+          <t>['Marketing', 'Quality', 'Supplies Quality', 'Prod Steward']</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>['Consolidated SMB portal', 'AI software development']</t>
+          <t>['Consumables design', 'Tank system efficiency']</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>AI features (Perfect Print, Perfect Scan, AI device management) are available and functional in the product release, validated by user acceptance testing and feedback from SMB customers.</t>
+          <t>Printer demonstrates lowest TCO in HP business tank portfolio, validated by internal/external benchmarks.</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.95</v>
+        <v>0.93</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 7, 10, 11</t>
+          <t>Magellan MRD, Page 4, Page 11</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -2466,50 +2466,50 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Lowest Business Total Cost of Ownership (TCO)</t>
+          <t>Maintenance-Free or Reduced Maintenance</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Design the Magellan printer to deliver HP's lowest business TCO for SMBs, including minimal intervention and maintenance requirements.</t>
+          <t>Design the printer to require minimal maintenance, with fewer parts to replace over its lifetime and customer-replaceable components.</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>SMB customers prioritize ROI and efficiency; minimizing TCO is a key selling point and competitive differentiator.</t>
+          <t>Reduces SMB operational burden, enhances reliability, and lowers service costs.</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>['Marketing', 'Quality', 'Prod Steward', 'BA']</t>
+          <t>['Quality', 'Supplies Quality', 'Prod Steward']</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>['Maintenance-free/low-maintenance design', 'Sustainability features']</t>
+          <t>['Serviceability design', 'Replaceable maintenance box']</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Independent cost analysis demonstrates Magellan's TCO is lower than comparable HP and competitor models for SMB use cases.</t>
+          <t>Printer has fewer replaceable parts than competitors, includes customer-replaceable maintenance box, and meets serviceability targets.</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 11</t>
+          <t>Magellan MRD, Page 4, Page 11</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -2517,17 +2517,17 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Customer Replaceable Parts and Serviceability</t>
+          <t>Sustainability – 60% Recycled Content Plastic (RCP)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Enable customer replaceable parts (e.g., maintenance box, PHA) and ensure serviceability through both customer and service center options, with clear thresholds for each.</t>
+          <t>Ensure printer design incorporates at least 60% recycled content plastic, exceeding competitor benchmarks (Epson 30%).</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Reduces downtime and support costs for SMBs without dedicated IT, improving overall user experience.</t>
+          <t>Supports HP’s sustainability goals and provides a competitive differentiator.</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2537,30 +2537,30 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>['Quality', 'R&amp;D Telemetry', 'Supplies Quality', 'Tech Reg']</t>
+          <t>['Prod Steward', 'Marketing']</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>['Warranty policies', 'Parts design']</t>
+          <t>['Material sourcing', 'Design engineering']</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Documentation and physical design allow end users to replace specified parts; service center support is available for other components. Field testing confirms successful replacement by non-IT staff.</t>
+          <t>Printer BOM verified to contain minimum 60% RCP, externally auditable.</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan MRD, Page 11</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -2568,41 +2568,41 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Keyed Ink Bottles for Supplies</t>
+          <t>Warranty and Serviceability</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Implement keyed ink bottles to ensure proper installation and reduce supply errors or counterfeit risks.</t>
+          <t>Provide a warranty of 80,000 pages or 2 years (whichever is first), with customer-replaceable components and service center support for major repairs.</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Prevents incorrect usage and supports supply chain integrity, a concern for SMBs managing multiple devices.</t>
+          <t>SMBs require reliability and easy servicing; reduces downtime and cost.</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>['Supplies Quality', 'Quality', 'Prod Steward']</t>
+          <t>['Quality', 'Supplies Quality', 'Prod Steward']</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>['Ink supply system design']</t>
+          <t>['Service parts design', 'Warranty policy']</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>All ink bottles are uniquely keyed and cannot be incorrectly installed. Testing demonstrates error prevention in typical SMB environments.</t>
+          <t>Warranty documentation matches requirement; printer supports customer-replaceable parts and service center repairs.</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -2619,50 +2619,50 @@
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SMB Portal for Device Management</t>
+          <t>Keyed Bottles for Consumables</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Develop a consolidated portal (SMB portal) for managing multiple printers, targeting the needs of unmanaged or lightly managed SMBs.</t>
+          <t>Introduce keyed bottles for ink and other consumables to prevent incorrect refills and ensure compatibility.</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Enables non-IT staff to manage fleets of printers efficiently, addressing a primary customer pain point.</t>
+          <t>Reduces user errors, ensures proper functioning, and supports sustainability goals.</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>['GXD', 'Marketing', 'R&amp;D Telemetry', 'BA']</t>
+          <t>['Supplies Quality', 'Prod Steward']</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>['AI manageability solutions', 'Cloud infrastructure']</t>
+          <t>['Consumables design']</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Portal is operational, supports management of 6-15 printers per SMB, and is validated via usability testing with target users.</t>
+          <t>All consumables are keyed and only fit designated printer models; error rate in refilling reduced.</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.95</v>
+        <v>0.88</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 7, 10</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -2670,17 +2670,17 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Support for PaaS and Advanced View SMB Portal (Non-PDL SKU)</t>
+          <t>PDL SKU Support and Speed Improvement</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Ensure the Magellan printer supports Printing-as-a-Service (PaaS) and Advanced View SMB portal for non-PDL SKUs.</t>
+          <t>Offer PDL SKU with improved speed (25/20 ppm) and support for PDL/PS printing and Blue Angel certification.</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Aligns with HP's strategic goal for PaaS acceleration and provides SMBs with flexible, scalable solutions.</t>
+          <t>Addresses higher-value business segments, enhances performance, and meets regulatory standards.</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2690,21 +2690,21 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>['Marketing', 'GXD', 'BA']</t>
+          <t>['Tech Reg', 'Quality', 'DVAR']</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>['Portal development', 'SKU differentiation']</t>
+          <t>['Firmware development', 'Certification process']</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Non-PDL SKUs are compatible with PaaS and Advanced View SMB portal, confirmed by integration and functional testing.</t>
+          <t>PDL SKU achieves 25/20 ppm speed, supports PDL/PS, and obtains Blue Angel certification.</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.8</v>
+        <v>0.87</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -2721,37 +2721,37 @@
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>PDL SKU Performance and Features</t>
+          <t>Non-PDL SKU Solutions</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>PDL SKUs must achieve print speeds of 25/20 ppm (improved from current 25/19), support PDL/PS, and comply with Blue Angel environmental certification.</t>
+          <t>Support SMB2.0 Solutions and Advanced View SMB portal, and enable PaaS for non-PDL SKU.</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Meets performance expectations for higher-end SMB segments and aligns with sustainability goals.</t>
+          <t>Expands manageability and solution coverage for SMBs using non-PDL SKU.</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>['Quality', 'Tech Reg', 'Prod Steward']</t>
+          <t>['Marketing', 'GXD', 'DVAR']</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>['PDL hardware/software development', 'Certification process']</t>
+          <t>['Portal and solution integration']</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>PDL SKUs pass speed benchmarks, support PDL/PS, and receive Blue Angel certification.</t>
+          <t>Non-PDL SKU integrates with SMB2.0 Solutions, Advanced View portal, and supports PaaS.</t>
         </is>
       </c>
       <c r="I46" t="n">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -2772,50 +2772,50 @@
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Sustainability – 60% Recycled Content Plastic (RCP)</t>
+          <t>Telemetry Requirements</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Design the Magellan printer to utilize at least 60% recycled content plastic, exceeding competitor standards (Epson 30%, Canon TBC).</t>
+          <t>Implement telemetry for device health, usage, and consumables monitoring to support proactive support and analytics.</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Supports HP’s sustainability leadership and is a key differentiator for environmentally conscious SMBs.</t>
+          <t>Enables predictive maintenance, improves customer experience, and supports HP’s service goals.</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>['Prod Steward', 'Tech Reg', 'Marketing']</t>
+          <t>['R&amp;D Telemetry', 'Quality']</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>['Supply chain sourcing', 'Manufacturing processes']</t>
+          <t>['Telemetry software development']</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Bill of materials and third-party verification confirm at least 60% RCP in final product.</t>
+          <t>Printer transmits telemetry data securely, supports analytics and proactive support.</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.9</v>
+        <v>0.87</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 11</t>
+          <t>Magellan MRD, Page 12</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
     </row>
@@ -2823,17 +2823,17 @@
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Warranty – 80k Pages or 2 Years</t>
+          <t>Mobile Printing and HP App Integration</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Offer a warranty covering either 80,000 pages or 2 years, whichever comes first, for the Magellan printer.</t>
+          <t>Enable seamless mobile printing via HP App, supporting SMB workflows and remote management.</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Provides assurance to SMBs regarding durability and reliability, supporting purchase decisions.</t>
+          <t>Meets modern SMB needs for mobile and flexible printing solutions.</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2843,30 +2843,30 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>['Quality', 'Marketing', 'BA']</t>
+          <t>['GXD', 'Marketing']</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>['Serviceability design', 'Warranty policy']</t>
+          <t>['App integration', 'Firmware support']</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Warranty terms are published and honored; field data shows compliance with warranty limits.</t>
+          <t>Printer supports mobile printing through HP App, verified in field tests.</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.85</v>
+        <v>0.88</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan MRD, Page 9</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
     </row>
@@ -2874,17 +2874,17 @@
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Mobile Printing and HP App Integration</t>
+          <t>Solutions/Services Monetization</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Enable mobile printing capabilities and seamless integration with the HP App for the Magellan printer.</t>
+          <t>Develop solutions/services that can be monetized, including AI enhancements and PaaS offerings for SMBs.</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Addresses modern SMB workflows and enhances user convenience.</t>
+          <t>Creates new revenue streams and enhances value proposition for SMB customers.</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2894,17 +2894,17 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>['GXD', 'Marketing', 'BA']</t>
+          <t>['Marketing', 'DVAR']</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>['App development', 'Firmware integration']</t>
+          <t>['Solution development', 'Business model design']</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Users can print from mobile devices via the HP App; successful end-to-end testing with iOS and Android devices.</t>
+          <t>Solutions/services are available for purchase or subscription, with clear monetization paths.</t>
         </is>
       </c>
       <c r="I49" t="n">
@@ -2912,12 +2912,12 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 9, 10</t>
+          <t>Magellan MRD, Page 9, Page 10</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
     </row>
@@ -2925,37 +2925,37 @@
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Telemetry Requirements</t>
+          <t>Repurpose and Post-Purchase Support</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Implement telemetry features to collect and report printer usage, health, and performance data for proactive support and analytics.</t>
+          <t>Design for easy repurposing and post-purchase support, including education, setup, install, registration, and sharing features.</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Enables HP and customers to monitor device health and usage, supporting predictive maintenance and improved service.</t>
+          <t>Improves customer satisfaction and extends printer lifecycle.</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>['R&amp;D Telemetry', 'Quality', 'BA']</t>
+          <t>['Quality', 'Prod Steward']</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>['Firmware development', 'Privacy compliance']</t>
+          <t>['Support tools', 'Documentation']</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Telemetry data is securely collected, transmitted, and accessible via SMB portal; compliance with privacy regulations is verified.</t>
+          <t>Printer supports repurposing, includes post-purchase support materials, and meets customer satisfaction targets.</t>
         </is>
       </c>
       <c r="I50" t="n">
@@ -2963,12 +2963,12 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 3, 12</t>
+          <t>Magellan MRD, Page 8</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
     </row>

--- a/consolidation/outputs/consolidated_requirements.xlsx
+++ b/consolidation/outputs/consolidated_requirements.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K50"/>
+  <dimension ref="A1:K60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,17 +481,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NGB Keyed Bottles with Increased Yield</t>
+          <t>NGB Keyed Ink Bottles with High Page Yield</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Develop new NGB keyed ink bottles supporting 6K Black and 6K CMY page yields, with bottle size for CMY &gt;8K.</t>
+          <t>Develop new NGB keyed ink bottles supporting 6,000 pages for black and 6,000 pages for CMY, with CMY bottle size supporting over 8,000 pages.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Increased ink capacity and unique keying improve user experience and reduce frequency of replacements, supporting higher page yield.</t>
+          <t>To improve customer value and reduce frequency of bottle replacement, supporting higher yield and competitive positioning.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -506,12 +506,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Requires compatibility with NOA-F and IDS systems.</t>
+          <t>Ink formulation compatibility, bottle manufacturing, IDS system integration</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Bottles must be keyed, support 6K Black and 6K CMY yields, and CMY bottle must have capacity &gt;8K. Successfully tested for fit and function in printer.</t>
+          <t>New bottles are released with tested yields: 6K for black, 6K+ for CMY, and CMY bottle size supports &gt;8K pages as verified by page yield tests.</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -537,12 +537,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ensure new ink bottles and filling system achieve spill-free performance during installation and use.</t>
+          <t>Ensure new bottles and filling system are designed for spill-free operation during user refill and service procedures.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Reduces customer complaints and warranty costs, improves brand perception.</t>
+          <t>To reduce customer complaints, warranty claims, and improve user experience and safety.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -552,21 +552,21 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>End Users, Service, R&amp;D</t>
+          <t>R&amp;D, Customer Support, End Users</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Integration with bottle design and NOA-F system.</t>
+          <t>Bottle design, IDS interface, user testing</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>No ink spill incidents in 99.9% of installation cycles during qualification testing.</t>
+          <t>No ink spillage reported in &gt;99% of user testing scenarios and warranty claims related to spillage do not exceed 0.1% of units sold.</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -588,12 +588,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Implement NOA-F with a metal foiled labyrinth and a lid label. No change to click-on push-push and TDF mechanisms.</t>
+          <t>Implement NOA-F (Non-OEM Accessory - Foil) with a metal foiled labyrinth design and lid label, maintaining current click-on push-push and TDF mechanisms.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Improves reliability and traceability, leverages existing mechanisms for cost and time efficiency.</t>
+          <t>To enhance security, reliability, and maintain compatibility with existing mechanisms while introducing new security features.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -603,17 +603,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>R&amp;D, Service, Manufacturing</t>
+          <t>R&amp;D, Security, Manufacturing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dependent on NOA-F and bottle design.</t>
+          <t>NOA-F design, manufacturing process updates</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>NOA-F units include metal foiled labyrinth and lid label, and pass reliability and traceability tests.</t>
+          <t>NOA-F passes security and reliability tests; maintains compatibility with push-push and TDF; metal foil and lid label present as per design.</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -634,17 +634,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Reuse Superamp Si PHA and Magi/Nessie Inks</t>
+          <t>Reuse SuperAmp Si PHA and Magi/Nessie Ink</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Reuse existing Superamp Si PHA and Magi/Nessie pigment inks without reformulation.</t>
+          <t>Continue using SuperAmp Si PHA and Magi/Nessie ink formulations, with no ink reformulation required for Magellan.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Reduces development time and cost, ensures proven ink quality.</t>
+          <t>To leverage existing, proven technology and reduce R&amp;D and qualification costs.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -654,17 +654,17 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>R&amp;D, Supply Chain, Manufacturing</t>
+          <t>R&amp;D, Manufacturing, Supply Chain</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Requires compatibility with new bottles and NOA-F.</t>
+          <t>Compatibility with new bottle and tank designs, IDS integration</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Superamp Si PHA and Magi/Nessie inks function as required with new system, no reformulation needed.</t>
+          <t>SuperAmp Si PHA and Magi/Nessie inks pass all compatibility and reliability tests with new Magellan hardware.</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -685,17 +685,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Reliability and Characterization Modelling</t>
+          <t>Reliability and Characterization Modeling</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Conduct reliability, WVTR, air gain, flow rate, and IDS characterization and modelling, including startup and NOA-F EOL.</t>
+          <t>Model and characterize reliability, WVTR (Water Vapor Transmission Rate), air gain, flow rate, IDS, startup, and NOA-F end-of-life (EOL) for the new platform.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Ensures system reliability, performance, and longevity.</t>
+          <t>To ensure new system meets reliability, performance, and service life goals.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -710,16 +710,16 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Related to IDS, NOA-F, and ink system design.</t>
+          <t>Data collection, simulation tools, IDS design</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>All models completed and validated against test data; system meets reliability targets.</t>
+          <t>Complete reliability models and reports demonstrating compliance with HP standards for all listed parameters.</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -736,17 +736,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ink Stability Modelling</t>
+          <t>Ink Stability Modeling for Tank Impact on Print Quality</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Model ink stability in tank and assess impact on print quality (PQ).</t>
+          <t>Perform ink stability modeling for the new tank design and assess impact on print quality (PQ).</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Prevents print quality degradation over time and ensures customer satisfaction.</t>
+          <t>To proactively address potential print quality issues due to tank/ink interactions.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -761,16 +761,16 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dependent on ink formulation and tank design.</t>
+          <t>Tank design, ink formulation data</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Stability model completed; PQ maintained over expected tank life.</t>
+          <t>Modeling completed; no negative impact to PQ identified or mitigation strategies in place.</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -787,17 +787,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NOA-F as Service Parts for Warranty Support</t>
+          <t>NOA-F Service Parts Warranty Support</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Provide NOA-F as service parts to support warranty claims and repairs.</t>
+          <t>NOA-F must be available as a service part for in-warranty support and replacement.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Improves serviceability and customer support for warranty repairs.</t>
+          <t>To meet service and warranty obligations, reducing downtime for customers.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -812,16 +812,16 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Requires stocking and logistics planning.</t>
+          <t>NOA-F design finalization, parts logistics</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>NOA-F available as service part and integrated in warranty process.</t>
+          <t>NOA-F available in service parts catalog and distributed to service centers by launch.</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -843,12 +843,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Integrate Acumen 6 technology on the ink bottle lid for enhanced authentication or tracking.</t>
+          <t>Integrate Acumen 6 (presumed tracking/ID technology) on the bottle lid for authentication or tracking.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Improves product authentication and anti-counterfeit measures.</t>
+          <t>To improve product traceability, security, and anti-counterfeiting.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -858,17 +858,17 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>R&amp;D, Security, Supply Chain</t>
+          <t>Security, Supply Chain</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dependent on lid and bottle design.</t>
+          <t>Lid design, Acumen 6 technology integration</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Acumen 6 successfully integrated and functional on production lids.</t>
+          <t>All lids have functional Acumen 6 features as verified by security audit.</t>
         </is>
       </c>
       <c r="I9" t="n">
@@ -889,17 +889,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Factory Line Modifications for NOA-F and Magi Ink Cart</t>
+          <t>Factory Line Modifications for NOA-F and New Bottles</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Modify existing SA14 line for NOA-F, add Magi ink cart and labelling tool in Orcus 5, and provide mold for 1 to 4 new keyed caps.</t>
+          <t>Modify existing SA14 production line for NOA-F, add Magi ink cart and labeling tool in Orcus 5, and create molds for 1 to 4 new keyed caps.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Enables manufacturing of new components and ensures production readiness.</t>
+          <t>To enable manufacturing of new components and ensure readiness for Magellan production.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -909,17 +909,17 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Manufacturing, Operations, R&amp;D</t>
+          <t>Manufacturing, Operations</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dependent on final design of NOA-F, ink cart, and caps.</t>
+          <t>Final product design, factory readiness, CapEx approval</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>SA14 line and Orcus 5 upgrades completed, new caps molded and validated in production.</t>
+          <t>SA14 and Orcus 5 lines modified and validated for Magellan production requirements.</t>
         </is>
       </c>
       <c r="I10" t="n">
@@ -945,12 +945,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Design system to allow customers to replace PHA and NOA-F components easily.</t>
+          <t>Design PHA (Printhead Assembly) and NOA-F to be customer-replaceable for improved serviceability.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Improves serviceability, reduces downtime and service costs.</t>
+          <t>To reduce service costs and downtime, empowering end users to perform basic maintenance.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -965,12 +965,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dependent on mechanical and user interface design.</t>
+          <t>Component design, user instructions, safety validation</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Customers can replace PHA and NOA-F with no tools and minimal instructions; validated in user testing.</t>
+          <t>End users can replace PHA and NOA-F using provided instructions without tools, as validated by usability studies.</t>
         </is>
       </c>
       <c r="I11" t="n">
@@ -991,17 +991,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Warranty Page Life Goal of 80k Pages</t>
+          <t>New Warranty Page Life Goal of 80K Pages</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Achieve new warranty page life goal of 80,000 pages per device.</t>
+          <t>Increase the warranty page life goal for the printer to 80,000 pages.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Extends product life and reduces total cost of ownership for users.</t>
+          <t>To offer a more competitive product with longer life and lower total cost of ownership.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1011,17 +1011,17 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>End Users, Service, Product Management</t>
+          <t>Product Management, End Users, Warranty</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dependent on reliability of critical components (PHA, NOA-F, ink system, etc.).</t>
+          <t>Reliability modeling, component durability</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Printer passes 80,000 page yield test with no critical failures during warranty period.</t>
+          <t>Warranty documentation updated; field units demonstrate &gt;80K page life in reliability testing.</t>
         </is>
       </c>
       <c r="I12" t="n">
@@ -1042,17 +1042,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Support for Hi + Hi PDL SKU (SKU 2) PaaS</t>
+          <t>SKU 2 (Hi + Hi PDL) Platform as a Service (PaaS) Support</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Develop and support a SKU for Hi + Hi PDL with Platform as a Service (PaaS) business model.</t>
+          <t>Support SKU 2 with high throughput and high PDL (Page Description Language) for Platform as a Service (PaaS) business model.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Targets business customers and enables flexible service offerings.</t>
+          <t>To address SMB and enterprise segments with managed print services and higher performance needs.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1062,21 +1062,21 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Product Management, Business Development, SMB/Enterprise Customers</t>
+          <t>Business, Product Management, SMB/Enterprise Customers</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Requires alignment with business model and service infrastructure.</t>
+          <t>Firmware, hardware capabilities, service platform integration</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>SKU 2 available for order with PaaS support, integrated with business systems.</t>
+          <t>SKU 2 available for PaaS; meets throughput and PDL requirements as per spec.</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1093,17 +1093,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Increase Tank Size for Reddington ID</t>
+          <t>Reddington ID with Increased Tank Size</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Increase tank size for Reddington ID product variant, with no change to Marconi-HI ADF.</t>
+          <t>Adopt Reddington ID for product with increased tank size; no change to Marconi-HI ADF (Automatic Document Feeder).</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Supports higher ink capacity and extended printing.</t>
+          <t>To align with new bottle/tank requirements while maintaining compatibility with proven ADF design.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1118,16 +1118,16 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Impacts packaging and mechanical design.</t>
+          <t>Tank redesign, mechanical integration, ADF compatibility</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Tank size increased and validated in Reddington ID variant, ADF remains unchanged.</t>
+          <t>Product passes integration and capacity tests; ADF unchanged from Marconi-HI.</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1144,41 +1144,41 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EPS Foam Packaging</t>
+          <t>EPEAT3, LOT4, and Blue Angel Environmental Compliance</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Implement EPS foam packaging for improved product protection during shipping.</t>
+          <t>Ensure product meets EPEAT3, LOT4, and Blue Angel requirements for PDL SKU.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Reduces shipping damage, improves customer satisfaction.</t>
+          <t>To satisfy regulatory and market-driven environmental standards.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Logistics, Manufacturing, End Users</t>
+          <t>Compliance, Marketing, Product Management</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Packaging design and supplier capabilities.</t>
+          <t>Product design, materials selection, certification processes</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>EPS foam packaging implemented and passes drop/shipping tests.</t>
+          <t>Product receives EPEAT3, LOT4, and Blue Angel certifications prior to launch.</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1195,41 +1195,41 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EPEAT3, LOT4, and Blue Angel Compliance for PDL SKU</t>
+          <t>Input and Output Tray Changes for Tank Protrusion</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ensure product meets EPEAT3, LOT4, and Blue Angel requirements for PDL SKU.</t>
+          <t>Modify input and output trays to accommodate tank protrusion and optimize product size.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Enables sales in regulated markets and supports sustainability goals.</t>
+          <t>To ensure mechanical compatibility and optimize product footprint.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Regulatory, Product Management, Sales</t>
+          <t>R&amp;D, Mechanical Design, Manufacturing</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dependent on product design and documentation.</t>
+          <t>Tank design finalization, tray redesign</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Product certified for EPEAT3, LOT4, and Blue Angel for PDL SKU.</t>
+          <t>Trays fit with final tank design and pass mechanical and usability tests.</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1246,17 +1246,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Input and Output Tray Changes for Tank Protrusion</t>
+          <t>4.3” CGD Display Integration</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Modify input and output trays to accommodate tank protrusion and optimize size.</t>
+          <t>Integrate a 4.3-inch CGD (Color Graphic Display) for improved user interface.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Ensures mechanical compatibility and minimizes device footprint.</t>
+          <t>To enhance user experience with a larger, more informative display.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1266,17 +1266,17 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing</t>
+          <t>End Users, Product Management</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tank and tray mechanical design.</t>
+          <t>Display sourcing, firmware UI design</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Trays modified and validated for tank fit and function.</t>
+          <t>Display integrated and passes usability and reliability tests.</t>
         </is>
       </c>
       <c r="I17" t="n">
@@ -1297,17 +1297,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>4.3” CGD Display</t>
+          <t>Platform with 4 Sayan Sibstar Tubes and New Routing</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Integrate a 4.3” CGD (Color Graphic Display) into the printer.</t>
+          <t>Leverage Sayan Sibstar tubes, implement four-tube routing and new integration for ink delivery.</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Improves user interface and accessibility.</t>
+          <t>To support higher ink flow and reliability for new tank system.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1317,17 +1317,17 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>End Users, Product Management</t>
+          <t>R&amp;D, Manufacturing</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Display hardware and firmware integration.</t>
+          <t>Tube sourcing, platform design</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>4.3” CGD display installed and passes usability and functional tests.</t>
+          <t>System passes ink flow and reliability tests with new tube configuration.</t>
         </is>
       </c>
       <c r="I18" t="n">
@@ -1348,41 +1348,41 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Platform with 4 Tubes and New Routing</t>
+          <t>Service Station Aerosol Management</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Leverage Sayan Sibstar tubes, implement new tube routing and integration for 4-tube platform.</t>
+          <t>Update service station with aerosol management and spit platform changes to accommodate new tank.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Supports new ink delivery architecture for improved reliability and performance.</t>
+          <t>To maintain print quality and reliability with new ink/tank configuration.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing</t>
+          <t>R&amp;D, Service</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tube and ink system design.</t>
+          <t>Service station design, platform integration</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>4-tube platform integrated, new routing validated for flow and reliability.</t>
+          <t>Aerosol management system operational and passes reliability tests.</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1399,17 +1399,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Service Station Aerosol Management</t>
+          <t>Carriage Dynamic and Force Model Update</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Update service station aerosol management with spit platform changes due to new tank design.</t>
+          <t>Update carriage dynamic and force models to account for new tube routing and increased weights.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Prevents contamination and ensures clean operation with larger tanks.</t>
+          <t>To ensure mechanical reliability and print quality with new hardware configuration.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>R&amp;D, Service</t>
+          <t>R&amp;D, Mechanical Engineering</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dependent on tank and service station design.</t>
+          <t>Carriage design, tube integration</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Aerosol management system updated and validated for new configuration.</t>
+          <t>Carriage system passes dynamic and force testing with new configuration.</t>
         </is>
       </c>
       <c r="I20" t="n">
@@ -1450,41 +1450,41 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Carriage Dynamic and Force Model Update</t>
+          <t>Paper Path Support for Increased Page Life</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Update carriage dynamic and force model to account for new tube routing and weights.</t>
+          <t>Update paper path components to support increased page life target of 80K pages.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Ensures reliable motion and print quality with new mechanical configuration.</t>
+          <t>To ensure durability and reliability over extended product life.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality Assurance</t>
+          <t>R&amp;D, Manufacturing, Quality Assurance</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tube routing and carriage design.</t>
+          <t>Material selection, durability testing</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Carriage model updated, system passes reliability and PQ tests.</t>
+          <t>Paper path components pass accelerated life testing for 80K pages.</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1501,41 +1501,41 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Paper Path to Support Increased Page Life</t>
+          <t>Ink Maintenance as Serviceable Part (Post 80K Life)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Redesign paper path to support increased page life (80k pages).</t>
+          <t>Design ink maintenance as a serviceable part to be replaced at service centers after 80K page life is reached.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Ensures mechanical durability and reliability over product lifespan.</t>
+          <t>To extend product life and maintain print quality for high-usage customers.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing, Quality Assurance</t>
+          <t>Service, End Users</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Paper path and materials selection.</t>
+          <t>Maintenance part design, service documentation</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Paper path passes 80k page durability test.</t>
+          <t>Part available and service process documented; field replaceable after 80K pages.</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1552,41 +1552,41 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ink Maintenance Serviceable Part (Post 80k Life)</t>
+          <t>New Make-Break and FI Connection for IDS</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Design ink maintenance as a serviceable part to be replaced post 80k page life at Service Center.</t>
+          <t>Implement new make-break and fluidic interconnect (FI) connection in IDS (Ink Delivery System) to support increased tank size and keying.</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Improves serviceability and extends product usable life.</t>
+          <t>To ensure secure, reliable, and user-friendly ink connections for new system.</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Service, End Users</t>
+          <t>R&amp;D, Manufacturing, End Users</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dependent on maintenance part design.</t>
+          <t>IDS design, keying mechanism</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Ink maintenance part can be replaced at service center after 80k pages.</t>
+          <t>New connections pass reliability, usability, and leak tests.</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1603,17 +1603,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>140ml K Bottles and New CMY Bottle Sizes</t>
+          <t>LEBI Ink-Tank with Increased Size, Keying, and LOI SHAID</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Introduce 140ml Black (K) bottles and new XX ml CMY bottles for the system.</t>
+          <t>Leverage LEBI ink-tank design with increased size, new keying, and LOI (Level of Ink) SHAID (presumed sensor/ID) for improved management.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Supports higher yield and aligns with system requirements.</t>
+          <t>To support higher yield, reduce errors, and improve ink management.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1623,17 +1623,17 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>R&amp;D, Supply Chain, Product Management</t>
+          <t>R&amp;D, Manufacturing, End Users</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Bottle and system design.</t>
+          <t>LEBI tank design, SHAID integration</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>140ml K and new CMY bottles available and validated for use.</t>
+          <t>Tank with increased size and SHAID passes functional and reliability tests.</t>
         </is>
       </c>
       <c r="I24" t="n">
@@ -1654,41 +1654,41 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>New IDS Make-Break and FI Connection</t>
+          <t>New IDS Startup Algorithm and Air Management</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Implement new IDS make-break and FI connection, leveraging LEBI ink-tank with increased size, keying, and LOI One SHAID.</t>
+          <t>Develop new startup algorithm and air management system for IDS to ensure optimal performance and reliability.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Improves reliability, traceability, and system integration.</t>
+          <t>To address new tank and bottle configuration, ensuring consistent print quality.</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing, Service</t>
+          <t>R&amp;D, Firmware</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>IDS and ink-tank design.</t>
+          <t>IDS hardware, firmware development</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>New IDS and FI connection integrated and validated in system tests.</t>
+          <t>Algorithm implemented and verified to meet startup and air management KPIs.</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -1705,17 +1705,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>New IDS Startup Algorithm and Air Management</t>
+          <t>New Print Quality Goals and Depletion Definition</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Develop new IDS startup algorithm and air management system for improved reliability.</t>
+          <t>Define and implement new print quality (PQ) goals and depletion criteria to align with new page yield definitions.</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Ensures consistent startup and operation, prevents air-related failures.</t>
+          <t>To ensure customer expectations are met for print quality and yield.</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1725,21 +1725,21 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>R&amp;D, Service</t>
+          <t>Product Management, R&amp;D, Quality Assurance</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>IDS and system firmware.</t>
+          <t>PQ definition, firmware updates</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Startup algorithm and air management pass reliability tests and meet startup KPIs.</t>
+          <t>New PQ goals and depletion criteria published and validated through testing.</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -1756,41 +1756,41 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>New Print Quality Goals and Depletion Definition</t>
+          <t>Reuse Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Define new print quality goals and depletion metrics to align with page yield definition.</t>
+          <t>Reuse Marconi Tux dASIC, Hannibal aASIC, and Raccoon PSU to reduce development cost and risk.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Ensures consistent print quality and accurate yield reporting.</t>
+          <t>To leverage proven components and accelerate time-to-market.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Product Management, R&amp;D, Quality Assurance</t>
+          <t>R&amp;D, Manufacturing, Supply Chain</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Testing and validation protocols.</t>
+          <t>Component availability, integration testing</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Print quality and depletion metrics defined, implemented, and validated.</t>
+          <t>Components integrated and pass system-level validation.</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -1807,41 +1807,41 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Reuse Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU</t>
+          <t>Stingray Wi-Fi Module and Dune Firmware</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Reuse Marconi Tux dASIC, Hannibal aASIC, and Raccoon PSU in the new system.</t>
+          <t>Integrate Stingray Wi-Fi module and Dune firmware for connectivity and feature support.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Leverages proven components to reduce cost and risk.</t>
+          <t>To offer wireless connectivity and required firmware features for Magellan.</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing, Supply Chain</t>
+          <t>R&amp;D, End Users, Product Management</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Compatibility with new architecture.</t>
+          <t>Module sourcing, firmware integration</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Components reused and validated in system integration tests.</t>
+          <t>Wi-Fi and firmware features operational and validated in system tests.</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -1858,41 +1858,41 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Stingray Wi-Fi Module Integration</t>
+          <t>Gauss4.xx Hardware and Firmware Security</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Integrate Stingray Wi-Fi module into the printer for wireless connectivity.</t>
+          <t>Implement Gauss4.xx security features in hardware and firmware to ensure data and device security.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Enables modern wireless features for end users.</t>
+          <t>To meet modern security standards and protect user data.</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>End Users, R&amp;D, Product Management</t>
+          <t>Security, R&amp;D, End Users</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Firmware and hardware integration.</t>
+          <t>HW/FW design, security testing</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Stingray Wi-Fi module functional and passes connectivity tests.</t>
+          <t>Device passes internal and external security audits for Gauss4.xx features.</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -1909,41 +1909,41 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Dune Firmware Platform</t>
+          <t>Business Model Support for Consumer, SMB, and Enterprise</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Utilize Dune firmware platform for the printer.</t>
+          <t>Design product and services to support Consumer, SMB, and Enterprise business models, including PaaS and WorkFromHome/Flexworker solutions.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Ensures consistency and reuse of proven firmware platform.</t>
+          <t>To maximize market reach and support diverse customer needs.</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>R&amp;D, Firmware Team</t>
+          <t>Business, Product Management, Sales</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Firmware integration and testing.</t>
+          <t>Service platform integration, SKU differentiation</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Dune firmware operational and passes system validation tests.</t>
+          <t>Product and services available for all targeted segments at launch.</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -1960,41 +1960,41 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Gauss4.xx Security (HW &amp; FW)</t>
+          <t>Onboarding and S&amp;O Pathways</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Implement Gauss4.xx security features in both hardware and firmware.</t>
+          <t>Support onboarding and S&amp;O (Setup &amp; Onboarding) paths for Consumer (HPX), HP One, SMB Portal, and ECP.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Enhances device security and compliance.</t>
+          <t>To streamline customer onboarding and improve experience across segments.</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Security, R&amp;D, IT</t>
+          <t>Product Management, Customer Support, Sales</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>HW and FW integration.</t>
+          <t>Onboarding workflow design, platform integration</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Gauss4.xx security features functional and pass security validation tests.</t>
+          <t>All onboarding paths operational and validated in user acceptance testing.</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -2011,17 +2011,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>High Throughput (25/20 ppm)</t>
+          <t>Scan Solution, SMB Manageability, and Enterprise Support</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Printer must support throughput of 25/20 pages per minute (PDL: 25/19 ppm).</t>
+          <t>Integrate scan solution, SMB manageability features, and enterprise support for WJA (Web Jetadmin), HPSM (HP Smart Management), and JAM.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Meets competitive benchmarks and customer expectations for speed.</t>
+          <t>To offer a full-featured solution for SMB and enterprise customers.</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2031,21 +2031,21 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>End Users, Product Management, Marketing</t>
+          <t>Business, Product Management, SMB/Enterprise Customers</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Mechanical, firmware, and ink system design.</t>
+          <t>Solution integration, firmware and software support</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Printer achieves 25/20 ppm (PDL: 25/19 ppm) in performance tests.</t>
+          <t>Scan, manageability, and enterprise support features fully functional at launch.</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -2062,45 +2062,45 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Serviceability - Customer Replaceable Maintenance Box</t>
+          <t>Client and Driver Support</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Design maintenance box to be customer replaceable for improved serviceability.</t>
+          <t>Support clients and drivers including HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Reduces downtime and service costs, increases user satisfaction.</t>
+          <t>To ensure broad compatibility and ease of use across platforms and deployment scenarios.</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>End Users, Service, Product Management</t>
+          <t>Product Management, End Users, IT Admins</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Maintenance box and system design.</t>
+          <t>Driver development, compatibility testing</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Customers can replace maintenance box without tools; validated in user tests.</t>
+          <t>All listed clients and drivers available and validated for Magellan at launch.</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2113,37 +2113,37 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SMB Solution Integration</t>
+          <t>Protect Micro/SMB Segments and Ink/Laser Profit Pool</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Integrate SMB manageability and solution support (e.g., WJA, HPSM, JAM).</t>
+          <t>Design features and pricing to protect HP’s micro/SMB segment and prevent profit pool erosion to competitors.</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Addresses needs of SMB customers for device management and integration.</t>
+          <t>To maintain HP’s market share and profitability in key segments.</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>SMB Customers, Product Management, IT</t>
+          <t>Business, Product Management, Sales</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Solution software and firmware integration.</t>
+          <t>Market analysis, pricing strategy</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>SMB solutions functional and validated in SMB customer environment.</t>
+          <t>Market share in micro/SMB maintained or grown post-launch.</t>
         </is>
       </c>
       <c r="I34" t="n">
@@ -2164,37 +2164,37 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>PaaS Support for Schedule</t>
+          <t>Lead with LaserJet, Flank with PDL in Medium/Enterprise</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Ensure PaaS (Platform as a Service) is supported according to schedule.</t>
+          <t>Strategically position LaserJet as lead offering and use PDL (presumably Page Description Language-enabled devices) to flank in medium and enterprise segments, targeting Epson as CISS grows.</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Aligns with business goals for flexible service offerings.</t>
+          <t>To win over competitors and grow share in expanding CISS (Continuous Ink Supply System) market.</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Business Development, Product Management</t>
+          <t>Business, Product Management, Sales</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Service infrastructure and go-to-market readiness.</t>
+          <t>Product portfolio strategy, marketing</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>PaaS offering live and available by scheduled launch date.</t>
+          <t>Share gains in medium/enterprise segments and CISS market measured in 12 months post-launch.</t>
         </is>
       </c>
       <c r="I35" t="n">
@@ -2215,41 +2215,41 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Host 12K-CMYK and Trade Page 6K Flexibility</t>
+          <t>Grow CISS Profitable Share in New Segments</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Allow flexibility to host 12K-CMYK and trade page 6K as needed.</t>
+          <t>Expand CISS offering into new market segments to grow profitable share.</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Enables support for different customer needs and market segments.</t>
+          <t>To capture new revenue streams and outpace competitors as CISS adoption increases.</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Product Management, Marketing</t>
+          <t>Business, Product Management, Sales</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>SKU and system configuration.</t>
+          <t>Market research, product adaptation</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>System can be configured for 12K-CMYK and 6K trade page options.</t>
+          <t>New segment launches with positive ROI within 18 months post-launch.</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -2259,20 +2259,24 @@
       <c r="K36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr"/>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Business Ink Tank Solution</t>
+          <t>Highly Leverage Watt-LE Mech Platform and Marconi-Hi Product</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Develop HP's first Business Ink Tank printer targeted at SMBs, delivering cost-effective, high-performance printing with a tank system.</t>
+          <t>Leverage existing Watt-LE mechanical platform and Marconi-Hi product (Reddington ID) and solutions for Magellan.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Addresses gap in HP's portfolio for CISS PLE Hi segment and competitive leakage.</t>
+          <t>To accelerate development and reduce cost by reusing proven platforms.</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2282,48 +2286,48 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>['Marketing', 'GXD', 'Quality', 'R&amp;D Telemetry', 'Supplies Quality', 'DVAR', 'Tech Reg', 'Prod Steward', 'BA']</t>
+          <t>R&amp;D, Manufacturing, Product Management</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>['Tank technology development']</t>
+          <t>Platform compatibility, integration testing</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Printer must utilize ink tank technology, be marketed as HP’s first business tank printer, and achieve targeted cost efficiency.</t>
+          <t>Platform integration complete with no critical issues before launch.</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 7, Page 12</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr"/>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>AI Productivity &amp; Manageability Solutions</t>
+          <t>Integrate CISS IDS, NOA-F, and Ink Tanks</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Integrate advanced AI features for productivity (Perfect Print/Scan) and device manageability, including workflow automation and support tools.</t>
+          <t>Integrate CISS IDS, NOA-F, and new ink tanks into the product platform.</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Differentiates Magellan from competitors, addresses SMB needs for efficiency and ease of management.</t>
+          <t>To deliver a cohesive, high-performance ink delivery solution.</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2333,17 +2337,17 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>['Marketing', 'GXD', 'Quality', 'R&amp;D Telemetry', 'Supplies Quality', 'DVAR']</t>
+          <t>R&amp;D, Product Management, Manufacturing</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>['SMB portal development', 'AI solution integration']</t>
+          <t>Component design, system integration</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Printer offers AI-powered print and scan solutions, workflow automation, and management tools accessible to SMB users.</t>
+          <t>All systems integrated and pass end-to-end functional testing.</t>
         </is>
       </c>
       <c r="I38" t="n">
@@ -2351,30 +2355,30 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, Page 7, Page 11</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr"/>
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SMB Portal for Printer Management</t>
+          <t>SuperAmp PHA Life at 65K Pages (Constrained)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Provide a consolidated portal specifically designed for SMBs to manage multiple printers, including device status, maintenance, and supplies.</t>
+          <t>Maintain SuperAmp PHA (Printhead Assembly) life at 65,000 pages as a non-flexible (constrained) requirement.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>SMBs lack dedicated IT teams; a portal simplifies management and reduces operational burden.</t>
+          <t>To ensure critical component reliability and minimize field failures.</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2384,99 +2388,99 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>['Marketing', 'GXD', 'Quality', 'R&amp;D Telemetry', 'DVAR']</t>
+          <t>R&amp;D, Quality Assurance, Service</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>['Portal software development', 'Integration with printer hardware']</t>
+          <t>Component testing, reliability validation</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Portal enables management of 6-15 printers, supports key device functions, and is user-friendly for office managers/generalist IT.</t>
+          <t>SuperAmp PHA consistently meets/exceeds 65K page life in reliability testing.</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 7, Page 10</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr"/>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Low Total Cost of Ownership (TCO)</t>
+          <t>Warranty Life of 2 Years (Optimized)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Achieve HP’s lowest business TCO for SMB tank printers through efficient consumables, minimal intervention, and sustainable design.</t>
+          <t>Provide a 2-year warranty life for the printer as an optimized (somewhat flexible) requirement.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>SMBs prioritize ROI and cost efficiency; competitive advantage over rivals.</t>
+          <t>To meet customer expectations and competitive benchmarks.</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>['Marketing', 'Quality', 'Supplies Quality', 'Prod Steward']</t>
+          <t>Product Management, Warranty, End Users</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>['Consumables design', 'Tank system efficiency']</t>
+          <t>Reliability modeling, warranty documentation</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Printer demonstrates lowest TCO in HP business tank portfolio, validated by internal/external benchmarks.</t>
+          <t>Warranty documentation published with 2-year coverage; field reliability supports warranty period.</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.93</v>
+        <v>0.85</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, Page 11</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr"/>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Maintenance-Free or Reduced Maintenance</t>
+          <t>Throughput 25/20 PPM (Optimized)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Design the printer to require minimal maintenance, with fewer parts to replace over its lifetime and customer-replaceable components.</t>
+          <t>Achieve throughput of 25 ppm (pages per minute) for standard and 20 ppm for PDL SKU.</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Reduces SMB operational burden, enhances reliability, and lowers service costs.</t>
+          <t>To deliver competitive print speed for target segments.</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2486,17 +2490,17 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>['Quality', 'Supplies Quality', 'Prod Steward']</t>
+          <t>Product Management, R&amp;D, End Users</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>['Serviceability design', 'Replaceable maintenance box']</t>
+          <t>Print engine design, firmware tuning</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Printer has fewer replaceable parts than competitors, includes customer-replaceable maintenance box, and meets serviceability targets.</t>
+          <t>Throughput verified by print speed tests for both SKUs.</t>
         </is>
       </c>
       <c r="I41" t="n">
@@ -2504,267 +2508,263 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, Page 11</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr"/>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Sustainability – 60% Recycled Content Plastic (RCP)</t>
+          <t>Serviceability – Maintenance Box (Optimized)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Ensure printer design incorporates at least 60% recycled content plastic, exceeding competitor benchmarks (Epson 30%).</t>
+          <t>Design maintenance box for improved serviceability, as an optimized requirement.</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Supports HP’s sustainability goals and provides a competitive differentiator.</t>
+          <t>To reduce downtime and service costs for users and HP.</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>['Prod Steward', 'Marketing']</t>
+          <t>Service, End Users, Product Management</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>['Material sourcing', 'Design engineering']</t>
+          <t>Box design, service process documentation</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Printer BOM verified to contain minimum 60% RCP, externally auditable.</t>
+          <t>Maintenance box can be replaced in &lt;5 minutes by trained personnel; validated by service trials.</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 11</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr"/>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Warranty and Serviceability</t>
+          <t>SMB Solution Support (Optimized)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Provide a warranty of 80,000 pages or 2 years (whichever is first), with customer-replaceable components and service center support for major repairs.</t>
+          <t>Develop and support solution features for SMB customers, as an optimized requirement.</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>SMBs require reliability and easy servicing; reduces downtime and cost.</t>
+          <t>To address SMB market needs and differentiate from competitors.</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>['Quality', 'Supplies Quality', 'Prod Steward']</t>
+          <t>Product Management, SMB Customers, Sales</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>['Service parts design', 'Warranty policy']</t>
+          <t>Solution development, feature integration</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Warranty documentation matches requirement; printer supports customer-replaceable parts and service center repairs.</t>
+          <t>SMB solution features available and validated with pilot customers.</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.93</v>
+        <v>0.8</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr"/>
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Keyed Bottles for Consumables</t>
+          <t>Host 12K-CMYK (Flexible)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Introduce keyed bottles for ink and other consumables to prevent incorrect refills and ensure compatibility.</t>
+          <t>Host support for 12,000-page yield CMYK configurations, as a flexible requirement.</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Reduces user errors, ensures proper functioning, and supports sustainability goals.</t>
+          <t>To enable future expansion or SKU differentiation if needed.</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>['Supplies Quality', 'Prod Steward']</t>
+          <t>Product Management, R&amp;D</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>['Consumables design']</t>
+          <t>Yield validation, supply chain planning</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>All consumables are keyed and only fit designated printer models; error rate in refilling reduced.</t>
+          <t>12K-CMYK configuration validated and ready for future deployment.</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.88</v>
+        <v>0.7</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr"/>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>PDL SKU Support and Speed Improvement</t>
+          <t>Trade Page 6K (Flexible)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Offer PDL SKU with improved speed (25/20 ppm) and support for PDL/PS printing and Blue Angel certification.</t>
+          <t>Support trade page yield of 6,000 pages as a flexible requirement.</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Addresses higher-value business segments, enhances performance, and meets regulatory standards.</t>
+          <t>To provide options for different market segments or trade programs.</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>['Tech Reg', 'Quality', 'DVAR']</t>
+          <t>Product Management, Sales</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>['Firmware development', 'Certification process']</t>
+          <t>Yield validation, SKU definition</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>PDL SKU achieves 25/20 ppm speed, supports PDL/PS, and obtains Blue Angel certification.</t>
+          <t>Trade page 6K configuration validated and available as needed.</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.87</v>
+        <v>0.7</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Non-PDL SKU Solutions</t>
+          <t>Business Ink Tank Printer</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Support SMB2.0 Solutions and Advanced View SMB portal, and enable PaaS for non-PDL SKU.</t>
+          <t>Develop HP’s first business ink tank printer targeted at SMBs, offering high performance and cost efficiency.</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Expands manageability and solution coverage for SMBs using non-PDL SKU.</t>
+          <t>To fill the gap in HP’s portfolio and compete in the CISS PLE Hi segment, addressing evolving customer needs for cost-effective printing.</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>['Marketing', 'GXD', 'DVAR']</t>
+          <t>['Marketing', 'GXD', 'Quality', 'R&amp;D Telemetry', 'Supplies Quality', 'DVAR', 'Tech Reg', 'Prod Steward', 'BA']</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>['Portal and solution integration']</t>
+          <t>CISS technology, ink tank system integration</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Non-PDL SKU integrates with SMB2.0 Solutions, Advanced View portal, and supports PaaS.</t>
+          <t>Printer model released with ink tank technology, validated for SMB segment, and achieves lowest business TCO.</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan MRD, Page 7, 11, 12</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2772,50 +2772,50 @@
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Telemetry Requirements</t>
+          <t>AI Productivity Solutions</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Implement telemetry for device health, usage, and consumables monitoring to support proactive support and analytics.</t>
+          <t>Integrate AI-powered productivity features for print, scan, and device management workflows.</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Enables predictive maintenance, improves customer experience, and supports HP’s service goals.</t>
+          <t>SMBs need automation and efficiency improvements without dedicated IT teams; AI features will differentiate the product and address key pain points.</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>['R&amp;D Telemetry', 'Quality']</t>
+          <t>['Marketing', 'GXD', 'Quality', 'R&amp;D Telemetry', 'BA']</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>['Telemetry software development']</t>
+          <t>SMB portal, device management platform, AI software development</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Printer transmits telemetry data securely, supports analytics and proactive support.</t>
+          <t>AI features for print, scan, and support implemented and validated in MVP; measurable reduction in manual tasks.</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.87</v>
+        <v>0.92</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 12</t>
+          <t>Magellan MRD, Page 4, 7, 10, 11</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -2823,50 +2823,50 @@
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Mobile Printing and HP App Integration</t>
+          <t>SMB Manageability Portal</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Enable seamless mobile printing via HP App, supporting SMB workflows and remote management.</t>
+          <t>Develop a consolidated portal for SMBs to manage printers and devices, targeting office managers and generalist IT staff.</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Meets modern SMB needs for mobile and flexible printing solutions.</t>
+          <t>Unmanaged/Lightly Managed SMBs lack dedicated IT; a portal simplifies device management and enhances customer experience.</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>['GXD', 'Marketing']</t>
+          <t>['Marketing', 'GXD', 'R&amp;D Telemetry', 'BA']</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>['App integration', 'Firmware support']</t>
+          <t>Portal software, device connectivity, AI integration</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Printer supports mobile printing through HP App, verified in field tests.</t>
+          <t>Portal released with device management features, user tested by office managers/generalist IT, and receives positive usability feedback.</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.88</v>
+        <v>0.9</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 9</t>
+          <t>Magellan MRD, Page 7, 10</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -2874,50 +2874,50 @@
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Solutions/Services Monetization</t>
+          <t>Low Total Cost of Ownership (TCO)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Develop solutions/services that can be monetized, including AI enhancements and PaaS offerings for SMBs.</t>
+          <t>Design the printer to deliver HP’s lowest business TCO, including minimal intervention and maintenance.</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Creates new revenue streams and enhances value proposition for SMB customers.</t>
+          <t>Cost efficiency is a top priority for SMBs; lower TCO is a key differentiator against competitors.</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>['Marketing', 'DVAR']</t>
+          <t>['Marketing', 'Quality', 'Supplies Quality', 'Prod Steward']</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>['Solution development', 'Business model design']</t>
+          <t>Ink tank technology, maintenance box design, sustainable materials</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Solutions/services are available for purchase or subscription, with clear monetization paths.</t>
+          <t>TCO calculation shows lowest cost vs. competitors, validated through market analysis and customer feedback.</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 9, Page 10</t>
+          <t>Magellan MRD, Page 4, 11</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -2925,50 +2925,560 @@
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Repurpose and Post-Purchase Support</t>
+          <t>Customer Replaceable Maintenance Box</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Design for easy repurposing and post-purchase support, including education, setup, install, registration, and sharing features.</t>
+          <t>Introduce a replaceable maintenance box that can be serviced by customers, reducing downtime and service costs.</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Improves customer satisfaction and extends printer lifecycle.</t>
+          <t>SMBs lack IT support; customer replaceability lowers maintenance barriers and improves uptime.</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>['Quality', 'Supplies Quality', 'Prod Steward', 'BA']</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Maintenance box design, warranty/service policies</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Maintenance box is user-replaceable, instructions provided, and successful replacement validated in user testing.</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr"/>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Keyed Ink Bottles</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Use keyed bottles for ink refilling to prevent errors and ensure correct usage.</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Minimize user errors and support ease of maintenance for SMBs with limited IT expertise.</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>['Supplies Quality', 'Prod Steward', 'Quality']</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Ink bottle design, compatibility with printer</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Ink bottles are keyed, tested for error prevention, and validated by customer feedback.</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr"/>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Non-PDL SKU with SMB Solutions</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Offer a Non-PDL SKU that supports SMB2.0 Solutions and Advanced View SMB portal, including PaaS support.</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Provide tailored solutions for SMBs needing advanced manageability and platform-as-a-service options.</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>['Marketing', 'GXD', 'R&amp;D Telemetry', 'BA']</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Portal development, PaaS integration</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Non-PDL SKU released with SMB solutions and portal integration; PaaS support validated.</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>PDL SKU Performance</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Provide a PDL SKU with improved speed (25/20 min) and support for PDL/PS and Blue Angel certification.</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Address performance needs for SMBs and ensure compliance with environmental standards.</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>['Marketing', 'GXD', 'Tech Reg', 'Quality']</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Printer speed optimization, Blue Angel compliance</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>PDL SKU meets speed targets and passes Blue Angel certification.</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr"/>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Sustainability – 60% Recycled Content Plastic (RCP)</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Design printer with at least 60% recycled content plastic, exceeding competitor standards (Epson 30%).</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>SMBs value sustainability; higher RCP differentiates HP and supports environmental goals.</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>['Prod Steward', 'Quality', 'Marketing']</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Material sourcing, manufacturing process</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Printer contains 60% RCP, validated by third-party certification.</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 11</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr"/>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Mobile Printing via HP App</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Enable mobile printing functionality through the HP App for SMB users.</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Office managers and generalist IT need easy, mobile access to printing solutions.</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>['Marketing', 'GXD', 'R&amp;D Telemetry']</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>HP App integration, printer connectivity</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Mobile printing is enabled, tested across major mobile platforms, and validated by user feedback.</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 9</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr"/>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Warranty – 80k pages or 2 years</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Provide warranty coverage for 80,000 pages or 2 years, whichever comes first.</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>SMBs require predictable maintenance and support; clear warranty terms increase purchase confidence.</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>['Quality', 'Prod Steward', 'BA']</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Service policies, maintenance tracking</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Warranty terms documented, tracked, and honored for all eligible printers.</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr"/>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Serviceability – PHA and MINK</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Ensure serviceability with PHA (customer replaceable) and MINK at service center for out-of-warranty cases.</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Reduce downtime and service costs for SMBs with minimal IT resources.</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>['Quality', 'Supplies Quality', 'Prod Steward']</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Service center setup, replacement parts availability</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>PHA and MINK service options available, validated through customer and service center feedback.</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr"/>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Telemetry Requirements</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Implement telemetry features for device monitoring, usage analytics, and remote support.</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Enable proactive support and device management for SMBs, improving reliability and user experience.</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>['R&amp;D Telemetry', 'BA', 'Quality']</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Telemetry software, portal integration</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Telemetry features implemented, data validated, and remote support enabled.</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 12</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr"/>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Advanced Scan Workflow</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Integrate advanced scan workflow features powered by AI, targeting SMB needs for efficient document handling.</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>SMBs need efficient, automated scan workflows to reduce manual tasks and improve productivity.</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>['Marketing', 'GXD', 'R&amp;D Telemetry', 'BA']</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>AI software, scan hardware integration</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Advanced scan workflow available, tested for efficiency, and validated by user feedback.</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 4, 7, 11</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr"/>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Solutions Monetization</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Develop mechanisms for monetizing solutions and services offered with Magellan over the next 3-5 years.</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Drive revenue growth and support ongoing innovation for SMB solutions.</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>['Quality', 'Prod Steward']</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>['Support tools', 'Documentation']</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Printer supports repurposing, includes post-purchase support materials, and meets customer satisfaction targets.</t>
-        </is>
-      </c>
-      <c r="I50" t="n">
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>['Marketing', 'BA']</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Portal, AI solutions, PaaS integration</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Monetization features implemented and revenue tracked over 3-5 years.</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
         <v>0.8</v>
       </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 8</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>14</t>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 9</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>15</t>
         </is>
       </c>
     </row>

--- a/consolidation/outputs/consolidated_requirements.xlsx
+++ b/consolidation/outputs/consolidated_requirements.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K60"/>
+  <dimension ref="A1:J52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Requirement ID</t>
+          <t>No</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -465,11 +465,6 @@
       <c r="J1" t="inlineStr">
         <is>
           <t>citation</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>No</t>
         </is>
       </c>
     </row>
@@ -481,17 +476,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NGB Keyed Ink Bottles with High Page Yield</t>
+          <t>HP’s First Business Ink Tank Printer</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Develop new NGB keyed ink bottles supporting 6,000 pages for black and 6,000 pages for CMY, with CMY bottle size supporting over 8,000 pages.</t>
+          <t>Develop and launch HP's first business-focused ink tank printer designed for SMBs, providing cost-efficient color printing and high performance.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>To improve customer value and reduce frequency of bottle replacement, supporting higher yield and competitive positioning.</t>
+          <t>Addresses a market gap in the CISS PLE Hi segment and reinforces HP's leadership in SMB printing solutions.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -501,17 +496,17 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Management, End Users</t>
+          <t>['Marketing', 'GXD', 'Quality', 'R&amp;D Telemetry', 'Supplies Quality', 'DVAR', 'Tech Reg', 'Prod Steward', 'BA']</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ink formulation compatibility, bottle manufacturing, IDS system integration</t>
+          <t>['Strategic intent to protect SMB segment', 'CISS PLE Hi market gap']</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>New bottles are released with tested yields: 6K for black, 6K+ for CMY, and CMY bottle size supports &gt;8K pages as verified by page yield tests.</t>
+          <t>Product launched and available for SMB segment with ink tank technology, validated as HP’s first business ink tank printer.</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -519,10 +514,9 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
+          <t>Magellan MRD, Page 6, Page 7, Page 12</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -532,17 +526,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Spill-Free Reliability for Ink Bottles</t>
+          <t>AI Productivity and Manageability Solutions</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ensure new bottles and filling system are designed for spill-free operation during user refill and service procedures.</t>
+          <t>Integrate advanced AI features for print, scan, and workflow management to enhance productivity and device manageability for SMBs.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>To reduce customer complaints, warranty claims, and improve user experience and safety.</t>
+          <t>SMBs require efficient solutions with minimal IT support; AI features differentiate HP from competitors and address customer pain points.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -552,28 +546,27 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>R&amp;D, Customer Support, End Users</t>
+          <t>['Marketing', 'GXD', 'Quality', 'R&amp;D Telemetry']</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bottle design, IDS interface, user testing</t>
+          <t>['SMB portal development', 'Device management features']</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>No ink spillage reported in &gt;99% of user testing scenarios and warranty claims related to spillage do not exceed 0.1% of units sold.</t>
+          <t>AI-powered print, scan, and workflow management features implemented and validated in product user testing.</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
+          <t>Magellan MRD, Page 4, Page 7, Page 10, Page 11</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -583,17 +576,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NOA-F with Metal Foiled Labyrinth and Lid Label</t>
+          <t>SMB Device Management Portal</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Implement NOA-F (Non-OEM Accessory - Foil) with a metal foiled labyrinth design and lid label, maintaining current click-on push-push and TDF mechanisms.</t>
+          <t>Develop a consolidated portal for SMBs to manage multiple printers, targeting unmanaged and lightly managed SMB environments.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>To enhance security, reliability, and maintain compatibility with existing mechanisms while introducing new security features.</t>
+          <t>SMBs often lack dedicated IT teams; a centralized portal simplifies device management and reduces operational overhead.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -603,28 +596,27 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>R&amp;D, Security, Manufacturing</t>
+          <t>['Marketing', 'GXD', 'R&amp;D Telemetry']</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>NOA-F design, manufacturing process updates</t>
+          <t>['AI solutions', 'Portal integration with device telemetry']</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>NOA-F passes security and reliability tests; maintains compatibility with push-push and TDF; metal foil and lid label present as per design.</t>
+          <t>Portal available for SMBs, supports management of multiple printers, validated through usability testing.</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
+          <t>Magellan MRD, Page 7, Page 10</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -634,17 +626,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Reuse SuperAmp Si PHA and Magi/Nessie Ink</t>
+          <t>Lowest Business TCO (Total Cost of Ownership)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Continue using SuperAmp Si PHA and Magi/Nessie ink formulations, with no ink reformulation required for Magellan.</t>
+          <t>Deliver HP’s lowest business TCO for SMB tank printers, including minimal intervention and optimized supply usage.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>To leverage existing, proven technology and reduce R&amp;D and qualification costs.</t>
+          <t>Cost efficiency is a key buying factor for SMBs and differentiates HP from competitors.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -654,28 +646,27 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing, Supply Chain</t>
+          <t>['Marketing', 'Quality', 'Supplies Quality']</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Compatibility with new bottle and tank designs, IDS integration</t>
+          <t>['Ink tank technology', 'Keyed bottles', 'Sustainability targets']</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>SuperAmp Si PHA and Magi/Nessie inks pass all compatibility and reliability tests with new Magellan hardware.</t>
+          <t>Product demonstrates lowest TCO in independent benchmarking versus competitors; minimal intervention required as documented.</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
+          <t>Magellan MRD, Page 4, Page 11</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -685,48 +676,47 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Reliability and Characterization Modeling</t>
+          <t>Maintenance-Free or Reduced Maintenance Design</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Model and characterize reliability, WVTR (Water Vapor Transmission Rate), air gain, flow rate, IDS, startup, and NOA-F end-of-life (EOL) for the new platform.</t>
+          <t>Engineer the printer for maintenance-free or reduced maintenance operation, minimizing parts replacement over product lifetime.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>To ensure new system meets reliability, performance, and service life goals.</t>
+          <t>SMBs value reliability and minimal maintenance due to lack of IT resources; this reduces downtime and operational costs.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality Assurance</t>
+          <t>['Quality', 'R&amp;D Telemetry', 'Supplies Quality']</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Data collection, simulation tools, IDS design</t>
+          <t>['Replaceable maintenance box', 'Serviceability features']</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Complete reliability models and reports demonstrating compliance with HP standards for all listed parameters.</t>
+          <t>Maintenance cycles are reduced compared to competitors; validated through lab testing and customer pilots.</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
+          <t>Magellan MRD, Page 4, Page 11</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -736,17 +726,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ink Stability Modeling for Tank Impact on Print Quality</t>
+          <t>Replaceable Maintenance Box</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Perform ink stability modeling for the new tank design and assess impact on print quality (PQ).</t>
+          <t>Include a replaceable maintenance box as a new feature to simplify servicing and extend product life.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>To proactively address potential print quality issues due to tank/ink interactions.</t>
+          <t>Enables easier maintenance for SMBs with limited IT support; aligns with the goal of reduced intervention and maintenance.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -756,17 +746,17 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality Assurance</t>
+          <t>['Quality', 'R&amp;D Telemetry', 'Supplies Quality']</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tank design, ink formulation data</t>
+          <t>['Maintenance-free design', 'Serviceability requirements']</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Modeling completed; no negative impact to PQ identified or mitigation strategies in place.</t>
+          <t>Maintenance box is user-replaceable and documented; validated via service center and customer feedback.</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -774,10 +764,9 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -787,48 +776,47 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NOA-F Service Parts Warranty Support</t>
+          <t>Keyed Bottles for Ink Refilling</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>NOA-F must be available as a service part for in-warranty support and replacement.</t>
+          <t>Implement keyed bottles for ink refilling to prevent errors and ensure compatibility.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>To meet service and warranty obligations, reducing downtime for customers.</t>
+          <t>Reduces risk of incorrect refilling, supports sustainability, and improves user experience for SMBs.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Service, Warranty, End Users</t>
+          <t>['Supplies Quality', 'Quality']</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>NOA-F design finalization, parts logistics</t>
+          <t>['Ink tank technology', 'Supply chain']</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>NOA-F available in service parts catalog and distributed to service centers by launch.</t>
+          <t>Keyed bottles provided for all ink refills; error rate in refilling reduced in usability testing.</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.95</v>
+        <v>0.88</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -838,48 +826,47 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Acumen 6 on Lid</t>
+          <t>Warranty and Serviceability</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Integrate Acumen 6 (presumed tracking/ID technology) on the bottle lid for authentication or tracking.</t>
+          <t>Provide warranty coverage of 80,000 pages or 2 years (whichever is first), with customer replaceable parts and service center support (PHA and MINK thresholds).</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>To improve product traceability, security, and anti-counterfeiting.</t>
+          <t>SMBs require reliable service options due to limited IT resources; warranty and serviceability are critical buying factors.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Security, Supply Chain</t>
+          <t>['Quality', 'Prod Steward']</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lid design, Acumen 6 technology integration</t>
+          <t>['Replaceable maintenance box', 'Service center process']</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>All lids have functional Acumen 6 features as verified by security audit.</t>
+          <t>Warranty terms implemented; customer replaceable parts available; service center process validated.</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.8</v>
+        <v>0.93</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -889,17 +876,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Factory Line Modifications for NOA-F and New Bottles</t>
+          <t>Sustainability – 60% RCP (Recycled Content Percentage)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Modify existing SA14 production line for NOA-F, add Magi ink cart and labeling tool in Orcus 5, and create molds for 1 to 4 new keyed caps.</t>
+          <t>Design printer with at least 60% recycled content, exceeding competitor benchmarks (Epson 30%, Canon TBC).</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>To enable manufacturing of new components and ensure readiness for Magellan production.</t>
+          <t>Sustainability is a differentiator and increasingly important for SMBs; supports HP’s environmental goals.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -909,17 +896,17 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Manufacturing, Operations</t>
+          <t>['Prod Steward', 'Marketing']</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Final product design, factory readiness, CapEx approval</t>
+          <t>['Supply chain sourcing', 'Design engineering']</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>SA14 and Orcus 5 lines modified and validated for Magellan production requirements.</t>
+          <t>Printer contains at least 60% recycled content; validated through supplier and manufacturing audits.</t>
         </is>
       </c>
       <c r="I10" t="n">
@@ -927,10 +914,9 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
+          <t>Magellan MRD, Page 11</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -940,48 +926,47 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Support Customer-Replaceable PHA and NOA-F</t>
+          <t>Mobile Printing via HP App</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Design PHA (Printhead Assembly) and NOA-F to be customer-replaceable for improved serviceability.</t>
+          <t>Enable mobile printing capabilities through the HP App for SMB users.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>To reduce service costs and downtime, empowering end users to perform basic maintenance.</t>
+          <t>Mobile printing is a core use case for SMBs and supports flexible work environments.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>End Users, Service, Product Management</t>
+          <t>['Marketing', 'GXD']</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Component design, user instructions, safety validation</t>
+          <t>['HP App integration']</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>End users can replace PHA and NOA-F using provided instructions without tools, as validated by usability studies.</t>
+          <t>Mobile printing feature available and validated in user acceptance testing.</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.9</v>
+        <v>0.89</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
+          <t>Magellan MRD, Page 9</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -991,48 +976,47 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>New Warranty Page Life Goal of 80K Pages</t>
+          <t>Support for PaaS (Printing as a Service)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Increase the warranty page life goal for the printer to 80,000 pages.</t>
+          <t>Ensure the printer supports Printing as a Service (PaaS) models, including SMB2.0 Solutions and Advanced View SMB portal.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>To offer a more competitive product with longer life and lower total cost of ownership.</t>
+          <t>PaaS offers flexible, scalable printing solutions for SMBs and aligns with HP’s strategic goals.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Product Management, End Users, Warranty</t>
+          <t>['DVAR', 'Tech Reg', 'Marketing']</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Reliability modeling, component durability</t>
+          <t>['SMB portal', 'Device management']</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Warranty documentation updated; field units demonstrate &gt;80K page life in reliability testing.</t>
+          <t>Printer supports PaaS features and is validated in enterprise deployment scenarios.</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.95</v>
+        <v>0.87</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
+          <t>Magellan MRD, Page 4, Page 10</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1042,17 +1026,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SKU 2 (Hi + Hi PDL) Platform as a Service (PaaS) Support</t>
+          <t>PDL SKU Performance and Compatibility</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Support SKU 2 with high throughput and high PDL (Page Description Language) for Platform as a Service (PaaS) business model.</t>
+          <t>Provide a PDL SKU with improved speed (25/20 min), PDL/PS support, and Blue Angel certification.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>To address SMB and enterprise segments with managed print services and higher performance needs.</t>
+          <t>Performance and compatibility are critical for SMBs with diverse printing needs; Blue Angel certification supports sustainability.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1062,28 +1046,27 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Business, Product Management, SMB/Enterprise Customers</t>
+          <t>['Quality', 'Tech Reg']</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Firmware, hardware capabilities, service platform integration</t>
+          <t>['Speed improvement', 'PDL/PS support', 'Certification process']</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>SKU 2 available for PaaS; meets throughput and PDL requirements as per spec.</t>
+          <t>PDL SKU meets performance targets and passes Blue Angel certification.</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
+          <t>Magellan MRD, Page 4</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1093,17 +1076,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Reddington ID with Increased Tank Size</t>
+          <t>Telemetry Requirements</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Adopt Reddington ID for product with increased tank size; no change to Marconi-HI ADF (Automatic Document Feeder).</t>
+          <t>Implement telemetry features for device monitoring, usage tracking, and predictive maintenance.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>To align with new bottle/tank requirements while maintaining compatibility with proven ADF design.</t>
+          <t>Telemetry enables proactive support, analytics, and improved device management for SMBs.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1113,17 +1096,17 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Product Management, R&amp;D</t>
+          <t>['R&amp;D Telemetry', 'BA']</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tank redesign, mechanical integration, ADF compatibility</t>
+          <t>['Portal integration', 'Device firmware']</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Product passes integration and capacity tests; ADF unchanged from Marconi-HI.</t>
+          <t>Telemetry features implemented and validated in portal and device analytics.</t>
         </is>
       </c>
       <c r="I14" t="n">
@@ -1131,10 +1114,9 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
+          <t>Magellan MRD, Page 12</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1144,17 +1126,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EPEAT3, LOT4, and Blue Angel Environmental Compliance</t>
+          <t>Perfect Print and Perfect Scan Solutions</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ensure product meets EPEAT3, LOT4, and Blue Angel requirements for PDL SKU.</t>
+          <t>Deliver advanced print and scan quality solutions enabled by AI, targeting SMB needs for accuracy and efficiency.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>To satisfy regulatory and market-driven environmental standards.</t>
+          <t>High-quality print and scan are top priorities for SMBs; AI solutions differentiate HP from competitors.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1164,28 +1146,27 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Compliance, Marketing, Product Management</t>
+          <t>['Marketing', 'Quality', 'GXD']</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Product design, materials selection, certification processes</t>
+          <t>['AI solutions', 'Device firmware']</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Product receives EPEAT3, LOT4, and Blue Angel certifications prior to launch.</t>
+          <t>Perfect Print and Perfect Scan features implemented and validated in product testing.</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.9</v>
+        <v>0.92</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
+          <t>Magellan MRD, Page 7, Page 11</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1195,17 +1176,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Input and Output Tray Changes for Tank Protrusion</t>
+          <t>Consolidated Solutions/Services Offering</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Modify input and output trays to accommodate tank protrusion and optimize product size.</t>
+          <t>Bundle solutions and services (including AI, device management, PaaS, mobile printing) to add value to hardware.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>To ensure mechanical compatibility and optimize product footprint.</t>
+          <t>Integrated solutions increase customer value and support HP’s strategic goals for SMB market leadership.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1215,252 +1196,247 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>R&amp;D, Mechanical Design, Manufacturing</t>
+          <t>['Marketing', 'DVAR', 'BA']</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tank design finalization, tray redesign</t>
+          <t>['Portal', 'AI solutions', 'PaaS support']</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Trays fit with final tank design and pass mechanical and usability tests.</t>
+          <t>Solutions/services bundle available and validated in customer pilots and market launch.</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.85</v>
+        <v>0.88</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
+          <t>Magellan MRD, Page 10, Page 11</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>4.3” CGD Display Integration</t>
+          <t>NGB Keyed Bottles with High Page Yield</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Integrate a 4.3-inch CGD (Color Graphic Display) for improved user interface.</t>
+          <t>Develop new NGB keyed ink bottles with 6,000 page yield for black and 6,000 for CMY; CMY bottles must support sizes &gt;8,000 pages.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>To enhance user experience with a larger, more informative display.</t>
+          <t>Supports high-volume printing and competitive positioning in SMB/Enterprise CISS segments.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>End Users, Product Management</t>
+          <t>R&amp;D, Product Management, SMB/Enterprise Customers</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Display sourcing, firmware UI design</t>
+          <t>Requires compatibility with NOA-F, IDS, PHA, and Magi/Nessie ink systems.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Display integrated and passes usability and reliability tests.</t>
+          <t>Bottles are available in required sizes, pass reliability and spill-free tests, and deliver specified yields in field tests.</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Platform with 4 Sayan Sibstar Tubes and New Routing</t>
+          <t>Spill-Free Reliability for Ink Bottles</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Leverage Sayan Sibstar tubes, implement four-tube routing and new integration for ink delivery.</t>
+          <t>Ensure new NGB bottles deliver spill-free reliability during user handling and refilling.</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>To support higher ink flow and reliability for new tank system.</t>
+          <t>Critical for customer satisfaction and reducing service incidents.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing</t>
+          <t>End Users, Support, Product Quality</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tube sourcing, platform design</t>
+          <t>Dependent on bottle and NOA-F design.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>System passes ink flow and reliability tests with new tube configuration.</t>
+          <t>Field and lab tests confirm zero spills during normal use.</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Service Station Aerosol Management</t>
+          <t>NOA-F with Metal Foiled Labyrinth and Lid Label</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Update service station with aerosol management and spit platform changes to accommodate new tank.</t>
+          <t>Implement NOA-F with a metal foiled labyrinth and lid label, maintaining compatibility with existing push-push and TDF mechanisms.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>To maintain print quality and reliability with new ink/tank configuration.</t>
+          <t>Enhances reliability and security of ink delivery system.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>R&amp;D, Service</t>
+          <t>R&amp;D, Product Management, Factory Operations</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Service station design, platform integration</t>
+          <t>Integration with existing hardware and bottle designs.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Aerosol management system operational and passes reliability tests.</t>
+          <t>NOA-F units pass all reliability and integration tests with new and legacy components.</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Carriage Dynamic and Force Model Update</t>
+          <t>Reuse Superamp Si PHA and Magi/Nessie Ink</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Update carriage dynamic and force models to account for new tube routing and increased weights.</t>
+          <t>Reuse Superamp Si PHA and Magi/Nessie ink without reformulation in the Magellan printer.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>To ensure mechanical reliability and print quality with new hardware configuration.</t>
+          <t>Reduces R&amp;D and validation costs, leverages proven components.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>R&amp;D, Mechanical Engineering</t>
+          <t>R&amp;D, Supply Chain, Product Management</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carriage design, tube integration</t>
+          <t>Ensures compatibility with new bottle and NOA-F systems.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Carriage system passes dynamic and force testing with new configuration.</t>
+          <t>System passes all print quality, reliability, and regulatory tests with reused components.</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Paper Path Support for Increased Page Life</t>
+          <t>Ink Stability and IDS Characterization</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Update paper path components to support increased page life target of 80K pages.</t>
+          <t>Model and validate ink stability, WVTR, air gain, flow rate, and IDS performance, including startup and NOA-F end-of-life scenarios.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>To ensure durability and reliability over extended product life.</t>
+          <t>Ensures consistent print quality and long-term reliability.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1470,252 +1446,247 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing, Quality Assurance</t>
+          <t>R&amp;D, Product Quality, Service</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Material selection, durability testing</t>
+          <t>Dependent on ink, IDS, and NOA-F design.</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Paper path components pass accelerated life testing for 80K pages.</t>
+          <t>All models and tests meet or exceed defined HP quality standards for stability and reliability.</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ink Maintenance as Serviceable Part (Post 80K Life)</t>
+          <t>NOA-F as Service Parts for Warranty Support</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Design ink maintenance as a serviceable part to be replaced at service centers after 80K page life is reached.</t>
+          <t>Provide NOA-F as service parts to support warranty obligations and field repairs.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>To extend product life and maintain print quality for high-usage customers.</t>
+          <t>Improves serviceability and reduces downtime for customers.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Service, End Users</t>
+          <t>Service, End Customers, Warranty Team</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Maintenance part design, service documentation</t>
+          <t>Requires supply chain and part number integration.</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Part available and service process documented; field replaceable after 80K pages.</t>
+          <t>NOA-F is available as a service part, with documented replacement procedure and inventory in place.</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>New Make-Break and FI Connection for IDS</t>
+          <t>Acumen 6 on Lid</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Implement new make-break and fluidic interconnect (FI) connection in IDS (Ink Delivery System) to support increased tank size and keying.</t>
+          <t>Implement Acumen 6 feature on the ink lid.</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>To ensure secure, reliable, and user-friendly ink connections for new system.</t>
+          <t>Supports traceability and anti-counterfeit measures.</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing, End Users</t>
+          <t>Security, Product Management, End Users</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>IDS design, keying mechanism</t>
+          <t>Requires lid design and Acumen 6 integration.</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>New connections pass reliability, usability, and leak tests.</t>
+          <t>All lids include Acumen 6 and pass traceability validation.</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>LEBI Ink-Tank with Increased Size, Keying, and LOI SHAID</t>
+          <t>Factory Line Modifications for NOA-F and Ink Cart</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Leverage LEBI ink-tank design with increased size, new keying, and LOI (Level of Ink) SHAID (presumed sensor/ID) for improved management.</t>
+          <t>Modify SA14 factory line for NOA-F; add Magi ink cart and labeling tool in Orcus 5 line.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>To support higher yield, reduce errors, and improve ink management.</t>
+          <t>Ensures manufacturing readiness for new components.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing, End Users</t>
+          <t>Manufacturing, Operations, R&amp;D</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>LEBI tank design, SHAID integration</t>
+          <t>Dependent on final NOA-F, ink cart, and labeling tool specifications.</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Tank with increased size and SHAID passes functional and reliability tests.</t>
+          <t>Factory lines are modified, validated, and achieve target production rates for new SKUs.</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>New IDS Startup Algorithm and Air Management</t>
+          <t>Support Customer-Replaceable PHA and NOA-F</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Develop new startup algorithm and air management system for IDS to ensure optimal performance and reliability.</t>
+          <t>Design PHA and NOA-F to be customer-replaceable for improved serviceability.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>To address new tank and bottle configuration, ensuring consistent print quality.</t>
+          <t>Reduces service costs and downtime, enhances user experience.</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>R&amp;D, Firmware</t>
+          <t>End Users, Service, Product Management</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>IDS hardware, firmware development</t>
+          <t>Requires user documentation and design for easy replacement.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Algorithm implemented and verified to meet startup and air management KPIs.</t>
+          <t>Users can replace PHA and NOA-F with standard tools and instructions; field tests confirm process is user-friendly.</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>New Print Quality Goals and Depletion Definition</t>
+          <t>Warranty Page Life Goal of 80k Pages</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Define and implement new print quality (PQ) goals and depletion criteria to align with new page yield definitions.</t>
+          <t>Design printer and key components to support a new warranty page life goal of 80,000 pages.</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>To ensure customer expectations are met for print quality and yield.</t>
+          <t>Meets competitive and contractual requirements for durability.</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1725,99 +1696,97 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Product Management, R&amp;D, Quality Assurance</t>
+          <t>Product Management, Warranty Team, End Users</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>PQ definition, firmware updates</t>
+          <t>Requires robust design of paperpath, ink system, and service parts.</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>New PQ goals and depletion criteria published and validated through testing.</t>
+          <t>Printers pass accelerated life tests for 80,000 pages under warranty conditions.</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Reuse Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU</t>
+          <t>SKU 2 (Hi + Hi PDL) PaaS Offering</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Reuse Marconi Tux dASIC, Hannibal aASIC, and Raccoon PSU to reduce development cost and risk.</t>
+          <t>Develop SKU 2 with high and high PDL configurations for Printer-as-a-Service (PaaS) business model.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>To leverage proven components and accelerate time-to-market.</t>
+          <t>Supports new business models and customer segments.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing, Supply Chain</t>
+          <t>Product Management, Sales, SMB/Enterprise Customers</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Component availability, integration testing</t>
+          <t>Requires configuration management and service integration.</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Components integrated and pass system-level validation.</t>
+          <t>SKU 2 is available for PaaS, with defined service and support packages.</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.95</v>
+        <v>0.8</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Stingray Wi-Fi Module and Dune Firmware</t>
+          <t>Reddington ID with Increased Tank Size</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Integrate Stingray Wi-Fi module and Dune firmware for connectivity and feature support.</t>
+          <t>Increase tank size for Reddington ID without changing Marconi-HI ADF; update input/output trays to align with tank protrusion.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>To offer wireless connectivity and required firmware features for Magellan.</t>
+          <t>Supports higher ink capacity and page yield.</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1827,17 +1796,17 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>R&amp;D, End Users, Product Management</t>
+          <t>Product Design, R&amp;D, End Users</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Module sourcing, firmware integration</t>
+          <t>Requires mechanical design changes and tray integration.</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Wi-Fi and firmware features operational and validated in system tests.</t>
+          <t>Tank size increased, trays fit and function correctly, and printer passes fit/form/function tests.</t>
         </is>
       </c>
       <c r="I28" t="n">
@@ -1848,78 +1817,76 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Gauss4.xx Hardware and Firmware Security</t>
+          <t>EPS Foam Packaging</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Implement Gauss4.xx security features in hardware and firmware to ensure data and device security.</t>
+          <t>Use EPS foam for packaging to protect the printer during shipment.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>To meet modern security standards and protect user data.</t>
+          <t>Reduces shipping damage and supports sustainability goals if recyclable.</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Security, R&amp;D, End Users</t>
+          <t>Logistics, Product Management, End Users</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>HW/FW design, security testing</t>
+          <t>Packaging design and supplier selection.</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Device passes internal and external security audits for Gauss4.xx features.</t>
+          <t>All shipments use EPS foam packaging, with damage rates below target threshold.</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Business Model Support for Consumer, SMB, and Enterprise</t>
+          <t>EPEAT3, LOT4, and Blue Angel Compliance</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Design product and services to support Consumer, SMB, and Enterprise business models, including PaaS and WorkFromHome/Flexworker solutions.</t>
+          <t>Ensure product meets EPEAT3, LOT4, and Blue Angel (for PDL SKU) environmental requirements.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>To maximize market reach and support diverse customer needs.</t>
+          <t>Enables sales in regulated markets and supports HP sustainability goals.</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1929,48 +1896,47 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Business, Product Management, Sales</t>
+          <t>Regulatory, Product Management, Sales</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Service platform integration, SKU differentiation</t>
+          <t>Requires documentation, testing, and certification.</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Product and services available for all targeted segments at launch.</t>
+          <t>Product is certified for EPEAT3, LOT4, and Blue Angel as applicable.</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Onboarding and S&amp;O Pathways</t>
+          <t>Size Optimization and 4.3” CGD Display</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Support onboarding and S&amp;O (Setup &amp; Onboarding) paths for Consumer (HPX), HP One, SMB Portal, and ECP.</t>
+          <t>Optimize printer size and integrate a 4.3-inch CGD display.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>To streamline customer onboarding and improve experience across segments.</t>
+          <t>Improves usability and fits market requirements for compact, feature-rich printers.</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1980,48 +1946,47 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Product Management, Customer Support, Sales</t>
+          <t>Product Design, End Users, Marketing</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Onboarding workflow design, platform integration</t>
+          <t>Mechanical and electrical integration of display.</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>All onboarding paths operational and validated in user acceptance testing.</t>
+          <t>Printer meets size targets and display passes usability and reliability tests.</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Scan Solution, SMB Manageability, and Enterprise Support</t>
+          <t>New Tube Routing and Integration</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Integrate scan solution, SMB manageability features, and enterprise support for WJA (Web Jetadmin), HPSM (HP Smart Management), and JAM.</t>
+          <t>Leverage Sayan Sibstar tubes and implement new tube routing and integration for 4-tube platform.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>To offer a full-featured solution for SMB and enterprise customers.</t>
+          <t>Supports increased ink flow and reliability for higher page yields.</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2031,17 +1996,17 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Business, Product Management, SMB/Enterprise Customers</t>
+          <t>R&amp;D, Manufacturing, Product Quality</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Solution integration, firmware and software support</t>
+          <t>Tube design, IDS, and carriage integration.</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Scan, manageability, and enterprise support features fully functional at launch.</t>
+          <t>Tube routing supports target flow rates and reliability in system tests.</t>
         </is>
       </c>
       <c r="I32" t="n">
@@ -2052,78 +2017,76 @@
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Client and Driver Support</t>
+          <t>Service Station Aerosol Management</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Support clients and drivers including HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD.</t>
+          <t>Update service station aerosol management with spit platform changes due to tank modifications.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>To ensure broad compatibility and ease of use across platforms and deployment scenarios.</t>
+          <t>Ensures clean operation and prevents contamination from increased ink handling.</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Product Management, End Users, IT Admins</t>
+          <t>R&amp;D, Service, Product Quality</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Driver development, compatibility testing</t>
+          <t>Service station and tank design changes.</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>All listed clients and drivers available and validated for Magellan at launch.</t>
+          <t>Aerosol management meets HP cleanliness and reliability standards in testing.</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Protect Micro/SMB Segments and Ink/Laser Profit Pool</t>
+          <t>Carriage Dynamic and Force Model Update</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Design features and pricing to protect HP’s micro/SMB segment and prevent profit pool erosion to competitors.</t>
+          <t>Update carriage dynamic and force models to account for new tube routing and increased weights.</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>To maintain HP’s market share and profitability in key segments.</t>
+          <t>Maintains print quality and reliability with new mechanical configuration.</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2133,48 +2096,47 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Business, Product Management, Sales</t>
+          <t>R&amp;D, Product Quality, Manufacturing</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Market analysis, pricing strategy</t>
+          <t>Tube, carriage, and weight changes.</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Market share in micro/SMB maintained or grown post-launch.</t>
+          <t>Carriage system passes dynamic and force validation tests.</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Lead with LaserJet, Flank with PDL in Medium/Enterprise</t>
+          <t>Paperpath Durability for Increased Page Life</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Strategically position LaserJet as lead offering and use PDL (presumably Page Description Language-enabled devices) to flank in medium and enterprise segments, targeting Epson as CISS grows.</t>
+          <t>Enhance paperpath to support increased page life target of 80,000 pages.</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>To win over competitors and grow share in expanding CISS (Continuous Ink Supply System) market.</t>
+          <t>Critical to meet new warranty and reliability goals.</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2184,99 +2146,97 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Business, Product Management, Sales</t>
+          <t>Product Quality, R&amp;D, End Users</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Product portfolio strategy, marketing</t>
+          <t>Material and design upgrades to paperpath components.</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Share gains in medium/enterprise segments and CISS market measured in 12 months post-launch.</t>
+          <t>Paperpath passes accelerated life testing for 80,000 pages.</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Grow CISS Profitable Share in New Segments</t>
+          <t>Ink Maintenance Serviceable Part (Post 80k Life)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Expand CISS offering into new market segments to grow profitable share.</t>
+          <t>Design ink maintenance as a serviceable part for replacement after 80,000 pages by service centers.</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>To capture new revenue streams and outpace competitors as CISS adoption increases.</t>
+          <t>Supports extended product life and reduces total cost of ownership.</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Business, Product Management, Sales</t>
+          <t>Service, End Users, Warranty Team</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Market research, product adaptation</t>
+          <t>Service procedures and part availability.</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>New segment launches with positive ROI within 18 months post-launch.</t>
+          <t>Service centers can replace ink maintenance part per documented procedure.</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Highly Leverage Watt-LE Mech Platform and Marconi-Hi Product</t>
+          <t>140ml K Bottles and New CMY Bottle Sizes</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Leverage existing Watt-LE mechanical platform and Marconi-Hi product (Reddington ID) and solutions for Magellan.</t>
+          <t>Introduce new 140ml black (K) bottles and appropriately sized CMY bottles for Magellan.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>To accelerate development and reduce cost by reusing proven platforms.</t>
+          <t>Supports higher page yield and new tank size.</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2286,17 +2246,17 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing, Product Management</t>
+          <t>R&amp;D, Product Management, Supply Chain</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Platform compatibility, integration testing</t>
+          <t>Bottle design and supply chain readiness.</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Platform integration complete with no critical issues before launch.</t>
+          <t>New bottles are available, validated, and integrated into supply chain.</t>
         </is>
       </c>
       <c r="I37" t="n">
@@ -2304,30 +2264,29 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Integrate CISS IDS, NOA-F, and Ink Tanks</t>
+          <t>New IDS Make-Break and FI Connection</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Integrate CISS IDS, NOA-F, and new ink tanks into the product platform.</t>
+          <t>Develop new make-break and FI (fluid interface) connection for IDS, leveraging LEBI ink-tank with increased size, keying, and LOI, with one SHAID.</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>To deliver a cohesive, high-performance ink delivery solution.</t>
+          <t>Ensures reliable ink delivery and system security.</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2337,17 +2296,17 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Management, Manufacturing</t>
+          <t>R&amp;D, Product Quality, Security</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Component design, system integration</t>
+          <t>IDS and ink-tank design updates.</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>All systems integrated and pass end-to-end functional testing.</t>
+          <t>System passes make-break, FI connection, and security validation tests.</t>
         </is>
       </c>
       <c r="I38" t="n">
@@ -2355,81 +2314,79 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SuperAmp PHA Life at 65K Pages (Constrained)</t>
+          <t>New IDS Startup Algorithm and Air Management</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Maintain SuperAmp PHA (Printhead Assembly) life at 65,000 pages as a non-flexible (constrained) requirement.</t>
+          <t>Implement new IDS startup algorithm and air management system.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>To ensure critical component reliability and minimize field failures.</t>
+          <t>Improves startup reliability and print quality.</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality Assurance, Service</t>
+          <t>R&amp;D, Product Quality, End Users</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Component testing, reliability validation</t>
+          <t>IDS hardware and firmware updates.</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>SuperAmp PHA consistently meets/exceeds 65K page life in reliability testing.</t>
+          <t>Startup and air management meet defined success rates in system tests.</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Warranty Life of 2 Years (Optimized)</t>
+          <t>New Servicing and Startup Algorithm</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Provide a 2-year warranty life for the printer as an optimized (somewhat flexible) requirement.</t>
+          <t>Develop new servicing and startup algorithm for Magellan platform.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>To meet customer expectations and competitive benchmarks.</t>
+          <t>Enhances reliability, minimizes ink waste, and improves customer experience.</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2439,17 +2396,17 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Product Management, Warranty, End Users</t>
+          <t>R&amp;D, Product Quality, Service</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Reliability modeling, warranty documentation</t>
+          <t>Firmware and IDS integration.</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Warranty documentation published with 2-year coverage; field reliability supports warranty period.</t>
+          <t>Algorithm passes reliability and efficiency benchmarks in system tests.</t>
         </is>
       </c>
       <c r="I40" t="n">
@@ -2457,281 +2414,279 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Throughput 25/20 PPM (Optimized)</t>
+          <t>New Print Quality (PQ) Goals and Depletion Metrics</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Achieve throughput of 25 ppm (pages per minute) for standard and 20 ppm for PDL SKU.</t>
+          <t>Establish new print quality goals and depletion metrics to align with page yield definitions.</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>To deliver competitive print speed for target segments.</t>
+          <t>Ensures consistent output and meets customer expectations for page yield.</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Product Management, R&amp;D, End Users</t>
+          <t>Product Quality, R&amp;D, End Users</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Print engine design, firmware tuning</t>
+          <t>Test method definition and validation.</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Throughput verified by print speed tests for both SKUs.</t>
+          <t>Product meets or exceeds new PQ and depletion targets in field and lab tests.</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Serviceability – Maintenance Box (Optimized)</t>
+          <t>Reuse of Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Design maintenance box for improved serviceability, as an optimized requirement.</t>
+          <t>Reuse Marconi Tux dASIC, Hannibal aASIC, and Raccoon PSU in Magellan platform.</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>To reduce downtime and service costs for users and HP.</t>
+          <t>Reduces development time and leverages proven electronics.</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Service, End Users, Product Management</t>
+          <t>R&amp;D, Product Management, Supply Chain</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Box design, service process documentation</t>
+          <t>Compatibility with new Magellan features and requirements.</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Maintenance box can be replaced in &lt;5 minutes by trained personnel; validated by service trials.</t>
+          <t>All reused components pass integration and reliability tests in Magellan.</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SMB Solution Support (Optimized)</t>
+          <t>Stingray Wi-Fi Module and Dune FW Integration</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Develop and support solution features for SMB customers, as an optimized requirement.</t>
+          <t>Integrate Stingray Wi-Fi module and Dune firmware (FW) into Magellan.</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>To address SMB market needs and differentiate from competitors.</t>
+          <t>Provides wireless connectivity and leverages existing firmware platform.</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Product Management, SMB Customers, Sales</t>
+          <t>R&amp;D, Product Management, End Users</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Solution development, feature integration</t>
+          <t>HW/FW compatibility and regulatory certification.</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>SMB solution features available and validated with pilot customers.</t>
+          <t>Wi-Fi and firmware pass all connectivity and functional tests in Magellan.</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Host 12K-CMYK (Flexible)</t>
+          <t>Gauss4.xx Security (HW &amp; FW)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Host support for 12,000-page yield CMYK configurations, as a flexible requirement.</t>
+          <t>Implement Gauss4.xx hardware and firmware security features in Magellan.</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>To enable future expansion or SKU differentiation if needed.</t>
+          <t>Ensures product security and compliance with HP security standards.</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Product Management, R&amp;D</t>
+          <t>Security, R&amp;D, Product Management</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Yield validation, supply chain planning</t>
+          <t>HW and FW integration with Magellan platform.</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>12K-CMYK configuration validated and ready for future deployment.</t>
+          <t>Security features pass HP security validation and external audit.</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Trade Page 6K (Flexible)</t>
+          <t>Strategic Segment Protection and Growth</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Support trade page yield of 6,000 pages as a flexible requirement.</t>
+          <t>Protect Micro/SMB segments, lead with LaserJet and flank with PDL in Medium/Enterprise, and grow CISS share in new segments.</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>To provide options for different market segments or trade programs.</t>
+          <t>Aligns product with HP’s strategic business goals and market positioning.</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Product Management, Sales</t>
+          <t>Business Leadership, Product Management, Sales</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Yield validation, SKU definition</t>
+          <t>Product features and market alignment.</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Trade page 6K configuration validated and available as needed.</t>
+          <t>Product launches with targeted features for each segment and achieves growth KPIs.</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr"/>
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Business Ink Tank Printer</t>
+          <t>Support for Multiple Business Models and Solutions</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Develop HP’s first business ink tank printer targeted at SMBs, offering high performance and cost efficiency.</t>
+          <t>Support Consumer, SMB, and Enterprise business models, including PaaS, WorkFromHome/Flexworker, and onboarding via HPX, HP One, SMB Portal, and ECP paths.</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>To fill the gap in HP’s portfolio and compete in the CISS PLE Hi segment, addressing evolving customer needs for cost-effective printing.</t>
+          <t>Expands addressable market and supports diverse customer needs.</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2741,48 +2696,47 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>['Marketing', 'GXD', 'Quality', 'R&amp;D Telemetry', 'Supplies Quality', 'DVAR', 'Tech Reg', 'Prod Steward', 'BA']</t>
+          <t>Sales, Product Management, End Users</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>CISS technology, ink tank system integration</t>
+          <t>Solution and service integration with platform.</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Printer model released with ink tank technology, validated for SMB segment, and achieves lowest business TCO.</t>
+          <t>Product is compatible with all listed business models and onboarding paths.</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 7, 11, 12</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr"/>
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>AI Productivity Solutions</t>
+          <t>Scan Solution, SMB Manageability, and Enterprise Support</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Integrate AI-powered productivity features for print, scan, and device management workflows.</t>
+          <t>Integrate scan solution, SMB manageability tools, and enterprise support (WJA, HPSM, JAM) into Magellan.</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>SMBs need automation and efficiency improvements without dedicated IT teams; AI features will differentiate the product and address key pain points.</t>
+          <t>Meets needs of business customers and supports managed print services.</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2792,48 +2746,47 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>['Marketing', 'GXD', 'Quality', 'R&amp;D Telemetry', 'BA']</t>
+          <t>SMB/Enterprise Customers, Product Management, IT Admins</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>SMB portal, device management platform, AI software development</t>
+          <t>Software and solution integration.</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>AI features for print, scan, and support implemented and validated in MVP; measurable reduction in manual tasks.</t>
+          <t>Product passes validation for all listed solutions and tools.</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.92</v>
+        <v>0.9</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 7, 10, 11</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr"/>
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SMB Manageability Portal</t>
+          <t>Client and Driver Support</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Develop a consolidated portal for SMBs to manage printers and devices, targeting office managers and generalist IT staff.</t>
+          <t>Ensure compatibility with HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD clients and drivers.</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Unmanaged/Lightly Managed SMBs lack dedicated IT; a portal simplifies device management and enhances customer experience.</t>
+          <t>Enables broad deployment and ease of use in diverse IT environments.</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2843,17 +2796,17 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>['Marketing', 'GXD', 'R&amp;D Telemetry', 'BA']</t>
+          <t>End Users, IT, Product Management</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Portal software, device connectivity, AI integration</t>
+          <t>Firmware and driver integration.</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Portal released with device management features, user tested by office managers/generalist IT, and receives positive usability feedback.</t>
+          <t>All listed clients and drivers are supported and pass compatibility tests.</t>
         </is>
       </c>
       <c r="I48" t="n">
@@ -2861,30 +2814,29 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 7, 10</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr"/>
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Low Total Cost of Ownership (TCO)</t>
+          <t>Schedule and SuperAmp PHA Life Constraint</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Design the printer to deliver HP’s lowest business TCO, including minimal intervention and maintenance.</t>
+          <t>Schedule and SuperAmp PHA life at 65K are the least flexible constraints for Magellan.</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Cost efficiency is a top priority for SMBs; lower TCO is a key differentiator against competitors.</t>
+          <t>Critical path items for project delivery and product reliability.</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2894,591 +2846,175 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>['Marketing', 'Quality', 'Supplies Quality', 'Prod Steward']</t>
+          <t>Project Management, R&amp;D, Manufacturing</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Ink tank technology, maintenance box design, sustainable materials</t>
+          <t>Project planning and PHA design/life validation.</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>TCO calculation shows lowest cost vs. competitors, validated through market analysis and customer feedback.</t>
+          <t>Project milestones and PHA life targets are met as scheduled.</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.93</v>
+        <v>0.95</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 11</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>4</t>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr"/>
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Customer Replaceable Maintenance Box</t>
+          <t>Warranty Life of 2 Years and Throughput Targets</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Introduce a replaceable maintenance box that can be serviced by customers, reducing downtime and service costs.</t>
+          <t>Optimize for warranty life of 2 years and throughput of 25/20 ppm (PDL).</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>SMBs lack IT support; customer replaceability lowers maintenance barriers and improves uptime.</t>
+          <t>Meets customer and competitive expectations for product performance.</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>End Users, Product Management, Sales</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Design, validation, and manufacturing.</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Product passes 2-year warranty and throughput validation tests.</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Serviceability (Maintenance Box)</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Optimize for serviceability with a maintenance box solution.</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Reduces downtime and service costs for customers.</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>['Quality', 'Supplies Quality', 'Prod Steward', 'BA']</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Maintenance box design, warranty/service policies</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Maintenance box is user-replaceable, instructions provided, and successful replacement validated in user testing.</t>
-        </is>
-      </c>
-      <c r="I50" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr"/>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Keyed Ink Bottles</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Use keyed bottles for ink refilling to prevent errors and ensure correct usage.</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Minimize user errors and support ease of maintenance for SMBs with limited IT expertise.</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>['Supplies Quality', 'Prod Steward', 'Quality']</t>
+          <t>Service, End Users, Product Management</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Ink bottle design, compatibility with printer</t>
+          <t>Maintenance box design and documentation.</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Ink bottles are keyed, tested for error prevention, and validated by customer feedback.</t>
+          <t>Maintenance box is user or service-replaceable and passes serviceability tests.</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.87</v>
+        <v>0.85</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>6</t>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr"/>
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Non-PDL SKU with SMB Solutions</t>
+          <t>Host 12K-CMYK and Trade Page 6K Flexibility</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Offer a Non-PDL SKU that supports SMB2.0 Solutions and Advanced View SMB portal, including PaaS support.</t>
+          <t>Allow flexibility in supporting host 12K-CMYK and trade page 6K yields as lower-priority/flexible requirements.</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Provide tailored solutions for SMBs needing advanced manageability and platform-as-a-service options.</t>
+          <t>Provides adaptability for future market or SKU changes.</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>['Marketing', 'GXD', 'R&amp;D Telemetry', 'BA']</t>
+          <t>Product Management, R&amp;D, Sales</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Portal development, PaaS integration</t>
+          <t>Ink system and firmware flexibility.</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Non-PDL SKU released with SMB solutions and portal integration; PaaS support validated.</t>
+          <t>System can be configured for these yields if required.</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.89</v>
+        <v>0.7</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr"/>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>PDL SKU Performance</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Provide a PDL SKU with improved speed (25/20 min) and support for PDL/PS and Blue Angel certification.</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Address performance needs for SMBs and ensure compliance with environmental standards.</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>['Marketing', 'GXD', 'Tech Reg', 'Quality']</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Printer speed optimization, Blue Angel compliance</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>PDL SKU meets speed targets and passes Blue Angel certification.</t>
-        </is>
-      </c>
-      <c r="I53" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr"/>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Sustainability – 60% Recycled Content Plastic (RCP)</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Design printer with at least 60% recycled content plastic, exceeding competitor standards (Epson 30%).</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>SMBs value sustainability; higher RCP differentiates HP and supports environmental goals.</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>['Prod Steward', 'Quality', 'Marketing']</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Material sourcing, manufacturing process</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Printer contains 60% RCP, validated by third-party certification.</t>
-        </is>
-      </c>
-      <c r="I54" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 11</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr"/>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Mobile Printing via HP App</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Enable mobile printing functionality through the HP App for SMB users.</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Office managers and generalist IT need easy, mobile access to printing solutions.</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>['Marketing', 'GXD', 'R&amp;D Telemetry']</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>HP App integration, printer connectivity</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Mobile printing is enabled, tested across major mobile platforms, and validated by user feedback.</t>
-        </is>
-      </c>
-      <c r="I55" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 9</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr"/>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Warranty – 80k pages or 2 years</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Provide warranty coverage for 80,000 pages or 2 years, whichever comes first.</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>SMBs require predictable maintenance and support; clear warranty terms increase purchase confidence.</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>['Quality', 'Prod Steward', 'BA']</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Service policies, maintenance tracking</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Warranty terms documented, tracked, and honored for all eligible printers.</t>
-        </is>
-      </c>
-      <c r="I56" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr"/>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Serviceability – PHA and MINK</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ensure serviceability with PHA (customer replaceable) and MINK at service center for out-of-warranty cases.</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Reduce downtime and service costs for SMBs with minimal IT resources.</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>['Quality', 'Supplies Quality', 'Prod Steward']</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>Service center setup, replacement parts availability</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>PHA and MINK service options available, validated through customer and service center feedback.</t>
-        </is>
-      </c>
-      <c r="I57" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 4</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr"/>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Telemetry Requirements</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Implement telemetry features for device monitoring, usage analytics, and remote support.</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>Enable proactive support and device management for SMBs, improving reliability and user experience.</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>['R&amp;D Telemetry', 'BA', 'Quality']</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>Telemetry software, portal integration</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Telemetry features implemented, data validated, and remote support enabled.</t>
-        </is>
-      </c>
-      <c r="I58" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 12</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr"/>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Advanced Scan Workflow</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Integrate advanced scan workflow features powered by AI, targeting SMB needs for efficient document handling.</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>SMBs need efficient, automated scan workflows to reduce manual tasks and improve productivity.</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>['Marketing', 'GXD', 'R&amp;D Telemetry', 'BA']</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>AI software, scan hardware integration</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Advanced scan workflow available, tested for efficiency, and validated by user feedback.</t>
-        </is>
-      </c>
-      <c r="I59" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 4, 7, 11</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr"/>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Solutions Monetization</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Develop mechanisms for monetizing solutions and services offered with Magellan over the next 3-5 years.</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>Drive revenue growth and support ongoing innovation for SMB solutions.</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>['Marketing', 'BA']</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>Portal, AI solutions, PaaS integration</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Monetization features implemented and revenue tracked over 3-5 years.</t>
-        </is>
-      </c>
-      <c r="I60" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 9</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>15</t>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
     </row>

--- a/consolidation/outputs/consolidated_requirements.xlsx
+++ b/consolidation/outputs/consolidated_requirements.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J52"/>
+  <dimension ref="A1:J59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,12 +481,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Develop and launch HP's first business-focused ink tank printer designed for SMBs, providing cost-efficient color printing and high performance.</t>
+          <t>Develop and launch HP's first business ink tank printer specifically targeted at unmanaged and lightly managed SMBs (5-250 employees, 6-15 printers, AMPV ~500 pages).</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Addresses a market gap in the CISS PLE Hi segment and reinforces HP's leadership in SMB printing solutions.</t>
+          <t>Addresses a gap in HP's portfolio (CISS PLE segment) and meets evolving customer needs for ROI, efficiency, and cost-effective printing.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -501,12 +501,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>['Strategic intent to protect SMB segment', 'CISS PLE Hi market gap']</t>
+          <t>Must align with SMB2.0 Solutions and Advanced View SMB portal; warranty and serviceability requirements.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Product launched and available for SMB segment with ink tank technology, validated as HP’s first business ink tank printer.</t>
+          <t>Product is launched and available for SMB customers; achieves targeted monthly sales run rate (20-30K units); receives positive feedback from target segment.</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -514,7 +514,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 6, Page 7, Page 12</t>
+          <t>Magellan MRD, Page 4, 6, 7, 11, 12</t>
         </is>
       </c>
     </row>
@@ -526,17 +526,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AI Productivity and Manageability Solutions</t>
+          <t>AI Productivity, Scan Workflow &amp; Manageability Solutions</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Integrate advanced AI features for print, scan, and workflow management to enhance productivity and device manageability for SMBs.</t>
+          <t>Integrate advanced AI-driven productivity, scan workflow, and manageability features to make managing SMB business printing easier.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SMBs require efficient solutions with minimal IT support; AI features differentiate HP from competitors and address customer pain points.</t>
+          <t>Differentiates HP from competitors, addresses key pain points for non-IT SMB decision makers, and supports solutions enhancement with AI.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -546,25 +546,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>['Marketing', 'GXD', 'Quality', 'R&amp;D Telemetry']</t>
+          <t>['Marketing', 'GXD', 'Quality', 'R&amp;D Telemetry', 'DVAR', 'BA']</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>['SMB portal development', 'Device management features']</t>
+          <t>Requires consolidated SMB portal; must support PaaS and device management features.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>AI-powered print, scan, and workflow management features implemented and validated in product user testing.</t>
+          <t>AI features implemented for print, scan, and support; validated through user testing; measurable improvement in productivity and manageability.</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.92</v>
+        <v>0.9</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, Page 7, Page 10, Page 11</t>
+          <t>Magellan MRD, Page 4, 7, 10, 11</t>
         </is>
       </c>
     </row>
@@ -576,17 +576,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SMB Device Management Portal</t>
+          <t>Lowest Business TCO with Minimal Intervention</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Develop a consolidated portal for SMBs to manage multiple printers, targeting unmanaged and lightly managed SMB environments.</t>
+          <t>Design the printer to deliver HP's lowest business total cost of ownership (TCO) with minimal user intervention required.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SMBs often lack dedicated IT teams; a centralized portal simplifies device management and reduces operational overhead.</t>
+          <t>Key purchase driver for SMBs seeking ROI and efficiency; competitive advantage over alternatives.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -596,25 +596,25 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>['Marketing', 'GXD', 'R&amp;D Telemetry']</t>
+          <t>['Marketing', 'Quality', 'Supplies Quality', 'Prod Steward']</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>['AI solutions', 'Portal integration with device telemetry']</t>
+          <t>Must support keyed bottles, maintenance-free claims, and sustainability requirements.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Portal available for SMBs, supports management of multiple printers, validated through usability testing.</t>
+          <t>TCO calculations show HP is lowest among competitors; minimal maintenance demonstrated in field trials; user feedback confirms ease of use.</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.91</v>
+        <v>0.85</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 7, Page 10</t>
+          <t>Magellan MRD, Page 4, 11</t>
         </is>
       </c>
     </row>
@@ -626,17 +626,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Lowest Business TCO (Total Cost of Ownership)</t>
+          <t>Serviceability: Customer Replaceable Parts</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Deliver HP’s lowest business TCO for SMB tank printers, including minimal intervention and optimized supply usage.</t>
+          <t>Printer must be designed for easy serviceability, with key components (PHA, maintenance box) being customer replaceable if out of warranty, and MINK replaceable at service centers.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Cost efficiency is a key buying factor for SMBs and differentiates HP from competitors.</t>
+          <t>Reduces downtime and service costs for SMBs without IT teams; supports post-purchase support and repurpose stages.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -646,17 +646,17 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>['Marketing', 'Quality', 'Supplies Quality']</t>
+          <t>['Quality', 'R&amp;D Telemetry', 'Supplies Quality', 'Prod Steward']</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>['Ink tank technology', 'Keyed bottles', 'Sustainability targets']</t>
+          <t>Warranty policy (80k pages or 2 years); maintenance-free design investigation.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Product demonstrates lowest TCO in independent benchmarking versus competitors; minimal intervention required as documented.</t>
+          <t>Serviceability features validated in design and user testing; parts are replaceable by customers as specified; meets warranty and service center requirements.</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -664,7 +664,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, Page 11</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
     </row>
@@ -676,17 +676,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Maintenance-Free or Reduced Maintenance Design</t>
+          <t>Keyed Bottles for Ink Supply</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Engineer the printer for maintenance-free or reduced maintenance operation, minimizing parts replacement over product lifetime.</t>
+          <t>Integrate keyed bottles to prevent incorrect ink filling and ensure ease of use for SMB customers.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>SMBs value reliability and minimal maintenance due to lack of IT resources; this reduces downtime and operational costs.</t>
+          <t>Improves user experience and reduces errors for non-IT trained office managers; supports sustainability and supplies quality.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -696,17 +696,17 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>['Quality', 'R&amp;D Telemetry', 'Supplies Quality']</t>
+          <t>['Supplies Quality', 'Quality', 'Prod Steward']</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>['Replaceable maintenance box', 'Serviceability features']</t>
+          <t>Must align with maintenance-free and sustainability goals.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Maintenance cycles are reduced compared to competitors; validated through lab testing and customer pilots.</t>
+          <t>Keyed bottles implemented and validated through user testing; error rates reduced compared to previous models.</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -714,7 +714,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, Page 11</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
     </row>
@@ -726,45 +726,45 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Replaceable Maintenance Box</t>
+          <t>SMB Portal for Printer Management</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Include a replaceable maintenance box as a new feature to simplify servicing and extend product life.</t>
+          <t>Develop a consolidated portal for SMBs to manage their printers, including device management, AI solutions, and support.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Enables easier maintenance for SMBs with limited IT support; aligns with the goal of reduced intervention and maintenance.</t>
+          <t>Addresses the needs of unmanaged/lightly managed SMBs; differentiates HP through manageability and AI features.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>['Quality', 'R&amp;D Telemetry', 'Supplies Quality']</t>
+          <t>['Marketing', 'GXD', 'R&amp;D Telemetry', 'DVAR', 'BA']</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>['Maintenance-free design', 'Serviceability requirements']</t>
+          <t>Requires integration with AI solutions and PaaS support.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Maintenance box is user-replaceable and documented; validated via service center and customer feedback.</t>
+          <t>Portal operational and accessible for SMB customers; device management, AI, and support features available; user adoption metrics achieved.</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan MRD, Page 7, 10</t>
         </is>
       </c>
     </row>
@@ -776,17 +776,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Keyed Bottles for Ink Refilling</t>
+          <t>Support for PaaS (Printer-as-a-Service)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Implement keyed bottles for ink refilling to prevent errors and ensure compatibility.</t>
+          <t>Ensure the printer supports Printer-as-a-Service (PaaS) models, including necessary telemetry and portal integration.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Reduces risk of incorrect refilling, supports sustainability, and improves user experience for SMBs.</t>
+          <t>Supports HP’s strategic goal for PaaS acceleration and coverage; enables new business models and recurring revenue.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -796,25 +796,25 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>['Supplies Quality', 'Quality']</t>
+          <t>['Marketing', 'R&amp;D Telemetry', 'DVAR', 'BA']</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>['Ink tank technology', 'Supply chain']</t>
+          <t>Requires telemetry requirements and portal integration.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Keyed bottles provided for all ink refills; error rate in refilling reduced in usability testing.</t>
+          <t>Printer is compatible with PaaS offerings; telemetry and portal features validated; business models enabled.</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan MRD, Page 4, 6, 10</t>
         </is>
       </c>
     </row>
@@ -826,41 +826,41 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Warranty and Serviceability</t>
+          <t>PDL/PS Support and Speed Improvement</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Provide warranty coverage of 80,000 pages or 2 years (whichever is first), with customer replaceable parts and service center support (PHA and MINK thresholds).</t>
+          <t>For PDL SKU, ensure support for PDL/PS and improve speed to 25/20 min (current 25/19).</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>SMBs require reliable service options due to limited IT resources; warranty and serviceability are critical buying factors.</t>
+          <t>Competitive positioning for medium and enterprise segments; addresses performance needs for SMBs.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>['Quality', 'Prod Steward']</t>
+          <t>['Marketing', 'Quality', 'R&amp;D Telemetry']</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>['Replaceable maintenance box', 'Service center process']</t>
+          <t>Must align with Blue Angel certification and hardware specs.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Warranty terms implemented; customer replaceable parts available; service center process validated.</t>
+          <t>PDL/PS support implemented; speed improvement validated through testing; meets performance targets.</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.93</v>
+        <v>0.8</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -876,45 +876,45 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Sustainability – 60% RCP (Recycled Content Percentage)</t>
+          <t>Blue Angel Certification</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Design printer with at least 60% recycled content, exceeding competitor benchmarks (Epson 30%, Canon TBC).</t>
+          <t>Ensure printer meets Blue Angel environmental certification requirements.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Sustainability is a differentiator and increasingly important for SMBs; supports HP’s environmental goals.</t>
+          <t>Supports sustainability claims and competitive differentiation; important for global markets.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>['Prod Steward', 'Marketing']</t>
+          <t>['Tech Reg', 'Prod Steward', 'Quality']</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>['Supply chain sourcing', 'Design engineering']</t>
+          <t>Must align with sustainability and hardware requirements.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Printer contains at least 60% recycled content; validated through supplier and manufacturing audits.</t>
+          <t>Blue Angel certification achieved; documentation available.</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 11</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
     </row>
@@ -926,45 +926,45 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Mobile Printing via HP App</t>
+          <t>Maintenance-Free or Reduced Maintenance Design</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Enable mobile printing capabilities through the HP App for SMB users.</t>
+          <t>Design printer to be maintenance-free or require less maintenance (fewer parts to replace over life).</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Mobile printing is a core use case for SMBs and supports flexible work environments.</t>
+          <t>Minimizes intervention for SMBs; increases reliability and customer satisfaction.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>['Marketing', 'GXD']</t>
+          <t>['Quality', 'Supplies Quality', 'Prod Steward']</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>['HP App integration']</t>
+          <t>Under investigation; must align with serviceability and sustainability requirements.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Mobile printing feature available and validated in user acceptance testing.</t>
+          <t>Maintenance-free or reduced maintenance features validated; user feedback confirms reduced intervention.</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.89</v>
+        <v>0.75</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 9</t>
+          <t>Magellan MRD, Page 11</t>
         </is>
       </c>
     </row>
@@ -976,45 +976,45 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Support for PaaS (Printing as a Service)</t>
+          <t>Sustainability: 60% RCP (Recycled Content Plastic)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ensure the printer supports Printing as a Service (PaaS) models, including SMB2.0 Solutions and Advanced View SMB portal.</t>
+          <t>Ensure printer uses at least 60% recycled content plastic (RCP), exceeding competitors (Epson 30%, Canon TBC).</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>PaaS offers flexible, scalable printing solutions for SMBs and aligns with HP’s strategic goals.</t>
+          <t>Supports HP’s sustainability goals and provides a competitive advantage.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>['DVAR', 'Tech Reg', 'Marketing']</t>
+          <t>['Prod Steward', 'Tech Reg', 'Marketing']</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>['SMB portal', 'Device management']</t>
+          <t>Must align with Blue Angel certification and supplies requirements.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Printer supports PaaS features and is validated in enterprise deployment scenarios.</t>
+          <t>Material sourcing validated; sustainability claims substantiated; 60% RCP usage documented.</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.87</v>
+        <v>0.9</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, Page 10</t>
+          <t>Magellan MRD, Page 11</t>
         </is>
       </c>
     </row>
@@ -1026,17 +1026,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PDL SKU Performance and Compatibility</t>
+          <t>Advanced Telemetry Requirements</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Provide a PDL SKU with improved speed (25/20 min), PDL/PS support, and Blue Angel certification.</t>
+          <t>Integrate telemetry features to support device management, PaaS, and post-purchase support.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Performance and compatibility are critical for SMBs with diverse printing needs; Blue Angel certification supports sustainability.</t>
+          <t>Enables remote management, analytics, and support for SMBs; supports HP’s strategic goals.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1046,25 +1046,25 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>['Quality', 'Tech Reg']</t>
+          <t>['R&amp;D Telemetry', 'DVAR', 'BA']</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>['Speed improvement', 'PDL/PS support', 'Certification process']</t>
+          <t>Requires portal and PaaS integration; must meet privacy and compliance standards.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>PDL SKU meets performance targets and passes Blue Angel certification.</t>
+          <t>Telemetry features implemented and validated; data privacy and compliance requirements met.</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan MRD, Page 12</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Telemetry Requirements</t>
+          <t>Mobile Printing via HP App</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Implement telemetry features for device monitoring, usage tracking, and predictive maintenance.</t>
+          <t>Support mobile printing through the HP App for ease of use and accessibility.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Telemetry enables proactive support, analytics, and improved device management for SMBs.</t>
+          <t>Meets customer expectations for modern office solutions; increases usability for SMBs.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1096,25 +1096,25 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>['R&amp;D Telemetry', 'BA']</t>
+          <t>['Marketing', 'GXD', 'BA']</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>['Portal integration', 'Device firmware']</t>
+          <t>Must integrate with SMB portal and device management.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Telemetry features implemented and validated in portal and device analytics.</t>
+          <t>Mobile printing feature operational; user feedback confirms ease of use.</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 12</t>
+          <t>Magellan MRD, Page 10</t>
         </is>
       </c>
     </row>
@@ -1126,45 +1126,45 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Perfect Print and Perfect Scan Solutions</t>
+          <t>Solutions Monetization</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Deliver advanced print and scan quality solutions enabled by AI, targeting SMB needs for accuracy and efficiency.</t>
+          <t>Enable monetization of solutions (AI, portal, services) as part of the printer offering.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>High-quality print and scan are top priorities for SMBs; AI solutions differentiate HP from competitors.</t>
+          <t>Supports HP’s strategic goal for profitable growth and new revenue streams.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>['Marketing', 'Quality', 'GXD']</t>
+          <t>['Marketing', 'BA', 'DVAR']</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>['AI solutions', 'Device firmware']</t>
+          <t>Requires portal and AI solutions integration; must comply with business models.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Perfect Print and Perfect Scan features implemented and validated in product testing.</t>
+          <t>Monetization features implemented; revenue targets achieved; business model validated.</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.92</v>
+        <v>0.75</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 7, Page 11</t>
+          <t>Magellan MRD, Page 9, 10</t>
         </is>
       </c>
     </row>
@@ -1176,45 +1176,45 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Consolidated Solutions/Services Offering</t>
+          <t>Consolidated Device Management Experience</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bundle solutions and services (including AI, device management, PaaS, mobile printing) to add value to hardware.</t>
+          <t>Provide a consolidated device management experience for SMBs, integrating AI, support, and telemetry.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Integrated solutions increase customer value and support HP’s strategic goals for SMB market leadership.</t>
+          <t>Differentiates HP from competitors; addresses key SMB pain points around manageability and support.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>['Marketing', 'DVAR', 'BA']</t>
+          <t>['Marketing', 'GXD', 'R&amp;D Telemetry', 'DVAR']</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>['Portal', 'AI solutions', 'PaaS support']</t>
+          <t>Requires portal, AI, and telemetry integration.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Solutions/services bundle available and validated in customer pilots and market launch.</t>
+          <t>Device management features validated; user adoption metrics achieved; positive feedback from SMBs.</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 10, Page 11</t>
+          <t>Magellan MRD, Page 10, 11</t>
         </is>
       </c>
     </row>
@@ -1231,12 +1231,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Develop new NGB keyed ink bottles with 6,000 page yield for black and 6,000 for CMY; CMY bottles must support sizes &gt;8,000 pages.</t>
+          <t>Develop and integrate NGB keyed ink bottles capable of 6K Black and 6K CMY page yield. CMY bottle size must be greater than 8K.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Supports high-volume printing and competitive positioning in SMB/Enterprise CISS segments.</t>
+          <t>High-yield bottles reduce frequency of replacement and operational cost, meeting market demand for efficiency and competitive positioning.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1246,17 +1246,17 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Management, SMB/Enterprise Customers</t>
+          <t>R&amp;D, Product Management, End Users</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Requires compatibility with NOA-F, IDS, PHA, and Magi/Nessie ink systems.</t>
+          <t>Ink system compatibility, bottle design, IDS, and tank size changes.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Bottles are available in required sizes, pass reliability and spill-free tests, and deliver specified yields in field tests.</t>
+          <t>Printer supports 6K Black and 6K CMY page yield with new keyed bottles; CMY bottle size &gt;8K verified in test prints.</t>
         </is>
       </c>
       <c r="I17" t="n">
@@ -1281,12 +1281,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ensure new NGB bottles deliver spill-free reliability during user handling and refilling.</t>
+          <t>Ensure the new ink bottle design provides spill-free reliability during installation and replacement.</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Critical for customer satisfaction and reducing service incidents.</t>
+          <t>Critical for user safety, product quality, and environmental compliance.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1296,21 +1296,21 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>End Users, Support, Product Quality</t>
+          <t>R&amp;D, Quality Assurance, End Users</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dependent on bottle and NOA-F design.</t>
+          <t>Bottle and tank interface design, IDS integration.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Field and lab tests confirm zero spills during normal use.</t>
+          <t>No ink spill incidents in 99% of test installations and replacements.</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1331,12 +1331,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Implement NOA-F with a metal foiled labyrinth and lid label, maintaining compatibility with existing push-push and TDF mechanisms.</t>
+          <t>Implement NOA-F with a metal foiled labyrinth and lid label; maintain existing push-push and TDF mechanisms.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Enhances reliability and security of ink delivery system.</t>
+          <t>Enhances reliability and security of ink delivery and prevents tampering.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1346,17 +1346,17 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Management, Factory Operations</t>
+          <t>R&amp;D, Factory, Service</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Integration with existing hardware and bottle designs.</t>
+          <t>NOA-F design, manufacturing process updates.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>NOA-F units pass all reliability and integration tests with new and legacy components.</t>
+          <t>NOA-F passes security, reliability, and compatibility tests with existing mechanisms.</t>
         </is>
       </c>
       <c r="I19" t="n">
@@ -1376,17 +1376,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Reuse Superamp Si PHA and Magi/Nessie Ink</t>
+          <t>Reuse SuperAmp Si PHA and Magi/Nessie Ink</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Reuse Superamp Si PHA and Magi/Nessie ink without reformulation in the Magellan printer.</t>
+          <t>Leverage existing SuperAmp Si PHA and Magi/Nessie pigment ink without reformulation for the new platform.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Reduces R&amp;D and validation costs, leverages proven components.</t>
+          <t>Reduces R&amp;D costs, expedites time to market, and maintains proven quality.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1396,17 +1396,17 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>R&amp;D, Supply Chain, Product Management</t>
+          <t>R&amp;D, Product Management, Supply Chain</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ensures compatibility with new bottle and NOA-F systems.</t>
+          <t>Compatibility with new system, IDS, and bottle design.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>System passes all print quality, reliability, and regulatory tests with reused components.</t>
+          <t>Existing SuperAmp Si PHA and Magi/Nessie ink function reliably in Magellan system without reformulation.</t>
         </is>
       </c>
       <c r="I20" t="n">
@@ -1426,17 +1426,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ink Stability and IDS Characterization</t>
+          <t>Ink System Reliability and Modelling</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Model and validate ink stability, WVTR, air gain, flow rate, and IDS performance, including startup and NOA-F end-of-life scenarios.</t>
+          <t>Model and characterize reliability, WVTR, air gain, flow rate, and IDS performance, including startup and NOA-F EOL.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Ensures consistent print quality and long-term reliability.</t>
+          <t>Ensures system robustness, print quality, and long-term reliability.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1446,21 +1446,21 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Quality, Service</t>
+          <t>R&amp;D, Quality Assurance</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dependent on ink, IDS, and NOA-F design.</t>
+          <t>IDS, NOA-F, ink system design.</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>All models and tests meet or exceed defined HP quality standards for stability and reliability.</t>
+          <t>Reliability and IDS models validated, system meets defined performance thresholds.</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1476,41 +1476,41 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>NOA-F as Service Parts for Warranty Support</t>
+          <t>Ink Stability Modelling</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Provide NOA-F as service parts to support warranty obligations and field repairs.</t>
+          <t>Perform ink stability modelling for the tank and assess impact on print quality (PQ).</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Improves serviceability and reduces downtime for customers.</t>
+          <t>Prevents ink degradation, ensures consistent print quality, and reduces service incidents.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Service, End Customers, Warranty Team</t>
+          <t>R&amp;D, Quality Assurance</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Requires supply chain and part number integration.</t>
+          <t>Ink/tank compatibility, environmental testing.</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>NOA-F is available as a service part, with documented replacement procedure and inventory in place.</t>
+          <t>Ink stability model created; no significant PQ degradation observed in accelerated aging tests.</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1526,41 +1526,41 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Acumen 6 on Lid</t>
+          <t>NOA-F as Service Part in Warranty</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Implement Acumen 6 feature on the ink lid.</t>
+          <t>NOA-F must be available as a service part for in-warranty support.</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Supports traceability and anti-counterfeit measures.</t>
+          <t>Improves serviceability and customer satisfaction by enabling quick replacement.</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Security, Product Management, End Users</t>
+          <t>Service, Warranty, End Users</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Requires lid design and Acumen 6 integration.</t>
+          <t>NOA-F inventory, service logistics.</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>All lids include Acumen 6 and pass traceability validation.</t>
+          <t>NOA-F listed as a service part and available for warranty claims.</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1576,17 +1576,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Factory Line Modifications for NOA-F and Ink Cart</t>
+          <t>Acumen 6 on Lid</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Modify SA14 factory line for NOA-F; add Magi ink cart and labeling tool in Orcus 5 line.</t>
+          <t>Integrate Acumen 6 (security/traceability feature) on the ink bottle lid.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Ensures manufacturing readiness for new components.</t>
+          <t>Enhances product traceability and anti-counterfeiting measures.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1596,17 +1596,17 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Manufacturing, Operations, R&amp;D</t>
+          <t>Security, R&amp;D, Supply Chain</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dependent on final NOA-F, ink cart, and labeling tool specifications.</t>
+          <t>Lid design, Acumen 6 compatibility.</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Factory lines are modified, validated, and achieve target production rates for new SKUs.</t>
+          <t>All bottle lids include Acumen 6 and pass traceability validation.</t>
         </is>
       </c>
       <c r="I24" t="n">
@@ -1626,17 +1626,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Support Customer-Replaceable PHA and NOA-F</t>
+          <t>Modify Existing Factory Line for NOA-F</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Design PHA and NOA-F to be customer-replaceable for improved serviceability.</t>
+          <t>Update SA14 line to support NOA-F and add Magi ink cart and labelling tool in Orcus 5.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Reduces service costs and downtime, enhances user experience.</t>
+          <t>Factory readiness for new components is essential for production ramp-up.</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1646,17 +1646,17 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>End Users, Service, Product Management</t>
+          <t>Manufacturing, Operations, R&amp;D</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Requires user documentation and design for easy replacement.</t>
+          <t>SA14 line, Orcus 5, tool procurement.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Users can replace PHA and NOA-F with standard tools and instructions; field tests confirm process is user-friendly.</t>
+          <t>Factory lines modified and validated for new components production.</t>
         </is>
       </c>
       <c r="I25" t="n">
@@ -1676,17 +1676,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Warranty Page Life Goal of 80k Pages</t>
+          <t>New Keyed Caps Molding</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Design printer and key components to support a new warranty page life goal of 80,000 pages.</t>
+          <t>Create molds for 1 to 4 new keyed bottle caps to support new bottle design.</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Meets competitive and contractual requirements for durability.</t>
+          <t>Supports anti-misuse and product differentiation in the market.</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1696,21 +1696,21 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Product Management, Warranty Team, End Users</t>
+          <t>Manufacturing, R&amp;D</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Requires robust design of paperpath, ink system, and service parts.</t>
+          <t>Bottle and cap design finalization.</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Printers pass accelerated life tests for 80,000 pages under warranty conditions.</t>
+          <t>Molds produced and first article inspection passed for all new cap designs.</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -1726,41 +1726,41 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SKU 2 (Hi + Hi PDL) PaaS Offering</t>
+          <t>Support Customer Replaceable PHA and NOA-F</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Develop SKU 2 with high and high PDL configurations for Printer-as-a-Service (PaaS) business model.</t>
+          <t>Design system for customer-replaceable PHA and NOA-F components.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Supports new business models and customer segments.</t>
+          <t>Improves user experience, reduces downtime, and service costs.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Product Management, Sales, SMB/Enterprise Customers</t>
+          <t>End Users, Service, Product Management</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Requires configuration management and service integration.</t>
+          <t>PHA and NOA-F module design, user documentation.</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>SKU 2 is available for PaaS, with defined service and support packages.</t>
+          <t>Users can replace PHA and NOA-F without technical assistance; validated in usability tests.</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -1776,17 +1776,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Reddington ID with Increased Tank Size</t>
+          <t>Warranty Page Life Goal of 80K Pages</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Increase tank size for Reddington ID without changing Marconi-HI ADF; update input/output trays to align with tank protrusion.</t>
+          <t>Printer must support a new warranty page life goal of 80,000 pages.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Supports higher ink capacity and page yield.</t>
+          <t>Addresses market need for durable, high-volume printing, and competitive warranty offering.</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1796,21 +1796,21 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Product Design, R&amp;D, End Users</t>
+          <t>Product Management, End Users, Service</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Requires mechanical design changes and tray integration.</t>
+          <t>Component reliability, service parts, QA testing.</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Tank size increased, trays fit and function correctly, and printer passes fit/form/function tests.</t>
+          <t>Printer passes 80,000 page life tests without critical failure.</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -1826,41 +1826,41 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>EPS Foam Packaging</t>
+          <t>SKU 2 (Hi + Hi PDL) PaaS Support</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Use EPS foam for packaging to protect the printer during shipment.</t>
+          <t>Develop SKU 2 with high throughput and PDL (Page Description Language) support for PaaS (Print as a Service) model.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Reduces shipping damage and supports sustainability goals if recyclable.</t>
+          <t>Expands market reach with flexible business models and high-performance features.</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Logistics, Product Management, End Users</t>
+          <t>Product Management, Sales, Service Providers</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Packaging design and supplier selection.</t>
+          <t>PDL integration, SKU definition, platform readiness.</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>All shipments use EPS foam packaging, with damage rates below target threshold.</t>
+          <t>SKU 2 available with PDL and PaaS features, validated in market pilots.</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -1876,17 +1876,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>EPEAT3, LOT4, and Blue Angel Compliance</t>
+          <t>Reddington ID with Increased Tank Size</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ensure product meets EPEAT3, LOT4, and Blue Angel (for PDL SKU) environmental requirements.</t>
+          <t>Adopt Reddington ID with increased tank size; no change to Marconi-HI ADF.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Enables sales in regulated markets and supports HP sustainability goals.</t>
+          <t>Supports higher page yield and aligns with new bottle sizes.</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1896,21 +1896,21 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Regulatory, Product Management, Sales</t>
+          <t>R&amp;D, Product Management, Manufacturing</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Requires documentation, testing, and certification.</t>
+          <t>Tank design, platform integration, ADF compatibility.</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Product is certified for EPEAT3, LOT4, and Blue Angel as applicable.</t>
+          <t>Tank size increased, system passes yield and fitment tests.</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -1926,17 +1926,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Size Optimization and 4.3” CGD Display</t>
+          <t>EPS Foam Packaging</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Optimize printer size and integrate a 4.3-inch CGD display.</t>
+          <t>Implement EPS foam packaging for the new product.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Improves usability and fits market requirements for compact, feature-rich printers.</t>
+          <t>Improves shipping robustness and reduces transit damage.</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1946,17 +1946,17 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Product Design, End Users, Marketing</t>
+          <t>Logistics, Manufacturing, End Users</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Mechanical and electrical integration of display.</t>
+          <t>Packaging design, supplier selection.</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Printer meets size targets and display passes usability and reliability tests.</t>
+          <t>EPS foam packaging passes drop and vibration tests.</t>
         </is>
       </c>
       <c r="I31" t="n">
@@ -1976,17 +1976,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>New Tube Routing and Integration</t>
+          <t>Compliance with EPEAT3, LOT4, and Blue Angel (for PDL SKU)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Leverage Sayan Sibstar tubes and implement new tube routing and integration for 4-tube platform.</t>
+          <t>Ensure the product meets EPEAT3, LOT4, and Blue Angel environmental and safety standards for PDL SKU.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Supports increased ink flow and reliability for higher page yields.</t>
+          <t>Required for regulatory compliance and market access in specific regions.</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1996,21 +1996,21 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing, Product Quality</t>
+          <t>Regulatory, Product Management, QA</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tube design, IDS, and carriage integration.</t>
+          <t>Design, materials, QA certification.</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Tube routing supports target flow rates and reliability in system tests.</t>
+          <t>Product certified for EPEAT3, LOT4, Blue Angel (PDL SKU).</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -2026,41 +2026,41 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Service Station Aerosol Management</t>
+          <t>Input and Output Tray Modifications</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Update service station aerosol management with spit platform changes due to tank modifications.</t>
+          <t>Modify input and output trays to accommodate tank protrusion and optimize size.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Ensures clean operation and prevents contamination from increased ink handling.</t>
+          <t>Ensures mechanical compatibility and user convenience with new tank design.</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>R&amp;D, Service, Product Quality</t>
+          <t>R&amp;D, Manufacturing, End Users</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Service station and tank design changes.</t>
+          <t>Tank and tray design updates.</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Aerosol management meets HP cleanliness and reliability standards in testing.</t>
+          <t>Trays function without interference and pass usability tests with new tank.</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -2076,41 +2076,41 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Carriage Dynamic and Force Model Update</t>
+          <t>4.3” CGD Display</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Update carriage dynamic and force models to account for new tube routing and increased weights.</t>
+          <t>Integrate a 4.3-inch CGD (Color Graphic Display) into the product.</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Maintains print quality and reliability with new mechanical configuration.</t>
+          <t>Enhances user interface and accessibility for advanced features.</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Quality, Manufacturing</t>
+          <t>Product Management, End Users</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tube, carriage, and weight changes.</t>
+          <t>Display sourcing, UI development.</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Carriage system passes dynamic and force validation tests.</t>
+          <t>4.3” CGD display operational and passes UI usability tests.</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -2126,17 +2126,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Paperpath Durability for Increased Page Life</t>
+          <t>Platform with 4 Sayan Sibstar Tubes and New Routing</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Enhance paperpath to support increased page life target of 80,000 pages.</t>
+          <t>Leverage Sayan Sibstar tubes with new routing and integration into the platform.</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Critical to meet new warranty and reliability goals.</t>
+          <t>Supports efficient ink delivery and system reliability.</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2146,21 +2146,21 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Product Quality, R&amp;D, End Users</t>
+          <t>R&amp;D, Manufacturing</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Material and design upgrades to paperpath components.</t>
+          <t>Tube design, routing validation.</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Paperpath passes accelerated life testing for 80,000 pages.</t>
+          <t>System operates reliably with 4 tubes and new routing; passes flow and stress tests.</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -2176,17 +2176,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Ink Maintenance Serviceable Part (Post 80k Life)</t>
+          <t>Service Station Aerosol Management</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Design ink maintenance as a serviceable part for replacement after 80,000 pages by service centers.</t>
+          <t>Update service station for improved aerosol management with spit platform changes due to the tank.</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Supports extended product life and reduces total cost of ownership.</t>
+          <t>Reduces service issues and maintains print quality in high-yield systems.</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Service, End Users, Warranty Team</t>
+          <t>R&amp;D, Service, QA</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Service procedures and part availability.</t>
+          <t>Service station and tank design updates.</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Service centers can replace ink maintenance part per documented procedure.</t>
+          <t>Aerosol levels within safe limits in service station tests.</t>
         </is>
       </c>
       <c r="I36" t="n">
@@ -2226,17 +2226,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>140ml K Bottles and New CMY Bottle Sizes</t>
+          <t>Carriage Dynamic and Force Model Update</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Introduce new 140ml black (K) bottles and appropriately sized CMY bottles for Magellan.</t>
+          <t>Update carriage dynamic and force models to account for new tube routing and increased weights.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Supports higher page yield and new tank size.</t>
+          <t>Ensures mechanical reliability and print accuracy with new system configuration.</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2246,17 +2246,17 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Management, Supply Chain</t>
+          <t>R&amp;D, QA</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Bottle design and supply chain readiness.</t>
+          <t>Carriage and tube design, platform integration.</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>New bottles are available, validated, and integrated into supply chain.</t>
+          <t>Carriage system passes force and dynamic tests with new configuration.</t>
         </is>
       </c>
       <c r="I37" t="n">
@@ -2276,17 +2276,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>New IDS Make-Break and FI Connection</t>
+          <t>Paper Path for Increased Page Life</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Develop new make-break and FI (fluid interface) connection for IDS, leveraging LEBI ink-tank with increased size, keying, and LOI, with one SHAID.</t>
+          <t>Design paper path to support increased page life up to 80K pages.</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Ensures reliable ink delivery and system security.</t>
+          <t>Supports new warranty and reliability goals, reduces maintenance.</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2296,21 +2296,21 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Quality, Security</t>
+          <t>R&amp;D, QA, Product Management</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>IDS and ink-tank design updates.</t>
+          <t>Paper path design, component durability.</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>System passes make-break, FI connection, and security validation tests.</t>
+          <t>Paper path operates reliably for 80,000 pages in durability tests.</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -2326,17 +2326,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>New IDS Startup Algorithm and Air Management</t>
+          <t>Ink Maintenance as Serviceable Part Post-80K</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Implement new IDS startup algorithm and air management system.</t>
+          <t>Design ink maintenance as a serviceable part to be replaced post-80K page life at service centers.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Improves startup reliability and print quality.</t>
+          <t>Facilitates long-term support and reduces total cost of ownership.</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2346,17 +2346,17 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Quality, End Users</t>
+          <t>Service, End Users, Product Management</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>IDS hardware and firmware updates.</t>
+          <t>Maintenance module design, service documentation.</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Startup and air management meet defined success rates in system tests.</t>
+          <t>Ink maintenance part is replaceable at service centers and documented in service manuals.</t>
         </is>
       </c>
       <c r="I39" t="n">
@@ -2376,41 +2376,41 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>New Servicing and Startup Algorithm</t>
+          <t>New Make-Break and FI Connection for IDS</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Develop new servicing and startup algorithm for Magellan platform.</t>
+          <t>Develop new make-break and FI (fluidic interface) connection for IDS.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Enhances reliability, minimizes ink waste, and improves customer experience.</t>
+          <t>Ensures reliable ink delivery and system performance.</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Quality, Service</t>
+          <t>R&amp;D, QA, Manufacturing</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Firmware and IDS integration.</t>
+          <t>IDS and connection design.</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Algorithm passes reliability and efficiency benchmarks in system tests.</t>
+          <t>New connections pass reliability and leak tests.</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -2426,17 +2426,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>New Print Quality (PQ) Goals and Depletion Metrics</t>
+          <t>Leverage LEBI Ink-Tank with Increased Size and Keying</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Establish new print quality goals and depletion metrics to align with page yield definitions.</t>
+          <t>Utilize LEBI ink-tank with increased size, new keying, and LOI (line of interface) One SHAID.</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Ensures consistent output and meets customer expectations for page yield.</t>
+          <t>Supports higher yields and prevents cross-use of incorrect bottles.</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2446,17 +2446,17 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Product Quality, R&amp;D, End Users</t>
+          <t>R&amp;D, Product Management, Manufacturing</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Test method definition and validation.</t>
+          <t>Tank and keying design, SHAID integration.</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Product meets or exceeds new PQ and depletion targets in field and lab tests.</t>
+          <t>Ink-tank system passes fitment and anti-misuse tests.</t>
         </is>
       </c>
       <c r="I41" t="n">
@@ -2476,17 +2476,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Reuse of Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU</t>
+          <t>New IDS Startup Algorithm and Air Management</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Reuse Marconi Tux dASIC, Hannibal aASIC, and Raccoon PSU in Magellan platform.</t>
+          <t>Develop new IDS startup algorithm and air management for improved reliability.</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Reduces development time and leverages proven electronics.</t>
+          <t>Reduces startup failures and air entrapment issues in the ink system.</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2496,21 +2496,21 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Management, Supply Chain</t>
+          <t>R&amp;D, QA</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Compatibility with new Magellan features and requirements.</t>
+          <t>IDS, firmware, platform integration.</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>All reused components pass integration and reliability tests in Magellan.</t>
+          <t>Startup success rate &gt;99% in system validation tests.</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -2526,17 +2526,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Stingray Wi-Fi Module and Dune FW Integration</t>
+          <t>New Servicing and Startup Algorithm</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Integrate Stingray Wi-Fi module and Dune firmware (FW) into Magellan.</t>
+          <t>Implement new servicing and startup algorithm for improved maintenance and reliability.</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Provides wireless connectivity and leverages existing firmware platform.</t>
+          <t>Reduces service events and ensures consistent startup performance.</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2546,17 +2546,17 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Management, End Users</t>
+          <t>R&amp;D, Service, QA</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>HW/FW compatibility and regulatory certification.</t>
+          <t>Firmware, IDS, service documentation.</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Wi-Fi and firmware pass all connectivity and functional tests in Magellan.</t>
+          <t>Servicing and startup algorithms validated in field and lab tests.</t>
         </is>
       </c>
       <c r="I43" t="n">
@@ -2576,17 +2576,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Gauss4.xx Security (HW &amp; FW)</t>
+          <t>New Print Quality Goals &amp; Depletion Metrics</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Implement Gauss4.xx hardware and firmware security features in Magellan.</t>
+          <t>Define new print quality (PQ) goals and depletion metrics to meet page yield definition.</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Ensures product security and compliance with HP security standards.</t>
+          <t>Ensures customer expectations for output quality and transparency in yield claims.</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2596,17 +2596,17 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Security, R&amp;D, Product Management</t>
+          <t>Product Management, QA, End Users</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>HW and FW integration with Magellan platform.</t>
+          <t>R&amp;D, QA, IDS, firmware.</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Security features pass HP security validation and external audit.</t>
+          <t>Print quality and depletion metrics documented and met in testing.</t>
         </is>
       </c>
       <c r="I44" t="n">
@@ -2626,17 +2626,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Strategic Segment Protection and Growth</t>
+          <t>Reuse Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Protect Micro/SMB segments, lead with LaserJet and flank with PDL in Medium/Enterprise, and grow CISS share in new segments.</t>
+          <t>Leverage existing Marconi Tux dASIC, Hannibal aASIC, and Raccoon PSU for the new platform.</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Aligns product with HP’s strategic business goals and market positioning.</t>
+          <t>Reduces development cost and accelerates time to market.</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2646,25 +2646,25 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Business Leadership, Product Management, Sales</t>
+          <t>R&amp;D, Product Management, Manufacturing</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Product features and market alignment.</t>
+          <t>Component compatibility, system integration.</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Product launches with targeted features for each segment and achieves growth KPIs.</t>
+          <t>Existing components function reliably in Magellan system.</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
@@ -2676,17 +2676,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Support for Multiple Business Models and Solutions</t>
+          <t>Stingray Wi-Fi Module Integration</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Support Consumer, SMB, and Enterprise business models, including PaaS, WorkFromHome/Flexworker, and onboarding via HPX, HP One, SMB Portal, and ECP paths.</t>
+          <t>Integrate Stingray Wi-Fi module for wireless connectivity.</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Expands addressable market and supports diverse customer needs.</t>
+          <t>Meets market expectations for modern connectivity and remote printing.</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2696,17 +2696,17 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sales, Product Management, End Users</t>
+          <t>End Users, Product Management</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Solution and service integration with platform.</t>
+          <t>Wi-Fi module sourcing, firmware integration.</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Product is compatible with all listed business models and onboarding paths.</t>
+          <t>Wi-Fi module passes connectivity and throughput tests.</t>
         </is>
       </c>
       <c r="I46" t="n">
@@ -2726,17 +2726,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Scan Solution, SMB Manageability, and Enterprise Support</t>
+          <t>Firmware: Dune</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Integrate scan solution, SMB manageability tools, and enterprise support (WJA, HPSM, JAM) into Magellan.</t>
+          <t>Utilize Dune firmware for system operation.</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Meets needs of business customers and supports managed print services.</t>
+          <t>Standardizes firmware across platform and leverages proven codebase.</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2746,17 +2746,17 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>SMB/Enterprise Customers, Product Management, IT Admins</t>
+          <t>R&amp;D, QA, Product Management</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Software and solution integration.</t>
+          <t>Firmware compatibility, feature integration.</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Product passes validation for all listed solutions and tools.</t>
+          <t>Dune firmware operational and passes system validation tests.</t>
         </is>
       </c>
       <c r="I47" t="n">
@@ -2776,17 +2776,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Client and Driver Support</t>
+          <t>Security: Gauss4.xx</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Ensure compatibility with HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD clients and drivers.</t>
+          <t>Integrate Gauss4.xx security for hardware and firmware.</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Enables broad deployment and ease of use in diverse IT environments.</t>
+          <t>Meets security requirements for enterprise and SMB customers.</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2796,17 +2796,17 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>End Users, IT, Product Management</t>
+          <t>Security, R&amp;D, Enterprise Customers</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Firmware and driver integration.</t>
+          <t>HW/FW integration, certification.</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>All listed clients and drivers are supported and pass compatibility tests.</t>
+          <t>Security features validated and pass penetration testing.</t>
         </is>
       </c>
       <c r="I48" t="n">
@@ -2826,17 +2826,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Schedule and SuperAmp PHA Life Constraint</t>
+          <t>Business Model and Solution Support</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Schedule and SuperAmp PHA life at 65K are the least flexible constraints for Magellan.</t>
+          <t>Support Consumer, SMB, and Enterprise business models, including PaaS, WorkFromHome, and Flexworker services.</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Critical path items for project delivery and product reliability.</t>
+          <t>Addresses diverse customer segments and increases market coverage.</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2846,25 +2846,25 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Project Management, R&amp;D, Manufacturing</t>
+          <t>Product Management, Sales, Service Providers</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Project planning and PHA design/life validation.</t>
+          <t>Solution and service integration, SKU differentiation.</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Project milestones and PHA life targets are met as scheduled.</t>
+          <t>All business models supported and validated in market pilots.</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
@@ -2876,17 +2876,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Warranty Life of 2 Years and Throughput Targets</t>
+          <t>Scan Solution Integration</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Optimize for warranty life of 2 years and throughput of 25/20 ppm (PDL).</t>
+          <t>Provide integrated scan solution for all supported business models.</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Meets customer and competitive expectations for product performance.</t>
+          <t>Meets functional requirements for SMB and Enterprise customers.</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2896,25 +2896,25 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>End Users, Product Management, Sales</t>
+          <t>End Users, Product Management, SMB/Enterprise Customers</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Design, validation, and manufacturing.</t>
+          <t>Scanner hardware, firmware integration.</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Product passes 2-year warranty and throughput validation tests.</t>
+          <t>Scan solution operational and passes functional tests.</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
@@ -2926,45 +2926,45 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Serviceability (Maintenance Box)</t>
+          <t>SMB Manageability and Enterprise Support</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Optimize for serviceability with a maintenance box solution.</t>
+          <t>Support SMB manageability and enterprise features, including WJA, HPSM, JAM.</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Reduces downtime and service costs for customers.</t>
+          <t>Critical for IT management in business environments.</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Service, End Users, Product Management</t>
+          <t>SMB/Enterprise Customers, IT, Product Management</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Maintenance box design and documentation.</t>
+          <t>Firmware, software integration.</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Maintenance box is user or service-replaceable and passes serviceability tests.</t>
+          <t>Manageability features validated with WJA, HPSM, JAM.</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
@@ -2976,43 +2976,393 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Host 12K-CMYK and Trade Page 6K Flexibility</t>
+          <t>Clients &amp; Drivers Compatibility</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Allow flexibility in supporting host 12K-CMYK and trade page 6K yields as lower-priority/flexible requirements.</t>
+          <t>Ensure compatibility with HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD clients and drivers.</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Provides adaptability for future market or SKU changes.</t>
+          <t>Enables flexible deployment and broad OS support.</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>End Users, IT, Product Management</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Driver development, platform validation.</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>All listed drivers and clients pass installation and functional tests.</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Schedule Adherence (Constrain)</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Project schedule is least flexible and must be adhered to as a business constraint.</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Critical for time-to-market and competitive positioning.</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Product Management, Program Management</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>All project deliverables and milestones.</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Project milestones met as per defined schedule.</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>SuperAmp PHA Life at 65K (Constrain)</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>SuperAmp PHA must achieve a minimum lifetime of 65,000 pages.</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Ensures reliability and reduces service costs within warranty period.</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>R&amp;D, QA, Service</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>PHA design, QA testing.</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>SuperAmp PHA passes 65,000-page life tests.</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Warranty Life of 2 Years (Optimize)</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Printer must support a warranty life of 2 years for all critical components.</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Meets market expectations and reduces customer risk.</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Product Management, End Users, Service</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Component reliability, QA testing.</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>All critical components pass 2-year accelerated life tests.</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Throughput 25/20 PPM (Optimize)</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Printer must achieve throughput of 25 pages per minute (ppm) for standard and 20 ppm for PDL.</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Competitive throughput performance required for target segments.</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Product Management, R&amp;D, End Users</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Engine design, firmware, QA testing.</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Printer achieves 25/20 ppm in standard and PDL tests.</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Serviceability: Maintenance Box (Optimize)</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Design maintenance box for improved serviceability and ease of replacement.</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Reduces downtime and service costs.</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Service, End Users, Product Management</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Maintenance box design, service documentation.</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Maintenance box is user/service replaceable and documented.</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Host 12K-CMYK (Flexible)</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Support host 12K-CMYK configuration as a flexible, lower-priority feature.</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Provides additional configuration for niche markets.</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Product Management, R&amp;D, Sales</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Ink system and firmware flexibility.</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>System can be configured for these yields if required.</t>
-        </is>
-      </c>
-      <c r="I52" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J52" t="inlineStr">
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Product Management, Niche Customers</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Ink system, firmware.</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Host 12K-CMYK configuration available and validated.</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Trade Page 6K (Flexible)</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Enable trade page configuration for 6K page yield as a flexible, lower-priority feature.</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Addresses specific trade or promotional requirements.</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Product Management, Trade Partners</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Firmware, IDS, bottle design.</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Trade page 6K configuration available and validated.</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J59" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>

--- a/consolidation/outputs/consolidated_requirements.xlsx
+++ b/consolidation/outputs/consolidated_requirements.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J59"/>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1231,12 +1231,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Develop and integrate NGB keyed ink bottles capable of 6K Black and 6K CMY page yield. CMY bottle size must be greater than 8K.</t>
+          <t>Develop new NGB keyed ink bottles capable of 6,000-page yield for Black and 6,000 for CMY, with bottle size for CMY supporting over 8,000 pages.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>High-yield bottles reduce frequency of replacement and operational cost, meeting market demand for efficiency and competitive positioning.</t>
+          <t>To meet increased customer demand for higher page yields and reduce frequency of bottle replacement.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1251,12 +1251,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ink system compatibility, bottle design, IDS, and tank size changes.</t>
+          <t>Integration with CISS, IDS compatibility, ink formulation reuse.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Printer supports 6K Black and 6K CMY page yield with new keyed bottles; CMY bottle size &gt;8K verified in test prints.</t>
+          <t>NGB bottles are validated to reliably deliver 6K Black and 6K CMY yields in standard test environments, with CMY bottle size exceeding 8K page capacity.</t>
         </is>
       </c>
       <c r="I17" t="n">
@@ -1276,17 +1276,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Spill-Free Reliability for Ink Bottles</t>
+          <t>Spill-Free Reliability for Bottles</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ensure the new ink bottle design provides spill-free reliability during installation and replacement.</t>
+          <t>Ensure that new bottles provide spill-free reliability during user handling, installation, and replacement.</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Critical for user safety, product quality, and environmental compliance.</t>
+          <t>To enhance user experience and reduce mess or product returns due to spills.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1296,21 +1296,21 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality Assurance, End Users</t>
+          <t>End Users, Customer Support, R&amp;D</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bottle and tank interface design, IDS integration.</t>
+          <t>Bottle design, NOA-F integration.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>No ink spill incidents in 99% of test installations and replacements.</t>
+          <t>Field and lab tests confirm spill-free operation across 99% of use cases.</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1331,12 +1331,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Implement NOA-F with a metal foiled labyrinth and lid label; maintain existing push-push and TDF mechanisms.</t>
+          <t>Implement a NOA-F (Non-Oxidizing Air Filter) with a metal foiled labyrinth and a labeled lid, maintaining existing push-push and TDF mechanisms.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Enhances reliability and security of ink delivery and prevents tampering.</t>
+          <t>To improve air filtration and reliability while ensuring user familiarity and easy operation.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1346,17 +1346,17 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>R&amp;D, Factory, Service</t>
+          <t>R&amp;D, Manufacturing, Service</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>NOA-F design, manufacturing process updates.</t>
+          <t>NOA-F part design, labeling process, push-push compatibility.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>NOA-F passes security, reliability, and compatibility tests with existing mechanisms.</t>
+          <t>NOA-F meets air filtration performance targets and passes all regulatory and internal reliability tests.</t>
         </is>
       </c>
       <c r="I19" t="n">
@@ -1376,17 +1376,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Reuse SuperAmp Si PHA and Magi/Nessie Ink</t>
+          <t>Support for Customer-Replaceable PHA and NOA-F</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Leverage existing SuperAmp Si PHA and Magi/Nessie pigment ink without reformulation for the new platform.</t>
+          <t>Enable end users to replace the Print Head Assembly (PHA) and NOA-F components themselves without technician intervention.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Reduces R&amp;D costs, expedites time to market, and maintains proven quality.</t>
+          <t>To reduce service costs, improve uptime, and enhance user empowerment.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1396,21 +1396,21 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Management, Supply Chain</t>
+          <t>End Users, Service, R&amp;D</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Compatibility with new system, IDS, and bottle design.</t>
+          <t>Design for serviceability, user documentation.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Existing SuperAmp Si PHA and Magi/Nessie ink function reliably in Magellan system without reformulation.</t>
+          <t>Users can replace PHA and NOA-F in under 10 minutes following provided instructions, with no service calls required in &gt;95% of cases.</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ink System Reliability and Modelling</t>
+          <t>Warranty Page Life Goal of 80,000 Pages</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Model and characterize reliability, WVTR, air gain, flow rate, and IDS performance, including startup and NOA-F EOL.</t>
+          <t>The printer must achieve a new warranty page life goal of 80,000 printed pages, exceeding previous models.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Ensures system robustness, print quality, and long-term reliability.</t>
+          <t>To provide competitive differentiation and support high-volume users.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1446,21 +1446,21 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality Assurance</t>
+          <t>Product Management, Warranty/Support, End Users</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>IDS, NOA-F, ink system design.</t>
+          <t>Component durability, ink system reliability, maintenance schedule.</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Reliability and IDS models validated, system meets defined performance thresholds.</t>
+          <t>Field units demonstrate &gt;80,000 pages without major failures under standard duty cycle.</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1476,17 +1476,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ink Stability Modelling</t>
+          <t>Input and Output Tray Redesign for Tank Protrusion</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Perform ink stability modelling for the tank and assess impact on print quality (PQ).</t>
+          <t>Modify input and output trays to align with and accommodate the increased tank protrusion resulting from larger ink tanks.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Prevents ink degradation, ensures consistent print quality, and reduces service incidents.</t>
+          <t>To ensure smooth paper handling and prevent jams or misfeeds due to hardware interference.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1496,17 +1496,17 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality Assurance</t>
+          <t>R&amp;D, Manufacturing, End Users</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ink/tank compatibility, environmental testing.</t>
+          <t>Tank design, chassis layout.</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Ink stability model created; no significant PQ degradation observed in accelerated aging tests.</t>
+          <t>Prototypes and production units pass all paper handling tests with new tray designs.</t>
         </is>
       </c>
       <c r="I22" t="n">
@@ -1526,37 +1526,37 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>NOA-F as Service Part in Warranty</t>
+          <t>4.3” CGD Display Integration</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>NOA-F must be available as a service part for in-warranty support.</t>
+          <t>Integrate a 4.3-inch color graphical display (CGD) as the main user interface for the printer.</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Improves serviceability and customer satisfaction by enabling quick replacement.</t>
+          <t>To provide enhanced user interaction and facilitate ease of operation for advanced functions.</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Service, Warranty, End Users</t>
+          <t>End Users, Marketing, R&amp;D</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>NOA-F inventory, service logistics.</t>
+          <t>Firmware UI, mechanical integration.</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>NOA-F listed as a service part and available for warranty claims.</t>
+          <t>Display is functional, responsive, and passes usability tests for all major workflows.</t>
         </is>
       </c>
       <c r="I23" t="n">
@@ -1576,41 +1576,41 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Acumen 6 on Lid</t>
+          <t>Service Station Aerosol Management</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Integrate Acumen 6 (security/traceability feature) on the ink bottle lid.</t>
+          <t>Implement aerosol management in the service station, with platform changes as required due to the new tank design.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Enhances product traceability and anti-counterfeiting measures.</t>
+          <t>To prevent ink aerosol contamination and maintain internal cleanliness and reliability.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Security, R&amp;D, Supply Chain</t>
+          <t>R&amp;D, Manufacturing, Service</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lid design, Acumen 6 compatibility.</t>
+          <t>Tank and service station design, airflow modeling.</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>All bottle lids include Acumen 6 and pass traceability validation.</t>
+          <t>Aerosol levels inside the printer remain within specified safety and reliability limits during operation and servicing.</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1626,17 +1626,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Modify Existing Factory Line for NOA-F</t>
+          <t>Paper Path Durability for 80,000 Page Life</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Update SA14 line to support NOA-F and add Magi ink cart and labelling tool in Orcus 5.</t>
+          <t>Redesign or reinforce the paper path to support the increased page life goal of 80,000 pages.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Factory readiness for new components is essential for production ramp-up.</t>
+          <t>To ensure reliable operation and minimize paper jams or failures over the product's extended life.</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1646,17 +1646,17 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Manufacturing, Operations, R&amp;D</t>
+          <t>R&amp;D, Quality, End Users</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>SA14 line, Orcus 5, tool procurement.</t>
+          <t>Material selection, mechanical design, durability testing.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Factory lines modified and validated for new components production.</t>
+          <t>Paper path components show no excessive wear or failure after 80,000 pages in durability tests.</t>
         </is>
       </c>
       <c r="I25" t="n">
@@ -1676,41 +1676,41 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>New Keyed Caps Molding</t>
+          <t>Ink Maintenance as Serviceable Part (Post 80k Life)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Create molds for 1 to 4 new keyed bottle caps to support new bottle design.</t>
+          <t>Design ink maintenance components to be serviceable by authorized service centers after 80,000 pages.</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Supports anti-misuse and product differentiation in the market.</t>
+          <t>To extend printer life and reduce total cost of ownership for high-usage customers.</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Manufacturing, R&amp;D</t>
+          <t>Service, End Users, Product Management</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Bottle and cap design finalization.</t>
+          <t>Service process, component modularity.</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Molds produced and first article inspection passed for all new cap designs.</t>
+          <t>Service centers can replace ink maintenance parts within 30 minutes and restore printer to full function.</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -1726,17 +1726,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Support Customer Replaceable PHA and NOA-F</t>
+          <t>New Make-Break and FI Connection for IDS</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Design system for customer-replaceable PHA and NOA-F components.</t>
+          <t>Develop a new make-break and fluidic interconnect (FI) connection for the IDS (Ink Delivery System), leveraging LEBI ink-tank with increased size and keying.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Improves user experience, reduces downtime, and service costs.</t>
+          <t>To support larger ink tanks and ensure reliable, error-free connections during installation and maintenance.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1746,21 +1746,21 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>End Users, Service, Product Management</t>
+          <t>R&amp;D, Manufacturing, Service</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>PHA and NOA-F module design, user documentation.</t>
+          <t>Ink tank design, IDS system integration.</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Users can replace PHA and NOA-F without technical assistance; validated in usability tests.</t>
+          <t>Connection passes all reliability, leak, and mis-insertion tests; supports increased tank size and keying.</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -1776,17 +1776,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Warranty Page Life Goal of 80K Pages</t>
+          <t>New IDS Startup Algorithm and Air Management</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Printer must support a new warranty page life goal of 80,000 pages.</t>
+          <t>Develop and implement a new startup algorithm for the IDS, with improved air management to ensure consistent ink flow and system reliability.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Addresses market need for durable, high-volume printing, and competitive warranty offering.</t>
+          <t>To address startup reliability and prevent air-related print quality issues with the new ink system.</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1796,21 +1796,21 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Product Management, End Users, Service</t>
+          <t>Firmware, R&amp;D, Service</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Component reliability, service parts, QA testing.</t>
+          <t>IDS hardware, firmware development.</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Printer passes 80,000 page life tests without critical failure.</t>
+          <t>Startup success rate &gt;99% in lab and field tests; no air-related faults within warranty period.</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -1826,17 +1826,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SKU 2 (Hi + Hi PDL) PaaS Support</t>
+          <t>New Print Quality (PQ) Goals and Depletion Metrics</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Develop SKU 2 with high throughput and PDL (Page Description Language) support for PaaS (Print as a Service) model.</t>
+          <t>Define and achieve new print quality goals and depletion metrics to match the higher page yield definition.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Expands market reach with flexible business models and high-performance features.</t>
+          <t>To ensure print quality remains high over the entire life and yield of the printer.</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1846,17 +1846,17 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Product Management, Sales, Service Providers</t>
+          <t>R&amp;D, Quality, Marketing</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>PDL integration, SKU definition, platform readiness.</t>
+          <t>Ink, print system integration, firmware.</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>SKU 2 available with PDL and PaaS features, validated in market pilots.</t>
+          <t>Print quality meets or exceeds benchmarks for all supported media types throughout depletion tests to full page yield.</t>
         </is>
       </c>
       <c r="I29" t="n">
@@ -1876,17 +1876,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Reddington ID with Increased Tank Size</t>
+          <t>EPEAT3, LOT4, and Blue Angel Compliance</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Adopt Reddington ID with increased tank size; no change to Marconi-HI ADF.</t>
+          <t>Ensure the product meets EPEAT3, LOT4, and Blue Angel requirements for environmental and efficiency standards (at least for PDL SKU).</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Supports higher page yield and aligns with new bottle sizes.</t>
+          <t>To comply with regulatory and market-driven environmental standards and enable sales in regulated markets.</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1896,17 +1896,17 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Management, Manufacturing</t>
+          <t>Regulatory, Marketing, End Users</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tank design, platform integration, ADF compatibility.</t>
+          <t>Component sourcing, product design, documentation.</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Tank size increased, system passes yield and fitment tests.</t>
+          <t>Product is certified as compliant with EPEAT3, LOT4, and Blue Angel by launch.</t>
         </is>
       </c>
       <c r="I30" t="n">
@@ -1931,12 +1931,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Implement EPS foam packaging for the new product.</t>
+          <t>Use EPS foam for packaging to protect the printer during shipping and handling.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Improves shipping robustness and reduces transit damage.</t>
+          <t>To minimize shipping damage and ensure product arrives safely to customers.</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Packaging design, supplier selection.</t>
+          <t>Packaging design, supply chain.</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>EPS foam packaging passes drop and vibration tests.</t>
+          <t>Packaging passes all drop and vibration tests without printer damage.</t>
         </is>
       </c>
       <c r="I31" t="n">
@@ -1976,41 +1976,41 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Compliance with EPEAT3, LOT4, and Blue Angel (for PDL SKU)</t>
+          <t>Platform with 4 Sayan Sibstar Tubes and New Routing</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Ensure the product meets EPEAT3, LOT4, and Blue Angel environmental and safety standards for PDL SKU.</t>
+          <t>Leverage Sayan Sibstar tubes with a new routing and integration scheme for the ink delivery platform.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Required for regulatory compliance and market access in specific regions.</t>
+          <t>To optimize ink flow, reliability, and manufacturability with the new tank system.</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Regulatory, Product Management, QA</t>
+          <t>R&amp;D, Manufacturing</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Design, materials, QA certification.</t>
+          <t>Ink system design, tube routing analysis.</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Product certified for EPEAT3, LOT4, Blue Angel (PDL SKU).</t>
+          <t>All tubes meet reliability and flow performance metrics in integration tests.</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -2026,41 +2026,41 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Input and Output Tray Modifications</t>
+          <t>Carriage Dynamics and Force Model Update</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Modify input and output trays to accommodate tank protrusion and optimize size.</t>
+          <t>Update the carriage dynamic and force model to account for new tube routing and increased component weights.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Ensures mechanical compatibility and user convenience with new tank design.</t>
+          <t>To ensure accurate and reliable printhead movement with hardware changes.</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing, End Users</t>
+          <t>R&amp;D, Mechanical Engineering</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tank and tray design updates.</t>
+          <t>Carriage design, tube integration.</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Trays function without interference and pass usability tests with new tank.</t>
+          <t>Carriage operates within force and accuracy tolerances in all tested scenarios.</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -2076,41 +2076,41 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>4.3” CGD Display</t>
+          <t>Support for Multiple Business Models and Solutions</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Integrate a 4.3-inch CGD (Color Graphic Display) into the product.</t>
+          <t>Support Consumer, SMB, and Enterprise business models, including PaaS, WorkFromHome/Flexworker, and onboarding via multiple S&amp;O paths (Consumer/HPX, HP One, SMB Portal, ECP).</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Enhances user interface and accessibility for advanced features.</t>
+          <t>To maximize addressable market and meet diverse customer needs.</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Product Management, End Users</t>
+          <t>Sales, Product Management, End Users</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Display sourcing, UI development.</t>
+          <t>Firmware, solutions integration, onboarding workflow.</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>4.3” CGD display operational and passes UI usability tests.</t>
+          <t>Printer supports all listed business models and onboarding paths in production firmware.</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -2126,41 +2126,41 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Platform with 4 Sayan Sibstar Tubes and New Routing</t>
+          <t>Scan Solution and SMB Manageability</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Leverage Sayan Sibstar tubes with new routing and integration into the platform.</t>
+          <t>Integrate scan solution and SMB manageability features, including support for WJA, HPSM, and JAM in Enterprise environments.</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Supports efficient ink delivery and system reliability.</t>
+          <t>To provide advanced document management and device management features for SMB and Enterprise customers.</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing</t>
+          <t>SMB, Enterprise IT, Product Management</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tube design, routing validation.</t>
+          <t>Firmware, solution integration, network stack.</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>System operates reliably with 4 tubes and new routing; passes flow and stress tests.</t>
+          <t>All listed management tools are supported and verified in enterprise test environments.</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -2176,41 +2176,41 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Service Station Aerosol Management</t>
+          <t>Client and Driver Support for HPX, PSA, SUPD, UPD, EasyStart, USS, UFD</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Update service station for improved aerosol management with spit platform changes due to the tank.</t>
+          <t>Ensure compatibility with HPX, PSA, SUPD, UPD clients and drivers, as well as EasyStart, USS, and UFD for installation and operation.</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Reduces service issues and maintains print quality in high-yield systems.</t>
+          <t>To provide seamless installation and operation across customer environments.</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>R&amp;D, Service, QA</t>
+          <t>End Users, IT, Support</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Service station and tank design updates.</t>
+          <t>Firmware, driver development.</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Aerosol levels within safe limits in service station tests.</t>
+          <t>All drivers and clients install and function correctly on supported operating systems.</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -2226,17 +2226,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Carriage Dynamic and Force Model Update</t>
+          <t>25/20ppm Print Speed (PDL: 25/19ppm)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Update carriage dynamic and force models to account for new tube routing and increased weights.</t>
+          <t>Printer must achieve a print speed of 25 pages per minute (ppm) for standard, and 25/19 ppm for PDL (Page Description Language) modes.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Ensures mechanical reliability and print accuracy with new system configuration.</t>
+          <t>To maintain competitiveness in performance-sensitive market segments.</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2246,17 +2246,17 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>R&amp;D, QA</t>
+          <t>Product Management, R&amp;D, End Users</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carriage and tube design, platform integration.</t>
+          <t>Print engine, firmware, paper path.</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Carriage system passes force and dynamic tests with new configuration.</t>
+          <t>Printer meets specified speeds in standard and PDL tests with supported media.</t>
         </is>
       </c>
       <c r="I37" t="n">
@@ -2276,17 +2276,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Paper Path for Increased Page Life</t>
+          <t>Reuse of SuperAmp PHA, Magi and Nessie Pigment Inks</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Design paper path to support increased page life up to 80K pages.</t>
+          <t>Reuse the existing SuperAmp PHA, Magi and Nessie pigment inks without reformulation for the new platform.</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Supports new warranty and reliability goals, reduces maintenance.</t>
+          <t>To reduce R&amp;D costs and leverage proven ink technologies.</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2296,21 +2296,21 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>R&amp;D, QA, Product Management</t>
+          <t>R&amp;D, Manufacturing, Supply Chain</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Paper path design, component durability.</t>
+          <t>Ink compatibility, printhead integration.</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Paper path operates reliably for 80,000 pages in durability tests.</t>
+          <t>No ink reformulation required; print quality and reliability match or exceed current benchmarks.</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -2326,41 +2326,41 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Ink Maintenance as Serviceable Part Post-80K</t>
+          <t>Security: Gauss4.xx (HW &amp; FW)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Design ink maintenance as a serviceable part to be replaced post-80K page life at service centers.</t>
+          <t>Implement Gauss4.xx hardware and firmware security features in the printer.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Facilitates long-term support and reduces total cost of ownership.</t>
+          <t>To ensure device and data security in line with HP and industry standards.</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Service, End Users, Product Management</t>
+          <t>IT, Security, Enterprise Customers</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Maintenance module design, service documentation.</t>
+          <t>Hardware and firmware design, compliance testing.</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Ink maintenance part is replaceable at service centers and documented in service manuals.</t>
+          <t>Device passes all internal and external security audits for Gauss4.xx compliance.</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -2376,41 +2376,41 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>New Make-Break and FI Connection for IDS</t>
+          <t>EPS Foam Packaging</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Develop new make-break and FI (fluidic interface) connection for IDS.</t>
+          <t>Utilize EPS foam packaging for safe product shipment.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Ensures reliable ink delivery and system performance.</t>
+          <t>To minimize damage during transportation and handling.</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>R&amp;D, QA, Manufacturing</t>
+          <t>Logistics, End Users</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>IDS and connection design.</t>
+          <t>Packaging design, supplier sourcing.</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>New connections pass reliability and leak tests.</t>
+          <t>No reported shipping damages in &gt;99% of shipments using EPS foam.</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -2426,17 +2426,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Leverage LEBI Ink-Tank with Increased Size and Keying</t>
+          <t>Blue Angel for PDL SKU</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Utilize LEBI ink-tank with increased size, new keying, and LOI (line of interface) One SHAID.</t>
+          <t>Ensure Blue Angel certification for PDL SKU to meet eco-label requirements.</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Supports higher yields and prevents cross-use of incorrect bottles.</t>
+          <t>To access eco-sensitive markets and fulfill customer procurement requirements.</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2446,17 +2446,17 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Management, Manufacturing</t>
+          <t>Marketing, Regulatory, Enterprise Customers</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tank and keying design, SHAID integration.</t>
+          <t>Product design, documentation, certification process.</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Ink-tank system passes fitment and anti-misuse tests.</t>
+          <t>PDL SKU is certified by Blue Angel by launch.</t>
         </is>
       </c>
       <c r="I41" t="n">
@@ -2465,906 +2465,6 @@
       <c r="J41" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>New IDS Startup Algorithm and Air Management</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Develop new IDS startup algorithm and air management for improved reliability.</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Reduces startup failures and air entrapment issues in the ink system.</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>R&amp;D, QA</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>IDS, firmware, platform integration.</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Startup success rate &gt;99% in system validation tests.</t>
-        </is>
-      </c>
-      <c r="I42" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>New Servicing and Startup Algorithm</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Implement new servicing and startup algorithm for improved maintenance and reliability.</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Reduces service events and ensures consistent startup performance.</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>R&amp;D, Service, QA</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Firmware, IDS, service documentation.</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Servicing and startup algorithms validated in field and lab tests.</t>
-        </is>
-      </c>
-      <c r="I43" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>New Print Quality Goals &amp; Depletion Metrics</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Define new print quality (PQ) goals and depletion metrics to meet page yield definition.</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Ensures customer expectations for output quality and transparency in yield claims.</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Product Management, QA, End Users</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>R&amp;D, QA, IDS, firmware.</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Print quality and depletion metrics documented and met in testing.</t>
-        </is>
-      </c>
-      <c r="I44" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Reuse Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Leverage existing Marconi Tux dASIC, Hannibal aASIC, and Raccoon PSU for the new platform.</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Reduces development cost and accelerates time to market.</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>R&amp;D, Product Management, Manufacturing</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Component compatibility, system integration.</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Existing components function reliably in Magellan system.</t>
-        </is>
-      </c>
-      <c r="I45" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Stingray Wi-Fi Module Integration</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Integrate Stingray Wi-Fi module for wireless connectivity.</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Meets market expectations for modern connectivity and remote printing.</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>End Users, Product Management</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Wi-Fi module sourcing, firmware integration.</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Wi-Fi module passes connectivity and throughput tests.</t>
-        </is>
-      </c>
-      <c r="I46" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Firmware: Dune</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Utilize Dune firmware for system operation.</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Standardizes firmware across platform and leverages proven codebase.</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>R&amp;D, QA, Product Management</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Firmware compatibility, feature integration.</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Dune firmware operational and passes system validation tests.</t>
-        </is>
-      </c>
-      <c r="I47" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Security: Gauss4.xx</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Integrate Gauss4.xx security for hardware and firmware.</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Meets security requirements for enterprise and SMB customers.</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Security, R&amp;D, Enterprise Customers</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>HW/FW integration, certification.</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Security features validated and pass penetration testing.</t>
-        </is>
-      </c>
-      <c r="I48" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Business Model and Solution Support</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Support Consumer, SMB, and Enterprise business models, including PaaS, WorkFromHome, and Flexworker services.</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Addresses diverse customer segments and increases market coverage.</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Product Management, Sales, Service Providers</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Solution and service integration, SKU differentiation.</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>All business models supported and validated in market pilots.</t>
-        </is>
-      </c>
-      <c r="I49" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Scan Solution Integration</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Provide integrated scan solution for all supported business models.</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Meets functional requirements for SMB and Enterprise customers.</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>End Users, Product Management, SMB/Enterprise Customers</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Scanner hardware, firmware integration.</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Scan solution operational and passes functional tests.</t>
-        </is>
-      </c>
-      <c r="I50" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>SMB Manageability and Enterprise Support</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Support SMB manageability and enterprise features, including WJA, HPSM, JAM.</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Critical for IT management in business environments.</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>SMB/Enterprise Customers, IT, Product Management</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Firmware, software integration.</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Manageability features validated with WJA, HPSM, JAM.</t>
-        </is>
-      </c>
-      <c r="I51" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Clients &amp; Drivers Compatibility</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ensure compatibility with HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD clients and drivers.</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Enables flexible deployment and broad OS support.</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>End Users, IT, Product Management</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Driver development, platform validation.</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>All listed drivers and clients pass installation and functional tests.</t>
-        </is>
-      </c>
-      <c r="I52" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Schedule Adherence (Constrain)</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Project schedule is least flexible and must be adhered to as a business constraint.</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Critical for time-to-market and competitive positioning.</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Product Management, Program Management</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>All project deliverables and milestones.</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Project milestones met as per defined schedule.</t>
-        </is>
-      </c>
-      <c r="I53" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>SuperAmp PHA Life at 65K (Constrain)</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>SuperAmp PHA must achieve a minimum lifetime of 65,000 pages.</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Ensures reliability and reduces service costs within warranty period.</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>R&amp;D, QA, Service</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>PHA design, QA testing.</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>SuperAmp PHA passes 65,000-page life tests.</t>
-        </is>
-      </c>
-      <c r="I54" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Warranty Life of 2 Years (Optimize)</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Printer must support a warranty life of 2 years for all critical components.</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Meets market expectations and reduces customer risk.</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Product Management, End Users, Service</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>Component reliability, QA testing.</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>All critical components pass 2-year accelerated life tests.</t>
-        </is>
-      </c>
-      <c r="I55" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Throughput 25/20 PPM (Optimize)</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Printer must achieve throughput of 25 pages per minute (ppm) for standard and 20 ppm for PDL.</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Competitive throughput performance required for target segments.</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Product Management, R&amp;D, End Users</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Engine design, firmware, QA testing.</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Printer achieves 25/20 ppm in standard and PDL tests.</t>
-        </is>
-      </c>
-      <c r="I56" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Serviceability: Maintenance Box (Optimize)</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Design maintenance box for improved serviceability and ease of replacement.</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Reduces downtime and service costs.</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Service, End Users, Product Management</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>Maintenance box design, service documentation.</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Maintenance box is user/service replaceable and documented.</t>
-        </is>
-      </c>
-      <c r="I57" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Host 12K-CMYK (Flexible)</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Support host 12K-CMYK configuration as a flexible, lower-priority feature.</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>Provides additional configuration for niche markets.</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Product Management, Niche Customers</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>Ink system, firmware.</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Host 12K-CMYK configuration available and validated.</t>
-        </is>
-      </c>
-      <c r="I58" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Trade Page 6K (Flexible)</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Enable trade page configuration for 6K page yield as a flexible, lower-priority feature.</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Addresses specific trade or promotional requirements.</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Product Management, Trade Partners</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>Firmware, IDS, bottle design.</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Trade page 6K configuration available and validated.</t>
-        </is>
-      </c>
-      <c r="I59" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
     </row>

--- a/consolidation/outputs/consolidated_requirements.xlsx
+++ b/consolidation/outputs/consolidated_requirements.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J41"/>
+  <dimension ref="A1:J46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,17 +476,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>HP’s First Business Ink Tank Printer</t>
+          <t>AI Productivity Solutions</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Develop and launch HP's first business ink tank printer specifically targeted at unmanaged and lightly managed SMBs (5-250 employees, 6-15 printers, AMPV ~500 pages).</t>
+          <t>Integrate advanced AI-based productivity features including Perfect Print and Perfect Scan to enhance workflow and manageability for SMB users.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Addresses a gap in HP's portfolio (CISS PLE segment) and meets evolving customer needs for ROI, efficiency, and cost-effective printing.</t>
+          <t>AI solutions are key differentiators and address SMB needs for efficiency and ease of management.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -501,12 +501,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Must align with SMB2.0 Solutions and Advanced View SMB portal; warranty and serviceability requirements.</t>
+          <t>['SMB portal integration']</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Product is launched and available for SMB customers; achieves targeted monthly sales run rate (20-30K units); receives positive feedback from target segment.</t>
+          <t>AI features (Perfect Print, Perfect Scan) are functional and demonstrably improve workflow efficiency in lab and field tests.</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -514,7 +514,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 6, 7, 11, 12</t>
+          <t>Magellan MRD, Page 7, Page 11</t>
         </is>
       </c>
     </row>
@@ -526,17 +526,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AI Productivity, Scan Workflow &amp; Manageability Solutions</t>
+          <t>SMB Device Management Portal</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Integrate advanced AI-driven productivity, scan workflow, and manageability features to make managing SMB business printing easier.</t>
+          <t>Develop a consolidated portal for small office device management, targeting unmanaged/lightly managed SMBs, enabling easy monitoring and control of printers.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Differentiates HP from competitors, addresses key pain points for non-IT SMB decision makers, and supports solutions enhancement with AI.</t>
+          <t>SMB customers lack dedicated IT; a portal simplifies management and aligns with customer pain points.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -546,17 +546,17 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>['Marketing', 'GXD', 'Quality', 'R&amp;D Telemetry', 'DVAR', 'BA']</t>
+          <t>['Marketing', 'GXD', 'Quality', 'R&amp;D Telemetry', 'Supplies Quality', 'DVAR', 'Tech Reg', 'Prod Steward', 'BA']</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Requires consolidated SMB portal; must support PaaS and device management features.</t>
+          <t>['AI solutions integration']</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>AI features implemented for print, scan, and support; validated through user testing; measurable improvement in productivity and manageability.</t>
+          <t>Portal is accessible, supports device management for SMBs, and passes usability testing with target customer profiles.</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -564,7 +564,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 7, 10, 11</t>
+          <t>Magellan MRD, Page 7, Page 10, Page 11</t>
         </is>
       </c>
     </row>
@@ -576,17 +576,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Lowest Business TCO with Minimal Intervention</t>
+          <t>Business Ink Tank Technology</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Design the printer to deliver HP's lowest business total cost of ownership (TCO) with minimal user intervention required.</t>
+          <t>Implement HP’s first business-focused ink tank solution with lowest business TCO, targeting SMB segment.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Key purchase driver for SMBs seeking ROI and efficiency; competitive advantage over alternatives.</t>
+          <t>Competitive gap in CISS PLE Hi segment; supports strategic intent to retain SMB market share.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -596,25 +596,25 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>['Marketing', 'Quality', 'Supplies Quality', 'Prod Steward']</t>
+          <t>['Marketing', 'Quality', 'Supplies Quality', 'Tech Reg', 'Prod Steward']</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Must support keyed bottles, maintenance-free claims, and sustainability requirements.</t>
+          <t>['Keyed bottles', 'Maintenance box design']</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>TCO calculations show HP is lowest among competitors; minimal maintenance demonstrated in field trials; user feedback confirms ease of use.</t>
+          <t>Ink tank solution delivers lowest TCO compared to competitors in independent testing.</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.85</v>
+        <v>0.92</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 11</t>
+          <t>Magellan MRD, Page 4, Page 6, Page 11, Page 12</t>
         </is>
       </c>
     </row>
@@ -626,41 +626,41 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Serviceability: Customer Replaceable Parts</t>
+          <t>Keyed Bottles for Ink Refill</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Printer must be designed for easy serviceability, with key components (PHA, maintenance box) being customer replaceable if out of warranty, and MINK replaceable at service centers.</t>
+          <t>Design and implement keyed bottles for ink refilling to ensure compatibility and minimize errors.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Reduces downtime and service costs for SMBs without IT teams; supports post-purchase support and repurpose stages.</t>
+          <t>Keyed bottles are listed as a dependency for serviceability and quality assurance.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>['Quality', 'R&amp;D Telemetry', 'Supplies Quality', 'Prod Steward']</t>
+          <t>['Supplies Quality', 'Quality', 'Prod Steward']</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Warranty policy (80k pages or 2 years); maintenance-free design investigation.</t>
+          <t>['Business Ink Tank Technology']</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Serviceability features validated in design and user testing; parts are replaceable by customers as specified; meets warranty and service center requirements.</t>
+          <t>Keyed bottles are tested for error-proof compatibility and accepted by service teams.</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -676,41 +676,41 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Keyed Bottles for Ink Supply</t>
+          <t>Replaceable Maintenance Box</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Integrate keyed bottles to prevent incorrect ink filling and ensure ease of use for SMB customers.</t>
+          <t>Develop a replaceable maintenance box for ease of servicing, with customer-replaceable option prioritized.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Improves user experience and reduces errors for non-IT trained office managers; supports sustainability and supplies quality.</t>
+          <t>New feature for Magellan, reduces service intervention and aligns with SMB needs for minimal maintenance.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>['Supplies Quality', 'Quality', 'Prod Steward']</t>
+          <t>['Quality', 'Prod Steward', 'Tech Reg']</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Must align with maintenance-free and sustainability goals.</t>
+          <t>['Serviceability design']</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Keyed bottles implemented and validated through user testing; error rates reduced compared to previous models.</t>
+          <t>Maintenance box is customer-replaceable in &gt;80% of cases, verified in service trials.</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.8</v>
+        <v>0.88</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -726,17 +726,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SMB Portal for Printer Management</t>
+          <t>Warranty and Serviceability</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Develop a consolidated portal for SMBs to manage their printers, including device management, AI solutions, and support.</t>
+          <t>Offer warranty of 80k pages or 2 years (whichever is first) with customer-replaceable PHA and MINK at service center.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Addresses the needs of unmanaged/lightly managed SMBs; differentiates HP through manageability and AI features.</t>
+          <t>Warranty and serviceability are key dependencies for market acceptance and reduced cost of ownership.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -746,17 +746,17 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>['Marketing', 'GXD', 'R&amp;D Telemetry', 'DVAR', 'BA']</t>
+          <t>['Quality', 'Prod Steward', 'Tech Reg']</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Requires integration with AI solutions and PaaS support.</t>
+          <t>['Replaceable Maintenance Box']</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Portal operational and accessible for SMB customers; device management, AI, and support features available; user adoption metrics achieved.</t>
+          <t>Warranty terms are published; serviceability meets threshold for customer-replaceable parts as defined by service center feedback.</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -764,7 +764,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 7, 10</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
     </row>
@@ -776,17 +776,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Support for PaaS (Printer-as-a-Service)</t>
+          <t>PDL SKU Speed Improvement</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ensure the printer supports Printer-as-a-Service (PaaS) models, including necessary telemetry and portal integration.</t>
+          <t>Improve PDL SKU speed to 25/20 ppm (from current 25/19), with support for PDL/PS and Blue Angel certification.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Supports HP’s strategic goal for PaaS acceleration and coverage; enables new business models and recurring revenue.</t>
+          <t>Speed improvement and certification are competitive differentiators for PDL SKUs.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -796,25 +796,25 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>['Marketing', 'R&amp;D Telemetry', 'DVAR', 'BA']</t>
+          <t>['R&amp;D Telemetry', 'Tech Reg', 'Quality']</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Requires telemetry requirements and portal integration.</t>
+          <t>['Business Ink Tank Technology']</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Printer is compatible with PaaS offerings; telemetry and portal features validated; business models enabled.</t>
+          <t>PDL SKU achieves 25/20 ppm in benchmark tests and passes Blue Angel certification.</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.85</v>
+        <v>0.87</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 6, 10</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
     </row>
@@ -826,45 +826,45 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PDL/PS Support and Speed Improvement</t>
+          <t>Sustainability - Recycled Content Percentage (RCP)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>For PDL SKU, ensure support for PDL/PS and improve speed to 25/20 min (current 25/19).</t>
+          <t>Ensure printer is manufactured with at least 60% recycled content (RCP), surpassing competitors (Epson 30%).</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Competitive positioning for medium and enterprise segments; addresses performance needs for SMBs.</t>
+          <t>Sustainability is a key differentiator and customer priority for SMBs.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>['Marketing', 'Quality', 'R&amp;D Telemetry']</t>
+          <t>['Prod Steward', 'Quality']</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Must align with Blue Angel certification and hardware specs.</t>
+          <t>['Supply chain sourcing']</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>PDL/PS support implemented; speed improvement validated through testing; meets performance targets.</t>
+          <t>Independent audit confirms 60% RCP in final product.</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.8</v>
+        <v>0.93</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan MRD, Page 11</t>
         </is>
       </c>
     </row>
@@ -876,17 +876,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Blue Angel Certification</t>
+          <t>Minimal Maintenance Design</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ensure printer meets Blue Angel environmental certification requirements.</t>
+          <t>Design printer for minimal maintenance, with fewer parts to replace over product lifetime.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Supports sustainability claims and competitive differentiation; important for global markets.</t>
+          <t>Maintenance free or less maintenance is a top feature requested by SMBs; reduces intervention and cost.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -896,17 +896,17 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>['Tech Reg', 'Prod Steward', 'Quality']</t>
+          <t>['Quality', 'Prod Steward']</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Must align with sustainability and hardware requirements.</t>
+          <t>['Replaceable Maintenance Box']</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Blue Angel certification achieved; documentation available.</t>
+          <t>Printer requires fewer maintenance interventions compared to competitors, as measured in field trials.</t>
         </is>
       </c>
       <c r="I10" t="n">
@@ -914,7 +914,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan MRD, Page 11</t>
         </is>
       </c>
     </row>
@@ -926,45 +926,45 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Maintenance-Free or Reduced Maintenance Design</t>
+          <t>PaaS Support</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Design printer to be maintenance-free or require less maintenance (fewer parts to replace over life).</t>
+          <t>Support Printer-as-a-Service (PaaS) business model, including integration with SMB2.0 Solutions and Advanced View SMB portal.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Minimizes intervention for SMBs; increases reliability and customer satisfaction.</t>
+          <t>PaaS is a strategic goal and dependency for Magellan’s business model.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>['Quality', 'Supplies Quality', 'Prod Steward']</t>
+          <t>['Marketing', 'GXD', 'BA']</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Under investigation; must align with serviceability and sustainability requirements.</t>
+          <t>['SMB portal']</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Maintenance-free or reduced maintenance features validated; user feedback confirms reduced intervention.</t>
+          <t>Printer and portal integrate seamlessly with PaaS platform; passes pilot deployment with SMB customers.</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.75</v>
+        <v>0.88</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 11</t>
+          <t>Magellan MRD, Page 4, Page 10</t>
         </is>
       </c>
     </row>
@@ -976,45 +976,45 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sustainability: 60% RCP (Recycled Content Plastic)</t>
+          <t>Telemetry Requirements</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ensure printer uses at least 60% recycled content plastic (RCP), exceeding competitors (Epson 30%, Canon TBC).</t>
+          <t>Implement robust telemetry features for device monitoring, usage analytics, and proactive support.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Supports HP’s sustainability goals and provides a competitive advantage.</t>
+          <t>Telemetry is required for manageability and support in SMB environments.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>['Prod Steward', 'Tech Reg', 'Marketing']</t>
+          <t>['R&amp;D Telemetry', 'Quality', 'BA']</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Must align with Blue Angel certification and supplies requirements.</t>
+          <t>['SMB portal']</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Material sourcing validated; sustainability claims substantiated; 60% RCP usage documented.</t>
+          <t>Telemetry data is accessible, accurate, and meets privacy/security standards in pilot tests.</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 11</t>
+          <t>Magellan MRD, Page 12</t>
         </is>
       </c>
     </row>
@@ -1026,17 +1026,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Advanced Telemetry Requirements</t>
+          <t>Mobile Printing via HP App</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Integrate telemetry features to support device management, PaaS, and post-purchase support.</t>
+          <t>Enable seamless mobile printing through the HP App, supporting SMB workflows.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Enables remote management, analytics, and support for SMBs; supports HP’s strategic goals.</t>
+          <t>Mobile printing is a key customer priority and enhances usability for SMBs.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1046,25 +1046,25 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>['R&amp;D Telemetry', 'DVAR', 'BA']</t>
+          <t>['GXD', 'Marketing']</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Requires portal and PaaS integration; must meet privacy and compliance standards.</t>
+          <t>['SMB portal']</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Telemetry features implemented and validated; data privacy and compliance requirements met.</t>
+          <t>Mobile printing is functional and passes usability tests with SMB users.</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 12</t>
+          <t>Magellan MRD, Page 10</t>
         </is>
       </c>
     </row>
@@ -1076,37 +1076,37 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Mobile Printing via HP App</t>
+          <t>Advanced Solutions Monetization</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Support mobile printing through the HP App for ease of use and accessibility.</t>
+          <t>Develop features and business models to monetize advanced AI and device management solutions for SMBs.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Meets customer expectations for modern office solutions; increases usability for SMBs.</t>
+          <t>Solutions monetization is a top priority for the next 3-5 years.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>['Marketing', 'GXD', 'BA']</t>
+          <t>['Marketing', 'BA']</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Must integrate with SMB portal and device management.</t>
+          <t>['AI solutions', 'SMB portal']</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Mobile printing feature operational; user feedback confirms ease of use.</t>
+          <t>Revenue is generated from advanced solutions in pilot programs.</t>
         </is>
       </c>
       <c r="I14" t="n">
@@ -1114,79 +1114,79 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 10</t>
+          <t>Magellan MRD, Page 9, Page 10</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Solutions Monetization</t>
+          <t>NGB Keyed Bottles with High Page Yield</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Enable monetization of solutions (AI, portal, services) as part of the printer offering.</t>
+          <t>Develop new NGB keyed ink bottles capable of delivering 6,000 pages for black and 6,000 pages for CMY, with CMY bottle size exceeding 8,000 pages.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Supports HP’s strategic goal for profitable growth and new revenue streams.</t>
+          <t>To increase consumable yield and reduce user intervention, supporting high-volume printing and competitive positioning against rivals.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>['Marketing', 'BA', 'DVAR']</t>
+          <t>R&amp;D, Product Management, Consumables Team</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Requires portal and AI solutions integration; must comply with business models.</t>
+          <t>Requires compatibility with existing and new ink platform (Magi/Nessie) and IDS system.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Monetization features implemented; revenue targets achieved; business model validated.</t>
+          <t>NGB bottles must be validated to deliver 6,000 pages (black/CMY) and CMY bottle must support &gt;8,000 pages in test environments.</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.75</v>
+        <v>0.95</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 9, 10</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Consolidated Device Management Experience</t>
+          <t>Spill-Free Reliability for Ink Bottles</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Provide a consolidated device management experience for SMBs, integrating AI, support, and telemetry.</t>
+          <t>Ensure new bottles and filling mechanism provide spill-free reliability during user refill operations.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Differentiates HP from competitors; addresses key SMB pain points around manageability and support.</t>
+          <t>Minimize mess and improve end-user experience, reducing warranty and support costs.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1196,47 +1196,47 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>['Marketing', 'GXD', 'R&amp;D Telemetry', 'DVAR']</t>
+          <t>R&amp;D, Customer Support, End Users</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Requires portal, AI, and telemetry integration.</t>
+          <t>Integration with bottle design and tank interface, IDS system.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Device management features validated; user adoption metrics achieved; positive feedback from SMBs.</t>
+          <t>User testing demonstrates &lt;1% spill rate during 100 consecutive refills in controlled conditions.</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 10, 11</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>NGB Keyed Bottles with High Page Yield</t>
+          <t>NOA-F with Metal Foiled Labyrinth and Lid Label</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Develop new NGB keyed ink bottles capable of 6,000-page yield for Black and 6,000 for CMY, with bottle size for CMY supporting over 8,000 pages.</t>
+          <t>Integrate a new NOA-F (Non-Original Accessory - Fill) with a metal foiled labyrinth and a lid label. No changes to click-on push-push and TDF mechanisms.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>To meet increased customer demand for higher page yields and reduce frequency of bottle replacement.</t>
+          <t>Enhance security, reliability, and product differentiation while maintaining compatibility with existing mechanisms.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1246,21 +1246,21 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Management, End Users</t>
+          <t>R&amp;D, Security, Service</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Integration with CISS, IDS compatibility, ink formulation reuse.</t>
+          <t>Dependent on NOA-F design and integration with bottle and tank.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>NGB bottles are validated to reliably deliver 6K Black and 6K CMY yields in standard test environments, with CMY bottle size exceeding 8K page capacity.</t>
+          <t>NOA-F passes reliability and security tests; click-on push-push and TDF unchanged.</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1271,22 +1271,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Spill-Free Reliability for Bottles</t>
+          <t>Reuse SuperAmp Si PHA and Magi/Nessie Ink</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ensure that new bottles provide spill-free reliability during user handling, installation, and replacement.</t>
+          <t>Continue using SuperAmp Si PHA and Magi/Nessie pigment inks without reformulation to ensure supply chain and cost efficiency.</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>To enhance user experience and reduce mess or product returns due to spills.</t>
+          <t>Reduces development time, leverages proven technology, and ensures supply chain continuity.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1296,21 +1296,21 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>End Users, Customer Support, R&amp;D</t>
+          <t>R&amp;D, Supply Chain, Manufacturing</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bottle design, NOA-F integration.</t>
+          <t>Dependent on compatibility with new bottle and tank design.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Field and lab tests confirm spill-free operation across 99% of use cases.</t>
+          <t>No ink reformulation required; print quality and reliability meet existing standards.</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1321,22 +1321,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>NOA-F with Metal Foiled Labyrinth and Lid Label</t>
+          <t>Ink Stability and Reliability Modelling</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Implement a NOA-F (Non-Oxidizing Air Filter) with a metal foiled labyrinth and a labeled lid, maintaining existing push-push and TDF mechanisms.</t>
+          <t>Model and validate ink stability, WVTR (Water Vapor Transmission Rate), air gain, flow rate, and IDS (Ink Delivery System) performance, including startup and NOA-F end-of-life scenarios.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>To improve air filtration and reliability while ensuring user familiarity and easy operation.</t>
+          <t>Ensures consistent print quality and reliability throughout product life cycle.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1346,17 +1346,17 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing, Service</t>
+          <t>R&amp;D, Quality Assurance</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>NOA-F part design, labeling process, push-push compatibility.</t>
+          <t>Requires finalized ink, bottle, and IDS design.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>NOA-F meets air filtration performance targets and passes all regulatory and internal reliability tests.</t>
+          <t>All parameters modeled and validated to meet PQ (Print Quality) and reliability standards over expected life.</t>
         </is>
       </c>
       <c r="I19" t="n">
@@ -1371,22 +1371,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Support for Customer-Replaceable PHA and NOA-F</t>
+          <t>Support for Services/Contractual and NOA-F as Service Parts</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Enable end users to replace the Print Head Assembly (PHA) and NOA-F components themselves without technician intervention.</t>
+          <t>NOA-F must be available as a service part for warranty and contract support scenarios.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>To reduce service costs, improve uptime, and enhance user empowerment.</t>
+          <t>Ensures serviceability and support for in-warranty devices, reducing downtime and improving customer satisfaction.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1396,17 +1396,17 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>End Users, Service, R&amp;D</t>
+          <t>Service, Warranty, End Users</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Design for serviceability, user documentation.</t>
+          <t>NOA-F design and supply chain integration.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Users can replace PHA and NOA-F in under 10 minutes following provided instructions, with no service calls required in &gt;95% of cases.</t>
+          <t>NOA-F listed as service part and available in service logistics system.</t>
         </is>
       </c>
       <c r="I20" t="n">
@@ -1421,46 +1421,46 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Warranty Page Life Goal of 80,000 Pages</t>
+          <t>Acumen 6 on Lid</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>The printer must achieve a new warranty page life goal of 80,000 printed pages, exceeding previous models.</t>
+          <t>Integrate Acumen 6 feature on the bottle or tank lid for enhanced tracking or authentication.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>To provide competitive differentiation and support high-volume users.</t>
+          <t>Improves traceability and potentially supports anti-counterfeit measures.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Product Management, Warranty/Support, End Users</t>
+          <t>Security, R&amp;D</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Component durability, ink system reliability, maintenance schedule.</t>
+          <t>Requires Acumen 6 technology integration.</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Field units demonstrate &gt;80,000 pages without major failures under standard duty cycle.</t>
+          <t>Acumen 6 is present and functional on all production lids.</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.95</v>
+        <v>0.8</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1471,46 +1471,46 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Input and Output Tray Redesign for Tank Protrusion</t>
+          <t>Factory Line Modifications for NOA-F and Ink Cart Integration</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Modify input and output trays to align with and accommodate the increased tank protrusion resulting from larger ink tanks.</t>
+          <t>Modify existing SA14 line for NOA-F production; add Magi ink cartridge and labeling tool to Orcus 5; provide molds for 1 to 4 new keyed caps.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>To ensure smooth paper handling and prevent jams or misfeeds due to hardware interference.</t>
+          <t>Supports manufacturing scalability and new product introduction with minimal investment.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing, End Users</t>
+          <t>Manufacturing, Operations</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tank design, chassis layout.</t>
+          <t>Dependent on finalized NOA-F and bottle designs.</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Prototypes and production units pass all paper handling tests with new tray designs.</t>
+          <t>Factory lines modified, validated, and ready for mass production.</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1521,42 +1521,42 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>4.3” CGD Display Integration</t>
+          <t>Support for Customer Replaceable PHA and NOA-F</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Integrate a 4.3-inch color graphical display (CGD) as the main user interface for the printer.</t>
+          <t>Design the product to allow end-users to replace PHA and NOA-F components without service intervention.</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>To provide enhanced user interaction and facilitate ease of operation for advanced functions.</t>
+          <t>Improves customer experience and reduces service costs.</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>End Users, Marketing, R&amp;D</t>
+          <t>End Users, Service</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Firmware UI, mechanical integration.</t>
+          <t>Dependent on product and component design.</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Display is functional, responsive, and passes usability tests for all major workflows.</t>
+          <t>Users can replace PHA and NOA-F using only instructions, with no tools required.</t>
         </is>
       </c>
       <c r="I23" t="n">
@@ -1571,46 +1571,46 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Service Station Aerosol Management</t>
+          <t>Warranty Page Life Goal of 80,000 Pages</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Implement aerosol management in the service station, with platform changes as required due to the new tank design.</t>
+          <t>Design product to support a new warranty page life goal of 80,000 pages.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>To prevent ink aerosol contamination and maintain internal cleanliness and reliability.</t>
+          <t>Enhances product value and reduces total cost of ownership for customers.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing, Service</t>
+          <t>Product Management, Warranty, End Users</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tank and service station design, airflow modeling.</t>
+          <t>Dependent on reliability modeling and component durability.</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Aerosol levels inside the printer remain within specified safety and reliability limits during operation and servicing.</t>
+          <t>Product passes accelerated life testing to 80,000 pages without failure.</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1621,46 +1621,46 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Paper Path Durability for 80,000 Page Life</t>
+          <t>SKU 2 PaaS (Hi + Hi PDL)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Redesign or reinforce the paper path to support the increased page life goal of 80,000 pages.</t>
+          <t>Offer a second SKU with high capacity and high PDL (Page Description Language) as a Platform as a Service (PaaS) option.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>To ensure reliable operation and minimize paper jams or failures over the product's extended life.</t>
+          <t>Addresses diverse customer segments and business models.</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality, End Users</t>
+          <t>Product Management, Marketing, Business Development</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Material selection, mechanical design, durability testing.</t>
+          <t>Dependent on SKU definition and platform capability.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Paper path components show no excessive wear or failure after 80,000 pages in durability tests.</t>
+          <t>SKU 2 available in product catalog and PaaS offering.</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -1671,46 +1671,46 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ink Maintenance as Serviceable Part (Post 80k Life)</t>
+          <t>Reddington ID with Increased Tank Size</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Design ink maintenance components to be serviceable by authorized service centers after 80,000 pages.</t>
+          <t>Adopt Reddington industrial design (ID) with a larger tank size to support higher ink capacity; no changes to Marconi-HI ADF.</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>To extend printer life and reduce total cost of ownership for high-usage customers.</t>
+          <t>Supports higher page yield and aligns with new product identity.</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Service, End Users, Product Management</t>
+          <t>ID Team, R&amp;D, Marketing</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Service process, component modularity.</t>
+          <t>Dependent on industrial design and tank engineering.</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Service centers can replace ink maintenance parts within 30 minutes and restore printer to full function.</t>
+          <t>Product prototype matches Reddington ID with increased tank size, passes ID review.</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -1721,46 +1721,46 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>New Make-Break and FI Connection for IDS</t>
+          <t>EPS Foam Packaging</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Develop a new make-break and fluidic interconnect (FI) connection for the IDS (Ink Delivery System), leveraging LEBI ink-tank with increased size and keying.</t>
+          <t>Implement EPS foam packaging for improved shipping and handling protection.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>To support larger ink tanks and ensure reliable, error-free connections during installation and maintenance.</t>
+          <t>Reduces damage in transit and supports sustainability goals (if recyclable).</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing, Service</t>
+          <t>Logistics, Sustainability, Customers</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Ink tank design, IDS system integration.</t>
+          <t>Dependent on packaging supplier and design.</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Connection passes all reliability, leak, and mis-insertion tests; supports increased tank size and keying.</t>
+          <t>EPS foam packaging passes drop and vibration tests per HP standards.</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -1771,22 +1771,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>New IDS Startup Algorithm and Air Management</t>
+          <t>EPEAT3, LOT4, and Blue Angel Compliance</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Develop and implement a new startup algorithm for the IDS, with improved air management to ensure consistent ink flow and system reliability.</t>
+          <t>Ensure product meets EPEAT3, LOT4, and Blue Angel requirements for environmental and energy efficiency (for PDL SKU).</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>To address startup reliability and prevent air-related print quality issues with the new ink system.</t>
+          <t>Enables sales in regulated markets and supports HP sustainability commitments.</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1796,17 +1796,17 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Firmware, R&amp;D, Service</t>
+          <t>Regulatory, Marketing, Product Management</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>IDS hardware, firmware development.</t>
+          <t>Dependent on compliance testing and certification.</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Startup success rate &gt;99% in lab and field tests; no air-related faults within warranty period.</t>
+          <t>Product certified for EPEAT3, LOT4, and Blue Angel prior to launch.</t>
         </is>
       </c>
       <c r="I28" t="n">
@@ -1821,46 +1821,46 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>New Print Quality (PQ) Goals and Depletion Metrics</t>
+          <t>Input/Output Tray Changes for Tank Protrusion</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Define and achieve new print quality goals and depletion metrics to match the higher page yield definition.</t>
+          <t>Redesign input and output trays to accommodate tank protrusion and optimize overall product size.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>To ensure print quality remains high over the entire life and yield of the printer.</t>
+          <t>Maintains usability and aesthetics with new tank size.</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality, Marketing</t>
+          <t>R&amp;D, ID Team, Manufacturing</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ink, print system integration, firmware.</t>
+          <t>Dependent on tank and tray design integration.</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Print quality meets or exceeds benchmarks for all supported media types throughout depletion tests to full page yield.</t>
+          <t>Trays fit with tank, pass usability and reliability tests.</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -1871,46 +1871,46 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>EPEAT3, LOT4, and Blue Angel Compliance</t>
+          <t>4.3” CGD Display Integration</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ensure the product meets EPEAT3, LOT4, and Blue Angel requirements for environmental and efficiency standards (at least for PDL SKU).</t>
+          <t>Integrate a 4.3-inch CGD (Color Graphic Display) for improved user interface and interaction.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>To comply with regulatory and market-driven environmental standards and enable sales in regulated markets.</t>
+          <t>Enhances user experience and supports advanced features.</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Regulatory, Marketing, End Users</t>
+          <t>End Users, UI/UX, Product Management</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Component sourcing, product design, documentation.</t>
+          <t>Dependent on display sourcing and UI development.</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Product is certified as compliant with EPEAT3, LOT4, and Blue Angel by launch.</t>
+          <t>4.3” CGD display present, passes usability and reliability tests.</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -1921,22 +1921,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>EPS Foam Packaging</t>
+          <t>New Tube Routing and Integration</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Use EPS foam for packaging to protect the printer during shipping and handling.</t>
+          <t>Leverage Sayan Sibstar tubes with new routing and integration for the ink delivery system (4 tubes).</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>To minimize shipping damage and ensure product arrives safely to customers.</t>
+          <t>Supports new tank and bottle design, improves reliability and flow.</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1946,17 +1946,17 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Logistics, Manufacturing, End Users</t>
+          <t>R&amp;D, Manufacturing</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Packaging design, supply chain.</t>
+          <t>Dependent on tube and tank design.</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Packaging passes all drop and vibration tests without printer damage.</t>
+          <t>Tube routing validated for reliability and flow in prototype units.</t>
         </is>
       </c>
       <c r="I31" t="n">
@@ -1971,22 +1971,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Platform with 4 Sayan Sibstar Tubes and New Routing</t>
+          <t>Service Station Aerosol Management</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Leverage Sayan Sibstar tubes with a new routing and integration scheme for the ink delivery platform.</t>
+          <t>Modify service station to manage aerosol emissions with changes to spit platform due to new tank.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>To optimize ink flow, reliability, and manufacturability with the new tank system.</t>
+          <t>Meets regulatory and safety requirements, improves reliability.</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1996,17 +1996,17 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing</t>
+          <t>R&amp;D, Regulatory, Quality Assurance</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ink system design, tube routing analysis.</t>
+          <t>Dependent on tank and service station design.</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>All tubes meet reliability and flow performance metrics in integration tests.</t>
+          <t>Aerosol management system passes emissions and reliability tests.</t>
         </is>
       </c>
       <c r="I32" t="n">
@@ -2021,22 +2021,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Carriage Dynamics and Force Model Update</t>
+          <t>Carriage Dynamic and Force Model Update</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Update the carriage dynamic and force model to account for new tube routing and increased component weights.</t>
+          <t>Update carriage dynamic and force model to accommodate new tube routing and increased weights from larger tank.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>To ensure accurate and reliable printhead movement with hardware changes.</t>
+          <t>Ensures printhead reliability and print quality with new configuration.</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2046,21 +2046,21 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>R&amp;D, Mechanical Engineering</t>
+          <t>R&amp;D, Reliability Engineering</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carriage design, tube integration.</t>
+          <t>Dependent on finalized tank and tube design.</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Carriage operates within force and accuracy tolerances in all tested scenarios.</t>
+          <t>Carriage model validated and passes reliability testing.</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -2071,22 +2071,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Support for Multiple Business Models and Solutions</t>
+          <t>Paper Path Enhancement for Increased Page Life</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Support Consumer, SMB, and Enterprise business models, including PaaS, WorkFromHome/Flexworker, and onboarding via multiple S&amp;O paths (Consumer/HPX, HP One, SMB Portal, ECP).</t>
+          <t>Enhance paper path design to support increased page life (80,000 pages).</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>To maximize addressable market and meet diverse customer needs.</t>
+          <t>Reduces jams and wear, supporting new warranty page life goal.</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2096,17 +2096,17 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sales, Product Management, End Users</t>
+          <t>R&amp;D, Reliability, End Users</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Firmware, solutions integration, onboarding workflow.</t>
+          <t>Dependent on paper path redesign and component selection.</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Printer supports all listed business models and onboarding paths in production firmware.</t>
+          <t>Paper path passes reliability testing for 80,000 pages without failure.</t>
         </is>
       </c>
       <c r="I34" t="n">
@@ -2121,22 +2121,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Scan Solution and SMB Manageability</t>
+          <t>Serviceable Ink Maintenance Part (Post 80K Life)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Integrate scan solution and SMB manageability features, including support for WJA, HPSM, and JAM in Enterprise environments.</t>
+          <t>Designate ink maintenance part as serviceable at service centers after 80,000-page life is reached.</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>To provide advanced document management and device management features for SMB and Enterprise customers.</t>
+          <t>Supports extended product life and serviceability, reducing total cost of ownership.</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2146,17 +2146,17 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>SMB, Enterprise IT, Product Management</t>
+          <t>Service, End Users</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Firmware, solution integration, network stack.</t>
+          <t>Dependent on maintenance part design and service documentation.</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>All listed management tools are supported and verified in enterprise test environments.</t>
+          <t>Maintenance part replacement procedure available and validated at service centers.</t>
         </is>
       </c>
       <c r="I35" t="n">
@@ -2171,22 +2171,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Client and Driver Support for HPX, PSA, SUPD, UPD, EasyStart, USS, UFD</t>
+          <t>New IDS Make-Break and FI Connection</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Ensure compatibility with HPX, PSA, SUPD, UPD clients and drivers, as well as EasyStart, USS, and UFD for installation and operation.</t>
+          <t>Implement new make-break and FI (Fluidic Interface) connection for the Ink Delivery System, leveraging LEBI ink-tank with increased size, keying, and LOI (Line of Identity) with one SHAID.</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>To provide seamless installation and operation across customer environments.</t>
+          <t>Improves reliability, reduces mis-installation, and supports increased tank size.</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>End Users, IT, Support</t>
+          <t>R&amp;D, Manufacturing, Service</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Firmware, driver development.</t>
+          <t>Dependent on IDS and tank design.</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>All drivers and clients install and function correctly on supported operating systems.</t>
+          <t>New IDS passes installation and reliability tests; SHAID present.</t>
         </is>
       </c>
       <c r="I36" t="n">
@@ -2221,22 +2221,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>25/20ppm Print Speed (PDL: 25/19ppm)</t>
+          <t>New IDS Startup Algorithm and Air Management</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Printer must achieve a print speed of 25 pages per minute (ppm) for standard, and 25/19 ppm for PDL (Page Description Language) modes.</t>
+          <t>Develop new startup algorithm and air management system for the IDS.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>To maintain competitiveness in performance-sensitive market segments.</t>
+          <t>Ensures reliable startup and operation with new ink system.</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2246,21 +2246,21 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Product Management, R&amp;D, End Users</t>
+          <t>R&amp;D, Firmware</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Print engine, firmware, paper path.</t>
+          <t>Dependent on IDS and firmware development.</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Printer meets specified speeds in standard and PDL tests with supported media.</t>
+          <t>Startup and air management pass reliability and performance tests.</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -2271,22 +2271,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Reuse of SuperAmp PHA, Magi and Nessie Pigment Inks</t>
+          <t>New Print Quality Goals &amp; Depletion Metrics</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Reuse the existing SuperAmp PHA, Magi and Nessie pigment inks without reformulation for the new platform.</t>
+          <t>Define and implement new print quality goals and depletion metrics to align with the new page yield definition.</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>To reduce R&amp;D costs and leverage proven ink technologies.</t>
+          <t>Ensures product performance meets customer and business expectations.</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2296,21 +2296,21 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing, Supply Chain</t>
+          <t>R&amp;D, Quality, Product Management</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ink compatibility, printhead integration.</t>
+          <t>Dependent on ink system and firmware updates.</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>No ink reformulation required; print quality and reliability match or exceed current benchmarks.</t>
+          <t>Print quality and depletion metrics validated in product testing.</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -2321,22 +2321,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Security: Gauss4.xx (HW &amp; FW)</t>
+          <t>Reuse of Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU, Stingray Wi-Fi Module, and Dune FW</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Implement Gauss4.xx hardware and firmware security features in the printer.</t>
+          <t>Leverage existing electronics and firmware components to reduce development time and cost.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>To ensure device and data security in line with HP and industry standards.</t>
+          <t>Speeds time to market and leverages proven, reliable components.</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2346,21 +2346,21 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>IT, Security, Enterprise Customers</t>
+          <t>R&amp;D, Firmware, Hardware</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hardware and firmware design, compliance testing.</t>
+          <t>Dependent on compatibility with new platform.</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Device passes all internal and external security audits for Gauss4.xx compliance.</t>
+          <t>All reused components pass integration and reliability testing.</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -2371,46 +2371,46 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>EPS Foam Packaging</t>
+          <t>Gauss4.xx Security (HW &amp; FW)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Utilize EPS foam packaging for safe product shipment.</t>
+          <t>Implement Gauss4.xx hardware and firmware security features.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>To minimize damage during transportation and handling.</t>
+          <t>Ensures product security and compliance with HP standards.</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Logistics, End Users</t>
+          <t>Security, Firmware, Product Management</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Packaging design, supplier sourcing.</t>
+          <t>Dependent on hardware and firmware integration.</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>No reported shipping damages in &gt;99% of shipments using EPS foam.</t>
+          <t>Security features pass HP security compliance testing.</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -2421,22 +2421,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Blue Angel for PDL SKU</t>
+          <t>High Throughput: 25/20 ppm (PDL: 25/19 ppm)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Ensure Blue Angel certification for PDL SKU to meet eco-label requirements.</t>
+          <t>Product must achieve print speeds of 25/20 ppm (pages per minute), with PDL throughput of 25/19 ppm.</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>To access eco-sensitive markets and fulfill customer procurement requirements.</t>
+          <t>Addresses market demand for high-speed printing and competitive positioning.</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2446,17 +2446,17 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Marketing, Regulatory, Enterprise Customers</t>
+          <t>Product Management, End Users</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Product design, documentation, certification process.</t>
+          <t>Dependent on print engine and firmware optimization.</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>PDL SKU is certified by Blue Angel by launch.</t>
+          <t>Product validated to achieve specified print speeds in standard test conditions.</t>
         </is>
       </c>
       <c r="I41" t="n">
@@ -2465,6 +2465,256 @@
       <c r="J41" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>SMB Solution and Manageability</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Provide SMB (Small and Medium Business) manageability features and solutions, including scan and enterprise support (WJA, HPSM, JAM).</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Meets needs of business customers and differentiates from competitors.</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>SMB Customers, Product Management, IT Admins</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Dependent on firmware and solution integration.</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>SMB manageability features available and functional in release firmware.</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>PaaS Support for WorkFromHome/Flexworker</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Enable Platform as a Service (PaaS) support for WorkFromHome and Flexworker use cases.</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Addresses changing work patterns and increases product relevance.</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Product Management, Marketing, End Users</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Dependent on PaaS platform integration.</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>WorkFromHome/Flexworker support available in PaaS offerings.</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Onboarding Paths for Multiple Segments</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Provide onboarding and S&amp;O (Setup &amp; Onboarding) paths for Consumer/HPX, HP One, SMB Portal, and ECP segments.</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Improves customer experience and broadens market reach.</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Product Management, End Users, IT Admins</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Dependent on onboarding workflow and solution integration.</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>All onboarding paths available and validated in product launch.</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Multi-Client and Driver Support</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Support HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD clients and drivers for maximum compatibility.</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Ensures broad compatibility with customer environments and IT infrastructures.</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>IT Admins, End Users, Product Management</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Dependent on driver development and integration.</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>All listed clients and drivers available and validated at launch.</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Strategic Segmentation and Competitive Positioning</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Protect Micro/SMB segments, lead with LaserJet, flank with PDL in Medium and Enterprise, and target CISS growth against competitors (e.g., Epson).</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Ensures HP retains and grows market share in key segments.</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Business Management, Product Management, Marketing</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Dependent on product positioning and marketing strategy.</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Segment strategies reflected in go-to-market and product launch plans.</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
     </row>

--- a/consolidation/outputs/consolidated_requirements.xlsx
+++ b/consolidation/outputs/consolidated_requirements.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K52"/>
+  <dimension ref="A1:K65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,17 +481,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Business Ink Tank Printer</t>
+          <t>Business Ink Tank Solution</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Develop HP's first business ink tank printer, targeting SMBs (5-250 employees, 6-15 printers, AMPV ~500 pages), offering lowest business TCO and powerful performance.</t>
+          <t>Develop HP’s first business ink tank printer targeted at SMBs, offering high-performance, cost-effective printing with low total cost of ownership (TCO).</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Address gap in HP's portfolio for CISS PLE Hi segment, retain SMB market share, and compete with emerging CISS solutions.</t>
+          <t>HP needs to fill a gap in the CISS PLE Hi segment and defend its SMB market share from competitors.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -506,18 +506,16 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>CISS technology integration, cost optimization, performance benchmarks.</t>
+          <t>['Sustainability features', 'AI productivity solutions']</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Product launch with ink tank technology, lowest TCO compared to HP's business printers, meets SMB usage profile.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0.95</t>
-        </is>
+          <t>Printer is released with ink tank technology, achieves lowest business TCO, and is marketed as HP’s first business ink tank.</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>0.95</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -534,17 +532,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AI Productivity, Scan Workflow &amp; Manageability Solutions</t>
+          <t>AI Productivity and Manageability Solutions</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Integrate advanced AI features for productivity, scan workflow, and device manageability, including a consolidated SMB portal.</t>
+          <t>Integrate advanced AI features for productivity and manageability, including Perfect Print, Perfect Scan, and an SMB portal for device management.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Enhance ease of management for SMBs with limited IT resources, differentiate from competitors with AI-driven solutions.</t>
+          <t>SMBs require easy-to-use, efficient solutions to manage their business printing without dedicated IT teams.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -554,23 +552,21 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>['Marketing', 'GXD', 'Quality', 'R&amp;D Telemetry', 'Supplies Quality', 'DVAR']</t>
+          <t>['Marketing', 'GXD', 'Quality', 'R&amp;D Telemetry']</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SMB portal development, AI feature integration, device management tools.</t>
+          <t>['SMB portal development', 'Device management features']</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Portal operational with AI-driven print/scan/support, validated by usability testing with SMB users.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0.9</t>
-        </is>
+          <t>AI features (Perfect Print/Scan) and SMB portal are fully functional and tested in the released product.</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>0.93</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -587,47 +583,45 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Customer Replaceable Maintenance Box</t>
+          <t>Consolidated Portal for Device Management (SMB Portal)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Design maintenance box to be customer-replaceable, reducing service intervention and downtime for SMBs.</t>
+          <t>Develop a consolidated portal for SMBs to manage printers, targeting unmanaged or lightly managed businesses, supporting device registration, setup, and ongoing management.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Minimize intervention, improve serviceability, and address new SMB segment use cases.</t>
+          <t>Office managers and generalist IT staff need a simple, unified interface to manage multiple printers.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>['Quality', 'R&amp;D Telemetry', 'Supplies Quality']</t>
+          <t>['GXD', 'Marketing', 'R&amp;D Telemetry']</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Service center support, maintenance box design, warranty policies.</t>
+          <t>['AI solutions integration']</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Maintenance box can be replaced by end users (office manager/generalist IT) with instructions, validated via field trials.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0.85</t>
-        </is>
+          <t>Portal is available, supports all required device management functions, and is validated with SMB user groups.</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>0.92</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan MRD, Page 7, 10, 11</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -640,17 +634,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Keyed Ink Bottles</t>
+          <t>Maintenance-Free or Reduced Maintenance Design</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Implement keyed ink bottles to prevent incorrect refilling and ensure compatibility with Magellan printers.</t>
+          <t>Design printer with maintenance-free or less maintenance features, including customer-replaceable parts and a replaceable maintenance box.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Reduce user error, improve reliability, and support sustainable supply chain.</t>
+          <t>SMBs without dedicated IT teams need printers that require minimal intervention and are easy to service.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -660,27 +654,25 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>['Supplies Quality', 'Quality']</t>
+          <t>['Quality', 'R&amp;D Telemetry', 'Supplies Quality']</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ink bottle design, printer compatibility checks.</t>
+          <t>['Serviceability features']</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Keyed bottles accepted only by Magellan printers; tested for error prevention in user scenarios.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0.9</t>
-        </is>
+          <t>Maintenance box is customer-replaceable, printer requires fewer parts to replace over its lifetime compared to competitors.</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0.85</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan MRD, Page 4, 11</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -693,47 +685,45 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Non-PDL SKU: SMB2.0 Solutions &amp; Advanced View SMB Portal</t>
+          <t>Sustainability – 60% Recycled Content Plastic (RCP)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Support SMB2.0 Solutions and Advanced View SMB portal for device management and monitoring for non-PDL SKUs.</t>
+          <t>Ensure printer is manufactured with at least 60% recycled content plastic (RCP), surpassing competitor benchmarks (Epson 30%, Canon TBC).</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Enable advanced manageability and monitoring for SMBs, especially unmanaged/lightly managed environments.</t>
+          <t>Sustainability is a key differentiator for SMB customers and aligns with HP’s corporate goals.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>['GXD', 'R&amp;D Telemetry']</t>
+          <t>['Prod Steward', 'Marketing']</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Portal development, SMB2.0 solution integration.</t>
+          <t>['Supply chain sourcing']</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Portal features available for non-PDL SKUs, verified via acceptance testing.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>0.85</t>
-        </is>
+          <t>Final product is independently verified to contain minimum 60% RCP in its construction.</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>0.9</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan MRD, Page 11</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -746,17 +736,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PDL SKU: Speed &amp; PDL/PS Support</t>
+          <t>Warranty and Serviceability</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Enhance speed for PDL SKUs (target: 25/20 min improvement) and ensure PDL/PS support.</t>
+          <t>Offer warranty of 80,000 pages or 2 years (whichever is first). Implement PHA (customer replaceable parts) and MINK (service center replaceable parts) thresholds for serviceability.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Meet performance expectations for SMBs and provide compatibility with professional workflows.</t>
+          <t>SMBs need reliable products with clear service options and minimal downtime.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -766,23 +756,21 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>['Marketing', 'GXD', 'Quality']</t>
+          <t>['Quality', 'Supplies Quality', 'R&amp;D Telemetry']</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Firmware development, hardware optimization.</t>
+          <t>['Maintenance design']</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>PDL SKU achieves specified speed improvement and supports PDL/PS; validated via performance tests.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0.9</t>
-        </is>
+          <t>Warranty terms are published, serviceability features implemented, and customer replaceability tested.</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>0.92</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -799,17 +787,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Blue Angel Certification</t>
+          <t>Keyed Bottles for Ink Refill</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Obtain Blue Angel environmental certification for Magellan printers.</t>
+          <t>Use keyed bottles for ink refilling to prevent incorrect installation and ensure ease of use for SMBs.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Demonstrate sustainability, meet regulatory requirements, and differentiate from competitors.</t>
+          <t>Reduces user error and simplifies maintenance for non-IT staff.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -819,23 +807,21 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>['Tech Reg', 'Prod Steward']</t>
+          <t>['Supplies Quality']</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Printer design, sustainability features, certification process.</t>
+          <t>['Ink tank design']</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Blue Angel certificate awarded for Magellan product line.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>0.85</t>
-        </is>
+          <t>Ink refill bottles are keyed, tested for user error prevention, and validated in usability studies.</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>0.88</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -852,43 +838,41 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Warranty Policy: 80k Pages or 2 Years</t>
+          <t>PDL SKU Performance</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Offer warranty coverage for 80,000 pages or 2 years, whichever comes first.</t>
+          <t>PDL SKU must support improved speed (25/20 min vs. current 25/19), PDL/PS support, and Blue Angel certification.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Provide assurance to SMB customers, align with competitive offerings, and manage risk.</t>
+          <t>Competitive performance and compliance are required for market success.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>['Quality', 'Marketing']</t>
+          <t>['Tech Reg', 'Quality']</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Warranty process, service center readiness.</t>
+          <t>['Hardware design', 'Software support']</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Warranty terms published and supported by HP service network; verified via customer documentation.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>0.95</t>
-        </is>
+          <t>PDL SKU meets speed targets, supports PDL/PS, and achieves Blue Angel certification.</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>0.87</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -905,47 +889,45 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Sustainability: 60% RCP</t>
+          <t>Mobile Printing via HP App</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ensure printer is manufactured with at least 60% recycled content plastic (RCP), surpassing competitors (Epson 30%).</t>
+          <t>Enable mobile printing functionality through the HP App for SMB users.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Position HP as sustainability leader, meet customer demand for eco-friendly products.</t>
+          <t>SMBs increasingly use mobile devices and require convenient printing solutions.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>['Prod Steward', 'Tech Reg']</t>
+          <t>['GXD', 'Marketing']</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Supply chain sourcing, manufacturing process, certification.</t>
+          <t>['App integration']</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>RCP percentage validated by third-party audit; included in product documentation.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>0.9</t>
-        </is>
+          <t>HP App supports mobile printing for Magellan printers, validated by SMB user testing.</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>0.9</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 11</t>
+          <t>Magellan MRD, Page 9</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -958,17 +940,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Maintenance Free or Less Maintenance</t>
+          <t>SMB2.0 Solutions and Advanced View SMB Portal Support (Non-PDL SKU)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Design printer with minimal maintenance requirements and fewer parts to replace over its lifetime.</t>
+          <t>Non-PDL SKU must support SMB2.0 Solutions and Advanced View SMB portal, and enable Platform-as-a-Service (PaaS).</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Reduce downtime, increase reliability for SMBs, and differentiate from competitors.</t>
+          <t>Expands solution offerings for SMBs and supports HP’s PaaS strategy.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -978,27 +960,25 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>['Quality', 'R&amp;D Telemetry']</t>
+          <t>['DVAR', 'BA']</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Component design, reliability testing.</t>
+          <t>['Portal development']</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Maintenance schedule reduced vs. traditional models; validated by lifecycle tests.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>0.8</t>
-        </is>
+          <t>Non-PDL SKU is integrated with SMB2.0 Solutions and Advanced View SMB portal, PaaS functionality is enabled.</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>0.89</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 11</t>
+          <t>Magellan MRD, Page 4, 10</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1011,17 +991,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PaaS Support</t>
+          <t>Telemetry Requirements</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Enable Printer-as-a-Service (PaaS) capabilities for Magellan printers.</t>
+          <t>Implement telemetry features for remote monitoring, device health, and usage analytics.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Support new business models, increase flexibility for SMBs, and align with HP strategic goals.</t>
+          <t>HP and SMBs need visibility into device performance for proactive support and optimization.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1031,27 +1011,25 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>['Marketing', 'DVAR', 'BA']</t>
+          <t>['R&amp;D Telemetry', 'Quality']</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>PaaS platform integration, billing system, device connectivity.</t>
+          <t>['Portal integration']</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Magellan printers operational within PaaS framework; verified by pilot deployments.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>0.85</t>
-        </is>
+          <t>Telemetry features are implemented, data is accessible via SMB portal, and meets HP analytics standards.</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>0.88</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 10</t>
+          <t>Magellan MRD, Page 12</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1064,17 +1042,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Mobile Printing via HP App</t>
+          <t>PaaS Support</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Support seamless mobile printing through HP App for SMB users.</t>
+          <t>Magellan must support Platform-as-a-Service (PaaS) capabilities for SMBs.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Enable flexible printing workflows, address mobile-first SMB environments.</t>
+          <t>Aligns with HP’s strategic goal for PaaS acceleration and coverage.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1084,99 +1062,95 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>['GXD', 'Marketing']</t>
+          <t>['DVAR', 'BA']</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>HP App compatibility, device connectivity.</t>
+          <t>['Portal and solution integration']</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Magellan printer recognized and operational in HP App; tested with SMB user scenarios.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>0.9</t>
-        </is>
+          <t>Magellan printer is compatible with HP’s PaaS offerings, validated in pilot deployments.</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>0.86</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 9</t>
+          <t>Magellan MRD, Page 4, 10</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+      <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Telemetry Requirements</t>
+          <t>NGB Keyed Ink Bottles with High Page Yield</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Integrate telemetry features for remote monitoring, diagnostics, and usage analytics.</t>
+          <t>Develop new NGB keyed ink bottles with 6,000-page yield for Black and CMY, and bottle size for CMY exceeding 8,000 pages.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Enable proactive support, improve manageability for SMBs, and enhance product reliability.</t>
+          <t>To meet market demand for higher page yield and reduce user intervention for ink replacement.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>['R&amp;D Telemetry', 'Quality']</t>
+          <t>R&amp;D, Product Management, End Users</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Telemetry module, portal integration.</t>
+          <t>Requires compatibility with CISS IDS and tank integration.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Telemetry data available and actionable in SMB portal; validated by field tests.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>0.85</t>
-        </is>
+          <t>Black and CMY bottles are keyed and deliver at least 6,000 pages for Black, 6,000 pages for CMY, and CMY bottle size supports &gt;8,000 pages.</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>0.95</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 12</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>NGB Keyed Bottles with High Page Yield</t>
+          <t>Spill-Free Reliability for Ink Bottles</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>The Magellan printer must support NGB keyed bottles with 6K Black and 6K CMY page yield. The bottle size for CMY should be greater than 8K.</t>
+          <t>Ensure spill-free reliability in bottle design and operation.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>To meet high page yield demands and provide spill-free reliability for customers, especially in SMB and enterprise segments.</t>
+          <t>To prevent ink wastage and mess during bottle handling and refilling, improving customer experience.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1186,17 +1160,17 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>R&amp;D, SMB, Enterprise Customers, Product Management</t>
+          <t>R&amp;D, End Users, Quality Assurance</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bottle design, IDS integration, ink stability modeling.</t>
+          <t>Dependent on bottle and tank design improvements.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Given the printer is loaded with NGB keyed bottles, when printing, then it should achieve 6K Black and 6K CMY page yields and CMY bottle size &gt;8K without spills.</t>
+          <t>Ink bottles must pass spill-free reliability tests under normal use conditions.</t>
         </is>
       </c>
       <c r="I15" t="n">
@@ -1209,7 +1183,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1217,17 +1191,17 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Spill-Free Reliability for Ink Bottles</t>
+          <t>NOA-F with Metal Foiled Labyrinth and Lid Label</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>The Magellan printer must deliver spill-free reliability during bottle installation and usage, including NOA-F with metal foiled labyrinth and lid label.</t>
+          <t>Integrate NOA-F with a metal foiled labyrinth and lid label, with no change to push-push and TDF mechanisms.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>To reduce mess and improve customer satisfaction during ink refilling and maintenance.</t>
+          <t>To improve reliability and traceability of NOA-F, while maintaining existing user interface.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1237,21 +1211,21 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>End Users, R&amp;D, Service Teams</t>
+          <t>R&amp;D, Manufacturing, Quality Assurance</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>NOA-F design, bottle engineering, lid label integration.</t>
+          <t>Dependent on NOA-F component design and assembly.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Given a user installs a bottle, when ink is transferred, then there should be no spills or leakage.</t>
+          <t>NOA-F units incorporate metal foiled labyrinth and lid label, and retain push-push and TDF mechanisms.</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1260,7 +1234,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1268,17 +1242,17 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>NOA-F Service Parts for Warranty Support</t>
+          <t>Reuse SuperAmp Si PHA</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>NOA-F components must be available as service parts to support warranty claims within the Magellan printer lifecycle.</t>
+          <t>Reuse SuperAmp Si PHA in the new Magellan printer design.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>To enable effective warranty support and reduce downtime for customers.</t>
+          <t>To leverage proven technology and reduce development costs.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1288,21 +1262,21 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Service Teams, Warranty Support, Customers</t>
+          <t>R&amp;D, Manufacturing, Cost Management</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>NOA-F inventory, service logistics.</t>
+          <t>Dependent on compatibility with new platform and ink systems.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Given a warranty claim, when service is performed, then NOA-F parts must be available and replaceable.</t>
+          <t>SuperAmp Si PHA is integrated and functional in Magellan printer prototypes.</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1311,7 +1285,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1319,41 +1293,41 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Acumen 6 Integration on Lid</t>
+          <t>Reuse Magi / Nessie Ink (No Ink Reformulation)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>The printer must integrate Acumen 6 technology on the ink bottle lid for improved reliability and traceability.</t>
+          <t>Use existing Magi and Nessie pigment inks without reformulation.</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>To enhance product reliability and enable traceability for service and quality control.</t>
+          <t>To maintain ink quality, compatibility, and reduce validation cycles.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality Assurance, Service Teams</t>
+          <t>R&amp;D, Manufacturing, Supply Chain</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lid engineering, Acumen 6 tech integration.</t>
+          <t>Dependent on ink system compatibility.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Given a bottle lid, when inspected, then Acumen 6 features must be present and functional.</t>
+          <t>Magellan printer operates with Magi and Nessie inks without reformulation.</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1362,7 +1336,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1370,17 +1344,17 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Factory Configuration for NOA-F and Ink Cart</t>
+          <t>Reliability, WVTR, Air Gain, Flow Rate, and IDS Characterization &amp; Modelling</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Modify existing SA 14 line for NOA-F and add Magi ink cart and labelling tool in Orcus 5. Mold for 1 to 4 new keyed caps.</t>
+          <t>Characterize and model reliability, WVTR (Water Vapor Transmission Rate), air gain, flow rate, and IDS (Ink Delivery System), including startup and NOA-F End of Life.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>To support production of new components and streamline manufacturing.</t>
+          <t>To ensure consistent performance and reliability throughout product lifecycle.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1390,21 +1364,21 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Manufacturing, R&amp;D, Operations</t>
+          <t>R&amp;D, Quality Assurance</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>SA 14 line, Orcus 5, new cap molds.</t>
+          <t>Requires data collection and modelling tools.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Given factory setup, when production starts, then NOA-F, Magi ink cart, and new keyed caps must be produced without bottlenecks.</t>
+          <t>Validated models and test reports for reliability, WVTR, air gain, flow rate, and IDS characterization.</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1413,7 +1387,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -1421,41 +1395,41 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Support Customer Replaceable PHA and NOA-F</t>
+          <t>Ink Stability Modelling for Tank and PQ Impact</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>The printer must allow customers to replace PHA and NOA-F components easily, reducing service calls and downtime.</t>
+          <t>Model ink stability in tank and its impact on print quality (PQ).</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>To improve serviceability and reduce maintenance costs.</t>
+          <t>To optimize ink performance and maintain high print quality over time.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>End Users, Service Teams, Product Management</t>
+          <t>R&amp;D, Quality Assurance</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>PHA and NOA-F design for user replaceability.</t>
+          <t>Requires tank design and ink system data.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Given a customer needs to replace PHA or NOA-F, when following instructions, then replacement should be possible without technical assistance.</t>
+          <t>Ink stability models demonstrate minimal PQ degradation over expected tank life.</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1464,7 +1438,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -1472,17 +1446,17 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>New Warranty Page Life Goal of 80k Pages</t>
+          <t>NOA-F as Service Parts in Warranty Support</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>The Magellan printer must support a new warranty page life goal of 80,000 pages for key components.</t>
+          <t>NOA-F components must be available as service parts for warranty support.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>To align with customer expectations and competitive benchmarks for durability and reliability.</t>
+          <t>To enable efficient service and repair during warranty period.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1492,21 +1466,21 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Product Management, Warranty Support, Customers</t>
+          <t>Service, Warranty, End Users</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Component durability, page yield validation.</t>
+          <t>Requires supply chain and inventory management.</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Given normal usage, when the printer reaches 80k pages, then components should still be within warranty and functional.</t>
+          <t>NOA-F parts are stocked and available for warranty service requests.</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.92</v>
+        <v>0.9</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1515,7 +1489,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -1523,17 +1497,17 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Reddington ID with Tank Size Increase</t>
+          <t>Acumen 6 on Lid</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>The product must use Reddington ID with an increase in tank size to accommodate higher ink volumes. No change to Marconi-HI ADF.</t>
+          <t>Integrate Acumen 6 technology on the lid of Magellan printer.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>To support higher page yields and reduce refill frequency.</t>
+          <t>To enhance lid functionality and possibly improve security or user experience.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1543,17 +1517,17 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Product Design, R&amp;D, Customers</t>
+          <t>R&amp;D, Product Management</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tank engineering, Reddington ID integration.</t>
+          <t>Dependent on lid design and Acumen 6 integration.</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Given the printer design, when inspected, then tank size must be increased and compatible with Reddington ID.</t>
+          <t>Acumen 6 is operational and validated on printer lid.</t>
         </is>
       </c>
       <c r="I22" t="n">
@@ -1566,7 +1540,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -1574,41 +1548,41 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>EPS Foam Packaging</t>
+          <t>Factory Configuration Updates for NOA-F and Ink Cart</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>The Magellan printer must be packaged using EPS foam for improved protection during shipping and handling.</t>
+          <t>Modify existing SA14 line for NOA-F, add Magi ink cart and labelling tool in Orcus 5. Assume PHA + Dry FI + USG + push-push are assembled in printer factory.</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>To reduce damage during transit and meet sustainability requirements (EPEAT3, LOT4, Blue Angel for PDL SKU).</t>
+          <t>To accommodate new components and streamline manufacturing.</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Logistics, Sustainability Teams, Customers</t>
+          <t>Manufacturing, Operations</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Packaging design, material sourcing.</t>
+          <t>Dependent on factory upgrade and process changes.</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Given packaged printer, when shipped, then EPS foam must protect against damage and meet certification requirements.</t>
+          <t>SA14 line and Orcus 5 are updated and validated for NOA-F, Magi ink cart, and labelling tool assembly.</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1617,7 +1591,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -1625,41 +1599,41 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Input and Output Tray Changes to Align with Tank Protrusion</t>
+          <t>Mold for 1 to 4 New Keyed Caps</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Input and output trays must be redesigned to accommodate tank protrusion resulting from increased tank size.</t>
+          <t>Develop mold tooling for 1 to 4 new keyed caps for ink bottles.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>To ensure smooth operation and avoid interference with tank design.</t>
+          <t>To support the new ink bottle design and prevent misfilling.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Product Design, R&amp;D, Manufacturing</t>
+          <t>R&amp;D, Manufacturing</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tank design, tray engineering.</t>
+          <t>Dependent on ink bottle design finalization.</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Given printer with increased tank, when trays are used, then they must operate without obstruction.</t>
+          <t>Molds for new keyed caps are produced and tested for compatibility.</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1668,7 +1642,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
     </row>
@@ -1676,41 +1650,41 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Size Optimization with 4.3” CGD</t>
+          <t>Leverage Watt LE / Marconi Hi mech + CISS</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Optimize printer size, including integration of 4.3” CGD display for improved user interface.</t>
+          <t>Leverage Watt LE and Marconi Hi mechanical platform and CISS (Continuous Ink Supply System) for Magellan printer.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>To enhance user experience and optimize space utilization.</t>
+          <t>To reduce development time and cost by using existing platforms.</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>End Users, Product Management, R&amp;D</t>
+          <t>R&amp;D, Manufacturing, Product Management</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Display sourcing, UI integration.</t>
+          <t>Dependent on compatibility of platforms with new features.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Given the printer, when powered on, then the 4.3” CGD display must be functional and size optimized.</t>
+          <t>Magellan printer prototypes successfully integrate Watt LE, Marconi Hi, and CISS.</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.75</v>
+        <v>0.95</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -1719,7 +1693,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
     </row>
@@ -1727,17 +1701,17 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Platform with 4 Tubes and New Tube Routing</t>
+          <t>Speed: 25/20ppm (PDL: 25/19ppm)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Leverage Sayan Sibstar tubes with new tube routing and integration for ink delivery.</t>
+          <t>Magellan printer must support print speeds of 25/20 pages per minute (PDL: 25/19ppm).</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>To improve ink flow, reliability, and support increased page life.</t>
+          <t>To meet competitive performance benchmarks for target segments.</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1747,21 +1721,21 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing, Service Teams</t>
+          <t>Product Management, Marketing, End Users</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tube engineering, platform design.</t>
+          <t>Dependent on hardware and firmware optimization.</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Given the printer, when printing, then ink must flow reliably through 4 tubes with new routing.</t>
+          <t>Printer achieves 25/20ppm (PDL: 25/19ppm) in test conditions.</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -1770,7 +1744,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
     </row>
@@ -1778,41 +1752,41 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Service Station Aerosol Management</t>
+          <t>Support Customer Replaceable PHA and NOA-F</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Implement aerosol management in the service station with spit platform changes due to tank design.</t>
+          <t>Magellan printer must allow customers to replace PHA and NOA-F components easily.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>To reduce ink aerosol emissions and improve environmental safety.</t>
+          <t>To improve serviceability and reduce downtime for end users.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Service Teams, Sustainability, R&amp;D</t>
+          <t>Service, End Users</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Service station design, spit platform engineering.</t>
+          <t>Dependent on component design and user instructions.</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Given service station operation, when in use, then aerosol emissions must be controlled and meet safety standards.</t>
+          <t>PHA and NOA-F are replaceable by customers with minimal tools and clear instructions.</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -1821,7 +1795,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
     </row>
@@ -1829,41 +1803,41 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Carriage Dynamic and Force Model Update</t>
+          <t>Support New Warranty Page Life Goal of 80k Pages</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Update carriage dynamic and force model to account for new tube routing and increased weights from tank changes.</t>
+          <t>Magellan printer must support a new warranty page life goal of 80,000 pages.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>To ensure reliable movement and prevent mechanical failures.</t>
+          <t>To provide longer warranty coverage and differentiate from competitors.</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing, Product Design</t>
+          <t>Product Management, Warranty, End Users</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tube routing, tank weight analysis.</t>
+          <t>Dependent on reliability and component durability.</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Given carriage operation, when moving, then force model must account for new weights and routing.</t>
+          <t>Printer reliably prints 80,000 pages within warranty period under standard usage.</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.75</v>
+        <v>0.95</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -1872,7 +1846,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -1880,37 +1854,37 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Paperpath Support for Increased Page Life</t>
+          <t>SKU 2 (Hi + Hi PDL) PaaS</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Design paperpath to support increased page life and durability for high volume printing.</t>
+          <t>Introduce SKU 2 with high page yield and high PDL (Page Description Language) as Product-as-a-Service (PaaS).</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>To ensure reliable operation over extended printer lifetime.</t>
+          <t>To target SMB and enterprise segments with flexible service models.</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Management, Service Teams</t>
+          <t>Product Management, Marketing, SMB, Enterprise Customers</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Paperpath engineering, durability testing.</t>
+          <t>Dependent on service platform and SKU configuration.</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Given printer operation, when printing high volumes, then paperpath must remain reliable and durable.</t>
+          <t>SKU 2 is available with high yield and high PDL, offered as PaaS.</t>
         </is>
       </c>
       <c r="I29" t="n">
@@ -1923,7 +1897,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
     </row>
@@ -1931,41 +1905,41 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Ink Maintenance Serviceable Part Post 80k Life</t>
+          <t>Reddington ID with Size Increase for Tank</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Enable ink maintenance as a serviceable part at service centers after 80k page life is reached.</t>
+          <t>Magellan printer adopts Reddington industrial design with increased tank size; no change to Marconi-HI ADF.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>To extend printer life and reduce total cost of ownership for customers.</t>
+          <t>To accommodate higher ink capacity and maintain design consistency.</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Service Centers, Customers, Product Management</t>
+          <t>R&amp;D, Product Management, Manufacturing</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Service part inventory, maintenance procedures.</t>
+          <t>Dependent on tank design and ID update.</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Given a printer at service center post 80k pages, when serviced, then ink maintenance must be possible and effective.</t>
+          <t>Printer features Reddington ID, tank size increased, ADF unchanged.</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -1974,7 +1948,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -1982,17 +1956,17 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>140ml K Bottles and xx ml CMY Bottles</t>
+          <t>EPS Foam Packaging</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Support new 140ml Black ink bottles and new CMY bottle sizes for increased yield.</t>
+          <t>Use EPS foam packaging for Magellan printer.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>To meet high volume printing needs and reduce refill frequency.</t>
+          <t>To protect product during shipping and meet environmental standards.</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2002,21 +1976,21 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Product Management, R&amp;D, Customers</t>
+          <t>Packaging, Logistics, Sustainability</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Bottle design, ink compatibility.</t>
+          <t>Dependent on packaging design and supply chain.</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Given new bottles, when installed, then printer must accept 140ml K and xx ml CMY bottles without issues.</t>
+          <t>EPS foam packaging is validated for drop/shipping tests and meets EPEAT3, LOT4, and Blue Angel requirements.</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -2025,7 +1999,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -2033,17 +2007,17 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>IDS New Make-break and FI Connection</t>
+          <t>EPEAT3 and LOT4 Requirement, Blue Angel for PDL SKU</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Implement new make-break and FI (Fluidic Interface) connection in IDS for improved reliability and ease of use.</t>
+          <t>Magellan printer must meet EPEAT3, LOT4, and Blue Angel certification requirements for PDL SKU.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>To reduce maintenance complexity and improve ink delivery system reliability.</t>
+          <t>To ensure environmental compliance and marketability in regulated markets.</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2053,21 +2027,21 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>R&amp;D, Service Teams, Manufacturing</t>
+          <t>Sustainability, Product Management, Marketing</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>IDS design, FI engineering.</t>
+          <t>Dependent on product design and certification processes.</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Given IDS operation, when connecting/disconnecting, then make-break and FI must be reliable and easy to use.</t>
+          <t>Printer achieves EPEAT3, LOT4, and Blue Angel certifications for PDL SKU.</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -2076,7 +2050,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -2084,41 +2058,41 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>LEBI Ink-tank with Increased Size, Keying, and LOI SHAID</t>
+          <t>Input Tray and Output Tray Changes for Tank Protrusion</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Leverage LEBI ink-tank design with increased size, keying, and LOI SHAID for improved compatibility and security.</t>
+          <t>Modify input and output trays to align with tank protrusion and optimize size.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>To support higher yields and prevent incorrect bottle installation.</t>
+          <t>To accommodate increased tank size and maintain usability.</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Management, Manufacturing</t>
+          <t>R&amp;D, Manufacturing, End Users</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>LEBI tank design, SHAID integration.</t>
+          <t>Dependent on tank and tray design.</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Given LEBI tank, when used, then increased size, keying, and SHAID must be functional.</t>
+          <t>Trays are redesigned and tested for compatibility with protruding tank.</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -2127,7 +2101,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -2135,17 +2109,17 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>New IDS Startup Algorithm and Air Management</t>
+          <t>4.3” CGD Display</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Develop new IDS startup algorithm and air management for improved reliability and ink flow.</t>
+          <t>Magellan printer must feature a 4.3-inch CGD (Color Graphic Display).</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>To prevent startup failures and ensure consistent ink delivery.</t>
+          <t>To improve user interface and control experience.</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2155,21 +2129,21 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>R&amp;D, Service Teams, Manufacturing</t>
+          <t>Product Management, End Users</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>IDS firmware, air management system.</t>
+          <t>Dependent on display integration and firmware.</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Given printer startup, when IDS is initialized, then algorithm must ensure reliable ink flow and air management.</t>
+          <t>Printer includes a functional 4.3-inch CGD display.</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -2178,7 +2152,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -2186,17 +2160,17 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>New Servicing and Startup Algorithm</t>
+          <t>Platform 4 Tubes – Leverage Sayan Sibstar Tubes, New Tube Routing &amp; Integration</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Implement new servicing and startup algorithm for improved maintenance and reliability.</t>
+          <t>Magellan printer platform must use 4 tubes, leveraging Sayan Sibstar tubes, with new routing and integration.</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>To reduce service time and improve printer reliability.</t>
+          <t>To optimize ink delivery and support new tank design.</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2206,21 +2180,21 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Service Teams, R&amp;D, End Users</t>
+          <t>R&amp;D, Manufacturing</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Servicing procedures, startup firmware.</t>
+          <t>Dependent on tube design and integration.</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Given printer servicing or startup, when algorithm is executed, then maintenance must be faster and more reliable.</t>
+          <t>Printer integrates 4 Sayan Sibstar tubes with new routing; validated for ink delivery.</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -2229,7 +2203,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -2237,37 +2211,37 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>New PQ Goals and Depletion to Meet Page Yield Definition</t>
+          <t>Service Station Aerosol Management with Spit Platform Changes</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Define new Print Quality (PQ) goals and depletion criteria to meet page yield definition for Magellan printer.</t>
+          <t>Service station must manage aerosol with spit platform changes due to tank design.</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>To ensure consistent print quality and align with page yield promises.</t>
+          <t>To maintain print quality and reduce maintenance issues.</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Product Management, R&amp;D, Quality Assurance</t>
+          <t>R&amp;D, Service, Quality Assurance</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>PQ testing, depletion modeling.</t>
+          <t>Dependent on service station and tank integration.</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Given printing operation, when page yield is reached, then PQ must meet defined standards.</t>
+          <t>Aerosol management system is validated and effective with new tank and spit platform.</t>
         </is>
       </c>
       <c r="I36" t="n">
@@ -2280,7 +2254,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -2288,17 +2262,17 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Reuse Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU</t>
+          <t>Carriage Dynamic and Force Model with Tube and New Weights</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Reuse Marconi Tux dASIC, Hannibal aASIC, and Raccoon PSU for Magellan printer to optimize cost and development time.</t>
+          <t>Model carriage dynamics and force considering new tube routing and weights.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>To leverage proven components and reduce investment.</t>
+          <t>To ensure reliable operation and prevent mechanical failures.</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2308,21 +2282,21 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing, Product Management</t>
+          <t>R&amp;D, Manufacturing, Quality Assurance</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Component compatibility, integration testing.</t>
+          <t>Dependent on tube integration and carriage design.</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Given printer assembly, when components are reused, then they must function as expected without integration issues.</t>
+          <t>Carriage dynamic and force models validated for new configuration.</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -2331,7 +2305,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -2339,41 +2313,41 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Stingray Wi-fi Module Integration</t>
+          <t>Paperpath to Support Increased Page Life</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Integrate Stingray Wi-fi module for wireless connectivity in Magellan printer.</t>
+          <t>Paperpath must be designed to support increased page life (80k pages).</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>To support modern connectivity requirements for SMB and enterprise customers.</t>
+          <t>To ensure durability and reliability for high-volume printing.</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>End Users, Product Management, R&amp;D</t>
+          <t>R&amp;D, Quality Assurance, End Users</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Wi-fi module sourcing, firmware integration.</t>
+          <t>Dependent on paperpath design and materials.</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Given printer, when Wi-fi is enabled, then Stingray module must provide reliable wireless connection.</t>
+          <t>Paperpath validated for 80,000-page life under standard usage.</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -2382,7 +2356,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -2390,17 +2364,17 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Dune Firmware Integration</t>
+          <t>Ink Maintenance Serviceable Part (Service Center) – Post 80k Life</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Integrate Dune firmware for Magellan printer operation and feature support.</t>
+          <t>Ink maintenance must be serviceable at Service Center after 80,000-page life.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>To enable advanced features and maintain firmware consistency.</t>
+          <t>To support post-warranty service and extend product lifecycle.</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2410,21 +2384,21 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Management, End Users</t>
+          <t>Service, End Users</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Firmware compatibility, feature testing.</t>
+          <t>Dependent on maintenance part design and service procedures.</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Given printer operation, when firmware is loaded, then Dune must support all required features.</t>
+          <t>Ink maintenance part is replaceable/serviceable after 80k page life.</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -2433,7 +2407,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -2441,17 +2415,17 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Gauss4.xx Security (HW &amp; FW)</t>
+          <t>SuperAmp PHA, NOA-F, Keyed Bottles, Magi and Nessie Pigment Inks, 140ml K Bottles (New), xx ml CMY Bottles</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Implement Gauss4.xx security for hardware and firmware to protect against threats and ensure data safety.</t>
+          <t>Magellan printer must support SuperAmp PHA, NOA-F, keyed bottles, Magi and Nessie pigment inks, new 140ml K bottles, and xx ml CMY bottles.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>To meet enterprise security requirements and protect user data.</t>
+          <t>To offer a comprehensive supply system for various print needs.</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2461,21 +2435,21 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Enterprise Customers, IT, Security Teams</t>
+          <t>R&amp;D, Supply Chain, Product Management</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>HW/FW integration, security validation.</t>
+          <t>Dependent on supply system integration and compatibility.</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Given printer operation, when security features are tested, then Gauss4.xx must prevent unauthorized access.</t>
+          <t>Printer supports all listed supplies and bottle sizes; validated in test prints.</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -2484,7 +2458,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -2492,17 +2466,17 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>EPEAT3, LOT4, Blue Angel Certification for PDL SKU</t>
+          <t>IDS New Make-Break and FI Connection</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Ensure Magellan printer meets EPEAT3, LOT4, and Blue Angel certification requirements for PDL SKU.</t>
+          <t>Implement new make-break and FI (Fluidic Interface) connection in IDS (Ink Delivery System).</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>To align with sustainability goals and regulatory requirements.</t>
+          <t>To improve reliability and ease of maintenance.</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2512,21 +2486,21 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sustainability Teams, Product Management, Customers</t>
+          <t>R&amp;D, Manufacturing, Service</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Certification process, design compliance.</t>
+          <t>Dependent on IDS redesign and component compatibility.</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Given printer SKU, when audited, then it must pass EPEAT3, LOT4, and Blue Angel certifications.</t>
+          <t>IDS features new make-break and FI connection; validated in prototype testing.</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -2535,7 +2509,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -2543,37 +2517,37 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Support Multiple Business Models and Solutions</t>
+          <t>Leverage LEBI Ink-Tank with Increased Size, Keying and LOI One SHAID</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Magellan printer must support consumer, SMB, and enterprise business models, including PaaS, WorkFromHome/Flexworker, onboarding paths (Consumer/HPX, HP One, SMB Portal, ECP), and solutions (Scan, SMB manageability, Enterprise support: WJA, HPSM, JAM).</t>
+          <t>Use LEBI ink-tank with increased size, keying, and LOI One SHAID for Magellan printer.</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>To maximize market reach and address diverse customer needs.</t>
+          <t>To support high-capacity ink supply and secure identification.</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Product Management, Sales, Customers</t>
+          <t>R&amp;D, Manufacturing, Product Management</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Solution integration, onboarding workflow.</t>
+          <t>Dependent on ink-tank design and LOI SHAID integration.</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Given deployment, when business model is selected, then printer must support relevant solutions and onboarding paths.</t>
+          <t>LEBI ink-tank is integrated with increased size, keying, and LOI One SHAID; validated in printer operation.</t>
         </is>
       </c>
       <c r="I42" t="n">
@@ -2586,7 +2560,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -2594,17 +2568,17 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Client &amp; Driver Support</t>
+          <t>New IDS Startup Algorithm and Air Management</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Magellan printer must support HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD clients and drivers for broad compatibility.</t>
+          <t>Develop new IDS startup algorithm and air management system.</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>To ensure ease of installation and operation across various customer environments.</t>
+          <t>To ensure optimal startup performance and prevent air-related failures.</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2614,21 +2588,21 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>End Users, IT, Product Management</t>
+          <t>R&amp;D, Quality Assurance</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Driver integration, client compatibility.</t>
+          <t>Dependent on IDS design and firmware.</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Given printer installation, when drivers are loaded, then all listed clients and drivers must be supported and functional.</t>
+          <t>IDS startup algorithm and air management validated for reliable printer startup.</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -2637,7 +2611,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -2645,41 +2619,41 @@
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Schedule Adherence (Q325-Q427)</t>
+          <t>New Servicing and Startup Algorithm</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Adhere to the defined schedule for hardware, NOA-F, and bottle checkpoints, and builds (Imech, BB1, BB2, TR, LP1, LP2, MP1/PP, SOR).</t>
+          <t>Implement new servicing and startup algorithms for Magellan printer.</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>To ensure timely delivery and meet market launch targets.</t>
+          <t>To improve reliability and reduce service incidents.</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Program Management, R&amp;D, Manufacturing</t>
+          <t>R&amp;D, Service, Quality Assurance</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Project management, milestone tracking.</t>
+          <t>Dependent on printer firmware and servicing procedures.</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Given project timeline, when checkpoints are reached, then schedule must be adhered to as defined.</t>
+          <t>Servicing and startup algorithms validated in field tests.</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -2688,7 +2662,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -2696,17 +2670,17 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SuperAmp PHA Life at 65K Pages</t>
+          <t>New Print Quality Goals &amp; Depletion to Meet Page Yield Definition</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>SuperAmp PHA component must support life of at least 65,000 pages before replacement.</t>
+          <t>Set new print quality (PQ) goals and depletion metrics to meet defined page yield.</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>To ensure durability and reduce maintenance frequency.</t>
+          <t>To ensure consistent print quality and accurate yield reporting.</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2716,30 +2690,30 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Product Management, Service Teams, Customers</t>
+          <t>R&amp;D, Quality Assurance, Product Management</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>PHA engineering, life testing.</t>
+          <t>Dependent on ink system and PQ testing.</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Given printer operation, when SuperAmp PHA reaches 65K pages, then it must remain functional without failure.</t>
+          <t>PQ goals and depletion metrics validated for defined page yield.</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -2747,17 +2721,17 @@
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Warranty Life of Pages (2 Years)</t>
+          <t>Reuse Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU, Stingray Wi-fi Module, FW Dune</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Magellan printer must offer warranty life of pages for at least 2 years.</t>
+          <t>Reuse Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU, Stingray Wi-fi module, and FW Dune in Magellan printer.</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>To increase customer confidence and align with competitive standards.</t>
+          <t>To leverage proven electronic and firmware components, reducing development risk and cost.</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2767,30 +2741,30 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Warranty Support, Product Management, Customers</t>
+          <t>R&amp;D, Manufacturing, Cost Management</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Component durability, warranty policy.</t>
+          <t>Dependent on compatibility with Magellan platform.</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Given printer purchase, when warranty is claimed within 2 years, then coverage must be provided for page life.</t>
+          <t>All listed components are integrated and validated in Magellan printer.</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -2798,17 +2772,17 @@
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Throughput of 25/20 PPM (PDL)</t>
+          <t>Gauss4.xx Security for Hardware and Firmware</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Magellan printer must achieve throughput of 25 pages per minute (ppm) and 20 ppm for PDL.</t>
+          <t>Implement Gauss4.xx security for hardware and firmware in Magellan printer.</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>To meet productivity requirements for SMB and enterprise users.</t>
+          <t>To ensure robust security and protect against threats.</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2818,17 +2792,17 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Product Management, SMB, Enterprise Customers</t>
+          <t>R&amp;D, Security, Product Management</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Printer engine design, speed validation.</t>
+          <t>Dependent on hardware and firmware integration.</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Given printing operation, when tested, then throughput must reach 25/20 ppm as defined.</t>
+          <t>Gauss4.xx security features operational and validated in Magellan printer.</t>
         </is>
       </c>
       <c r="I47" t="n">
@@ -2836,12 +2810,12 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -2849,50 +2823,50 @@
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Serviceability (Maintenance Box)</t>
+          <t>Business Model: Consumer, SMB, and Enterprise Support</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Magellan printer must provide easy serviceability, including maintenance box for quick access and servicing.</t>
+          <t>Magellan printer must support business models for Consumer, SMB, and Enterprise segments.</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>To reduce maintenance time and improve customer satisfaction.</t>
+          <t>To expand market reach and address diverse customer needs.</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Service Teams, End Users, Product Management</t>
+          <t>Product Management, Marketing, Sales</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Maintenance box design, service workflow.</t>
+          <t>Dependent on solution and service platform integration.</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Given printer maintenance, when box is accessed, then service must be performed easily and efficiently.</t>
+          <t>Printer and services are available for Consumer, SMB, and Enterprise customers.</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -2900,17 +2874,17 @@
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SMB Solution Support</t>
+          <t>Solution and Services: Scan Solution, SMB Manageability, Enterprise Support</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Magellan printer must offer SMB solution features for manageability and productivity.</t>
+          <t>Magellan printer must provide scan solution, SMB manageability, and enterprise support (WJA, HPSM, JAM).</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>To address SMB customer needs and differentiate from competitors.</t>
+          <t>To offer comprehensive solutions for targeted segments.</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2920,30 +2894,30 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>SMB Customers, Product Management, Sales</t>
+          <t>Product Management, SMB, Enterprise Customers</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Solution integration, feature development.</t>
+          <t>Dependent on software and service integration.</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Given SMB deployment, when solution is used, then manageability features must be functional.</t>
+          <t>Printer supports scan solution, SMB manageability, and enterprise features (WJA, HPSM, JAM).</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>36</t>
         </is>
       </c>
     </row>
@@ -2951,50 +2925,50 @@
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t>PaaS (Print as a Service) Schedule Support</t>
+          <t>Clients &amp; Drivers: HPX, PSA, SUPD, UPD, EasyStart, USS, UFD</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Magellan printer must be compatible with PaaS business model and schedule requirements.</t>
+          <t>Magellan printer must support clients and drivers including HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD.</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>To enable flexible business offerings and align with market trends.</t>
+          <t>To ensure compatibility with HP ecosystem and user platforms.</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Product Management, Sales, SMB, Enterprise Customers</t>
+          <t>R&amp;D, Product Management, End Users</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>PaaS workflow, schedule integration.</t>
+          <t>Dependent on driver and client integration.</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Given PaaS deployment, when schedule is followed, then printer must support business model requirements.</t>
+          <t>Printer supports all listed clients and drivers; validated in installation tests.</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>37</t>
         </is>
       </c>
     </row>
@@ -3002,41 +2976,41 @@
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Host 12K-CMYK Capability (Flexible Priority)</t>
+          <t>Protect Micro/SMB Segments and Safeguard HP’s Ink/Laser Profit Pool</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Magellan printer should be capable of hosting 12K CMYK page yields, subject to flexible prioritization.</t>
+          <t>Magellan printer must be designed to protect HP's market share in Micro and SMB segments and prevent profit pool erosion to competitors.</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>To address future high volume needs and allow flexibility in product roadmap.</t>
+          <t>To maintain HP's leadership and profitability.</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Product Management, R&amp;D, Customers</t>
+          <t>Product Management, Marketing, Sales</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Ink system scaling, bottle design.</t>
+          <t>Dependent on competitive features and pricing.</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Given printer upgrade, when tested, then 12K CMYK hosting must be possible if prioritized.</t>
+          <t>Market share in Micro/SMB segments maintained or increased post-launch.</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -3045,7 +3019,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>38</t>
         </is>
       </c>
     </row>
@@ -3053,50 +3027,713 @@
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Trade Page 6K (Flexible Priority)</t>
+          <t>Lead with LaserJet and Flank with PDL in Medium and Enterprise</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Magellan printer should support trade page yield of 6K, allowing flexibility in prioritization.</t>
+          <t>Magellan printer must support strategy to lead with LaserJet and flank with PDL in Medium and Enterprise segments to win over competitors.</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>To address market trade segment needs with flexible prioritization.</t>
+          <t>To strengthen HP’s position in Medium and Enterprise segments against competitors like Epson.</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Product Management, Marketing, Sales</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Dependent on product positioning and feature set.</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Competitive positioning validated in market analysis and sales results.</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Grow CISS Profitable Share by Playing in New Segments</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Magellan printer must enable growth of profitable CISS share by targeting new market segments.</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>To expand HP's CISS market share and profitability.</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Product Management, Marketing, Sales</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Dependent on segment identification and tailored features.</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>CISS share grows in new segments post-launch.</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr"/>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Highly Leverage Watt-LE Mech Platform, Marconi-Hi Product (Reddington ID), and Solutions</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Magellan printer must leverage Watt-LE mechanical platform, Marconi-Hi product (Reddington ID), and solutions for development.</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>To reduce development time and cost by using proven platforms and solutions.</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>R&amp;D, Manufacturing, Product Management</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Dependent on platform compatibility.</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Magellan printer development leverages all listed platforms and solutions.</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr"/>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Integrate CISS IDS, NOA-F, and Ink Tanks</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Magellan printer must integrate CISS IDS, NOA-F, and ink tanks for seamless operation.</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>To optimize ink delivery and reliability.</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>R&amp;D, Manufacturing, Product Management</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Dependent on system integration and compatibility.</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Printer integrates CISS IDS, NOA-F, and ink tanks; validated in operation tests.</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr"/>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>New NGB Keyed Ink Bottles</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Magellan printer must use new NGB keyed ink bottles.</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>To prevent misfilling and ensure correct ink usage.</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>R&amp;D, Manufacturing, End Users</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Dependent on bottle design and keying system.</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Printer accepts only keyed NGB bottles; validated in user tests.</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr"/>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Schedule Constraint: Q3 2025 Launch</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Magellan printer development must adhere to schedule with launch by August 20, 2025 (Q3 2025).</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>To meet market timing and business objectives.</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Product Management, R&amp;D, Manufacturing, Marketing</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Dependent on project management and milestone tracking.</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Printer is launched by August 20, 2025.</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr"/>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>SuperAmp PHA Life at 65K Pages (Constraint)</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>SuperAmp PHA must have a life of 65,000 pages as a constraint.</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>To ensure reliability and meet service requirements.</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>R&amp;D, Service, Quality Assurance</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Dependent on PHA design and testing.</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>SuperAmp PHA reliably operates for 65,000 pages.</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr"/>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Warranty Life of Pages, 2 Years (Optimize)</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Magellan printer must optimize for warranty life of pages and 2-year coverage.</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>To provide competitive warranty terms and customer assurance.</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Product Management, Warranty, End Users</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Dependent on reliability and warranty policy.</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Printer is warranted for defined page life and 2 years.</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr"/>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Throughput 25/20 PDL (Optimize)</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Magellan printer must optimize for throughput of 25/20 pages per minute (PDL).</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>To meet performance expectations for target segments.</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Product Management, R&amp;D, Marketing</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Dependent on hardware and firmware optimization.</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Printer achieves throughput of 25/20 PDL in test conditions.</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr"/>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Serviceability Maintenance Box (Optimize)</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Magellan printer must optimize for serviceability via maintenance box.</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>To improve ease of maintenance and reduce downtime.</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Service, End Users, R&amp;D</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Dependent on maintenance box design and service procedures.</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Maintenance box is serviceable and validated in service tests.</t>
+        </is>
+      </c>
+      <c r="I61" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr"/>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>SMB Solution (Optimize)</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Magellan printer must optimize for SMB solution features.</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>To address SMB segment needs and improve manageability.</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Product Management, SMB Customers</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Dependent on solution integration.</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Printer delivers SMB solution features validated in SMB use cases.</t>
+        </is>
+      </c>
+      <c r="I62" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr"/>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>PaaS Schedule (Optimize)</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Magellan printer must optimize for PaaS (Product-as-a-Service) schedule.</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>To align service offerings with product launch.</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Product Management, Marketing, Service</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Dependent on PaaS platform readiness.</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>PaaS offering is available at product launch.</t>
+        </is>
+      </c>
+      <c r="I63" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr"/>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Host 12K-CMYK (Flexible)</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Magellan printer must flexibly support hosting 12,000-page yield for CMYK.</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>To enable higher capacity options for certain markets.</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Product Management, Sales, Trade Customers</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Page yield modeling, ink system design.</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Given trade segment deployment, when tested, then 6K trade page yield must be achievable if prioritized.</t>
-        </is>
-      </c>
-      <c r="I52" t="n">
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Product Management, Marketing, End Users</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Dependent on ink system and bottle design.</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Printer supports 12,000-page yield for CMYK; validated in test prints.</t>
+        </is>
+      </c>
+      <c r="I64" t="n">
         <v>0.7</v>
       </c>
-      <c r="J52" t="inlineStr">
+      <c r="J64" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>38</t>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr"/>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Trade Page 6K (Flexible)</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Magellan printer must flexibly support trade page yield of 6,000 pages.</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>To enable product configuration for trade and channel requirements.</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Product Management, Marketing, Channel Partners</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Dependent on configuration options.</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Printer supports trade page yield of 6,000 pages; validated in channel tests.</t>
+        </is>
+      </c>
+      <c r="I65" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>52</t>
         </is>
       </c>
     </row>

--- a/consolidation/outputs/consolidated_requirements.xlsx
+++ b/consolidation/outputs/consolidated_requirements.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,61 +425,61 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K65"/>
+  <dimension ref="A1:K76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Rationale</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Stakeholders</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Dependencies</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Confidence</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>citation</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Requirement ID</t>
         </is>
@@ -481,17 +493,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Business Ink Tank Solution</t>
+          <t>AI Productivity and Manageability Solutions</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Develop HP’s first business ink tank printer targeted at SMBs, offering high-performance, cost-effective printing with low total cost of ownership (TCO).</t>
+          <t>Integrate advanced AI-powered productivity features and scan workflow solutions to enhance business manageability for SMBs. Includes AI-driven print and scan optimization, automated workflows, and device management capabilities.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>HP needs to fill a gap in the CISS PLE Hi segment and defend its SMB market share from competitors.</t>
+          <t>AI solutions are a key differentiator for Magellan, addressing SMB needs for efficiency and ease of management without dedicated IT staff.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -501,17 +513,17 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>['Marketing', 'GXD', 'Quality', 'R&amp;D Telemetry', 'Supplies Quality', 'DVAR', 'Tech Reg', 'Prod Steward', 'BA']</t>
+          <t>['Marketing', 'GXD', 'Quality', 'R&amp;D Telemetry', 'BA']</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>['Sustainability features', 'AI productivity solutions']</t>
+          <t>['SMB portal for device management']</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Printer is released with ink tank technology, achieves lowest business TCO, and is marketed as HP’s first business ink tank.</t>
+          <t>AI features must be integrated and demonstrably improve productivity and manageability; validated through user testing and performance benchmarks.</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -519,7 +531,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 6, 7, 11, 12</t>
+          <t>Magellan MRD, Page 4, Page 7, Page 11</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -532,17 +544,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AI Productivity and Manageability Solutions</t>
+          <t>SMB Device Management Portal</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Integrate advanced AI features for productivity and manageability, including Perfect Print, Perfect Scan, and an SMB portal for device management.</t>
+          <t>Develop a consolidated portal for SMBs to manage multiple printers, including device status, usage analytics, maintenance alerts, and remote configuration.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SMBs require easy-to-use, efficient solutions to manage their business printing without dedicated IT teams.</t>
+          <t>Unmanaged and lightly managed SMBs require easy, centralized management as they lack dedicated IT teams.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -552,25 +564,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>['Marketing', 'GXD', 'Quality', 'R&amp;D Telemetry']</t>
+          <t>['Marketing', 'GXD', 'Quality', 'R&amp;D Telemetry', 'BA']</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>['SMB portal development', 'Device management features']</t>
+          <t>['AI Productivity and Manageability Solutions']</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>AI features (Perfect Print/Scan) and SMB portal are fully functional and tested in the released product.</t>
+          <t>Portal must support multi-device management, provide real-time analytics and maintenance notifications, and be accessible via web and mobile.</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 7, 10, 11</t>
+          <t>Magellan MRD, Page 7, Page 10</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -583,17 +595,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Consolidated Portal for Device Management (SMB Portal)</t>
+          <t>Lowest Business Total Cost of Ownership (TCO)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Develop a consolidated portal for SMBs to manage printers, targeting unmanaged or lightly managed businesses, supporting device registration, setup, and ongoing management.</t>
+          <t>Design Magellan to deliver HP’s lowest business TCO for SMBs, including cost-efficient consumables, minimal intervention, and high-yield ink tanks.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Office managers and generalist IT staff need a simple, unified interface to manage multiple printers.</t>
+          <t>Cost efficiency is a primary buying factor for SMBs; HP must compete on TCO to win market share.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -603,25 +615,25 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>['GXD', 'Marketing', 'R&amp;D Telemetry']</t>
+          <t>['Marketing', 'Quality', 'Supplies Quality', 'BA']</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>['AI solutions integration']</t>
+          <t>['Keyed bottles', 'High-yield tanks']</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Portal is available, supports all required device management functions, and is validated with SMB user groups.</t>
+          <t>TCO must be demonstrably lower than competitors in independent testing; consumables must be cost-effective and require minimal replacement.</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.92</v>
+        <v>0.9</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 7, 10, 11</t>
+          <t>Magellan MRD, Page 4, Page 11</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -634,17 +646,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Maintenance-Free or Reduced Maintenance Design</t>
+          <t>Customer Replaceable Maintenance Box</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Design printer with maintenance-free or less maintenance features, including customer-replaceable parts and a replaceable maintenance box.</t>
+          <t>Provide a maintenance box that is easily replaceable by customers, minimizing service intervention and downtime.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>SMBs without dedicated IT teams need printers that require minimal intervention and are easy to service.</t>
+          <t>SMBs need minimal maintenance and fast recovery; reducing service calls improves efficiency and customer satisfaction.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -654,25 +666,25 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>['Quality', 'R&amp;D Telemetry', 'Supplies Quality']</t>
+          <t>['Quality', 'Supplies Quality', 'DVAR']</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>['Serviceability features']</t>
+          <t>['Serviceability: PHA – customer replaceable']</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Maintenance box is customer-replaceable, printer requires fewer parts to replace over its lifetime compared to competitors.</t>
+          <t>Maintenance box must be replaceable by end-users with clear instructions; validated through usability testing.</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.85</v>
+        <v>0.88</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 11</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -685,45 +697,45 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sustainability – 60% Recycled Content Plastic (RCP)</t>
+          <t>Keyed Bottles for Ink Tanks</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ensure printer is manufactured with at least 60% recycled content plastic (RCP), surpassing competitor benchmarks (Epson 30%, Canon TBC).</t>
+          <t>Use keyed bottles for ink refilling to prevent incorrect filling and ensure ease of use.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Sustainability is a key differentiator for SMB customers and aligns with HP’s corporate goals.</t>
+          <t>Keyed bottles reduce user errors and streamline maintenance for SMBs with limited technical expertise.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>['Prod Steward', 'Marketing']</t>
+          <t>['Supplies Quality', 'Quality']</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>['Supply chain sourcing']</t>
+          <t>['High-yield ink tanks']</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Final product is independently verified to contain minimum 60% RCP in its construction.</t>
+          <t>Ink bottles must be keyed and prevent incorrect refilling; validated by error rate reduction in testing.</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.9</v>
+        <v>0.87</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 11</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -736,17 +748,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Warranty and Serviceability</t>
+          <t>High-Yield Ink Tanks</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Offer warranty of 80,000 pages or 2 years (whichever is first). Implement PHA (customer replaceable parts) and MINK (service center replaceable parts) thresholds for serviceability.</t>
+          <t>Equip Magellan with high-yield ink tanks for extended printing capacity and reduced refill frequency.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>SMBs need reliable products with clear service options and minimal downtime.</t>
+          <t>SMBs print high volumes and need efficient, low-intervention consumables.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -756,21 +768,21 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>['Quality', 'Supplies Quality', 'R&amp;D Telemetry']</t>
+          <t>['Supplies Quality', 'Quality']</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>['Maintenance design']</t>
+          <t>['Keyed bottles']</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Warranty terms are published, serviceability features implemented, and customer replaceability tested.</t>
+          <t>Ink tanks must support AMPV of 500 pages/month for 2 years or 80k pages, whichever is first.</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.92</v>
+        <v>0.9</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -787,41 +799,41 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Keyed Bottles for Ink Refill</t>
+          <t>Warranty: 80k Pages or 2 Years</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Use keyed bottles for ink refilling to prevent incorrect installation and ensure ease of use for SMBs.</t>
+          <t>Offer a warranty covering either 80,000 pages or 2 years, whichever comes first, to assure reliability and value.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Reduces user error and simplifies maintenance for non-IT staff.</t>
+          <t>SMBs need predictable, reliable service and coverage for high-volume use.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>['Supplies Quality']</t>
+          <t>['Quality', 'Marketing']</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>['Ink tank design']</t>
+          <t>['High-yield ink tanks']</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Ink refill bottles are keyed, tested for user error prevention, and validated in usability studies.</t>
+          <t>Warranty terms must be documented, and coverage validated for both page count and time duration.</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.88</v>
+        <v>0.93</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -838,17 +850,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PDL SKU Performance</t>
+          <t>PaaS (Printing as a Service) Support</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>PDL SKU must support improved speed (25/20 min vs. current 25/19), PDL/PS support, and Blue Angel certification.</t>
+          <t>Enable Magellan to support Printing as a Service (PaaS), including subscription management and advanced portal integration.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Competitive performance and compliance are required for market success.</t>
+          <t>PaaS is a strategic goal for HP and aligns with SMB needs for flexible, managed services.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -858,25 +870,25 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>['Tech Reg', 'Quality']</t>
+          <t>['Marketing', 'Tech Reg', 'Prod Steward']</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>['Hardware design', 'Software support']</t>
+          <t>['SMB portal', 'AI solutions']</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>PDL SKU meets speed targets, supports PDL/PS, and achieves Blue Angel certification.</t>
+          <t>Printer must integrate with SMB2.0 Solutions and Advanced View SMB portal, supporting PaaS workflows.</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.87</v>
+        <v>0.89</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4</t>
+          <t>Magellan MRD, Page 4, Page 10</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -889,17 +901,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Mobile Printing via HP App</t>
+          <t>PDL/PS Support for PDL SKU</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Enable mobile printing functionality through the HP App for SMB users.</t>
+          <t>Provide PDL/PS (Page Description Language/PostScript) support for PDL SKU, including speed improvements (target 25/20 min).</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>SMBs increasingly use mobile devices and require convenient printing solutions.</t>
+          <t>PDL/PS support is required for advanced office environments and compatibility with business workflows.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -909,25 +921,25 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>['GXD', 'Marketing']</t>
+          <t>['R&amp;D Telemetry', 'DVAR']</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>['App integration']</t>
+          <t>['PDL SKU']</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>HP App supports mobile printing for Magellan printers, validated by SMB user testing.</t>
+          <t>PDL SKU must achieve target speed and support PDL/PS protocols; validated by performance testing.</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 9</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -940,17 +952,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SMB2.0 Solutions and Advanced View SMB Portal Support (Non-PDL SKU)</t>
+          <t>Blue Angel Certification</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Non-PDL SKU must support SMB2.0 Solutions and Advanced View SMB portal, and enable Platform-as-a-Service (PaaS).</t>
+          <t>Ensure Magellan meets Blue Angel environmental certification for PDL SKU.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Expands solution offerings for SMBs and supports HP’s PaaS strategy.</t>
+          <t>Blue Angel certification is required for compliance and competitive positioning in certain markets.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -960,25 +972,25 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>['DVAR', 'BA']</t>
+          <t>['Prod Steward', 'Tech Reg']</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>['Portal development']</t>
+          <t>['PDL SKU']</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Non-PDL SKU is integrated with SMB2.0 Solutions and Advanced View SMB portal, PaaS functionality is enabled.</t>
+          <t>Printer must pass Blue Angel certification tests and documentation.</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 4, 10</t>
+          <t>Magellan MRD, Page 4</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -991,45 +1003,45 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Telemetry Requirements</t>
+          <t>Perfect Print and Perfect Scan</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Implement telemetry features for remote monitoring, device health, and usage analytics.</t>
+          <t>Deliver superior print and scan quality through AI-driven optimization, ensuring consistent results and minimal errors.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>HP and SMBs need visibility into device performance for proactive support and optimization.</t>
+          <t>Print and scan quality is a top customer need and competitive differentiator.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>['R&amp;D Telemetry', 'Quality']</t>
+          <t>['Quality', 'Marketing', 'GXD']</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>['Portal integration']</t>
+          <t>['AI Productivity and Manageability Solutions']</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Telemetry features are implemented, data is accessible via SMB portal, and meets HP analytics standards.</t>
+          <t>Print and scan quality must exceed industry benchmarks and be validated by independent testing.</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.88</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Magellan MRD, Page 12</t>
+          <t>Magellan MRD, Page 7, Page 11</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1042,166 +1054,166 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PaaS Support</t>
+          <t>Sustainability: 60% Recycled Content Plastic (RCP)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Magellan must support Platform-as-a-Service (PaaS) capabilities for SMBs.</t>
+          <t>Use 60% recycled content plastic in Magellan’s construction, exceeding competitor standards (Epson 30%).</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Aligns with HP’s strategic goal for PaaS acceleration and coverage.</t>
+          <t>Sustainability is a key differentiator and meets regulatory and customer expectations.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>['Prod Steward', 'Tech Reg']</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>['Material sourcing']</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Printer construction must be validated to use 60% RCP; confirmed by supply chain audits.</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Magellan MRD, Page 11</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Mobile Printing via HP App</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Enable seamless mobile printing through the HP App for SMB users.</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Mobile printing is a growing need for SMBs, supporting flexible work environments.</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>['DVAR', 'BA']</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>['Portal and solution integration']</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Magellan printer is compatible with HP’s PaaS offerings, validated in pilot deployments.</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Magellan MRD, Page 4, 10</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr"/>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>NGB Keyed Ink Bottles with High Page Yield</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Develop new NGB keyed ink bottles with 6,000-page yield for Black and CMY, and bottle size for CMY exceeding 8,000 pages.</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>To meet market demand for higher page yield and reduce user intervention for ink replacement.</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Management, End Users</t>
+          <t>['Marketing', 'GXD']</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Requires compatibility with CISS IDS and tank integration.</t>
+          <t>['SMB portal']</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Black and CMY bottles are keyed and deliver at least 6,000 pages for Black, 6,000 pages for CMY, and CMY bottle size supports &gt;8,000 pages.</t>
+          <t>Printer must support HP App integration and allow remote/mobile print jobs.</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.95</v>
+        <v>0.88</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Magellan MRD, Page 9, Page 10</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Spill-Free Reliability for Ink Bottles</t>
+          <t>Advanced Telemetry Requirements</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ensure spill-free reliability in bottle design and operation.</t>
+          <t>Implement telemetry features for remote monitoring, usage analytics, and predictive maintenance.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>To prevent ink wastage and mess during bottle handling and refilling, improving customer experience.</t>
+          <t>Telemetry improves manageability, supports PaaS, and enables proactive support for SMBs.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>R&amp;D, End Users, Quality Assurance</t>
+          <t>['R&amp;D Telemetry', 'Quality']</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dependent on bottle and tank design improvements.</t>
+          <t>['SMB portal']</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Ink bottles must pass spill-free reliability tests under normal use conditions.</t>
+          <t>Telemetry must provide real-time data, analytics, and alerting; validated by system integration tests.</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 1</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Magellan MRD, Page 3, Page 12</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>NOA-F with Metal Foiled Labyrinth and Lid Label</t>
+          <t>NGB Keyed Bottles with High Page Yield</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Integrate NOA-F with a metal foiled labyrinth and lid label, with no change to push-push and TDF mechanisms.</t>
+          <t>The Magellan printer must support NGB keyed bottles with 6,000-page yield for black and CMY inks. CMY bottle size must support yields greater than 8,000 pages.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>To improve reliability and traceability of NOA-F, while maintaining existing user interface.</t>
+          <t>High-yield bottles reduce refill frequency and support business/enterprise requirements for efficiency.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1211,21 +1223,21 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing, Quality Assurance</t>
+          <t>R&amp;D, Director, SMB, Enterprise Customers</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dependent on NOA-F component design and assembly.</t>
+          <t>Bottle design, ink compatibility, platform integration</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>NOA-F units incorporate metal foiled labyrinth and lid label, and retain push-push and TDF mechanisms.</t>
+          <t>Printer can accept and use NGB keyed bottles, achieving at least 6,000-page yield for black and CMY; CMY bottles must be sized for &gt;8,000 pages.</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1234,7 +1246,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1242,17 +1254,17 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Reuse SuperAmp Si PHA</t>
+          <t>Spill-Free Reliability for Ink Bottles</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Reuse SuperAmp Si PHA in the new Magellan printer design.</t>
+          <t>Ink bottle and tank system must ensure spill-free reliability during refilling and maintenance.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>To leverage proven technology and reduce development costs.</t>
+          <t>Prevents damage, improves user experience, and reduces warranty claims.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1262,21 +1274,21 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing, Cost Management</t>
+          <t>R&amp;D, Service Teams, End Users</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dependent on compatibility with new platform and ink systems.</t>
+          <t>Bottle design, tank interface</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>SuperAmp Si PHA is integrated and functional in Magellan printer prototypes.</t>
+          <t>No ink spills during refill or maintenance in &gt;99% of tested scenarios.</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1285,7 +1297,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1293,17 +1305,17 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Reuse Magi / Nessie Ink (No Ink Reformulation)</t>
+          <t>NOA-F with Metal Foiled Labyrinth and Lid Label</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Use existing Magi and Nessie pigment inks without reformulation.</t>
+          <t>The NOA-F must include a metal foiled labyrinth and lid label, with no changes to click-on push-push and TDF mechanisms.</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>To maintain ink quality, compatibility, and reduce validation cycles.</t>
+          <t>Enhances reliability and traceability; maintains compatibility with existing mechanisms.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1313,21 +1325,21 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing, Supply Chain</t>
+          <t>R&amp;D, Service Teams, Factory</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dependent on ink system compatibility.</t>
+          <t>NOA-F design, labeling process</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Magellan printer operates with Magi and Nessie inks without reformulation.</t>
+          <t>NOA-F units manufactured with metal foiled labyrinth and lid label, compatible with click-on push-push and TDF.</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.95</v>
+        <v>0.93</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1336,7 +1348,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1344,17 +1356,17 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Reliability, WVTR, Air Gain, Flow Rate, and IDS Characterization &amp; Modelling</t>
+          <t>Reuse SuperAmp Si PHA</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Characterize and model reliability, WVTR (Water Vapor Transmission Rate), air gain, flow rate, and IDS (Ink Delivery System), including startup and NOA-F End of Life.</t>
+          <t>Magellan must reuse SuperAmp Si PHA technology in its platform.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>To ensure consistent performance and reliability throughout product lifecycle.</t>
+          <t>Leverages proven technology, reduces development cost and risk.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1364,21 +1376,21 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality Assurance</t>
+          <t>R&amp;D, Manufacturing</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Requires data collection and modelling tools.</t>
+          <t>SuperAmp Si PHA compatibility</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Validated models and test reports for reliability, WVTR, air gain, flow rate, and IDS characterization.</t>
+          <t>SuperAmp Si PHA integrated and functional in Magellan platform.</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.9</v>
+        <v>0.92</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1387,7 +1399,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1395,41 +1407,41 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ink Stability Modelling for Tank and PQ Impact</t>
+          <t>Reuse Magi/Nessie Ink (No Reformulation)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Model ink stability in tank and its impact on print quality (PQ).</t>
+          <t>Magellan must use existing Magi and Nessie pigment inks without reformulation.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>To optimize ink performance and maintain high print quality over time.</t>
+          <t>Ensures ink reliability, reduces qualification time, and leverages existing supply chain.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality Assurance</t>
+          <t>R&amp;D, Supply Chain, Manufacturing</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Requires tank design and ink system data.</t>
+          <t>Ink compatibility with platform</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Ink stability models demonstrate minimal PQ degradation over expected tank life.</t>
+          <t>Magellan printer accepts and prints with Magi/Nessie inks, with no reformulation required.</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.85</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1438,7 +1450,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1446,17 +1458,17 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NOA-F as Service Parts in Warranty Support</t>
+          <t>Reliability, WVTR, Air Gain, Flow Rate and IDS Characterization</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>NOA-F components must be available as service parts for warranty support.</t>
+          <t>Magellan must support reliability, WVTR, air gain, flow rate, and IDS characterization and modeling, including startup and NOA-F EOL.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>To enable efficient service and repair during warranty period.</t>
+          <t>Ensures robust performance and longevity; critical for warranty and service.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1466,21 +1478,21 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Service, Warranty, End Users</t>
+          <t>R&amp;D, Service, Quality Assurance</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Requires supply chain and inventory management.</t>
+          <t>IDS, NOA-F, modeling tools</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>NOA-F parts are stocked and available for warranty service requests.</t>
+          <t>Documented models and test results for reliability, WVTR, air gain, flow rate, and IDS, including startup and NOA-F EOL scenarios.</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.9</v>
+        <v>0.88</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1489,7 +1501,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -1497,17 +1509,17 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Acumen 6 on Lid</t>
+          <t>Ink Stability Modeling</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Integrate Acumen 6 technology on the lid of Magellan printer.</t>
+          <t>Perform ink stability modeling for tank and impact to print quality (PQ).</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>To enhance lid functionality and possibly improve security or user experience.</t>
+          <t>Ensures consistent print quality and reduces risk of ink degradation over time.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1517,21 +1529,21 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Management</t>
+          <t>R&amp;D, Quality Assurance</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dependent on lid design and Acumen 6 integration.</t>
+          <t>Ink formulation, tank design</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Acumen 6 is operational and validated on printer lid.</t>
+          <t>Ink stability model completed and validated for tank and PQ impact.</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1540,7 +1552,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -1548,17 +1560,17 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Factory Configuration Updates for NOA-F and Ink Cart</t>
+          <t>NOA-F Service Parts in Warranty Support</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Modify existing SA14 line for NOA-F, add Magi ink cart and labelling tool in Orcus 5. Assume PHA + Dry FI + USG + push-push are assembled in printer factory.</t>
+          <t>NOA-F must be available as service parts for warranty support.</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>To accommodate new components and streamline manufacturing.</t>
+          <t>Reduces downtime and improves customer satisfaction during warranty repairs.</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1568,17 +1580,17 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Manufacturing, Operations</t>
+          <t>Service Teams, Warranty Support, End Users</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dependent on factory upgrade and process changes.</t>
+          <t>NOA-F supply chain</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>SA14 line and Orcus 5 are updated and validated for NOA-F, Magi ink cart, and labelling tool assembly.</t>
+          <t>NOA-F parts available and replaceable under warranty conditions.</t>
         </is>
       </c>
       <c r="I23" t="n">
@@ -1591,7 +1603,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -1599,41 +1611,41 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Mold for 1 to 4 New Keyed Caps</t>
+          <t>Acumen 6 on Lid</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Develop mold tooling for 1 to 4 new keyed caps for ink bottles.</t>
+          <t>Acumen 6 must be applied to the lid for traceability and authentication.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>To support the new ink bottle design and prevent misfilling.</t>
+          <t>Improves product traceability and anti-counterfeit measures.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing</t>
+          <t>R&amp;D, Manufacturing, Service Teams</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dependent on ink bottle design finalization.</t>
+          <t>Labeling process</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Molds for new keyed caps are produced and tested for compatibility.</t>
+          <t>Acumen 6 present and scannable on every lid produced.</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1642,7 +1654,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -1650,17 +1662,17 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Leverage Watt LE / Marconi Hi mech + CISS</t>
+          <t>Modify SA14 Line for NOA-F</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Leverage Watt LE and Marconi Hi mechanical platform and CISS (Continuous Ink Supply System) for Magellan printer.</t>
+          <t>Factory configuration must modify existing SA14 line to support NOA-F production.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>To reduce development time and cost by using existing platforms.</t>
+          <t>Ensures manufacturing capability for new NOA-F parts.</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1670,21 +1682,21 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing, Product Management</t>
+          <t>Manufacturing, Factory Operations</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dependent on compatibility of platforms with new features.</t>
+          <t>SA14 line modification</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Magellan printer prototypes successfully integrate Watt LE, Marconi Hi, and CISS.</t>
+          <t>SA14 line operational for NOA-F production.</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -1693,7 +1705,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -1701,17 +1713,17 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Speed: 25/20ppm (PDL: 25/19ppm)</t>
+          <t>Add Magi Ink Cart and Labelling Tool in Orcus 5</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Magellan printer must support print speeds of 25/20 pages per minute (PDL: 25/19ppm).</t>
+          <t>Orcus 5 factory must add Magi ink cartridge and labeling tool for production.</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>To meet competitive performance benchmarks for target segments.</t>
+          <t>Supports new ink and labeling requirements for Magellan.</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1721,21 +1733,21 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Product Management, Marketing, End Users</t>
+          <t>Manufacturing, Factory Operations</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dependent on hardware and firmware optimization.</t>
+          <t>Orcus 5 configuration</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Printer achieves 25/20ppm (PDL: 25/19ppm) in test conditions.</t>
+          <t>Magi ink cart and labeling tool installed and operational in Orcus 5.</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -1744,7 +1756,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
     </row>
@@ -1752,17 +1764,17 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Support Customer Replaceable PHA and NOA-F</t>
+          <t>Assembly of PHA + Dry FI + USG + Push Push in Printer Factory</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Magellan printer must allow customers to replace PHA and NOA-F components easily.</t>
+          <t>Printer factory must assemble PHA, Dry FI, USG, and push-push components.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>To improve serviceability and reduce downtime for end users.</t>
+          <t>Ensures complete assembly and integration of critical modules.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1772,21 +1784,21 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Service, End Users</t>
+          <t>Manufacturing, Factory Operations</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dependent on component design and user instructions.</t>
+          <t>Component supply, assembly process</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>PHA and NOA-F are replaceable by customers with minimal tools and clear instructions.</t>
+          <t>Printer factory produces units with all four components assembled.</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -1795,7 +1807,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
     </row>
@@ -1803,17 +1815,17 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Support New Warranty Page Life Goal of 80k Pages</t>
+          <t>ISDO Capex for SA14 Line, Magi/Nessie Ink Cart and Label Tool, Mold for 1-4 New Keyed Caps</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Magellan printer must support a new warranty page life goal of 80,000 pages.</t>
+          <t>Allocate ISDO Capex for SA14 line upgrades, Magi/Nessie ink cart and labeling tool in Orcus 5, and molds for 1-4 new keyed caps.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>To provide longer warranty coverage and differentiate from competitors.</t>
+          <t>Enables production of new components and supports scale-up.</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1823,21 +1835,21 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Product Management, Warranty, End Users</t>
+          <t>Finance, Manufacturing, R&amp;D</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dependent on reliability and component durability.</t>
+          <t>Capex allocation, factory upgrades</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Printer reliably prints 80,000 pages within warranty period under standard usage.</t>
+          <t>Capex allocated and upgrades completed for SA14, Orcus 5, and molds.</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.95</v>
+        <v>0.87</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -1846,7 +1858,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
     </row>
@@ -1854,41 +1866,41 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SKU 2 (Hi + Hi PDL) PaaS</t>
+          <t>Leverage Watt LE/Marconi Hi Mech + CISS</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Introduce SKU 2 with high page yield and high PDL (Page Description Language) as Product-as-a-Service (PaaS).</t>
+          <t>Magellan must leverage existing Watt LE and Marconi Hi mechanical platforms, integrating CISS.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>To target SMB and enterprise segments with flexible service models.</t>
+          <t>Reduces development time and cost, improves reliability.</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Product Management, Marketing, SMB, Enterprise Customers</t>
+          <t>R&amp;D, Manufacturing, Product Management</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dependent on service platform and SKU configuration.</t>
+          <t>Platform compatibility, CISS integration</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>SKU 2 is available with high yield and high PDL, offered as PaaS.</t>
+          <t>Magellan platform integrates Watt LE/Marconi Hi mech and CISS successfully.</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -1897,7 +1909,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
     </row>
@@ -1905,17 +1917,17 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Reddington ID with Size Increase for Tank</t>
+          <t>Print Speed: 25/20ppm (PDL: 25/19ppm)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Magellan printer adopts Reddington industrial design with increased tank size; no change to Marconi-HI ADF.</t>
+          <t>Magellan printer must achieve print speeds of 25/20 pages per minute (PDL: 25/19ppm).</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>To accommodate higher ink capacity and maintain design consistency.</t>
+          <t>Meets market and business requirements for throughput.</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1925,21 +1937,21 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Management, Manufacturing</t>
+          <t>Product Management, End Users, SMB, Enterprise</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dependent on tank design and ID update.</t>
+          <t>Platform performance, ink system</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Printer features Reddington ID, tank size increased, ADF unchanged.</t>
+          <t>Printer achieves specified print speeds in standard test conditions.</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.9</v>
+        <v>0.92</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -1948,7 +1960,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -1956,41 +1968,41 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>EPS Foam Packaging</t>
+          <t>Customer Replaceable PHA and NOA-F</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Use EPS foam packaging for Magellan printer.</t>
+          <t>Magellan must support customer replaceable PHA and NOA-F modules.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>To protect product during shipping and meet environmental standards.</t>
+          <t>Improves serviceability and reduces downtime for end users.</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Packaging, Logistics, Sustainability</t>
+          <t>Service Teams, End Users</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dependent on packaging design and supply chain.</t>
+          <t>Module design, user instructions</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>EPS foam packaging is validated for drop/shipping tests and meets EPEAT3, LOT4, and Blue Angel requirements.</t>
+          <t>End users can replace PHA and NOA-F modules without technical assistance.</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -1999,7 +2011,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
     </row>
@@ -2007,17 +2019,17 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>EPEAT3 and LOT4 Requirement, Blue Angel for PDL SKU</t>
+          <t>Warranty Page Life Goal of 80k Pages</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Magellan printer must meet EPEAT3, LOT4, and Blue Angel certification requirements for PDL SKU.</t>
+          <t>Magellan must achieve a new warranty page life goal of 80,000 pages.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>To ensure environmental compliance and marketability in regulated markets.</t>
+          <t>Extends product longevity and reduces warranty claims.</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2027,21 +2039,21 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sustainability, Product Management, Marketing</t>
+          <t>Product Management, Service Teams, End Users</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dependent on product design and certification processes.</t>
+          <t>Component reliability, ink system, platform design</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Printer achieves EPEAT3, LOT4, and Blue Angel certifications for PDL SKU.</t>
+          <t>Printer achieves 80,000-page life under warranty conditions.</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -2050,7 +2062,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -2058,41 +2070,41 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Input Tray and Output Tray Changes for Tank Protrusion</t>
+          <t>SKU 2 (Hi + Hi PDL) PaaS</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Modify input and output trays to align with tank protrusion and optimize size.</t>
+          <t>Magellan must offer SKU 2 (Hi + Hi PDL) as Platform-as-a-Service (PaaS).</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>To accommodate increased tank size and maintain usability.</t>
+          <t>Supports flexible business models and market segmentation.</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing, End Users</t>
+          <t>Product Management, SMB, Enterprise</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dependent on tank and tray design.</t>
+          <t>SKU definition, PaaS platform</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Trays are redesigned and tested for compatibility with protruding tank.</t>
+          <t>SKU 2 available as PaaS offering.</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -2101,7 +2113,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -2109,41 +2121,41 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>4.3” CGD Display</t>
+          <t>Reddington ID with Tank Size Increase</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Magellan printer must feature a 4.3-inch CGD (Color Graphic Display).</t>
+          <t>Magellan must use Reddington ID with increased tank size. No change to Marconi-HI ADF.</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>To improve user interface and control experience.</t>
+          <t>Supports higher yield and aligns with existing product identity.</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Product Management, End Users</t>
+          <t>Product Management, R&amp;D</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dependent on display integration and firmware.</t>
+          <t>Tank design, Reddington ID integration</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Printer includes a functional 4.3-inch CGD display.</t>
+          <t>Magellan printer uses Reddington ID and tank size is increased as specified.</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -2152,7 +2164,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -2160,41 +2172,41 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Platform 4 Tubes – Leverage Sayan Sibstar Tubes, New Tube Routing &amp; Integration</t>
+          <t>EPS Foam Packaging</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Magellan printer platform must use 4 tubes, leveraging Sayan Sibstar tubes, with new routing and integration.</t>
+          <t>Magellan must use EPS foam packaging for protection during shipping.</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>To optimize ink delivery and support new tank design.</t>
+          <t>Improves product safety and reduces damage during transit.</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing</t>
+          <t>Manufacturing, Logistics, End Users</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dependent on tube design and integration.</t>
+          <t>Packaging design</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Printer integrates 4 Sayan Sibstar tubes with new routing; validated for ink delivery.</t>
+          <t>EPS foam packaging used for all shipped units.</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -2203,7 +2215,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -2211,41 +2223,41 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Service Station Aerosol Management with Spit Platform Changes</t>
+          <t>EPEAT3, LOT4, Blue Angel Requirements for PDL SKU</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Service station must manage aerosol with spit platform changes due to tank design.</t>
+          <t>Magellan must meet EPEAT3, LOT4, and Blue Angel requirements for PDL SKU.</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>To maintain print quality and reduce maintenance issues.</t>
+          <t>Ensures compliance with environmental and quality standards.</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>R&amp;D, Service, Quality Assurance</t>
+          <t>Regulatory, Product Management, R&amp;D</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dependent on service station and tank integration.</t>
+          <t>PDL SKU definition, compliance process</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Aerosol management system is validated and effective with new tank and spit platform.</t>
+          <t>PDL SKU certified for EPEAT3, LOT4, and Blue Angel.</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -2254,7 +2266,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -2262,17 +2274,17 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Carriage Dynamic and Force Model with Tube and New Weights</t>
+          <t>Input/Output Tray Changes for Tank Protrusion</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Model carriage dynamics and force considering new tube routing and weights.</t>
+          <t>Input and output trays must be changed to align with tank protrusion.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>To ensure reliable operation and prevent mechanical failures.</t>
+          <t>Ensures proper fit and function with increased tank size.</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2282,21 +2294,21 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing, Quality Assurance</t>
+          <t>R&amp;D, Manufacturing</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dependent on tube integration and carriage design.</t>
+          <t>Tray design, tank integration</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Carriage dynamic and force models validated for new configuration.</t>
+          <t>Input/output trays modified and functional with tank protrusion.</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.85</v>
+        <v>0.87</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -2305,7 +2317,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -2313,41 +2325,41 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Paperpath to Support Increased Page Life</t>
+          <t>Size Optimization</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Paperpath must be designed to support increased page life (80k pages).</t>
+          <t>Optimize printer size to accommodate new tank and component changes.</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>To ensure durability and reliability for high-volume printing.</t>
+          <t>Improves space efficiency and user experience.</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality Assurance, End Users</t>
+          <t>R&amp;D, Product Management</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dependent on paperpath design and materials.</t>
+          <t>Tank and component design</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Paperpath validated for 80,000-page life under standard usage.</t>
+          <t>Printer size optimized for new tank and components without sacrificing functionality.</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -2356,7 +2368,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -2364,41 +2376,41 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Ink Maintenance Serviceable Part (Service Center) – Post 80k Life</t>
+          <t>4.3” CGD Display</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Ink maintenance must be serviceable at Service Center after 80,000-page life.</t>
+          <t>Magellan must include a 4.3” CGD display for user interface.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>To support post-warranty service and extend product lifecycle.</t>
+          <t>Enhances usability and supports advanced features.</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Service, End Users</t>
+          <t>End Users, Product Management</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dependent on maintenance part design and service procedures.</t>
+          <t>Display integration, UI design</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Ink maintenance part is replaceable/serviceable after 80k page life.</t>
+          <t>Printer includes and operates with 4.3” CGD display.</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -2407,7 +2419,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -2415,17 +2427,17 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SuperAmp PHA, NOA-F, Keyed Bottles, Magi and Nessie Pigment Inks, 140ml K Bottles (New), xx ml CMY Bottles</t>
+          <t>Platform with 4 Tubes and Sayan Sibstar Tubes</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Magellan printer must support SuperAmp PHA, NOA-F, keyed bottles, Magi and Nessie pigment inks, new 140ml K bottles, and xx ml CMY bottles.</t>
+          <t>Magellan must leverage Sayan Sibstar tubes, with new routing and integration for 4-tube platform.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>To offer a comprehensive supply system for various print needs.</t>
+          <t>Supports CISS and ink flow requirements.</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2435,17 +2447,17 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>R&amp;D, Supply Chain, Product Management</t>
+          <t>R&amp;D, Manufacturing</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dependent on supply system integration and compatibility.</t>
+          <t>Tube design, routing integration</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Printer supports all listed supplies and bottle sizes; validated in test prints.</t>
+          <t>Printer platform uses 4 tubes with Sayan Sibstar tubes and new routing.</t>
         </is>
       </c>
       <c r="I40" t="n">
@@ -2458,7 +2470,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -2466,17 +2478,17 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>IDS New Make-Break and FI Connection</t>
+          <t>Service Station Aerosol Management</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Implement new make-break and FI (Fluidic Interface) connection in IDS (Ink Delivery System).</t>
+          <t>Service station must manage aerosols with spit platform changes due to tank.</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>To improve reliability and ease of maintenance.</t>
+          <t>Reduces contamination and ensures print quality.</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2486,17 +2498,17 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing, Service</t>
+          <t>R&amp;D, Manufacturing, Quality Assurance</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dependent on IDS redesign and component compatibility.</t>
+          <t>Service station design, spit platform integration</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>IDS features new make-break and FI connection; validated in prototype testing.</t>
+          <t>Aerosol management system implemented and functional in service station.</t>
         </is>
       </c>
       <c r="I41" t="n">
@@ -2509,7 +2521,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -2517,17 +2529,17 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Leverage LEBI Ink-Tank with Increased Size, Keying and LOI One SHAID</t>
+          <t>Carriage Dynamic and Force Model with Tube and New Weights</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Use LEBI ink-tank with increased size, keying, and LOI One SHAID for Magellan printer.</t>
+          <t>Carriage must be dynamically modeled for force with tube integration and new component weights.</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>To support high-capacity ink supply and secure identification.</t>
+          <t>Ensures mechanical reliability and optimal print performance.</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2537,17 +2549,17 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing, Product Management</t>
+          <t>R&amp;D, Manufacturing</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dependent on ink-tank design and LOI SHAID integration.</t>
+          <t>Carriage design, tube integration</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>LEBI ink-tank is integrated with increased size, keying, and LOI One SHAID; validated in printer operation.</t>
+          <t>Dynamic force model completed and validated for carriage with tubes and new weights.</t>
         </is>
       </c>
       <c r="I42" t="n">
@@ -2560,7 +2572,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -2568,17 +2580,17 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>New IDS Startup Algorithm and Air Management</t>
+          <t>Paperpath to Support Increased Page Life</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Develop new IDS startup algorithm and air management system.</t>
+          <t>Paperpath must be designed to support increased page life (80k).</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>To ensure optimal startup performance and prevent air-related failures.</t>
+          <t>Ensures reliability and longevity for high-volume users.</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2588,17 +2600,17 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality Assurance</t>
+          <t>R&amp;D, Service Teams, End Users</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dependent on IDS design and firmware.</t>
+          <t>Paperpath design, page life modeling</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>IDS startup algorithm and air management validated for reliable printer startup.</t>
+          <t>Paperpath supports 80k page life without significant wear or failure.</t>
         </is>
       </c>
       <c r="I43" t="n">
@@ -2611,7 +2623,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -2619,17 +2631,17 @@
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>New Servicing and Startup Algorithm</t>
+          <t>Ink Maintenance Serviceable Part (Post 80k Life)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Implement new servicing and startup algorithms for Magellan printer.</t>
+          <t>Ink maintenance must be a serviceable part, replaceable at service centers after 80k page life.</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>To improve reliability and reduce service incidents.</t>
+          <t>Supports extended product use and reduces maintenance costs.</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2639,17 +2651,17 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>R&amp;D, Service, Quality Assurance</t>
+          <t>Service Teams, End Users</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dependent on printer firmware and servicing procedures.</t>
+          <t>Maintenance part design, service center process</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Servicing and startup algorithms validated in field tests.</t>
+          <t>Ink maintenance part is replaceable at service centers after 80k page life.</t>
         </is>
       </c>
       <c r="I44" t="n">
@@ -2662,7 +2674,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -2670,17 +2682,17 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>New Print Quality Goals &amp; Depletion to Meet Page Yield Definition</t>
+          <t>SuperAmp PHA, NOA-F, Keyed Bottles, Magi and Nessie Pigment Inks</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Set new print quality (PQ) goals and depletion metrics to meet defined page yield.</t>
+          <t>Magellan must support SuperAmp PHA, NOA-F, keyed bottles, Magi, and Nessie pigment inks.</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>To ensure consistent print quality and accurate yield reporting.</t>
+          <t>Ensures compatibility with advanced ink and supply technologies.</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2690,17 +2702,17 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>R&amp;D, Quality Assurance, Product Management</t>
+          <t>R&amp;D, Manufacturing, Product Management</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dependent on ink system and PQ testing.</t>
+          <t>Component compatibility</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>PQ goals and depletion metrics validated for defined page yield.</t>
+          <t>Printer supports and operates with all specified supplies.</t>
         </is>
       </c>
       <c r="I45" t="n">
@@ -2713,7 +2725,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -2721,41 +2733,41 @@
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Reuse Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU, Stingray Wi-fi Module, FW Dune</t>
+          <t>140ml K Bottles and xx ml CMY Bottles</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Reuse Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU, Stingray Wi-fi module, and FW Dune in Magellan printer.</t>
+          <t>Magellan must use 140ml black bottles and appropriately sized CMY bottles (exact size TBD).</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>To leverage proven electronic and firmware components, reducing development risk and cost.</t>
+          <t>Supports high-yield requirements and efficient ink usage.</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing, Cost Management</t>
+          <t>R&amp;D, Manufacturing</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dependent on compatibility with Magellan platform.</t>
+          <t>Bottle sizing, ink system</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>All listed components are integrated and validated in Magellan printer.</t>
+          <t>Printer uses 140ml K bottles and specified CMY bottles.</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -2764,7 +2776,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -2772,17 +2784,17 @@
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Gauss4.xx Security for Hardware and Firmware</t>
+          <t>IDS New Make-break and FI Connection</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Implement Gauss4.xx security for hardware and firmware in Magellan printer.</t>
+          <t>IDS must support new make-break and FI connection.</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>To ensure robust security and protect against threats.</t>
+          <t>Improves reliability and serviceability of ink delivery system.</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2792,17 +2804,17 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>R&amp;D, Security, Product Management</t>
+          <t>R&amp;D, Service Teams</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dependent on hardware and firmware integration.</t>
+          <t>IDS design, FI connection</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Gauss4.xx security features operational and validated in Magellan printer.</t>
+          <t>IDS supports new make-break and FI connection in all units.</t>
         </is>
       </c>
       <c r="I47" t="n">
@@ -2815,7 +2827,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -2823,17 +2835,17 @@
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Business Model: Consumer, SMB, and Enterprise Support</t>
+          <t>Leverage LEBI Ink-tank with Increased Size, Keying, and LOI One SHAID</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Magellan printer must support business models for Consumer, SMB, and Enterprise segments.</t>
+          <t>Magellan must leverage LEBI ink-tank with increased size, keying, and LOI One SHAID.</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>To expand market reach and address diverse customer needs.</t>
+          <t>Supports high-yield and secure ink delivery.</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2843,17 +2855,17 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Product Management, Marketing, Sales</t>
+          <t>R&amp;D, Manufacturing, Product Management</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dependent on solution and service platform integration.</t>
+          <t>LEBI ink-tank design, SHAID integration</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Printer and services are available for Consumer, SMB, and Enterprise customers.</t>
+          <t>Printer uses LEBI ink-tank with increased size, keying, and LOI One SHAID.</t>
         </is>
       </c>
       <c r="I48" t="n">
@@ -2866,7 +2878,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -2874,17 +2886,17 @@
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Solution and Services: Scan Solution, SMB Manageability, Enterprise Support</t>
+          <t>New IDS Startup Algorithm and Air Management</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Magellan printer must provide scan solution, SMB manageability, and enterprise support (WJA, HPSM, JAM).</t>
+          <t>IDS must include new startup algorithm and air management for improved reliability.</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>To offer comprehensive solutions for targeted segments.</t>
+          <t>Reduces startup failures and ensures consistent ink flow.</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2894,17 +2906,17 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Product Management, SMB, Enterprise Customers</t>
+          <t>R&amp;D, Service Teams</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dependent on software and service integration.</t>
+          <t>IDS design, algorithm development</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Printer supports scan solution, SMB manageability, and enterprise features (WJA, HPSM, JAM).</t>
+          <t>IDS startup algorithm and air management implemented and validated.</t>
         </is>
       </c>
       <c r="I49" t="n">
@@ -2917,7 +2929,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -2925,17 +2937,17 @@
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Clients &amp; Drivers: HPX, PSA, SUPD, UPD, EasyStart, USS, UFD</t>
+          <t>New Servicing and Startup Algorithm</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Magellan printer must support clients and drivers including HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD.</t>
+          <t>Magellan must implement new servicing and startup algorithms for improved reliability and user experience.</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>To ensure compatibility with HP ecosystem and user platforms.</t>
+          <t>Reduces service calls and improves startup success rate.</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2945,17 +2957,17 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>R&amp;D, Product Management, End Users</t>
+          <t>R&amp;D, Service Teams, End Users</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dependent on driver and client integration.</t>
+          <t>Algorithm development, IDS integration</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Printer supports all listed clients and drivers; validated in installation tests.</t>
+          <t>New servicing and startup algorithms operational in all units.</t>
         </is>
       </c>
       <c r="I50" t="n">
@@ -2968,7 +2980,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -2976,17 +2988,17 @@
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Protect Micro/SMB Segments and Safeguard HP’s Ink/Laser Profit Pool</t>
+          <t>New PQ Goals &amp; Depletion to Meet Page Yield Definition</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Magellan printer must be designed to protect HP's market share in Micro and SMB segments and prevent profit pool erosion to competitors.</t>
+          <t>Magellan must set new print quality (PQ) goals and depletion rates to meet defined page yield.</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>To maintain HP's leadership and profitability.</t>
+          <t>Ensures consistent output and meets yield expectations.</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2996,17 +3008,17 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Product Management, Marketing, Sales</t>
+          <t>R&amp;D, Product Management, End Users</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dependent on competitive features and pricing.</t>
+          <t>PQ goal definition, depletion modeling</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Market share in Micro/SMB segments maintained or increased post-launch.</t>
+          <t>Printer achieves PQ goals and depletion rates as defined for page yield.</t>
         </is>
       </c>
       <c r="I51" t="n">
@@ -3014,12 +3026,12 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>36</t>
         </is>
       </c>
     </row>
@@ -3027,17 +3039,17 @@
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Lead with LaserJet and Flank with PDL in Medium and Enterprise</t>
+          <t>Reuse Marconi Tux dASIC, Hannibal aASIC, Raccoon PSU</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Magellan printer must support strategy to lead with LaserJet and flank with PDL in Medium and Enterprise segments to win over competitors.</t>
+          <t>Magellan must reuse Marconi Tux dASIC, Hannibal aASIC, and Raccoon PSU.</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>To strengthen HP’s position in Medium and Enterprise segments against competitors like Epson.</t>
+          <t>Leverages proven hardware, reduces development cost and risk.</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3047,17 +3059,17 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Product Management, Marketing, Sales</t>
+          <t>R&amp;D, Manufacturing</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dependent on product positioning and feature set.</t>
+          <t>Hardware compatibility</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Competitive positioning validated in market analysis and sales results.</t>
+          <t>Printer uses and operates with specified hardware components.</t>
         </is>
       </c>
       <c r="I52" t="n">
@@ -3065,12 +3077,12 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
     </row>
@@ -3078,17 +3090,17 @@
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Grow CISS Profitable Share by Playing in New Segments</t>
+          <t>Stingray Wi-fi Module</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Magellan printer must enable growth of profitable CISS share by targeting new market segments.</t>
+          <t>Magellan must integrate Stingray Wi-fi module for wireless connectivity.</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>To expand HP's CISS market share and profitability.</t>
+          <t>Supports modern connectivity requirements for end users.</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3098,17 +3110,17 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Product Management, Marketing, Sales</t>
+          <t>End Users, Product Management</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dependent on segment identification and tailored features.</t>
+          <t>Wi-fi module integration</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>CISS share grows in new segments post-launch.</t>
+          <t>Printer connects wirelessly using Stingray Wi-fi module.</t>
         </is>
       </c>
       <c r="I53" t="n">
@@ -3116,12 +3128,12 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>38</t>
         </is>
       </c>
     </row>
@@ -3129,17 +3141,17 @@
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Highly Leverage Watt-LE Mech Platform, Marconi-Hi Product (Reddington ID), and Solutions</t>
+          <t>FW Dune Integration</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Magellan printer must leverage Watt-LE mechanical platform, Marconi-Hi product (Reddington ID), and solutions for development.</t>
+          <t>Magellan must use FW Dune firmware platform.</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>To reduce development time and cost by using proven platforms and solutions.</t>
+          <t>Ensures compatibility and leverages existing firmware technology.</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3149,30 +3161,30 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing, Product Management</t>
+          <t>R&amp;D, Manufacturing</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dependent on platform compatibility.</t>
+          <t>Firmware integration</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Magellan printer development leverages all listed platforms and solutions.</t>
+          <t>Printer operates with FW Dune firmware.</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>39</t>
         </is>
       </c>
     </row>
@@ -3180,17 +3192,17 @@
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Integrate CISS IDS, NOA-F, and Ink Tanks</t>
+          <t>Security: Gauss4.xx HW &amp; FW</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Magellan printer must integrate CISS IDS, NOA-F, and ink tanks for seamless operation.</t>
+          <t>Magellan must implement Gauss4.xx hardware and firmware security features.</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>To optimize ink delivery and reliability.</t>
+          <t>Protects against threats and ensures product integrity.</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3200,30 +3212,30 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing, Product Management</t>
+          <t>R&amp;D, Security Teams, Product Management</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dependent on system integration and compatibility.</t>
+          <t>HW and FW integration</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Printer integrates CISS IDS, NOA-F, and ink tanks; validated in operation tests.</t>
+          <t>Printer meets Gauss4.xx security requirements.</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>40</t>
         </is>
       </c>
     </row>
@@ -3231,17 +3243,17 @@
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>New NGB Keyed Ink Bottles</t>
+          <t>Schedule Adherence</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Magellan printer must use new NGB keyed ink bottles.</t>
+          <t>Magellan must adhere to defined schedule checkpoints for HW, NOA-F, and Bottle.</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>To prevent misfilling and ensure correct ink usage.</t>
+          <t>Ensures timely delivery and aligns with business priorities.</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3251,30 +3263,30 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>R&amp;D, Manufacturing, End Users</t>
+          <t>Product Management, Project Teams</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dependent on bottle design and keying system.</t>
+          <t>Schedule definition, milestone tracking</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Printer accepts only keyed NGB bottles; validated in user tests.</t>
+          <t>All checkpoints met on schedule as defined.</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>41</t>
         </is>
       </c>
     </row>
@@ -3282,17 +3294,17 @@
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Schedule Constraint: Q3 2025 Launch</t>
+          <t>Business Model: Consumer, SMB, Enterprise</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Magellan printer development must adhere to schedule with launch by August 20, 2025 (Q3 2025).</t>
+          <t>Magellan must support business models for consumer, SMB, and enterprise segments.</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>To meet market timing and business objectives.</t>
+          <t>Maximizes market reach and supports diverse customer needs.</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3302,30 +3314,30 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Product Management, R&amp;D, Manufacturing, Marketing</t>
+          <t>Product Management, Sales, Marketing</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dependent on project management and milestone tracking.</t>
+          <t>Business model definition</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Printer is launched by August 20, 2025.</t>
+          <t>Magellan available and marketed to consumer, SMB, and enterprise segments.</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>42</t>
         </is>
       </c>
     </row>
@@ -3333,50 +3345,50 @@
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>SuperAmp PHA Life at 65K Pages (Constraint)</t>
+          <t>Service: PaaS and WorkFromHome/Flexworker</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>SuperAmp PHA must have a life of 65,000 pages as a constraint.</t>
+          <t>Magellan must support Platform-as-a-Service (PaaS) and WorkFromHome/Flexworker service models.</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>To ensure reliability and meet service requirements.</t>
+          <t>Addresses new market trends and customer needs.</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>R&amp;D, Service, Quality Assurance</t>
+          <t>Product Management, SMB, Enterprise</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dependent on PHA design and testing.</t>
+          <t>Service model integration</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>SuperAmp PHA reliably operates for 65,000 pages.</t>
+          <t>Magellan supports PaaS and WorkFromHome/Flexworker services.</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>43</t>
         </is>
       </c>
     </row>
@@ -3384,17 +3396,17 @@
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Warranty Life of Pages, 2 Years (Optimize)</t>
+          <t>Onboarding/S&amp;O Pathways</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Magellan printer must optimize for warranty life of pages and 2-year coverage.</t>
+          <t>Magellan must support onboarding and S&amp;O pathways for Consumer/HPX, HP One, SMB Portal, and ECP.</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>To provide competitive warranty terms and customer assurance.</t>
+          <t>Facilitates smooth onboarding and integration for all customer segments.</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3404,17 +3416,17 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Product Management, Warranty, End Users</t>
+          <t>Product Management, Sales, Service Teams</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dependent on reliability and warranty policy.</t>
+          <t>Pathway definition, integration</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Printer is warranted for defined page life and 2 years.</t>
+          <t>Magellan onboarding supports all specified pathways.</t>
         </is>
       </c>
       <c r="I59" t="n">
@@ -3422,12 +3434,12 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>44</t>
         </is>
       </c>
     </row>
@@ -3435,50 +3447,50 @@
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Throughput 25/20 PDL (Optimize)</t>
+          <t>Scan Solution, SMB Manageability, Enterprise Support (WJA, HPSM, JAM)</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Magellan printer must optimize for throughput of 25/20 pages per minute (PDL).</t>
+          <t>Magellan must support scan solution, SMB manageability, and enterprise support including WJA, HPSM, and JAM.</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>To meet performance expectations for target segments.</t>
+          <t>Ensures comprehensive functionality for all market segments.</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Product Management, R&amp;D, Marketing</t>
+          <t>Product Management, SMB, Enterprise, Service Teams</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dependent on hardware and firmware optimization.</t>
+          <t>Solution integration</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Printer achieves throughput of 25/20 PDL in test conditions.</t>
+          <t>Magellan supports scan, SMB manageability, and enterprise support features.</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>45</t>
         </is>
       </c>
     </row>
@@ -3486,50 +3498,50 @@
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Serviceability Maintenance Box (Optimize)</t>
+          <t>Clients &amp; Drivers: HPX, PSA, SUPD, UPD, EasyStart, USS, UFD</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Magellan printer must optimize for serviceability via maintenance box.</t>
+          <t>Magellan must support HPX, PSA, SUPD, UPD, EasyStart, USS, and UFD clients and drivers.</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>To improve ease of maintenance and reduce downtime.</t>
+          <t>Ensures compatibility with HP ecosystem and customer requirements.</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Service, End Users, R&amp;D</t>
+          <t>Product Management, R&amp;D, End Users</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dependent on maintenance box design and service procedures.</t>
+          <t>Driver and client integration</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Maintenance box is serviceable and validated in service tests.</t>
+          <t>Magellan supports all specified clients and drivers.</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Magellan_SI_1-pager.pdf, page 2</t>
+          <t>Magellan_SI_1-pager.pdf, page 1</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>46</t>
         </is>
       </c>
     </row>
@@ -3537,41 +3549,41 @@
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SMB Solution (Optimize)</t>
+          <t>Protect Micro/SMB Segments and HP’s Ink/Laser Profit Pool</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Magellan printer must optimize for SMB solution features.</t>
+          <t>Magellan must protect micro/SMB segments and HP’s traditional ink/laser profit pool from competitors.</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>To address SMB segment needs and improve manageability.</t>
+          <t>Maintains HP’s market share and profitability.</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Product Management, SMB Customers</t>
+          <t>Product Management, Sales, Marketing</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dependent on solution integration.</t>
+          <t>Business strategy alignment</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Printer delivers SMB solution features validated in SMB use cases.</t>
+          <t>Market share and profit pool protected as measured by quarterly reports.</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -3580,7 +3592,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>47</t>
         </is>
       </c>
     </row>
@@ -3588,41 +3600,41 @@
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="inlineStr">
         <is>
-          <t>PaaS Schedule (Optimize)</t>
+          <t>Lead with LaserJet, Flank with PDL in Medium/Enterprise Segments</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Magellan printer must optimize for PaaS (Product-as-a-Service) schedule.</t>
+          <t>Magellan must lead with LaserJet and flank with PDL in medium and enterprise segments to win over competitors as CISS grows.</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>To align service offerings with product launch.</t>
+          <t>Strategic positioning to maximize market share and growth.</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Product Management, Marketing, Service</t>
+          <t>Product Management, Sales, Marketing</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dependent on PaaS platform readiness.</t>
+          <t>Segment strategy alignment</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>PaaS offering is available at product launch.</t>
+          <t>Market share gains in medium/enterprise segments measured by sales data.</t>
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -3631,7 +3643,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>48</t>
         </is>
       </c>
     </row>
@@ -3639,41 +3651,41 @@
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Host 12K-CMYK (Flexible)</t>
+          <t>Grow CISS Profitable Share in New Segments</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Magellan printer must flexibly support hosting 12,000-page yield for CMYK.</t>
+          <t>Magellan must grow CISS profitable share by entering new segments.</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>To enable higher capacity options for certain markets.</t>
+          <t>Expands business opportunities and increases profitability.</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Product Management, Marketing, End Users</t>
+          <t>Product Management, Sales, Marketing</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dependent on ink system and bottle design.</t>
+          <t>CISS integration, segment targeting</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Printer supports 12,000-page yield for CMYK; validated in test prints.</t>
+          <t>CISS share growth in new segments measured by sales and profit reports.</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -3682,7 +3694,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>49</t>
         </is>
       </c>
     </row>
@@ -3690,50 +3702,611 @@
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Trade Page 6K (Flexible)</t>
+          <t>Highly Leverage Watt-LE Mech Platform, Marconi-Hi Product (Reddington ID), and Solutions</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Magellan printer must flexibly support trade page yield of 6,000 pages.</t>
+          <t>Magellan must highly leverage Watt-LE mechanical platform, Marconi-Hi product (Reddington ID), and solutions.</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>To enable product configuration for trade and channel requirements.</t>
+          <t>Reduces development cost and risk, improves reliability.</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>R&amp;D, Manufacturing, Product Management</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Platform compatibility</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Magellan leverages specified platforms and solutions successfully.</t>
+        </is>
+      </c>
+      <c r="I65" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr"/>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Integrate CISS IDS, NOA-F, and Ink Tanks</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Magellan must integrate CISS IDS, NOA-F, and ink tanks for improved ink delivery and reliability.</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Ensures robust and efficient ink system.</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>R&amp;D, Manufacturing, Product Management</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Component integration</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>CISS IDS, NOA-F, and ink tanks integrated and functional in Magellan.</t>
+        </is>
+      </c>
+      <c r="I66" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr"/>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>New NGB Keyed Ink Bottles</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Magellan must support new NGB keyed ink bottles.</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Improves reliability, reduces counterfeit risk, and supports high-yield requirements.</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>R&amp;D, Manufacturing, Product Management</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Bottle design, platform integration</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Magellan supports and operates with new NGB keyed ink bottles.</t>
+        </is>
+      </c>
+      <c r="I67" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr"/>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Schedule (Least Flexible Constraint)</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Magellan must strictly adhere to schedule as the least flexible constraint.</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Ensures timely market launch and aligns with business priorities.</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Product Management, Project Teams</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Schedule definition, milestone tracking</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>All milestones met as scheduled.</t>
+        </is>
+      </c>
+      <c r="I68" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr"/>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>SuperAmp PHA Life at 65K (Least Flexible Constraint)</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>SuperAmp PHA must have a life of at least 65,000 pages as a least flexible constraint.</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Ensures product reliability and meets warranty requirements.</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>R&amp;D, Service Teams, End Users</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>PHA design, reliability testing</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>SuperAmp PHA achieves 65,000-page life in standard tests.</t>
+        </is>
+      </c>
+      <c r="I69" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr"/>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Warranty Life of Pages (2 Years)</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Magellan must support a warranty life of pages for 2 years.</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Meets customer expectations and reduces warranty claims.</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Product Management, Service Teams, End Users</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Component reliability, ink system</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Printer achieves warranty life of pages for 2 years in standard conditions.</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr"/>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Throughput 25/20 PDL (Optimize Constraint)</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Magellan must achieve throughput of 25/20 pages per minute for PDL as an optimize constraint.</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Supports business and enterprise requirements for efficiency.</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Product Management, End Users, SMB, Enterprise</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Platform performance, ink system</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Printer achieves specified throughput in standard tests.</t>
+        </is>
+      </c>
+      <c r="I71" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr"/>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Serviceability (Maintenance Box)</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Magellan must support serviceability with a maintenance box as an optimize constraint.</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Improves maintenance efficiency and reduces downtime.</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Service Teams, End Users</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Maintenance box design, service process</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Printer includes and supports maintenance box for serviceability.</t>
+        </is>
+      </c>
+      <c r="I72" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr"/>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>SMB Solution (Optimize Constraint)</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Magellan must support SMB solution as an optimize constraint.</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Addresses SMB market needs and improves manageability.</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Product Management, SMB</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Solution integration</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Magellan supports SMB solution features and manageability.</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr"/>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>PaaS (Schedule, Optimize Constraint)</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Magellan must support Platform-as-a-Service (PaaS) as a schedule, optimize constraint.</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Enables flexible business models and supports market segmentation.</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Product Management, SMB, Enterprise</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>PaaS platform integration</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Magellan supports PaaS offering as scheduled.</t>
+        </is>
+      </c>
+      <c r="I74" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr"/>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Host 12K-CMYK (Flexible Constraint)</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Magellan must support host 12K-CMYK as a flexible constraint.</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Allows adaptability for high-yield requirements.</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Product Management, Marketing, Channel Partners</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>Dependent on configuration options.</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Printer supports trade page yield of 6,000 pages; validated in channel tests.</t>
-        </is>
-      </c>
-      <c r="I65" t="n">
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>R&amp;D, Product Management</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Ink system design</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Magellan supports host 12K-CMYK as specified.</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
         <v>0.7</v>
       </c>
-      <c r="J65" t="inlineStr">
+      <c r="J75" t="inlineStr">
         <is>
           <t>Magellan_SI_1-pager.pdf, page 2</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>52</t>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr"/>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Trade Page 6K (Flexible Constraint)</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Magellan must support trade page 6K as a flexible constraint.</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Allows adaptability for trade segment requirements.</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Product Management, Sales</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Page yield definition</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Magellan supports trade page 6K as specified.</t>
+        </is>
+      </c>
+      <c r="I76" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Magellan_SI_1-pager.pdf, page 2</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>61</t>
         </is>
       </c>
     </row>
